--- a/Result/checksun_type/塑化劑(可塑劑).xlsx
+++ b/Result/checksun_type/塑化劑(可塑劑).xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-3.35</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1569.646</t>
+          <t>1335.381</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>10.45</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -908,12 +908,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-2.61</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>28.41</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>-1.94</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,73 +988,73 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>7.16</t>
+          <t>6.09</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-4.95</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>1570</t>
+          <t>1335</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>83.87</t>
+          <t>27.42</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>81.18</t>
+          <t>67.74</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>-2.04</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>10.276</t>
+          <t>10.31</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>10.31</t>
+          <t>10.3</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
@@ -1069,12 +1069,12 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>1372.99</t>
+          <t>-185.15</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-100.18</t>
+          <t>-100.34</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,41 +1099,41 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>38463209.05137482</t>
+          <t>38437371.74783237</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>16427808.0</t>
+          <t>13722530.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>31153996.2</t>
+          <t>24615513.2</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>24262247.7</t>
+          <t>24233663.8</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>26236307.54</t>
+          <t>25886365.74</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>6891748</t>
+          <t>381849</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-531020.4642383313</t>
+          <t>-537185.6959741293</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>394668.89</v>
+        <v>-571094.47</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-3.81</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1182,37 +1182,37 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>-3.623742331228572</t>
+          <t>-11.96408371040724</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>-12.29899075583554</t>
+          <t>-13.59414944504011</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>-22.11692503222121</t>
+          <t>-19.633719693908</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>62.95</t>
+          <t>63.1</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>14104</t>
+          <t>13632</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1262,7 +1262,7 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>10.4</t>
+          <t>10.45</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>10.3</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>10.45</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>3754.177</t>
+          <t>1569.646</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>10.5</t>
+          <t>10.45</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,17 +1334,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-3.47</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-2.61</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>33.22</t>
+          <t>28.41</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17.12</t>
+          <t>7.16</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,47 +1440,47 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>1570</t>
+          <t>1335</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>91.94</t>
+          <t>83.87</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>65.05</t>
+          <t>81.18</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>10.236</t>
+          <t>10.276</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
@@ -1490,29 +1490,29 @@
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>10.21</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>10.22</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>73.66</t>
+          <t>1372.99</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
           <t>-0.00</t>
         </is>
       </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>-0.00</t>
-        </is>
-      </c>
       <c r="AS3" t="inlineStr">
         <is>
           <t>0.54</t>
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-100.80</t>
+          <t>-100.18</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,41 +1530,41 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>38463209.05137482</t>
+          <t>38437371.74783237</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>39557030.0</t>
+          <t>16427808.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>32036639.0</t>
+          <t>31153996.2</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>24048236.4</t>
+          <t>24262247.7</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>26253921.64</t>
+          <t>26236307.54</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>7988402</t>
+          <t>6891748</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-699327.6204268641</t>
+          <t>-531020.4642383313</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>1470384.31</v>
+        <v>394668.89</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1613,27 +1613,27 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>-3.623742331228572</t>
+          <t>-11.96408371040724</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>-12.29899075583554</t>
+          <t>-13.59414944504011</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>-22.11692503222121</t>
+          <t>-19.633719693908</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1643,7 +1643,7 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>62.95</t>
+          <t>63.1</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>14104</t>
+          <t>13632</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1698,7 +1698,7 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>10.75</t>
+          <t>10.6</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>10.5</t>
+          <t>10.45</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2725.546</t>
+          <t>3754.177</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>10.35</t>
+          <t>10.5</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,17 +1765,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>-3.96</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-2.61</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>31.50</t>
+          <t>33.22</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12.43</t>
+          <t>17.12</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,52 +1871,52 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>1570</t>
+          <t>1335</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>67.74</t>
+          <t>91.94</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>34.41</t>
+          <t>65.05</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>10.246</t>
+          <t>10.236</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>10.29</t>
+          <t>10.31</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
@@ -1926,22 +1926,22 @@
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>10.19</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-359.87</t>
+          <t>73.66</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.00</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-0.00</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-100.95</t>
+          <t>-100.80</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,41 +1961,41 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>38463209.05137482</t>
+          <t>38437371.74783237</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>28336240.0</t>
+          <t>39557030.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>28101764.2</t>
+          <t>32036639.0</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>21370450.7</t>
+          <t>24048236.4</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>26117511.38</t>
+          <t>26253921.64</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>6731313</t>
+          <t>7988402</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-1093820.699285948</t>
+          <t>-699327.6204268641</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>476475.97</v>
+        <v>1470384.31</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-1.43</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2044,37 +2044,37 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>-3.623742331228572</t>
+          <t>-11.96408371040724</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>-12.29899075583554</t>
+          <t>-13.59414944504011</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>-22.11692503222121</t>
+          <t>-19.633719693908</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>62.95</t>
+          <t>63.1</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>14104</t>
+          <t>13632</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2124,22 +2124,22 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>10.15</t>
+          <t>10.4</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>10.6</t>
+          <t>10.75</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>10.15</t>
+          <t>10.3</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>10.35</t>
+          <t>10.5</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2459.513</t>
+          <t>2725.546</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>10.15</t>
+          <t>10.35</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,17 +2196,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>-2.48</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-2.61</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>26.88</t>
+          <t>31.50</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11.22</t>
+          <t>12.43</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-0.56</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,47 +2302,47 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>1570</t>
+          <t>1335</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>35.48</t>
+          <t>67.74</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>25.16</t>
+          <t>34.41</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>10.196</t>
+          <t>10.246</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
@@ -2357,22 +2357,22 @@
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>10.18</t>
+          <t>10.19</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-6995.52</t>
+          <t>-359.87</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.00</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-100.10</t>
+          <t>-100.95</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,41 +2392,41 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>38463209.05137482</t>
+          <t>38437371.74783237</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>25033958.0</t>
+          <t>28336240.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>25855602.0</t>
+          <t>28101764.2</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>20377785.6</t>
+          <t>21370450.7</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>25837516.22</t>
+          <t>26117511.38</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>5477816</t>
+          <t>6731313</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-1379329.1848641</t>
+          <t>-1093820.699285948</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>241817.41</v>
+        <v>476475.97</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-3.33</t>
+          <t>-1.43</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2475,37 +2475,37 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>-3.623742331228572</t>
+          <t>-11.96408371040724</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>-12.29899075583554</t>
+          <t>-13.59414944504011</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>-22.11692503222121</t>
+          <t>-19.633719693908</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>62.95</t>
+          <t>63.1</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>14104</t>
+          <t>13632</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2555,22 +2555,22 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>10.15</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>10.4</t>
+          <t>10.6</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>9.96</t>
+          <t>10.15</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>10.15</t>
+          <t>10.35</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-3.14</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>4676.474</t>
+          <t>2459.513</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>9.93</t>
+          <t>10.15</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,17 +2627,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-2.61</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>17.89</t>
+          <t>26.88</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-3.59</t>
+          <t>-1.46</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,12 +2712,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>21.33</t>
+          <t>11.22</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -2733,42 +2733,42 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>1570</t>
+          <t>1335</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>35.48</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>41.11</t>
+          <t>25.16</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-2.61</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
@@ -2778,7 +2778,7 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>10.33</t>
+          <t>10.29</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
@@ -2788,22 +2788,22 @@
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>10.17</t>
+          <t>10.18</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-476.65</t>
+          <t>-6995.52</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.00</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-98.43</t>
+          <t>-100.10</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,41 +2823,41 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>38463209.05137482</t>
+          <t>38437371.74783237</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>46414945.0</t>
+          <t>25033958.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>23851814.4</t>
+          <t>25855602.0</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>20231760.7</t>
+          <t>20377785.6</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>25751255.74</t>
+          <t>25837516.22</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>3620053</t>
+          <t>5477816</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-1674083.111667096</t>
+          <t>-1379329.1848641</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>251770.49</v>
+        <v>241817.41</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-5.43</t>
+          <t>-3.33</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2906,37 +2906,37 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>-3.623742331228572</t>
+          <t>-11.96408371040724</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>-12.29899075583554</t>
+          <t>-13.59414944504011</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>-22.11692503222121</t>
+          <t>-19.633719693908</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>62.95</t>
+          <t>63.1</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>14104</t>
+          <t>13632</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>10.4</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>9.72</t>
+          <t>9.96</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>9.93</t>
+          <t>10.15</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-2.9</t>
+          <t>-3.14</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2017.475</t>
+          <t>4676.474</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>10.25</t>
+          <t>9.93</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-2.61</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>17.89</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-3.59</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>9.20</t>
+          <t>21.33</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,77 +3164,77 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>1570</t>
+          <t>1335</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>43.68</t>
+          <t>41.11</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>-2.61</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-1.54</t>
+          <t>-1.26</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>10.22</t>
+          <t>10.196</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>10.38</t>
+          <t>10.33</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>10.21</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>10.15</t>
+          <t>10.17</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-116.74</t>
+          <t>-476.65</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.00</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-96.57</t>
+          <t>-98.43</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,41 +3254,41 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>38463209.05137482</t>
+          <t>38437371.74783237</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>20841022.0</t>
+          <t>46414945.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>17370499.2</t>
+          <t>23851814.4</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>17407208.9</t>
+          <t>20231760.7</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>25485299.38</t>
+          <t>25751255.74</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-36709</t>
+          <t>3620053</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-2024238.312393929</t>
+          <t>-1674083.111667096</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>-2033822.66</v>
+        <v>251770.49</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-2.38</t>
+          <t>-5.43</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3337,37 +3337,37 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>-3.623742331228572</t>
+          <t>-11.96408371040724</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>-12.29899075583554</t>
+          <t>-13.59414944504011</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>-22.11692503222121</t>
+          <t>-19.633719693908</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>62.95</t>
+          <t>63.1</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>14104</t>
+          <t>13632</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3417,22 +3417,22 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>10.35</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>10.5</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>9.72</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>10.25</t>
+          <t>9.93</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>4.41</t>
+          <t>-2.9</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1911.185</t>
+          <t>2017.475</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,84 +3479,84 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
+          <t>10.25</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-1.49</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>-2.61</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>-0.21</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>-65.0</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>2025-10-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>2025-10-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>2025-09-23 00:00:00</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>2025-10-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>10.65</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>10.3</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
           <t>10.55</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>-0.96</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>-0.57</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>-25.08</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>-65.0</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>2025-10-27 00:00:00</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>2025-10-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>2025-09-23 00:00:00</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>2025-10-16 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>10.65</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>10.3</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>10.55</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>10.3</t>
-        </is>
-      </c>
       <c r="V8" t="inlineStr">
         <is>
           <t>0</t>
@@ -3564,7 +3564,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>8.72</t>
+          <t>9.20</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3595,275 +3595,275 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>1570</t>
+          <t>1335</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>83.33</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>35.47</t>
+          <t>43.68</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>3.43</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-1.78</t>
+          <t>-1.54</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
+          <t>10.22</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>10.38</t>
+        </is>
+      </c>
+      <c r="AN8" t="inlineStr">
+        <is>
+          <t>10.21</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>10.15</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>-116.74</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>-0.00</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>0.54</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr">
+        <is>
+          <t>-96.57</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>2025/11/13</t>
+        </is>
+      </c>
+      <c r="AV8" t="inlineStr">
+        <is>
+          <t>38437371.74783237</t>
+        </is>
+      </c>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>20841022.0</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>17370499.2</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>17407208.9</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>25485299.38</t>
+        </is>
+      </c>
+      <c r="BA8" t="inlineStr">
+        <is>
+          <t>-36709</t>
+        </is>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>-2024238.312393929</t>
+        </is>
+      </c>
+      <c r="BC8" t="n">
+        <v>-2033822.66</v>
+      </c>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE8" t="inlineStr">
+        <is>
+          <t>10.5</t>
+        </is>
+      </c>
+      <c r="BF8" t="inlineStr">
+        <is>
+          <t>2025/10/14</t>
+        </is>
+      </c>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>-2.38</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>聯成</t>
+        </is>
+      </c>
+      <c r="BI8" t="inlineStr">
+        <is>
+          <t>聯成</t>
+        </is>
+      </c>
+      <c r="BJ8" t="inlineStr">
+        <is>
+          <t>塑膠工業</t>
+        </is>
+      </c>
+      <c r="BK8" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL8" t="inlineStr">
+        <is>
+          <t>0.78</t>
+        </is>
+      </c>
+      <c r="BM8" t="inlineStr">
+        <is>
+          <t>-11.96408371040724</t>
+        </is>
+      </c>
+      <c r="BN8" t="inlineStr">
+        <is>
+          <t>-13.59414944504011</t>
+        </is>
+      </c>
+      <c r="BO8" t="inlineStr">
+        <is>
+          <t>-19.633719693908</t>
+        </is>
+      </c>
+      <c r="BP8" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BQ8" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BR8" t="inlineStr">
+        <is>
+          <t>0.46</t>
+        </is>
+      </c>
+      <c r="BS8" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="BT8" t="inlineStr">
+        <is>
+          <t>10.97</t>
+        </is>
+      </c>
+      <c r="BU8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BV8" t="inlineStr">
+        <is>
+          <t>0.96%</t>
+        </is>
+      </c>
+      <c r="BW8" t="inlineStr">
+        <is>
+          <t>-3.42%</t>
+        </is>
+      </c>
+      <c r="BX8" t="inlineStr">
+        <is>
+          <t>63.1</t>
+        </is>
+      </c>
+      <c r="BY8" t="inlineStr">
+        <is>
+          <t>13632</t>
+        </is>
+      </c>
+      <c r="BZ8" t="inlineStr">
+        <is>
+          <t>可塑劑(DOP)76.00%、聚氯乙烯13.00%、酸酐6.00%、其他5.00% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA8" t="inlineStr">
+        <is>
+          <t>聯成-塑膠工業-上市</t>
+        </is>
+      </c>
+      <c r="CB8" t="inlineStr">
+        <is>
+          <t>塑膠工業右下上市</t>
+        </is>
+      </c>
+      <c r="CC8" t="inlineStr">
+        <is>
+          <t>10.35</t>
+        </is>
+      </c>
+      <c r="CD8" t="inlineStr">
+        <is>
+          <t>10.5</t>
+        </is>
+      </c>
+      <c r="CE8" t="inlineStr">
+        <is>
           <t>10.2</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>10.38</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>10.23</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>10.13</t>
-        </is>
-      </c>
-      <c r="AP8" t="inlineStr">
-        <is>
-          <t>-96.16</t>
-        </is>
-      </c>
-      <c r="AQ8" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>0.02</t>
-        </is>
-      </c>
-      <c r="AS8" t="inlineStr">
-        <is>
-          <t>0.54</t>
-        </is>
-      </c>
-      <c r="AT8" t="inlineStr">
-        <is>
-          <t>-95.56</t>
-        </is>
-      </c>
-      <c r="AU8" t="inlineStr">
-        <is>
-          <t>2025/11/13</t>
-        </is>
-      </c>
-      <c r="AV8" t="inlineStr">
-        <is>
-          <t>38463209.05137482</t>
-        </is>
-      </c>
-      <c r="AW8" t="inlineStr">
-        <is>
-          <t>19882656.0</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>16059833.8</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>21436958.2</t>
-        </is>
-      </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>25694765.18</t>
-        </is>
-      </c>
-      <c r="BA8" t="inlineStr">
-        <is>
-          <t>-5377124</t>
-        </is>
-      </c>
-      <c r="BB8" t="inlineStr">
-        <is>
-          <t>-2022495.703504821</t>
-        </is>
-      </c>
-      <c r="BC8" t="n">
-        <v>-2486256.04</v>
-      </c>
-      <c r="BD8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE8" t="inlineStr">
-        <is>
-          <t>10.5</t>
-        </is>
-      </c>
-      <c r="BF8" t="inlineStr">
-        <is>
-          <t>2025/10/14</t>
-        </is>
-      </c>
-      <c r="BG8" t="inlineStr">
-        <is>
-          <t>0.48</t>
-        </is>
-      </c>
-      <c r="BH8" t="inlineStr">
-        <is>
-          <t>聯成</t>
-        </is>
-      </c>
-      <c r="BI8" t="inlineStr">
-        <is>
-          <t>聯成</t>
-        </is>
-      </c>
-      <c r="BJ8" t="inlineStr">
-        <is>
-          <t>塑膠工業</t>
-        </is>
-      </c>
-      <c r="BK8" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BL8" t="inlineStr">
-        <is>
-          <t>0.78</t>
-        </is>
-      </c>
-      <c r="BM8" t="inlineStr">
-        <is>
-          <t>-3.623742331228572</t>
-        </is>
-      </c>
-      <c r="BN8" t="inlineStr">
-        <is>
-          <t>-12.29899075583554</t>
-        </is>
-      </c>
-      <c r="BO8" t="inlineStr">
-        <is>
-          <t>-22.11692503222121</t>
-        </is>
-      </c>
-      <c r="BP8" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BQ8" t="inlineStr">
-        <is>
-          <t>價漲量增</t>
-        </is>
-      </c>
-      <c r="BR8" t="inlineStr">
-        <is>
-          <t>0.47</t>
-        </is>
-      </c>
-      <c r="BS8" t="inlineStr">
-        <is>
-          <t>1.44</t>
-        </is>
-      </c>
-      <c r="BT8" t="inlineStr">
-        <is>
-          <t>10.97</t>
-        </is>
-      </c>
-      <c r="BU8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BV8" t="inlineStr">
-        <is>
-          <t>0.96%</t>
-        </is>
-      </c>
-      <c r="BW8" t="inlineStr">
-        <is>
-          <t>-3.42%</t>
-        </is>
-      </c>
-      <c r="BX8" t="inlineStr">
-        <is>
-          <t>62.95</t>
-        </is>
-      </c>
-      <c r="BY8" t="inlineStr">
-        <is>
-          <t>14104</t>
-        </is>
-      </c>
-      <c r="BZ8" t="inlineStr">
-        <is>
-          <t>可塑劑(DOP)76.00%、聚氯乙烯13.00%、酸酐6.00%、其他5.00% (2024年)</t>
-        </is>
-      </c>
-      <c r="CA8" t="inlineStr">
-        <is>
-          <t>聯成-塑膠工業-上市</t>
-        </is>
-      </c>
-      <c r="CB8" t="inlineStr">
-        <is>
-          <t>塑膠工業右下上市</t>
-        </is>
-      </c>
-      <c r="CC8" t="inlineStr">
-        <is>
-          <t>10.2</t>
-        </is>
-      </c>
-      <c r="CD8" t="inlineStr">
-        <is>
-          <t>10.55</t>
-        </is>
-      </c>
-      <c r="CE8" t="inlineStr">
-        <is>
-          <t>10.15</t>
-        </is>
-      </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>10.55</t>
+          <t>10.25</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>4.41</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1707.926</t>
+          <t>1911.185</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>10.55</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,17 +3920,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>3.35</t>
+          <t>-4.46</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-2.61</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-29.56</t>
+          <t>-25.08</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-1.94</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>7.79</t>
+          <t>8.72</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,275 +4026,275 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>1570</t>
+          <t>1335</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>7.69</t>
+          <t>83.33</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>7.69</t>
+          <t>35.47</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>3.43</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-2.15</t>
+          <t>-1.78</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
+          <t>10.2</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>10.38</t>
+        </is>
+      </c>
+      <c r="AN9" t="inlineStr">
+        <is>
+          <t>10.23</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>10.13</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>-96.16</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>0.54</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr">
+        <is>
+          <t>-95.56</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>2025/11/13</t>
+        </is>
+      </c>
+      <c r="AV9" t="inlineStr">
+        <is>
+          <t>38437371.74783237</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>19882656.0</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>16059833.8</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>21436958.2</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>25694765.18</t>
+        </is>
+      </c>
+      <c r="BA9" t="inlineStr">
+        <is>
+          <t>-5377124</t>
+        </is>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>-2022495.703504821</t>
+        </is>
+      </c>
+      <c r="BC9" t="n">
+        <v>-2486256.04</v>
+      </c>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE9" t="inlineStr">
+        <is>
+          <t>10.5</t>
+        </is>
+      </c>
+      <c r="BF9" t="inlineStr">
+        <is>
+          <t>2025/10/14</t>
+        </is>
+      </c>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>0.48</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>聯成</t>
+        </is>
+      </c>
+      <c r="BI9" t="inlineStr">
+        <is>
+          <t>聯成</t>
+        </is>
+      </c>
+      <c r="BJ9" t="inlineStr">
+        <is>
+          <t>塑膠工業</t>
+        </is>
+      </c>
+      <c r="BK9" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL9" t="inlineStr">
+        <is>
+          <t>0.78</t>
+        </is>
+      </c>
+      <c r="BM9" t="inlineStr">
+        <is>
+          <t>-11.96408371040724</t>
+        </is>
+      </c>
+      <c r="BN9" t="inlineStr">
+        <is>
+          <t>-13.59414944504011</t>
+        </is>
+      </c>
+      <c r="BO9" t="inlineStr">
+        <is>
+          <t>-19.633719693908</t>
+        </is>
+      </c>
+      <c r="BP9" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BQ9" t="inlineStr">
+        <is>
+          <t>價漲量增</t>
+        </is>
+      </c>
+      <c r="BR9" t="inlineStr">
+        <is>
+          <t>0.47</t>
+        </is>
+      </c>
+      <c r="BS9" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="BT9" t="inlineStr">
+        <is>
+          <t>10.97</t>
+        </is>
+      </c>
+      <c r="BU9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BV9" t="inlineStr">
+        <is>
+          <t>0.96%</t>
+        </is>
+      </c>
+      <c r="BW9" t="inlineStr">
+        <is>
+          <t>-3.42%</t>
+        </is>
+      </c>
+      <c r="BX9" t="inlineStr">
+        <is>
+          <t>63.1</t>
+        </is>
+      </c>
+      <c r="BY9" t="inlineStr">
+        <is>
+          <t>13632</t>
+        </is>
+      </c>
+      <c r="BZ9" t="inlineStr">
+        <is>
+          <t>可塑劑(DOP)76.00%、聚氯乙烯13.00%、酸酐6.00%、其他5.00% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA9" t="inlineStr">
+        <is>
+          <t>聯成-塑膠工業-上市</t>
+        </is>
+      </c>
+      <c r="CB9" t="inlineStr">
+        <is>
+          <t>塑膠工業右下上市</t>
+        </is>
+      </c>
+      <c r="CC9" t="inlineStr">
+        <is>
+          <t>10.2</t>
+        </is>
+      </c>
+      <c r="CD9" t="inlineStr">
+        <is>
+          <t>10.55</t>
+        </is>
+      </c>
+      <c r="CE9" t="inlineStr">
+        <is>
           <t>10.15</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>10.37</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>10.23</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>10.1</t>
-        </is>
-      </c>
-      <c r="AP9" t="inlineStr">
-        <is>
-          <t>-182.94</t>
-        </is>
-      </c>
-      <c r="AQ9" t="inlineStr">
-        <is>
-          <t>-0.02</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>0.03</t>
-        </is>
-      </c>
-      <c r="AS9" t="inlineStr">
-        <is>
-          <t>0.54</t>
-        </is>
-      </c>
-      <c r="AT9" t="inlineStr">
-        <is>
-          <t>-94.50</t>
-        </is>
-      </c>
-      <c r="AU9" t="inlineStr">
-        <is>
-          <t>2025/11/13</t>
-        </is>
-      </c>
-      <c r="AV9" t="inlineStr">
-        <is>
-          <t>38463209.05137482</t>
-        </is>
-      </c>
-      <c r="AW9" t="inlineStr">
-        <is>
-          <t>17105429.0</t>
-        </is>
-      </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>14639137.2</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>20782895.4</t>
-        </is>
-      </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>25947572.9</t>
-        </is>
-      </c>
-      <c r="BA9" t="inlineStr">
-        <is>
-          <t>-6143758</t>
-        </is>
-      </c>
-      <c r="BB9" t="inlineStr">
-        <is>
-          <t>-1938175.643107979</t>
-        </is>
-      </c>
-      <c r="BC9" t="n">
-        <v>-2941112.5</v>
-      </c>
-      <c r="BD9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE9" t="inlineStr">
-        <is>
-          <t>10.5</t>
-        </is>
-      </c>
-      <c r="BF9" t="inlineStr">
-        <is>
-          <t>2025/10/14</t>
-        </is>
-      </c>
-      <c r="BG9" t="inlineStr">
-        <is>
-          <t>-3.81</t>
-        </is>
-      </c>
-      <c r="BH9" t="inlineStr">
-        <is>
-          <t>聯成</t>
-        </is>
-      </c>
-      <c r="BI9" t="inlineStr">
-        <is>
-          <t>聯成</t>
-        </is>
-      </c>
-      <c r="BJ9" t="inlineStr">
-        <is>
-          <t>塑膠工業</t>
-        </is>
-      </c>
-      <c r="BK9" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BL9" t="inlineStr">
-        <is>
-          <t>0.78</t>
-        </is>
-      </c>
-      <c r="BM9" t="inlineStr">
-        <is>
-          <t>-3.623742331228572</t>
-        </is>
-      </c>
-      <c r="BN9" t="inlineStr">
-        <is>
-          <t>-12.29899075583554</t>
-        </is>
-      </c>
-      <c r="BO9" t="inlineStr">
-        <is>
-          <t>-22.11692503222121</t>
-        </is>
-      </c>
-      <c r="BP9" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BQ9" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BR9" t="inlineStr">
-        <is>
-          <t>0.45</t>
-        </is>
-      </c>
-      <c r="BS9" t="inlineStr">
-        <is>
-          <t>1.44</t>
-        </is>
-      </c>
-      <c r="BT9" t="inlineStr">
-        <is>
-          <t>10.97</t>
-        </is>
-      </c>
-      <c r="BU9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BV9" t="inlineStr">
-        <is>
-          <t>0.96%</t>
-        </is>
-      </c>
-      <c r="BW9" t="inlineStr">
-        <is>
-          <t>-3.42%</t>
-        </is>
-      </c>
-      <c r="BX9" t="inlineStr">
-        <is>
-          <t>62.95</t>
-        </is>
-      </c>
-      <c r="BY9" t="inlineStr">
-        <is>
-          <t>14104</t>
-        </is>
-      </c>
-      <c r="BZ9" t="inlineStr">
-        <is>
-          <t>可塑劑(DOP)76.00%、聚氯乙烯13.00%、酸酐6.00%、其他5.00% (2024年)</t>
-        </is>
-      </c>
-      <c r="CA9" t="inlineStr">
-        <is>
-          <t>聯成-塑膠工業-上市</t>
-        </is>
-      </c>
-      <c r="CB9" t="inlineStr">
-        <is>
-          <t>塑膠工業右下上市</t>
-        </is>
-      </c>
-      <c r="CC9" t="inlineStr">
-        <is>
-          <t>10.1</t>
-        </is>
-      </c>
-      <c r="CD9" t="inlineStr">
-        <is>
-          <t>10.15</t>
-        </is>
-      </c>
-      <c r="CE9" t="inlineStr">
-        <is>
-          <t>9.85</t>
-        </is>
-      </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>10.55</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1474.031</t>
+          <t>1707.926</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>10.15</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4351,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-2.61</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-29.46</t>
+          <t>-29.56</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>-1.94</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>6.72</t>
+          <t>7.79</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,77 +4457,77 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>1570</t>
+          <t>1335</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>15.38</t>
+          <t>7.69</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>5.13</t>
+          <t>7.69</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>-2.15</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>10.18</t>
+          <t>10.15</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>10.38</t>
+          <t>10.37</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>10.25</t>
+          <t>10.23</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>10.07</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-125.13</t>
+          <t>-182.94</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-91.98</t>
+          <t>-94.50</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,41 +4547,41 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>38463209.05137482</t>
+          <t>38437371.74783237</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>15015020.0</t>
+          <t>17105429.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>14899969.2</t>
+          <t>14639137.2</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>21123172.9</t>
+          <t>20782895.4</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>27016759.02</t>
+          <t>25947572.9</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-6223203</t>
+          <t>-6143758</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-1755823.487700998</t>
+          <t>-1938175.643107979</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>-3188307.68</v>
+        <v>-2941112.5</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-3.33</t>
+          <t>-3.81</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4630,22 +4630,22 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>-3.623742331228572</t>
+          <t>-11.96408371040724</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>-12.29899075583554</t>
+          <t>-13.59414944504011</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>-22.11692503222121</t>
+          <t>-19.633719693908</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -4660,7 +4660,7 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>62.95</t>
+          <t>63.1</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>14104</t>
+          <t>13632</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4715,17 +4715,17 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>10.25</t>
+          <t>10.15</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
+          <t>9.85</t>
+        </is>
+      </c>
+      <c r="CF10" t="inlineStr">
+        <is>
           <t>10.1</t>
-        </is>
-      </c>
-      <c r="CF10" t="inlineStr">
-        <is>
-          <t>10.15</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1388.526</t>
+          <t>1474.031</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>10.05</t>
+          <t>10.15</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>3.83</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-2.61</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-21.58</t>
+          <t>-29.46</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-2.43</t>
+          <t>-1.46</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>6.33</t>
+          <t>6.72</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,47 +4888,47 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>1570</t>
+          <t>1335</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>15.38</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>5.13</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-1.69</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>10.21</t>
+          <t>10.18</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
@@ -4938,27 +4938,27 @@
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>10.26</t>
+          <t>10.25</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>10.04</t>
+          <t>10.07</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-96.97</t>
+          <t>-125.13</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-89.47</t>
+          <t>-91.98</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,41 +4978,41 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>38463209.05137482</t>
+          <t>38437371.74783237</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>14008369.0</t>
+          <t>15015020.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>16611707.0</t>
+          <t>14899969.2</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>21181803.0</t>
+          <t>21123172.9</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>27684361.26</t>
+          <t>27016759.02</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-4570096</t>
+          <t>-6223203</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-1495371.817099823</t>
+          <t>-1755823.487700998</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>-3203603.12</v>
+        <v>-3188307.68</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-4.29</t>
+          <t>-3.33</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5061,22 +5061,22 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>-3.623742331228572</t>
+          <t>-11.96408371040724</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>-12.29899075583554</t>
+          <t>-13.59414944504011</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>-22.11692503222121</t>
+          <t>-19.633719693908</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5091,7 +5091,7 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>62.95</t>
+          <t>63.1</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>14104</t>
+          <t>13632</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>10.05</t>
+          <t>10.15</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1397.2</t>
+          <t>1388.526</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>10.15</t>
+          <t>10.05</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-2.61</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-21.35</t>
+          <t>-21.58</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>-2.43</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>6.37</t>
+          <t>6.33</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-2.46</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,12 +5319,12 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>1570</t>
+          <t>1335</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5339,57 +5339,57 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-1.57</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-1.69</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>2.18</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>10.33</t>
+          <t>10.21</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>10.4</t>
+          <t>10.38</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>10.28</t>
+          <t>10.26</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>10.01</t>
+          <t>10.04</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-60.33</t>
+          <t>-96.97</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-86.92</t>
+          <t>-89.47</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,41 +5409,41 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>38463209.05137482</t>
+          <t>38437371.74783237</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>14287695.0</t>
+          <t>14008369.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>17443918.6</t>
+          <t>16611707.0</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>22179537.3</t>
+          <t>21181803.0</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>28937417.34</t>
+          <t>27684361.26</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-4735618</t>
+          <t>-4570096</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-1184784.307360538</t>
+          <t>-1495371.817099823</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>-3003183.89</v>
+        <v>-3203603.12</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-3.33</t>
+          <t>-4.29</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5492,22 +5492,22 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>-3.623742331228572</t>
+          <t>-11.96408371040724</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>-12.29899075583554</t>
+          <t>-13.59414944504011</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>-22.11692503222121</t>
+          <t>-19.633719693908</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5522,7 +5522,7 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>62.95</t>
+          <t>63.1</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>14104</t>
+          <t>13632</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5572,22 +5572,22 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>10.4</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>10.4</t>
+          <t>10.25</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>10.15</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>10.15</t>
+          <t>10.05</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">

--- a/Result/checksun_type/塑化劑(可塑劑).xlsx
+++ b/Result/checksun_type/塑化劑(可塑劑).xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-3.35</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1335.381</t>
+          <t>2500.445</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -908,12 +908,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-2.61</t>
+          <t>-2.57</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>-2.43</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-1.94</t>
+          <t>-2.91</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,73 +988,73 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>6.09</t>
+          <t>11.41</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-4.95</t>
+          <t>-1.60</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>1335</t>
+          <t>2500</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>27.42</t>
+          <t>11.29</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>67.74</t>
+          <t>40.86</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-2.04</t>
+          <t>-2.72</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>10.31</t>
+          <t>10.28</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>10.3</t>
+          <t>10.28</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
@@ -1069,19 +1069,19 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-185.15</t>
+          <t>-293.77</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
+          <t>-0.03</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
           <t>-0.01</t>
         </is>
       </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>-0.00</t>
-        </is>
-      </c>
       <c r="AS2" t="inlineStr">
         <is>
           <t>0.54</t>
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-100.34</t>
+          <t>-101.27</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,41 +1099,41 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>38437371.74783237</t>
+          <t>38436244.78354979</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>13722530.0</t>
+          <t>25104257.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>24615513.2</t>
+          <t>24629573.0</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>24233663.8</t>
+          <t>25242587.5</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>25886365.74</t>
+          <t>25777972.78</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>381849</t>
+          <t>-613014</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-537185.6959741293</t>
+          <t>-512883.5795906829</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>-571094.47</v>
+        <v>-379221.94</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-3.81</t>
+          <t>-4.76</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1212,7 +1212,7 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>63.1</t>
+          <t>62.66</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>13632</t>
+          <t>13497</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1262,22 +1262,22 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>10.45</t>
+          <t>10.05</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>10.6</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>9.96</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-3.35</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1569.646</t>
+          <t>1335.381</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>10.45</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,17 +1334,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-3.47</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-2.61</t>
+          <t>-2.57</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>28.41</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>-1.94</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,73 +1419,73 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>7.16</t>
+          <t>6.09</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-4.95</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>1335</t>
+          <t>2500</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>83.87</t>
+          <t>27.42</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>81.18</t>
+          <t>67.74</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>-2.04</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>10.276</t>
+          <t>10.31</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>10.31</t>
+          <t>10.3</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>1372.99</t>
+          <t>-185.15</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-100.18</t>
+          <t>-100.34</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,41 +1530,41 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>38437371.74783237</t>
+          <t>38436244.78354979</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>16427808.0</t>
+          <t>13722530.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>31153996.2</t>
+          <t>24615513.2</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>24262247.7</t>
+          <t>24233663.8</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>26236307.54</t>
+          <t>25886365.74</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>6891748</t>
+          <t>381849</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-531020.4642383313</t>
+          <t>-537185.6959741293</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>394668.89</v>
+        <v>-571094.47</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-3.81</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1628,22 +1628,22 @@
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>63.1</t>
+          <t>62.66</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>13632</t>
+          <t>13497</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1693,7 +1693,7 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>10.4</t>
+          <t>10.45</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
@@ -1703,12 +1703,12 @@
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>10.3</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>10.45</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>3754.177</t>
+          <t>1569.646</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>10.5</t>
+          <t>10.45</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,17 +1765,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-3.96</t>
+          <t>-4.5</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-2.61</t>
+          <t>-2.57</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>33.22</t>
+          <t>28.41</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17.12</t>
+          <t>7.16</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,47 +1871,47 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>1335</t>
+          <t>2500</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>91.94</t>
+          <t>83.87</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>65.05</t>
+          <t>81.18</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>10.236</t>
+          <t>10.276</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
@@ -1921,29 +1921,29 @@
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>10.21</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>10.22</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>73.66</t>
+          <t>1372.99</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
           <t>-0.00</t>
         </is>
       </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>-0.00</t>
-        </is>
-      </c>
       <c r="AS4" t="inlineStr">
         <is>
           <t>0.54</t>
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-100.80</t>
+          <t>-100.18</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,41 +1961,41 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>38437371.74783237</t>
+          <t>38436244.78354979</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>39557030.0</t>
+          <t>16427808.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>32036639.0</t>
+          <t>31153996.2</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>24048236.4</t>
+          <t>24262247.7</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>26253921.64</t>
+          <t>26236307.54</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>7988402</t>
+          <t>6891748</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-699327.6204268641</t>
+          <t>-531020.4642383313</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>1470384.31</v>
+        <v>394668.89</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2059,12 +2059,12 @@
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>63.1</t>
+          <t>62.66</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>13632</t>
+          <t>13497</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2129,7 +2129,7 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>10.75</t>
+          <t>10.6</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
@@ -2139,7 +2139,7 @@
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>10.5</t>
+          <t>10.45</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2725.546</t>
+          <t>3754.177</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>10.35</t>
+          <t>10.5</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,17 +2196,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-2.48</t>
+          <t>-5.0</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-2.61</t>
+          <t>-2.57</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>31.50</t>
+          <t>33.22</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12.43</t>
+          <t>17.12</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,52 +2302,52 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>1335</t>
+          <t>2500</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>67.74</t>
+          <t>91.94</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>34.41</t>
+          <t>65.05</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>10.246</t>
+          <t>10.236</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>10.29</t>
+          <t>10.31</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
@@ -2357,22 +2357,22 @@
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>10.19</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-359.87</t>
+          <t>73.66</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.00</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-0.00</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-100.95</t>
+          <t>-100.80</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,41 +2392,41 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>38437371.74783237</t>
+          <t>38436244.78354979</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>28336240.0</t>
+          <t>39557030.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>28101764.2</t>
+          <t>32036639.0</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>21370450.7</t>
+          <t>24048236.4</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>26117511.38</t>
+          <t>26253921.64</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>6731313</t>
+          <t>7988402</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-1093820.699285948</t>
+          <t>-699327.6204268641</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>476475.97</v>
+        <v>1470384.31</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-1.43</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2490,22 +2490,22 @@
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>63.1</t>
+          <t>62.66</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>13632</t>
+          <t>13497</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2555,22 +2555,22 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>10.15</t>
+          <t>10.4</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>10.6</t>
+          <t>10.75</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>10.15</t>
+          <t>10.3</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>10.35</t>
+          <t>10.5</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2459.513</t>
+          <t>2725.546</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>10.15</t>
+          <t>10.35</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,17 +2627,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-3.5</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-2.61</t>
+          <t>-2.57</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>26.88</t>
+          <t>31.50</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11.22</t>
+          <t>12.43</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-0.56</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2733,47 +2733,47 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>1335</t>
+          <t>2500</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>35.48</t>
+          <t>67.74</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>25.16</t>
+          <t>34.41</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>10.196</t>
+          <t>10.246</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
@@ -2788,22 +2788,22 @@
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>10.18</t>
+          <t>10.19</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-6995.52</t>
+          <t>-359.87</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.00</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-100.10</t>
+          <t>-100.95</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,41 +2823,41 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>38437371.74783237</t>
+          <t>38436244.78354979</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>25033958.0</t>
+          <t>28336240.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>25855602.0</t>
+          <t>28101764.2</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>20377785.6</t>
+          <t>21370450.7</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>25837516.22</t>
+          <t>26117511.38</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>5477816</t>
+          <t>6731313</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-1379329.1848641</t>
+          <t>-1093820.699285948</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>241817.41</v>
+        <v>476475.97</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-3.33</t>
+          <t>-1.43</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2921,22 +2921,22 @@
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>63.1</t>
+          <t>62.66</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>13632</t>
+          <t>13497</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>10.15</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>10.4</t>
+          <t>10.6</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>9.96</t>
+          <t>10.15</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>10.15</t>
+          <t>10.35</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-3.14</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>4676.474</t>
+          <t>2459.513</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>9.93</t>
+          <t>10.15</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>-1.5</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-2.61</t>
+          <t>-2.57</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>17.89</t>
+          <t>26.88</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-3.59</t>
+          <t>-1.46</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,12 +3143,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>21.33</t>
+          <t>11.22</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -3164,42 +3164,42 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>1335</t>
+          <t>2500</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>35.48</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>41.11</t>
+          <t>25.16</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-2.61</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
@@ -3209,7 +3209,7 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>10.33</t>
+          <t>10.29</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
@@ -3219,22 +3219,22 @@
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>10.17</t>
+          <t>10.18</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-476.65</t>
+          <t>-6995.52</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.00</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-98.43</t>
+          <t>-100.10</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,41 +3254,41 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>38437371.74783237</t>
+          <t>38436244.78354979</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>46414945.0</t>
+          <t>25033958.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>23851814.4</t>
+          <t>25855602.0</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>20231760.7</t>
+          <t>20377785.6</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>25751255.74</t>
+          <t>25837516.22</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>3620053</t>
+          <t>5477816</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-1674083.111667096</t>
+          <t>-1379329.1848641</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>251770.49</v>
+        <v>241817.41</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-5.43</t>
+          <t>-3.33</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3352,22 +3352,22 @@
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>63.1</t>
+          <t>62.66</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>13632</t>
+          <t>13497</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3417,22 +3417,22 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>10.4</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>9.72</t>
+          <t>9.96</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>9.93</t>
+          <t>10.15</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-2.9</t>
+          <t>-3.14</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2017.475</t>
+          <t>4676.474</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>10.25</t>
+          <t>9.93</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,17 +3489,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-2.61</t>
+          <t>-2.57</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>17.89</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-3.59</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>9.20</t>
+          <t>21.33</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3595,77 +3595,77 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>1335</t>
+          <t>2500</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>43.68</t>
+          <t>41.11</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>-2.61</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-1.54</t>
+          <t>-1.26</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>10.22</t>
+          <t>10.196</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>10.38</t>
+          <t>10.33</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>10.21</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>10.15</t>
+          <t>10.17</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-116.74</t>
+          <t>-476.65</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.00</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-96.57</t>
+          <t>-98.43</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,41 +3685,41 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>38437371.74783237</t>
+          <t>38436244.78354979</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>20841022.0</t>
+          <t>46414945.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>17370499.2</t>
+          <t>23851814.4</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>17407208.9</t>
+          <t>20231760.7</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>25485299.38</t>
+          <t>25751255.74</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-36709</t>
+          <t>3620053</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-2024238.312393929</t>
+          <t>-1674083.111667096</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>-2033822.66</v>
+        <v>251770.49</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-2.38</t>
+          <t>-5.43</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3783,22 +3783,22 @@
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>63.1</t>
+          <t>62.66</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>13632</t>
+          <t>13497</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3848,22 +3848,22 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>10.35</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>10.5</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>9.72</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>10.25</t>
+          <t>9.93</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>4.41</t>
+          <t>-2.9</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1911.185</t>
+          <t>2017.475</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,84 +3910,84 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
+          <t>10.25</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-2.5</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>-2.57</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>-0.21</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>-65.0</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>2025-10-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>2025-10-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>2025-09-23 00:00:00</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>2025-10-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>10.65</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>10.3</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
           <t>10.55</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>-4.46</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>-2.61</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>-25.08</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>-65.0</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>2025-10-27 00:00:00</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>2025-10-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>2025-09-23 00:00:00</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>2025-10-16 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>10.65</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>10.3</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>10.55</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>10.3</t>
-        </is>
-      </c>
       <c r="V9" t="inlineStr">
         <is>
           <t>0</t>
@@ -3995,7 +3995,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>8.72</t>
+          <t>9.20</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,275 +4026,275 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>1335</t>
+          <t>2500</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>83.33</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>35.47</t>
+          <t>43.68</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>3.43</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-1.78</t>
+          <t>-1.54</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
+          <t>10.22</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>10.38</t>
+        </is>
+      </c>
+      <c r="AN9" t="inlineStr">
+        <is>
+          <t>10.21</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>10.15</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>-116.74</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>-0.00</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>0.54</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr">
+        <is>
+          <t>-96.57</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>2025/11/13</t>
+        </is>
+      </c>
+      <c r="AV9" t="inlineStr">
+        <is>
+          <t>38436244.78354979</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>20841022.0</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>17370499.2</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>17407208.9</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>25485299.38</t>
+        </is>
+      </c>
+      <c r="BA9" t="inlineStr">
+        <is>
+          <t>-36709</t>
+        </is>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>-2024238.312393929</t>
+        </is>
+      </c>
+      <c r="BC9" t="n">
+        <v>-2033822.66</v>
+      </c>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE9" t="inlineStr">
+        <is>
+          <t>10.5</t>
+        </is>
+      </c>
+      <c r="BF9" t="inlineStr">
+        <is>
+          <t>2025/10/14</t>
+        </is>
+      </c>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>-2.38</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>聯成</t>
+        </is>
+      </c>
+      <c r="BI9" t="inlineStr">
+        <is>
+          <t>聯成</t>
+        </is>
+      </c>
+      <c r="BJ9" t="inlineStr">
+        <is>
+          <t>塑膠工業</t>
+        </is>
+      </c>
+      <c r="BK9" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL9" t="inlineStr">
+        <is>
+          <t>0.78</t>
+        </is>
+      </c>
+      <c r="BM9" t="inlineStr">
+        <is>
+          <t>-11.96408371040724</t>
+        </is>
+      </c>
+      <c r="BN9" t="inlineStr">
+        <is>
+          <t>-13.59414944504011</t>
+        </is>
+      </c>
+      <c r="BO9" t="inlineStr">
+        <is>
+          <t>-19.633719693908</t>
+        </is>
+      </c>
+      <c r="BP9" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BQ9" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BR9" t="inlineStr">
+        <is>
+          <t>0.46</t>
+        </is>
+      </c>
+      <c r="BS9" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="BT9" t="inlineStr">
+        <is>
+          <t>10.97</t>
+        </is>
+      </c>
+      <c r="BU9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BV9" t="inlineStr">
+        <is>
+          <t>0.96%</t>
+        </is>
+      </c>
+      <c r="BW9" t="inlineStr">
+        <is>
+          <t>-3.42%</t>
+        </is>
+      </c>
+      <c r="BX9" t="inlineStr">
+        <is>
+          <t>62.66</t>
+        </is>
+      </c>
+      <c r="BY9" t="inlineStr">
+        <is>
+          <t>13497</t>
+        </is>
+      </c>
+      <c r="BZ9" t="inlineStr">
+        <is>
+          <t>可塑劑(DOP)76.00%、聚氯乙烯13.00%、酸酐6.00%、其他5.00% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA9" t="inlineStr">
+        <is>
+          <t>聯成-塑膠工業-上市</t>
+        </is>
+      </c>
+      <c r="CB9" t="inlineStr">
+        <is>
+          <t>塑膠工業右下上市</t>
+        </is>
+      </c>
+      <c r="CC9" t="inlineStr">
+        <is>
+          <t>10.35</t>
+        </is>
+      </c>
+      <c r="CD9" t="inlineStr">
+        <is>
+          <t>10.5</t>
+        </is>
+      </c>
+      <c r="CE9" t="inlineStr">
+        <is>
           <t>10.2</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>10.38</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>10.23</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>10.13</t>
-        </is>
-      </c>
-      <c r="AP9" t="inlineStr">
-        <is>
-          <t>-96.16</t>
-        </is>
-      </c>
-      <c r="AQ9" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>0.02</t>
-        </is>
-      </c>
-      <c r="AS9" t="inlineStr">
-        <is>
-          <t>0.54</t>
-        </is>
-      </c>
-      <c r="AT9" t="inlineStr">
-        <is>
-          <t>-95.56</t>
-        </is>
-      </c>
-      <c r="AU9" t="inlineStr">
-        <is>
-          <t>2025/11/13</t>
-        </is>
-      </c>
-      <c r="AV9" t="inlineStr">
-        <is>
-          <t>38437371.74783237</t>
-        </is>
-      </c>
-      <c r="AW9" t="inlineStr">
-        <is>
-          <t>19882656.0</t>
-        </is>
-      </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>16059833.8</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>21436958.2</t>
-        </is>
-      </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>25694765.18</t>
-        </is>
-      </c>
-      <c r="BA9" t="inlineStr">
-        <is>
-          <t>-5377124</t>
-        </is>
-      </c>
-      <c r="BB9" t="inlineStr">
-        <is>
-          <t>-2022495.703504821</t>
-        </is>
-      </c>
-      <c r="BC9" t="n">
-        <v>-2486256.04</v>
-      </c>
-      <c r="BD9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE9" t="inlineStr">
-        <is>
-          <t>10.5</t>
-        </is>
-      </c>
-      <c r="BF9" t="inlineStr">
-        <is>
-          <t>2025/10/14</t>
-        </is>
-      </c>
-      <c r="BG9" t="inlineStr">
-        <is>
-          <t>0.48</t>
-        </is>
-      </c>
-      <c r="BH9" t="inlineStr">
-        <is>
-          <t>聯成</t>
-        </is>
-      </c>
-      <c r="BI9" t="inlineStr">
-        <is>
-          <t>聯成</t>
-        </is>
-      </c>
-      <c r="BJ9" t="inlineStr">
-        <is>
-          <t>塑膠工業</t>
-        </is>
-      </c>
-      <c r="BK9" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BL9" t="inlineStr">
-        <is>
-          <t>0.78</t>
-        </is>
-      </c>
-      <c r="BM9" t="inlineStr">
-        <is>
-          <t>-11.96408371040724</t>
-        </is>
-      </c>
-      <c r="BN9" t="inlineStr">
-        <is>
-          <t>-13.59414944504011</t>
-        </is>
-      </c>
-      <c r="BO9" t="inlineStr">
-        <is>
-          <t>-19.633719693908</t>
-        </is>
-      </c>
-      <c r="BP9" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BQ9" t="inlineStr">
-        <is>
-          <t>價漲量增</t>
-        </is>
-      </c>
-      <c r="BR9" t="inlineStr">
-        <is>
-          <t>0.47</t>
-        </is>
-      </c>
-      <c r="BS9" t="inlineStr">
-        <is>
-          <t>1.48</t>
-        </is>
-      </c>
-      <c r="BT9" t="inlineStr">
-        <is>
-          <t>10.97</t>
-        </is>
-      </c>
-      <c r="BU9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BV9" t="inlineStr">
-        <is>
-          <t>0.96%</t>
-        </is>
-      </c>
-      <c r="BW9" t="inlineStr">
-        <is>
-          <t>-3.42%</t>
-        </is>
-      </c>
-      <c r="BX9" t="inlineStr">
-        <is>
-          <t>63.1</t>
-        </is>
-      </c>
-      <c r="BY9" t="inlineStr">
-        <is>
-          <t>13632</t>
-        </is>
-      </c>
-      <c r="BZ9" t="inlineStr">
-        <is>
-          <t>可塑劑(DOP)76.00%、聚氯乙烯13.00%、酸酐6.00%、其他5.00% (2024年)</t>
-        </is>
-      </c>
-      <c r="CA9" t="inlineStr">
-        <is>
-          <t>聯成-塑膠工業-上市</t>
-        </is>
-      </c>
-      <c r="CB9" t="inlineStr">
-        <is>
-          <t>塑膠工業右下上市</t>
-        </is>
-      </c>
-      <c r="CC9" t="inlineStr">
-        <is>
-          <t>10.2</t>
-        </is>
-      </c>
-      <c r="CD9" t="inlineStr">
-        <is>
-          <t>10.55</t>
-        </is>
-      </c>
-      <c r="CE9" t="inlineStr">
-        <is>
-          <t>10.15</t>
-        </is>
-      </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>10.55</t>
+          <t>10.25</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>4.41</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1707.926</t>
+          <t>1911.185</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>10.55</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4351,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-5.5</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-2.61</t>
+          <t>-2.57</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-29.56</t>
+          <t>-25.08</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-1.94</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>7.79</t>
+          <t>8.72</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,275 +4457,275 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>1335</t>
+          <t>2500</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>7.69</t>
+          <t>83.33</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>7.69</t>
+          <t>35.47</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>3.43</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-2.15</t>
+          <t>-1.78</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
+          <t>10.2</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>10.38</t>
+        </is>
+      </c>
+      <c r="AN10" t="inlineStr">
+        <is>
+          <t>10.23</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>10.13</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr">
+        <is>
+          <t>-96.16</t>
+        </is>
+      </c>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>0.54</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr">
+        <is>
+          <t>-95.56</t>
+        </is>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>2025/11/13</t>
+        </is>
+      </c>
+      <c r="AV10" t="inlineStr">
+        <is>
+          <t>38436244.78354979</t>
+        </is>
+      </c>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>19882656.0</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>16059833.8</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>21436958.2</t>
+        </is>
+      </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>25694765.18</t>
+        </is>
+      </c>
+      <c r="BA10" t="inlineStr">
+        <is>
+          <t>-5377124</t>
+        </is>
+      </c>
+      <c r="BB10" t="inlineStr">
+        <is>
+          <t>-2022495.703504821</t>
+        </is>
+      </c>
+      <c r="BC10" t="n">
+        <v>-2486256.04</v>
+      </c>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE10" t="inlineStr">
+        <is>
+          <t>10.5</t>
+        </is>
+      </c>
+      <c r="BF10" t="inlineStr">
+        <is>
+          <t>2025/10/14</t>
+        </is>
+      </c>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>0.48</t>
+        </is>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>聯成</t>
+        </is>
+      </c>
+      <c r="BI10" t="inlineStr">
+        <is>
+          <t>聯成</t>
+        </is>
+      </c>
+      <c r="BJ10" t="inlineStr">
+        <is>
+          <t>塑膠工業</t>
+        </is>
+      </c>
+      <c r="BK10" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL10" t="inlineStr">
+        <is>
+          <t>0.78</t>
+        </is>
+      </c>
+      <c r="BM10" t="inlineStr">
+        <is>
+          <t>-11.96408371040724</t>
+        </is>
+      </c>
+      <c r="BN10" t="inlineStr">
+        <is>
+          <t>-13.59414944504011</t>
+        </is>
+      </c>
+      <c r="BO10" t="inlineStr">
+        <is>
+          <t>-19.633719693908</t>
+        </is>
+      </c>
+      <c r="BP10" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BQ10" t="inlineStr">
+        <is>
+          <t>價漲量增</t>
+        </is>
+      </c>
+      <c r="BR10" t="inlineStr">
+        <is>
+          <t>0.47</t>
+        </is>
+      </c>
+      <c r="BS10" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="BT10" t="inlineStr">
+        <is>
+          <t>10.97</t>
+        </is>
+      </c>
+      <c r="BU10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BV10" t="inlineStr">
+        <is>
+          <t>0.96%</t>
+        </is>
+      </c>
+      <c r="BW10" t="inlineStr">
+        <is>
+          <t>-3.42%</t>
+        </is>
+      </c>
+      <c r="BX10" t="inlineStr">
+        <is>
+          <t>62.66</t>
+        </is>
+      </c>
+      <c r="BY10" t="inlineStr">
+        <is>
+          <t>13497</t>
+        </is>
+      </c>
+      <c r="BZ10" t="inlineStr">
+        <is>
+          <t>可塑劑(DOP)76.00%、聚氯乙烯13.00%、酸酐6.00%、其他5.00% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA10" t="inlineStr">
+        <is>
+          <t>聯成-塑膠工業-上市</t>
+        </is>
+      </c>
+      <c r="CB10" t="inlineStr">
+        <is>
+          <t>塑膠工業右下上市</t>
+        </is>
+      </c>
+      <c r="CC10" t="inlineStr">
+        <is>
+          <t>10.2</t>
+        </is>
+      </c>
+      <c r="CD10" t="inlineStr">
+        <is>
+          <t>10.55</t>
+        </is>
+      </c>
+      <c r="CE10" t="inlineStr">
+        <is>
           <t>10.15</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>10.37</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>10.23</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>10.1</t>
-        </is>
-      </c>
-      <c r="AP10" t="inlineStr">
-        <is>
-          <t>-182.94</t>
-        </is>
-      </c>
-      <c r="AQ10" t="inlineStr">
-        <is>
-          <t>-0.02</t>
-        </is>
-      </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>0.03</t>
-        </is>
-      </c>
-      <c r="AS10" t="inlineStr">
-        <is>
-          <t>0.54</t>
-        </is>
-      </c>
-      <c r="AT10" t="inlineStr">
-        <is>
-          <t>-94.50</t>
-        </is>
-      </c>
-      <c r="AU10" t="inlineStr">
-        <is>
-          <t>2025/11/13</t>
-        </is>
-      </c>
-      <c r="AV10" t="inlineStr">
-        <is>
-          <t>38437371.74783237</t>
-        </is>
-      </c>
-      <c r="AW10" t="inlineStr">
-        <is>
-          <t>17105429.0</t>
-        </is>
-      </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>14639137.2</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>20782895.4</t>
-        </is>
-      </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>25947572.9</t>
-        </is>
-      </c>
-      <c r="BA10" t="inlineStr">
-        <is>
-          <t>-6143758</t>
-        </is>
-      </c>
-      <c r="BB10" t="inlineStr">
-        <is>
-          <t>-1938175.643107979</t>
-        </is>
-      </c>
-      <c r="BC10" t="n">
-        <v>-2941112.5</v>
-      </c>
-      <c r="BD10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE10" t="inlineStr">
-        <is>
-          <t>10.5</t>
-        </is>
-      </c>
-      <c r="BF10" t="inlineStr">
-        <is>
-          <t>2025/10/14</t>
-        </is>
-      </c>
-      <c r="BG10" t="inlineStr">
-        <is>
-          <t>-3.81</t>
-        </is>
-      </c>
-      <c r="BH10" t="inlineStr">
-        <is>
-          <t>聯成</t>
-        </is>
-      </c>
-      <c r="BI10" t="inlineStr">
-        <is>
-          <t>聯成</t>
-        </is>
-      </c>
-      <c r="BJ10" t="inlineStr">
-        <is>
-          <t>塑膠工業</t>
-        </is>
-      </c>
-      <c r="BK10" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BL10" t="inlineStr">
-        <is>
-          <t>0.78</t>
-        </is>
-      </c>
-      <c r="BM10" t="inlineStr">
-        <is>
-          <t>-11.96408371040724</t>
-        </is>
-      </c>
-      <c r="BN10" t="inlineStr">
-        <is>
-          <t>-13.59414944504011</t>
-        </is>
-      </c>
-      <c r="BO10" t="inlineStr">
-        <is>
-          <t>-19.633719693908</t>
-        </is>
-      </c>
-      <c r="BP10" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BQ10" t="inlineStr">
-        <is>
-          <t>價-量增</t>
-        </is>
-      </c>
-      <c r="BR10" t="inlineStr">
-        <is>
-          <t>0.45</t>
-        </is>
-      </c>
-      <c r="BS10" t="inlineStr">
-        <is>
-          <t>1.48</t>
-        </is>
-      </c>
-      <c r="BT10" t="inlineStr">
-        <is>
-          <t>10.97</t>
-        </is>
-      </c>
-      <c r="BU10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BV10" t="inlineStr">
-        <is>
-          <t>0.96%</t>
-        </is>
-      </c>
-      <c r="BW10" t="inlineStr">
-        <is>
-          <t>-3.42%</t>
-        </is>
-      </c>
-      <c r="BX10" t="inlineStr">
-        <is>
-          <t>63.1</t>
-        </is>
-      </c>
-      <c r="BY10" t="inlineStr">
-        <is>
-          <t>13632</t>
-        </is>
-      </c>
-      <c r="BZ10" t="inlineStr">
-        <is>
-          <t>可塑劑(DOP)76.00%、聚氯乙烯13.00%、酸酐6.00%、其他5.00% (2024年)</t>
-        </is>
-      </c>
-      <c r="CA10" t="inlineStr">
-        <is>
-          <t>聯成-塑膠工業-上市</t>
-        </is>
-      </c>
-      <c r="CB10" t="inlineStr">
-        <is>
-          <t>塑膠工業右下上市</t>
-        </is>
-      </c>
-      <c r="CC10" t="inlineStr">
-        <is>
-          <t>10.1</t>
-        </is>
-      </c>
-      <c r="CD10" t="inlineStr">
-        <is>
-          <t>10.15</t>
-        </is>
-      </c>
-      <c r="CE10" t="inlineStr">
-        <is>
-          <t>9.85</t>
-        </is>
-      </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>10.55</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1474.031</t>
+          <t>1707.926</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>10.15</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-2.61</t>
+          <t>-2.57</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-29.46</t>
+          <t>-29.56</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>-1.94</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>6.72</t>
+          <t>7.79</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,77 +4888,77 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>1335</t>
+          <t>2500</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>15.38</t>
+          <t>7.69</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>5.13</t>
+          <t>7.69</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>-2.15</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>10.18</t>
+          <t>10.15</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>10.38</t>
+          <t>10.37</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>10.25</t>
+          <t>10.23</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>10.07</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-125.13</t>
+          <t>-182.94</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-91.98</t>
+          <t>-94.50</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,41 +4978,41 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>38437371.74783237</t>
+          <t>38436244.78354979</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>15015020.0</t>
+          <t>17105429.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>14899969.2</t>
+          <t>14639137.2</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>21123172.9</t>
+          <t>20782895.4</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>27016759.02</t>
+          <t>25947572.9</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-6223203</t>
+          <t>-6143758</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-1755823.487700998</t>
+          <t>-1938175.643107979</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>-3188307.68</v>
+        <v>-2941112.5</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-3.33</t>
+          <t>-3.81</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5091,7 +5091,7 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>63.1</t>
+          <t>62.66</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>13632</t>
+          <t>13497</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5146,17 +5146,17 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>10.25</t>
+          <t>10.15</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
+          <t>9.85</t>
+        </is>
+      </c>
+      <c r="CF11" t="inlineStr">
+        <is>
           <t>10.1</t>
-        </is>
-      </c>
-      <c r="CF11" t="inlineStr">
-        <is>
-          <t>10.15</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1388.526</t>
+          <t>1474.031</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>10.05</t>
+          <t>10.15</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>-1.5</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-2.61</t>
+          <t>-2.57</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-21.58</t>
+          <t>-29.46</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-2.43</t>
+          <t>-1.46</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>6.33</t>
+          <t>6.72</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,47 +5319,47 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>1335</t>
+          <t>2500</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>15.38</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>5.13</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-1.69</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>10.21</t>
+          <t>10.18</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
@@ -5369,27 +5369,27 @@
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>10.26</t>
+          <t>10.25</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>10.04</t>
+          <t>10.07</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-96.97</t>
+          <t>-125.13</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-89.47</t>
+          <t>-91.98</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,41 +5409,41 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>38437371.74783237</t>
+          <t>38436244.78354979</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>14008369.0</t>
+          <t>15015020.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>16611707.0</t>
+          <t>14899969.2</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>21181803.0</t>
+          <t>21123172.9</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>27684361.26</t>
+          <t>27016759.02</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-4570096</t>
+          <t>-6223203</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-1495371.817099823</t>
+          <t>-1755823.487700998</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>-3203603.12</v>
+        <v>-3188307.68</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-4.29</t>
+          <t>-3.33</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5507,7 +5507,7 @@
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5522,7 +5522,7 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>63.1</t>
+          <t>62.66</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>13632</t>
+          <t>13497</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5572,7 +5572,7 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
@@ -5582,12 +5582,12 @@
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>10.05</t>
+          <t>10.15</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">

--- a/Result/checksun_type/塑化劑(可塑劑).xlsx
+++ b/Result/checksun_type/塑化劑(可塑劑).xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-4.1</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2500.445</t>
+          <t>3938.682</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>9.59</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -908,12 +908,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-2.57</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-2.43</t>
+          <t>-2.69</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -923,7 +923,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-2.91</t>
+          <t>-6.89</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11.41</t>
+          <t>17.97</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-1.60</t>
+          <t>-4.07</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,57 +1009,57 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>2500</t>
+          <t>3939</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>11.29</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>40.86</t>
+          <t>12.9</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-2.72</t>
+          <t>-5.31</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>10.28</t>
+          <t>10.128</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>10.28</t>
+          <t>10.25</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>10.21</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
@@ -1069,17 +1069,17 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-293.77</t>
+          <t>-268.37</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-101.27</t>
+          <t>-103.85</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,41 +1099,41 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>38436244.78354979</t>
+          <t>38463741.81700289</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>25104257.0</t>
+          <t>38346124.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>24629573.0</t>
+          <t>26631549.8</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>25242587.5</t>
+          <t>27366657.0</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>25777972.78</t>
+          <t>26177335.2</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-613014</t>
+          <t>-735107</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-512883.5795906829</t>
+          <t>-317407.7356947591</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>-379221.94</v>
+        <v>757709.41</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-4.76</t>
+          <t>-8.67</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1197,22 +1197,22 @@
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>62.66</t>
+          <t>62.64</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>13497</t>
+          <t>12944</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1262,22 +1262,22 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>10.05</t>
+          <t>9.99</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>9.99</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>9.96</t>
+          <t>9.58</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>9.59</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-3.35</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1335.381</t>
+          <t>2500.445</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,17 +1334,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-4.28</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-2.57</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>-2.43</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-1.94</t>
+          <t>-2.91</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,73 +1419,73 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>6.09</t>
+          <t>11.41</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-4.95</t>
+          <t>-1.60</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>2500</t>
+          <t>3939</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>27.42</t>
+          <t>11.29</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>67.74</t>
+          <t>40.86</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-2.04</t>
+          <t>-2.72</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>10.31</t>
+          <t>10.28</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>10.3</t>
+          <t>10.28</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
@@ -1500,19 +1500,19 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-185.15</t>
+          <t>-293.77</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
+          <t>-0.03</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
           <t>-0.01</t>
         </is>
       </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>-0.00</t>
-        </is>
-      </c>
       <c r="AS3" t="inlineStr">
         <is>
           <t>0.54</t>
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-100.34</t>
+          <t>-101.27</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,41 +1530,41 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>38436244.78354979</t>
+          <t>38463741.81700289</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>13722530.0</t>
+          <t>25104257.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>24615513.2</t>
+          <t>24629573.0</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>24233663.8</t>
+          <t>25242587.5</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>25886365.74</t>
+          <t>25777972.78</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>381849</t>
+          <t>-613014</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-537185.6959741293</t>
+          <t>-512883.5795906829</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>-571094.47</v>
+        <v>-379221.94</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-3.81</t>
+          <t>-4.76</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1628,12 +1628,12 @@
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1643,7 +1643,7 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>62.66</t>
+          <t>62.64</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>13497</t>
+          <t>12944</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1693,22 +1693,22 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>10.45</t>
+          <t>10.05</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>10.6</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>9.96</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-3.35</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1569.646</t>
+          <t>1335.381</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>10.45</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,17 +1765,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-4.5</t>
+          <t>-5.32</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-2.57</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>28.41</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1785,7 +1785,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>-1.94</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,73 +1850,73 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>7.16</t>
+          <t>6.09</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-4.95</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>2500</t>
+          <t>3939</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>83.87</t>
+          <t>27.42</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>81.18</t>
+          <t>67.74</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>-2.04</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>10.276</t>
+          <t>10.31</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>10.31</t>
+          <t>10.3</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
@@ -1931,12 +1931,12 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>1372.99</t>
+          <t>-185.15</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-100.18</t>
+          <t>-100.34</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,41 +1961,41 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>38436244.78354979</t>
+          <t>38463741.81700289</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>16427808.0</t>
+          <t>13722530.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>31153996.2</t>
+          <t>24615513.2</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>24262247.7</t>
+          <t>24233663.8</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>26236307.54</t>
+          <t>25886365.74</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>6891748</t>
+          <t>381849</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-531020.4642383313</t>
+          <t>-537185.6959741293</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>394668.89</v>
+        <v>-571094.47</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-3.81</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2059,22 +2059,22 @@
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>62.66</t>
+          <t>62.64</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>13497</t>
+          <t>12944</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2124,7 +2124,7 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>10.4</t>
+          <t>10.45</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
@@ -2134,12 +2134,12 @@
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>10.3</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>10.45</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3754.177</t>
+          <t>1569.646</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>10.5</t>
+          <t>10.45</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,17 +2196,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-5.0</t>
+          <t>-8.97</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-2.57</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>33.22</t>
+          <t>28.41</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17.12</t>
+          <t>7.16</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,47 +2302,47 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>2500</t>
+          <t>3939</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>91.94</t>
+          <t>83.87</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>65.05</t>
+          <t>81.18</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>10.236</t>
+          <t>10.276</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
@@ -2352,29 +2352,29 @@
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>10.21</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>10.22</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>73.66</t>
+          <t>1372.99</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
           <t>-0.00</t>
         </is>
       </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>-0.00</t>
-        </is>
-      </c>
       <c r="AS5" t="inlineStr">
         <is>
           <t>0.54</t>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-100.80</t>
+          <t>-100.18</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,41 +2392,41 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>38436244.78354979</t>
+          <t>38463741.81700289</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>39557030.0</t>
+          <t>16427808.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>32036639.0</t>
+          <t>31153996.2</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>24048236.4</t>
+          <t>24262247.7</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>26253921.64</t>
+          <t>26236307.54</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>7988402</t>
+          <t>6891748</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-699327.6204268641</t>
+          <t>-531020.4642383313</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>1470384.31</v>
+        <v>394668.89</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2490,12 +2490,12 @@
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2505,7 +2505,7 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>62.66</t>
+          <t>62.64</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>13497</t>
+          <t>12944</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2560,7 +2560,7 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>10.75</t>
+          <t>10.6</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
@@ -2570,7 +2570,7 @@
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>10.5</t>
+          <t>10.45</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2725.546</t>
+          <t>3754.177</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>10.35</t>
+          <t>10.5</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,17 +2627,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-3.5</t>
+          <t>-9.49</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-2.57</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>31.50</t>
+          <t>33.22</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2647,7 +2647,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12.43</t>
+          <t>17.12</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2733,52 +2733,52 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>2500</t>
+          <t>3939</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>67.74</t>
+          <t>91.94</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>34.41</t>
+          <t>65.05</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>10.246</t>
+          <t>10.236</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>10.29</t>
+          <t>10.31</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
@@ -2788,22 +2788,22 @@
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>10.19</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-359.87</t>
+          <t>73.66</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.00</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-0.00</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-100.95</t>
+          <t>-100.80</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,41 +2823,41 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>38436244.78354979</t>
+          <t>38463741.81700289</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>28336240.0</t>
+          <t>39557030.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>28101764.2</t>
+          <t>32036639.0</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>21370450.7</t>
+          <t>24048236.4</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>26117511.38</t>
+          <t>26253921.64</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>6731313</t>
+          <t>7988402</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-1093820.699285948</t>
+          <t>-699327.6204268641</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>476475.97</v>
+        <v>1470384.31</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-1.43</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2921,22 +2921,22 @@
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>62.66</t>
+          <t>62.64</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>13497</t>
+          <t>12944</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>10.15</t>
+          <t>10.4</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>10.6</t>
+          <t>10.75</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>10.15</t>
+          <t>10.3</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>10.35</t>
+          <t>10.5</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2459.513</t>
+          <t>2725.546</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>10.15</t>
+          <t>10.35</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-1.5</t>
+          <t>-7.92</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-2.57</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>26.88</t>
+          <t>31.50</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11.22</t>
+          <t>12.43</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-0.56</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,47 +3164,47 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>2500</t>
+          <t>3939</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>35.48</t>
+          <t>67.74</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>25.16</t>
+          <t>34.41</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>10.196</t>
+          <t>10.246</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
@@ -3219,22 +3219,22 @@
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>10.18</t>
+          <t>10.19</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-6995.52</t>
+          <t>-359.87</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.00</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-100.10</t>
+          <t>-100.95</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,41 +3254,41 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>38436244.78354979</t>
+          <t>38463741.81700289</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>25033958.0</t>
+          <t>28336240.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>25855602.0</t>
+          <t>28101764.2</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>20377785.6</t>
+          <t>21370450.7</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>25837516.22</t>
+          <t>26117511.38</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>5477816</t>
+          <t>6731313</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-1379329.1848641</t>
+          <t>-1093820.699285948</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>241817.41</v>
+        <v>476475.97</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-3.33</t>
+          <t>-1.43</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3352,22 +3352,22 @@
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>62.66</t>
+          <t>62.64</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>13497</t>
+          <t>12944</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3417,22 +3417,22 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>10.15</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>10.4</t>
+          <t>10.6</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>9.96</t>
+          <t>10.15</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>10.15</t>
+          <t>10.35</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-3.14</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>4676.474</t>
+          <t>2459.513</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>9.93</t>
+          <t>10.15</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,17 +3489,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>-5.84</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-2.57</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>17.89</t>
+          <t>26.88</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3509,7 +3509,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-3.59</t>
+          <t>-1.46</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,12 +3574,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>21.33</t>
+          <t>11.22</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -3595,42 +3595,42 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>2500</t>
+          <t>3939</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>35.48</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>41.11</t>
+          <t>25.16</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-2.61</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
@@ -3640,7 +3640,7 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>10.33</t>
+          <t>10.29</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
@@ -3650,22 +3650,22 @@
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>10.17</t>
+          <t>10.18</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-476.65</t>
+          <t>-6995.52</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.00</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-98.43</t>
+          <t>-100.10</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,41 +3685,41 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>38436244.78354979</t>
+          <t>38463741.81700289</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>46414945.0</t>
+          <t>25033958.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>23851814.4</t>
+          <t>25855602.0</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>20231760.7</t>
+          <t>20377785.6</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>25751255.74</t>
+          <t>25837516.22</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>3620053</t>
+          <t>5477816</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-1674083.111667096</t>
+          <t>-1379329.1848641</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>251770.49</v>
+        <v>241817.41</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-5.43</t>
+          <t>-3.33</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3783,22 +3783,22 @@
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>62.66</t>
+          <t>62.64</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>13497</t>
+          <t>12944</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3848,22 +3848,22 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>10.4</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>9.72</t>
+          <t>9.96</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>9.93</t>
+          <t>10.15</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-2.9</t>
+          <t>-3.14</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2017.475</t>
+          <t>4676.474</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>10.25</t>
+          <t>9.93</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,17 +3920,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-2.5</t>
+          <t>-3.55</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-2.57</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>17.89</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3940,7 +3940,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-3.59</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>9.20</t>
+          <t>21.33</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,77 +4026,77 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>2500</t>
+          <t>3939</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>43.68</t>
+          <t>41.11</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>-2.61</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-1.54</t>
+          <t>-1.26</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>10.22</t>
+          <t>10.196</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>10.38</t>
+          <t>10.33</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>10.21</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>10.15</t>
+          <t>10.17</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-116.74</t>
+          <t>-476.65</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.00</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-96.57</t>
+          <t>-98.43</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,41 +4116,41 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>38436244.78354979</t>
+          <t>38463741.81700289</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>20841022.0</t>
+          <t>46414945.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>17370499.2</t>
+          <t>23851814.4</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>17407208.9</t>
+          <t>20231760.7</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>25485299.38</t>
+          <t>25751255.74</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-36709</t>
+          <t>3620053</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-2024238.312393929</t>
+          <t>-1674083.111667096</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>-2033822.66</v>
+        <v>251770.49</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-2.38</t>
+          <t>-5.43</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4214,22 +4214,22 @@
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>62.66</t>
+          <t>62.64</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>13497</t>
+          <t>12944</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4279,22 +4279,22 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>10.35</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>10.5</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>9.72</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>10.25</t>
+          <t>9.93</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>4.41</t>
+          <t>-2.9</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1911.185</t>
+          <t>2017.475</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,84 +4341,84 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
+          <t>10.25</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-6.88</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>-1.87</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>-0.21</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>2025-10-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>2025-10-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>2025-09-23 00:00:00</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>2025-10-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>10.65</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>10.3</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
           <t>10.55</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>-5.5</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>-2.57</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>-25.08</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>-65.0</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>2025-10-27 00:00:00</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>2025-10-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>2025-09-23 00:00:00</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>2025-10-16 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>10.65</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>10.3</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>10.55</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>10.3</t>
-        </is>
-      </c>
       <c r="V10" t="inlineStr">
         <is>
           <t>0</t>
@@ -4426,7 +4426,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>8.72</t>
+          <t>9.20</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,275 +4457,275 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>2500</t>
+          <t>3939</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>83.33</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>35.47</t>
+          <t>43.68</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>3.43</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-1.78</t>
+          <t>-1.54</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
+          <t>10.22</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>10.38</t>
+        </is>
+      </c>
+      <c r="AN10" t="inlineStr">
+        <is>
+          <t>10.21</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>10.15</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr">
+        <is>
+          <t>-116.74</t>
+        </is>
+      </c>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>-0.00</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>0.54</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr">
+        <is>
+          <t>-96.57</t>
+        </is>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>2025/11/13</t>
+        </is>
+      </c>
+      <c r="AV10" t="inlineStr">
+        <is>
+          <t>38463741.81700289</t>
+        </is>
+      </c>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>20841022.0</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>17370499.2</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>17407208.9</t>
+        </is>
+      </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>25485299.38</t>
+        </is>
+      </c>
+      <c r="BA10" t="inlineStr">
+        <is>
+          <t>-36709</t>
+        </is>
+      </c>
+      <c r="BB10" t="inlineStr">
+        <is>
+          <t>-2024238.312393929</t>
+        </is>
+      </c>
+      <c r="BC10" t="n">
+        <v>-2033822.66</v>
+      </c>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE10" t="inlineStr">
+        <is>
+          <t>10.5</t>
+        </is>
+      </c>
+      <c r="BF10" t="inlineStr">
+        <is>
+          <t>2025/10/14</t>
+        </is>
+      </c>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>-2.38</t>
+        </is>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>聯成</t>
+        </is>
+      </c>
+      <c r="BI10" t="inlineStr">
+        <is>
+          <t>聯成</t>
+        </is>
+      </c>
+      <c r="BJ10" t="inlineStr">
+        <is>
+          <t>塑膠工業</t>
+        </is>
+      </c>
+      <c r="BK10" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL10" t="inlineStr">
+        <is>
+          <t>0.78</t>
+        </is>
+      </c>
+      <c r="BM10" t="inlineStr">
+        <is>
+          <t>-11.96408371040724</t>
+        </is>
+      </c>
+      <c r="BN10" t="inlineStr">
+        <is>
+          <t>-13.59414944504011</t>
+        </is>
+      </c>
+      <c r="BO10" t="inlineStr">
+        <is>
+          <t>-19.633719693908</t>
+        </is>
+      </c>
+      <c r="BP10" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BQ10" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="BR10" t="inlineStr">
+        <is>
+          <t>0.46</t>
+        </is>
+      </c>
+      <c r="BS10" t="inlineStr">
+        <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="BT10" t="inlineStr">
+        <is>
+          <t>10.97</t>
+        </is>
+      </c>
+      <c r="BU10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BV10" t="inlineStr">
+        <is>
+          <t>0.96%</t>
+        </is>
+      </c>
+      <c r="BW10" t="inlineStr">
+        <is>
+          <t>-3.42%</t>
+        </is>
+      </c>
+      <c r="BX10" t="inlineStr">
+        <is>
+          <t>62.64</t>
+        </is>
+      </c>
+      <c r="BY10" t="inlineStr">
+        <is>
+          <t>12944</t>
+        </is>
+      </c>
+      <c r="BZ10" t="inlineStr">
+        <is>
+          <t>可塑劑(DOP)76.00%、聚氯乙烯13.00%、酸酐6.00%、其他5.00% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA10" t="inlineStr">
+        <is>
+          <t>聯成-塑膠工業-上市</t>
+        </is>
+      </c>
+      <c r="CB10" t="inlineStr">
+        <is>
+          <t>塑膠工業右下上市</t>
+        </is>
+      </c>
+      <c r="CC10" t="inlineStr">
+        <is>
+          <t>10.35</t>
+        </is>
+      </c>
+      <c r="CD10" t="inlineStr">
+        <is>
+          <t>10.5</t>
+        </is>
+      </c>
+      <c r="CE10" t="inlineStr">
+        <is>
           <t>10.2</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>10.38</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>10.23</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>10.13</t>
-        </is>
-      </c>
-      <c r="AP10" t="inlineStr">
-        <is>
-          <t>-96.16</t>
-        </is>
-      </c>
-      <c r="AQ10" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>0.02</t>
-        </is>
-      </c>
-      <c r="AS10" t="inlineStr">
-        <is>
-          <t>0.54</t>
-        </is>
-      </c>
-      <c r="AT10" t="inlineStr">
-        <is>
-          <t>-95.56</t>
-        </is>
-      </c>
-      <c r="AU10" t="inlineStr">
-        <is>
-          <t>2025/11/13</t>
-        </is>
-      </c>
-      <c r="AV10" t="inlineStr">
-        <is>
-          <t>38436244.78354979</t>
-        </is>
-      </c>
-      <c r="AW10" t="inlineStr">
-        <is>
-          <t>19882656.0</t>
-        </is>
-      </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>16059833.8</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>21436958.2</t>
-        </is>
-      </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>25694765.18</t>
-        </is>
-      </c>
-      <c r="BA10" t="inlineStr">
-        <is>
-          <t>-5377124</t>
-        </is>
-      </c>
-      <c r="BB10" t="inlineStr">
-        <is>
-          <t>-2022495.703504821</t>
-        </is>
-      </c>
-      <c r="BC10" t="n">
-        <v>-2486256.04</v>
-      </c>
-      <c r="BD10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE10" t="inlineStr">
-        <is>
-          <t>10.5</t>
-        </is>
-      </c>
-      <c r="BF10" t="inlineStr">
-        <is>
-          <t>2025/10/14</t>
-        </is>
-      </c>
-      <c r="BG10" t="inlineStr">
-        <is>
-          <t>0.48</t>
-        </is>
-      </c>
-      <c r="BH10" t="inlineStr">
-        <is>
-          <t>聯成</t>
-        </is>
-      </c>
-      <c r="BI10" t="inlineStr">
-        <is>
-          <t>聯成</t>
-        </is>
-      </c>
-      <c r="BJ10" t="inlineStr">
-        <is>
-          <t>塑膠工業</t>
-        </is>
-      </c>
-      <c r="BK10" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BL10" t="inlineStr">
-        <is>
-          <t>0.78</t>
-        </is>
-      </c>
-      <c r="BM10" t="inlineStr">
-        <is>
-          <t>-11.96408371040724</t>
-        </is>
-      </c>
-      <c r="BN10" t="inlineStr">
-        <is>
-          <t>-13.59414944504011</t>
-        </is>
-      </c>
-      <c r="BO10" t="inlineStr">
-        <is>
-          <t>-19.633719693908</t>
-        </is>
-      </c>
-      <c r="BP10" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BQ10" t="inlineStr">
-        <is>
-          <t>價漲量增</t>
-        </is>
-      </c>
-      <c r="BR10" t="inlineStr">
-        <is>
-          <t>0.47</t>
-        </is>
-      </c>
-      <c r="BS10" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
-      </c>
-      <c r="BT10" t="inlineStr">
-        <is>
-          <t>10.97</t>
-        </is>
-      </c>
-      <c r="BU10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BV10" t="inlineStr">
-        <is>
-          <t>0.96%</t>
-        </is>
-      </c>
-      <c r="BW10" t="inlineStr">
-        <is>
-          <t>-3.42%</t>
-        </is>
-      </c>
-      <c r="BX10" t="inlineStr">
-        <is>
-          <t>62.66</t>
-        </is>
-      </c>
-      <c r="BY10" t="inlineStr">
-        <is>
-          <t>13497</t>
-        </is>
-      </c>
-      <c r="BZ10" t="inlineStr">
-        <is>
-          <t>可塑劑(DOP)76.00%、聚氯乙烯13.00%、酸酐6.00%、其他5.00% (2024年)</t>
-        </is>
-      </c>
-      <c r="CA10" t="inlineStr">
-        <is>
-          <t>聯成-塑膠工業-上市</t>
-        </is>
-      </c>
-      <c r="CB10" t="inlineStr">
-        <is>
-          <t>塑膠工業右下上市</t>
-        </is>
-      </c>
-      <c r="CC10" t="inlineStr">
-        <is>
-          <t>10.2</t>
-        </is>
-      </c>
-      <c r="CD10" t="inlineStr">
-        <is>
-          <t>10.55</t>
-        </is>
-      </c>
-      <c r="CE10" t="inlineStr">
-        <is>
-          <t>10.15</t>
-        </is>
-      </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>10.55</t>
+          <t>10.25</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>4.41</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1707.926</t>
+          <t>1911.185</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>10.55</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-10.01</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-2.57</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-29.56</t>
+          <t>-25.08</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4802,7 +4802,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-1.94</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>7.79</t>
+          <t>8.72</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,275 +4888,275 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>2500</t>
+          <t>3939</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>7.69</t>
+          <t>83.33</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>7.69</t>
+          <t>35.47</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>3.43</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-2.15</t>
+          <t>-1.78</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
+          <t>10.2</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>10.38</t>
+        </is>
+      </c>
+      <c r="AN11" t="inlineStr">
+        <is>
+          <t>10.23</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>10.13</t>
+        </is>
+      </c>
+      <c r="AP11" t="inlineStr">
+        <is>
+          <t>-96.16</t>
+        </is>
+      </c>
+      <c r="AQ11" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>0.54</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr">
+        <is>
+          <t>-95.56</t>
+        </is>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>2025/11/13</t>
+        </is>
+      </c>
+      <c r="AV11" t="inlineStr">
+        <is>
+          <t>38463741.81700289</t>
+        </is>
+      </c>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>19882656.0</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>16059833.8</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>21436958.2</t>
+        </is>
+      </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>25694765.18</t>
+        </is>
+      </c>
+      <c r="BA11" t="inlineStr">
+        <is>
+          <t>-5377124</t>
+        </is>
+      </c>
+      <c r="BB11" t="inlineStr">
+        <is>
+          <t>-2022495.703504821</t>
+        </is>
+      </c>
+      <c r="BC11" t="n">
+        <v>-2486256.04</v>
+      </c>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE11" t="inlineStr">
+        <is>
+          <t>10.5</t>
+        </is>
+      </c>
+      <c r="BF11" t="inlineStr">
+        <is>
+          <t>2025/10/14</t>
+        </is>
+      </c>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>0.48</t>
+        </is>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>聯成</t>
+        </is>
+      </c>
+      <c r="BI11" t="inlineStr">
+        <is>
+          <t>聯成</t>
+        </is>
+      </c>
+      <c r="BJ11" t="inlineStr">
+        <is>
+          <t>塑膠工業</t>
+        </is>
+      </c>
+      <c r="BK11" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL11" t="inlineStr">
+        <is>
+          <t>0.78</t>
+        </is>
+      </c>
+      <c r="BM11" t="inlineStr">
+        <is>
+          <t>-11.96408371040724</t>
+        </is>
+      </c>
+      <c r="BN11" t="inlineStr">
+        <is>
+          <t>-13.59414944504011</t>
+        </is>
+      </c>
+      <c r="BO11" t="inlineStr">
+        <is>
+          <t>-19.633719693908</t>
+        </is>
+      </c>
+      <c r="BP11" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BQ11" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BR11" t="inlineStr">
+        <is>
+          <t>0.47</t>
+        </is>
+      </c>
+      <c r="BS11" t="inlineStr">
+        <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="BT11" t="inlineStr">
+        <is>
+          <t>10.97</t>
+        </is>
+      </c>
+      <c r="BU11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BV11" t="inlineStr">
+        <is>
+          <t>0.96%</t>
+        </is>
+      </c>
+      <c r="BW11" t="inlineStr">
+        <is>
+          <t>-3.42%</t>
+        </is>
+      </c>
+      <c r="BX11" t="inlineStr">
+        <is>
+          <t>62.64</t>
+        </is>
+      </c>
+      <c r="BY11" t="inlineStr">
+        <is>
+          <t>12944</t>
+        </is>
+      </c>
+      <c r="BZ11" t="inlineStr">
+        <is>
+          <t>可塑劑(DOP)76.00%、聚氯乙烯13.00%、酸酐6.00%、其他5.00% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA11" t="inlineStr">
+        <is>
+          <t>聯成-塑膠工業-上市</t>
+        </is>
+      </c>
+      <c r="CB11" t="inlineStr">
+        <is>
+          <t>塑膠工業右下上市</t>
+        </is>
+      </c>
+      <c r="CC11" t="inlineStr">
+        <is>
+          <t>10.2</t>
+        </is>
+      </c>
+      <c r="CD11" t="inlineStr">
+        <is>
+          <t>10.55</t>
+        </is>
+      </c>
+      <c r="CE11" t="inlineStr">
+        <is>
           <t>10.15</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>10.37</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>10.23</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>10.1</t>
-        </is>
-      </c>
-      <c r="AP11" t="inlineStr">
-        <is>
-          <t>-182.94</t>
-        </is>
-      </c>
-      <c r="AQ11" t="inlineStr">
-        <is>
-          <t>-0.02</t>
-        </is>
-      </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>0.03</t>
-        </is>
-      </c>
-      <c r="AS11" t="inlineStr">
-        <is>
-          <t>0.54</t>
-        </is>
-      </c>
-      <c r="AT11" t="inlineStr">
-        <is>
-          <t>-94.50</t>
-        </is>
-      </c>
-      <c r="AU11" t="inlineStr">
-        <is>
-          <t>2025/11/13</t>
-        </is>
-      </c>
-      <c r="AV11" t="inlineStr">
-        <is>
-          <t>38436244.78354979</t>
-        </is>
-      </c>
-      <c r="AW11" t="inlineStr">
-        <is>
-          <t>17105429.0</t>
-        </is>
-      </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>14639137.2</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr">
-        <is>
-          <t>20782895.4</t>
-        </is>
-      </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>25947572.9</t>
-        </is>
-      </c>
-      <c r="BA11" t="inlineStr">
-        <is>
-          <t>-6143758</t>
-        </is>
-      </c>
-      <c r="BB11" t="inlineStr">
-        <is>
-          <t>-1938175.643107979</t>
-        </is>
-      </c>
-      <c r="BC11" t="n">
-        <v>-2941112.5</v>
-      </c>
-      <c r="BD11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE11" t="inlineStr">
-        <is>
-          <t>10.5</t>
-        </is>
-      </c>
-      <c r="BF11" t="inlineStr">
-        <is>
-          <t>2025/10/14</t>
-        </is>
-      </c>
-      <c r="BG11" t="inlineStr">
-        <is>
-          <t>-3.81</t>
-        </is>
-      </c>
-      <c r="BH11" t="inlineStr">
-        <is>
-          <t>聯成</t>
-        </is>
-      </c>
-      <c r="BI11" t="inlineStr">
-        <is>
-          <t>聯成</t>
-        </is>
-      </c>
-      <c r="BJ11" t="inlineStr">
-        <is>
-          <t>塑膠工業</t>
-        </is>
-      </c>
-      <c r="BK11" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BL11" t="inlineStr">
-        <is>
-          <t>0.78</t>
-        </is>
-      </c>
-      <c r="BM11" t="inlineStr">
-        <is>
-          <t>-11.96408371040724</t>
-        </is>
-      </c>
-      <c r="BN11" t="inlineStr">
-        <is>
-          <t>-13.59414944504011</t>
-        </is>
-      </c>
-      <c r="BO11" t="inlineStr">
-        <is>
-          <t>-19.633719693908</t>
-        </is>
-      </c>
-      <c r="BP11" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BQ11" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BR11" t="inlineStr">
-        <is>
-          <t>0.45</t>
-        </is>
-      </c>
-      <c r="BS11" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
-      </c>
-      <c r="BT11" t="inlineStr">
-        <is>
-          <t>10.97</t>
-        </is>
-      </c>
-      <c r="BU11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BV11" t="inlineStr">
-        <is>
-          <t>0.96%</t>
-        </is>
-      </c>
-      <c r="BW11" t="inlineStr">
-        <is>
-          <t>-3.42%</t>
-        </is>
-      </c>
-      <c r="BX11" t="inlineStr">
-        <is>
-          <t>62.66</t>
-        </is>
-      </c>
-      <c r="BY11" t="inlineStr">
-        <is>
-          <t>13497</t>
-        </is>
-      </c>
-      <c r="BZ11" t="inlineStr">
-        <is>
-          <t>可塑劑(DOP)76.00%、聚氯乙烯13.00%、酸酐6.00%、其他5.00% (2024年)</t>
-        </is>
-      </c>
-      <c r="CA11" t="inlineStr">
-        <is>
-          <t>聯成-塑膠工業-上市</t>
-        </is>
-      </c>
-      <c r="CB11" t="inlineStr">
-        <is>
-          <t>塑膠工業右下上市</t>
-        </is>
-      </c>
-      <c r="CC11" t="inlineStr">
-        <is>
-          <t>10.1</t>
-        </is>
-      </c>
-      <c r="CD11" t="inlineStr">
-        <is>
-          <t>10.15</t>
-        </is>
-      </c>
-      <c r="CE11" t="inlineStr">
-        <is>
-          <t>9.85</t>
-        </is>
-      </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>10.55</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1474.031</t>
+          <t>1707.926</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>10.15</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-1.5</t>
+          <t>-5.32</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-2.57</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-29.46</t>
+          <t>-29.56</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5233,7 +5233,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>-1.94</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>6.72</t>
+          <t>7.79</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,77 +5319,77 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>2500</t>
+          <t>3939</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>15.38</t>
+          <t>7.69</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>5.13</t>
+          <t>7.69</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>-2.15</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>10.18</t>
+          <t>10.15</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>10.38</t>
+          <t>10.37</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>10.25</t>
+          <t>10.23</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>10.07</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-125.13</t>
+          <t>-182.94</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-91.98</t>
+          <t>-94.50</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,41 +5409,41 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>38436244.78354979</t>
+          <t>38463741.81700289</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>15015020.0</t>
+          <t>17105429.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>14899969.2</t>
+          <t>14639137.2</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>21123172.9</t>
+          <t>20782895.4</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>27016759.02</t>
+          <t>25947572.9</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-6223203</t>
+          <t>-6143758</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-1755823.487700998</t>
+          <t>-1938175.643107979</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>-3188307.68</v>
+        <v>-2941112.5</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-3.33</t>
+          <t>-3.81</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5507,7 +5507,7 @@
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5522,7 +5522,7 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>62.66</t>
+          <t>62.64</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>13497</t>
+          <t>12944</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5577,17 +5577,17 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>10.25</t>
+          <t>10.15</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
+          <t>9.85</t>
+        </is>
+      </c>
+      <c r="CF12" t="inlineStr">
+        <is>
           <t>10.1</t>
-        </is>
-      </c>
-      <c r="CF12" t="inlineStr">
-        <is>
-          <t>10.15</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">

--- a/Result/checksun_type/塑化劑(可塑劑).xlsx
+++ b/Result/checksun_type/塑化劑(可塑劑).xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-4.1</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>3938.682</t>
+          <t>1866.918</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>9.59</t>
+          <t>9.73</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -908,12 +908,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-4.08</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-2.69</t>
+          <t>-17.77</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-6.89</t>
+          <t>-5.53</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17.97</t>
+          <t>8.52</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-4.07</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,52 +1009,52 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>3939</t>
+          <t>1867</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>15.38</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>12.9</t>
+          <t>8.89</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-5.31</t>
+          <t>-2.45</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>10.128</t>
+          <t>9.974</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>10.25</t>
+          <t>10.21</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
@@ -1069,17 +1069,17 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-268.37</t>
+          <t>-177.09</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-103.85</t>
+          <t>-106.90</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,41 +1099,41 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>38463741.81700289</t>
+          <t>38447782.22805756</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>38346124.0</t>
+          <t>18247885.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>26631549.8</t>
+          <t>22369720.8</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>27366657.0</t>
+          <t>27203179.9</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>26177335.2</t>
+          <t>26271252.44</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-735107</t>
+          <t>-4833459</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-317407.7356947591</t>
+          <t>-264383.362935614</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>757709.41</v>
+        <v>27250.69</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-8.67</t>
+          <t>-7.33</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1197,22 +1197,22 @@
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>12944</t>
+          <t>13132</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1262,22 +1262,22 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>9.99</t>
+          <t>9.77</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>9.99</t>
+          <t>9.95</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>9.58</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>9.59</t>
+          <t>9.73</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-4.1</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2500.445</t>
+          <t>3938.682</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>9.59</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,17 +1334,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-4.28</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-4.08</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-2.43</t>
+          <t>-2.69</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-2.91</t>
+          <t>-6.89</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11.41</t>
+          <t>17.97</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-1.60</t>
+          <t>-4.07</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,57 +1440,57 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>3939</t>
+          <t>1867</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>11.29</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>40.86</t>
+          <t>12.9</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-2.72</t>
+          <t>-5.31</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>10.28</t>
+          <t>10.128</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>10.28</t>
+          <t>10.25</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>10.21</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
@@ -1500,17 +1500,17 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-293.77</t>
+          <t>-268.37</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-101.27</t>
+          <t>-103.85</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,41 +1530,41 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>38463741.81700289</t>
+          <t>38447782.22805756</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>25104257.0</t>
+          <t>38346124.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>24629573.0</t>
+          <t>26631549.8</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>25242587.5</t>
+          <t>27366657.0</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>25777972.78</t>
+          <t>26177335.2</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-613014</t>
+          <t>-735107</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-512883.5795906829</t>
+          <t>-317407.7356947591</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>-379221.94</v>
+        <v>757709.41</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-4.76</t>
+          <t>-8.67</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1628,22 +1628,22 @@
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1673,7 +1673,7 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>12944</t>
+          <t>13132</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1693,22 +1693,22 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>10.05</t>
+          <t>9.99</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>9.99</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>9.96</t>
+          <t>9.58</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>9.59</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-3.35</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1335.381</t>
+          <t>2500.445</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,17 +1765,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-5.32</t>
+          <t>-2.77</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-4.08</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>-2.43</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-1.94</t>
+          <t>-2.91</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,73 +1850,73 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>6.09</t>
+          <t>11.41</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-4.95</t>
+          <t>-1.60</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>3939</t>
+          <t>1867</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>27.42</t>
+          <t>11.29</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>67.74</t>
+          <t>40.86</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-2.04</t>
+          <t>-2.72</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>10.31</t>
+          <t>10.28</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>10.3</t>
+          <t>10.28</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
@@ -1931,19 +1931,19 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-185.15</t>
+          <t>-293.77</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
+          <t>-0.03</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
           <t>-0.01</t>
         </is>
       </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>-0.00</t>
-        </is>
-      </c>
       <c r="AS4" t="inlineStr">
         <is>
           <t>0.54</t>
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-100.34</t>
+          <t>-101.27</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,41 +1961,41 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>38463741.81700289</t>
+          <t>38447782.22805756</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>13722530.0</t>
+          <t>25104257.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>24615513.2</t>
+          <t>24629573.0</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>24233663.8</t>
+          <t>25242587.5</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>25886365.74</t>
+          <t>25777972.78</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>381849</t>
+          <t>-613014</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-537185.6959741293</t>
+          <t>-512883.5795906829</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>-571094.47</v>
+        <v>-379221.94</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-3.81</t>
+          <t>-4.76</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2059,12 +2059,12 @@
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>12944</t>
+          <t>13132</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2124,22 +2124,22 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>10.45</t>
+          <t>10.05</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>10.6</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>9.96</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-3.35</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1569.646</t>
+          <t>1335.381</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>10.45</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,17 +2196,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-8.97</t>
+          <t>-3.8</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-4.08</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>28.41</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>-1.94</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,73 +2281,73 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>7.16</t>
+          <t>6.09</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-4.95</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>3939</t>
+          <t>1867</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>83.87</t>
+          <t>27.42</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>81.18</t>
+          <t>67.74</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>-2.04</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>10.276</t>
+          <t>10.31</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>10.31</t>
+          <t>10.3</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>1372.99</t>
+          <t>-185.15</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-100.18</t>
+          <t>-100.34</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,41 +2392,41 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>38463741.81700289</t>
+          <t>38447782.22805756</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>16427808.0</t>
+          <t>13722530.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>31153996.2</t>
+          <t>24615513.2</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>24262247.7</t>
+          <t>24233663.8</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>26236307.54</t>
+          <t>25886365.74</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>6891748</t>
+          <t>381849</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-531020.4642383313</t>
+          <t>-537185.6959741293</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>394668.89</v>
+        <v>-571094.47</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-3.81</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2490,22 +2490,22 @@
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2535,7 +2535,7 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>12944</t>
+          <t>13132</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2555,7 +2555,7 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>10.4</t>
+          <t>10.45</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
@@ -2565,12 +2565,12 @@
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>10.3</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>10.45</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>3754.177</t>
+          <t>1569.646</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>10.5</t>
+          <t>10.45</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,17 +2627,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-9.49</t>
+          <t>-7.4</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-4.08</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>33.22</t>
+          <t>28.41</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17.12</t>
+          <t>7.16</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2733,47 +2733,47 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>3939</t>
+          <t>1867</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>91.94</t>
+          <t>83.87</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>65.05</t>
+          <t>81.18</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>10.236</t>
+          <t>10.276</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
@@ -2783,29 +2783,29 @@
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>10.21</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>10.22</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>73.66</t>
+          <t>1372.99</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
           <t>-0.00</t>
         </is>
       </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>-0.00</t>
-        </is>
-      </c>
       <c r="AS6" t="inlineStr">
         <is>
           <t>0.54</t>
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-100.80</t>
+          <t>-100.18</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,41 +2823,41 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>38463741.81700289</t>
+          <t>38447782.22805756</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>39557030.0</t>
+          <t>16427808.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>32036639.0</t>
+          <t>31153996.2</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>24048236.4</t>
+          <t>24262247.7</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>26253921.64</t>
+          <t>26236307.54</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>7988402</t>
+          <t>6891748</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-699327.6204268641</t>
+          <t>-531020.4642383313</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>1470384.31</v>
+        <v>394668.89</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2921,12 +2921,12 @@
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2966,7 +2966,7 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>12944</t>
+          <t>13132</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2991,7 +2991,7 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>10.75</t>
+          <t>10.6</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
@@ -3001,7 +3001,7 @@
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>10.5</t>
+          <t>10.45</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2725.546</t>
+          <t>3754.177</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>10.35</t>
+          <t>10.5</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-7.92</t>
+          <t>-7.91</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-4.08</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>31.50</t>
+          <t>33.22</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12.43</t>
+          <t>17.12</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,52 +3164,52 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>3939</t>
+          <t>1867</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>67.74</t>
+          <t>91.94</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>34.41</t>
+          <t>65.05</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>10.246</t>
+          <t>10.236</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>10.29</t>
+          <t>10.31</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
@@ -3219,22 +3219,22 @@
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>10.19</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-359.87</t>
+          <t>73.66</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.00</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-0.00</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-100.95</t>
+          <t>-100.80</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,41 +3254,41 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>38463741.81700289</t>
+          <t>38447782.22805756</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>28336240.0</t>
+          <t>39557030.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>28101764.2</t>
+          <t>32036639.0</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>21370450.7</t>
+          <t>24048236.4</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>26117511.38</t>
+          <t>26253921.64</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>6731313</t>
+          <t>7988402</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-1093820.699285948</t>
+          <t>-699327.6204268641</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>476475.97</v>
+        <v>1470384.31</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-1.43</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3352,22 +3352,22 @@
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3397,7 +3397,7 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>12944</t>
+          <t>13132</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3417,22 +3417,22 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>10.15</t>
+          <t>10.4</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>10.6</t>
+          <t>10.75</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>10.15</t>
+          <t>10.3</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>10.35</t>
+          <t>10.5</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2459.513</t>
+          <t>2725.546</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>10.15</t>
+          <t>10.35</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,17 +3489,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-5.84</t>
+          <t>-6.37</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-4.08</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>26.88</t>
+          <t>31.50</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11.22</t>
+          <t>12.43</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-0.56</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3595,47 +3595,47 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>3939</t>
+          <t>1867</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>35.48</t>
+          <t>67.74</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>25.16</t>
+          <t>34.41</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>10.196</t>
+          <t>10.246</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
@@ -3650,22 +3650,22 @@
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>10.18</t>
+          <t>10.19</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-6995.52</t>
+          <t>-359.87</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.00</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-100.10</t>
+          <t>-100.95</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,41 +3685,41 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>38463741.81700289</t>
+          <t>38447782.22805756</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>25033958.0</t>
+          <t>28336240.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>25855602.0</t>
+          <t>28101764.2</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>20377785.6</t>
+          <t>21370450.7</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>25837516.22</t>
+          <t>26117511.38</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>5477816</t>
+          <t>6731313</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-1379329.1848641</t>
+          <t>-1093820.699285948</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>241817.41</v>
+        <v>476475.97</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-3.33</t>
+          <t>-1.43</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3783,22 +3783,22 @@
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3828,7 +3828,7 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>12944</t>
+          <t>13132</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3848,22 +3848,22 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>10.15</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>10.4</t>
+          <t>10.6</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>9.96</t>
+          <t>10.15</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>10.15</t>
+          <t>10.35</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-3.14</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>4676.474</t>
+          <t>2459.513</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>9.93</t>
+          <t>10.15</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,17 +3920,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-3.55</t>
+          <t>-4.32</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-4.08</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>17.89</t>
+          <t>26.88</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-3.59</t>
+          <t>-1.46</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,12 +4005,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>21.33</t>
+          <t>11.22</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -4026,42 +4026,42 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>3939</t>
+          <t>1867</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>35.48</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>41.11</t>
+          <t>25.16</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-2.61</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
@@ -4071,7 +4071,7 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>10.33</t>
+          <t>10.29</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
@@ -4081,22 +4081,22 @@
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>10.17</t>
+          <t>10.18</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-476.65</t>
+          <t>-6995.52</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.00</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-98.43</t>
+          <t>-100.10</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,41 +4116,41 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>38463741.81700289</t>
+          <t>38447782.22805756</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>46414945.0</t>
+          <t>25033958.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>23851814.4</t>
+          <t>25855602.0</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>20231760.7</t>
+          <t>20377785.6</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>25751255.74</t>
+          <t>25837516.22</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>3620053</t>
+          <t>5477816</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-1674083.111667096</t>
+          <t>-1379329.1848641</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>251770.49</v>
+        <v>241817.41</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-5.43</t>
+          <t>-3.33</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4214,22 +4214,22 @@
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4259,7 +4259,7 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>12944</t>
+          <t>13132</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4279,22 +4279,22 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>10.4</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>9.72</t>
+          <t>9.96</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>9.93</t>
+          <t>10.15</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-2.9</t>
+          <t>-3.14</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2017.475</t>
+          <t>4676.474</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>10.25</t>
+          <t>9.93</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4351,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-6.88</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-4.08</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>17.89</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-3.59</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>9.20</t>
+          <t>21.33</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,77 +4457,77 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>3939</t>
+          <t>1867</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>43.68</t>
+          <t>41.11</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>-2.61</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-1.54</t>
+          <t>-1.26</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>10.22</t>
+          <t>10.196</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>10.38</t>
+          <t>10.33</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>10.21</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>10.15</t>
+          <t>10.17</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-116.74</t>
+          <t>-476.65</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.00</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-96.57</t>
+          <t>-98.43</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,41 +4547,41 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>38463741.81700289</t>
+          <t>38447782.22805756</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>20841022.0</t>
+          <t>46414945.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>17370499.2</t>
+          <t>23851814.4</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>17407208.9</t>
+          <t>20231760.7</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>25485299.38</t>
+          <t>25751255.74</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-36709</t>
+          <t>3620053</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-2024238.312393929</t>
+          <t>-1674083.111667096</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>-2033822.66</v>
+        <v>251770.49</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-2.38</t>
+          <t>-5.43</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -4655,12 +4655,12 @@
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4690,7 +4690,7 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>12944</t>
+          <t>13132</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4710,22 +4710,22 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>10.35</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>10.5</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>9.72</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>10.25</t>
+          <t>9.93</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>4.41</t>
+          <t>-2.9</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1911.185</t>
+          <t>2017.475</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,84 +4772,84 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
+          <t>10.25</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-5.34</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>-4.08</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>-0.21</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2025-10-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2025-10-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>2025-09-23 00:00:00</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>2025-10-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>10.65</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>10.3</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
           <t>10.55</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>-10.01</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>-1.87</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>-25.08</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>2025-10-27 00:00:00</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>2025-10-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>2025-09-23 00:00:00</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>2025-10-16 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>10.65</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>10.3</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>10.55</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>10.3</t>
-        </is>
-      </c>
       <c r="V11" t="inlineStr">
         <is>
           <t>0</t>
@@ -4857,7 +4857,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>8.72</t>
+          <t>9.20</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,275 +4888,275 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>3939</t>
+          <t>1867</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>83.33</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>35.47</t>
+          <t>43.68</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>3.43</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-1.78</t>
+          <t>-1.54</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
+          <t>10.22</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>10.38</t>
+        </is>
+      </c>
+      <c r="AN11" t="inlineStr">
+        <is>
+          <t>10.21</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>10.15</t>
+        </is>
+      </c>
+      <c r="AP11" t="inlineStr">
+        <is>
+          <t>-116.74</t>
+        </is>
+      </c>
+      <c r="AQ11" t="inlineStr">
+        <is>
+          <t>-0.00</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>0.54</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr">
+        <is>
+          <t>-96.57</t>
+        </is>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>2025/11/13</t>
+        </is>
+      </c>
+      <c r="AV11" t="inlineStr">
+        <is>
+          <t>38447782.22805756</t>
+        </is>
+      </c>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>20841022.0</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>17370499.2</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>17407208.9</t>
+        </is>
+      </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>25485299.38</t>
+        </is>
+      </c>
+      <c r="BA11" t="inlineStr">
+        <is>
+          <t>-36709</t>
+        </is>
+      </c>
+      <c r="BB11" t="inlineStr">
+        <is>
+          <t>-2024238.312393929</t>
+        </is>
+      </c>
+      <c r="BC11" t="n">
+        <v>-2033822.66</v>
+      </c>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE11" t="inlineStr">
+        <is>
+          <t>10.5</t>
+        </is>
+      </c>
+      <c r="BF11" t="inlineStr">
+        <is>
+          <t>2025/10/14</t>
+        </is>
+      </c>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>-2.38</t>
+        </is>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>聯成</t>
+        </is>
+      </c>
+      <c r="BI11" t="inlineStr">
+        <is>
+          <t>聯成</t>
+        </is>
+      </c>
+      <c r="BJ11" t="inlineStr">
+        <is>
+          <t>塑膠工業</t>
+        </is>
+      </c>
+      <c r="BK11" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL11" t="inlineStr">
+        <is>
+          <t>0.78</t>
+        </is>
+      </c>
+      <c r="BM11" t="inlineStr">
+        <is>
+          <t>-11.96408371040724</t>
+        </is>
+      </c>
+      <c r="BN11" t="inlineStr">
+        <is>
+          <t>-13.59414944504011</t>
+        </is>
+      </c>
+      <c r="BO11" t="inlineStr">
+        <is>
+          <t>-19.633719693908</t>
+        </is>
+      </c>
+      <c r="BP11" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BQ11" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BR11" t="inlineStr">
+        <is>
+          <t>0.46</t>
+        </is>
+      </c>
+      <c r="BS11" t="inlineStr">
+        <is>
+          <t>1.54</t>
+        </is>
+      </c>
+      <c r="BT11" t="inlineStr">
+        <is>
+          <t>10.97</t>
+        </is>
+      </c>
+      <c r="BU11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BV11" t="inlineStr">
+        <is>
+          <t>0.96%</t>
+        </is>
+      </c>
+      <c r="BW11" t="inlineStr">
+        <is>
+          <t>-3.42%</t>
+        </is>
+      </c>
+      <c r="BX11" t="inlineStr">
+        <is>
+          <t>62.64</t>
+        </is>
+      </c>
+      <c r="BY11" t="inlineStr">
+        <is>
+          <t>13132</t>
+        </is>
+      </c>
+      <c r="BZ11" t="inlineStr">
+        <is>
+          <t>可塑劑(DOP)76.00%、聚氯乙烯13.00%、酸酐6.00%、其他5.00% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA11" t="inlineStr">
+        <is>
+          <t>聯成-塑膠工業-上市</t>
+        </is>
+      </c>
+      <c r="CB11" t="inlineStr">
+        <is>
+          <t>塑膠工業右下上市</t>
+        </is>
+      </c>
+      <c r="CC11" t="inlineStr">
+        <is>
+          <t>10.35</t>
+        </is>
+      </c>
+      <c r="CD11" t="inlineStr">
+        <is>
+          <t>10.5</t>
+        </is>
+      </c>
+      <c r="CE11" t="inlineStr">
+        <is>
           <t>10.2</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>10.38</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>10.23</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>10.13</t>
-        </is>
-      </c>
-      <c r="AP11" t="inlineStr">
-        <is>
-          <t>-96.16</t>
-        </is>
-      </c>
-      <c r="AQ11" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>0.02</t>
-        </is>
-      </c>
-      <c r="AS11" t="inlineStr">
-        <is>
-          <t>0.54</t>
-        </is>
-      </c>
-      <c r="AT11" t="inlineStr">
-        <is>
-          <t>-95.56</t>
-        </is>
-      </c>
-      <c r="AU11" t="inlineStr">
-        <is>
-          <t>2025/11/13</t>
-        </is>
-      </c>
-      <c r="AV11" t="inlineStr">
-        <is>
-          <t>38463741.81700289</t>
-        </is>
-      </c>
-      <c r="AW11" t="inlineStr">
-        <is>
-          <t>19882656.0</t>
-        </is>
-      </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>16059833.8</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr">
-        <is>
-          <t>21436958.2</t>
-        </is>
-      </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>25694765.18</t>
-        </is>
-      </c>
-      <c r="BA11" t="inlineStr">
-        <is>
-          <t>-5377124</t>
-        </is>
-      </c>
-      <c r="BB11" t="inlineStr">
-        <is>
-          <t>-2022495.703504821</t>
-        </is>
-      </c>
-      <c r="BC11" t="n">
-        <v>-2486256.04</v>
-      </c>
-      <c r="BD11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE11" t="inlineStr">
-        <is>
-          <t>10.5</t>
-        </is>
-      </c>
-      <c r="BF11" t="inlineStr">
-        <is>
-          <t>2025/10/14</t>
-        </is>
-      </c>
-      <c r="BG11" t="inlineStr">
-        <is>
-          <t>0.48</t>
-        </is>
-      </c>
-      <c r="BH11" t="inlineStr">
-        <is>
-          <t>聯成</t>
-        </is>
-      </c>
-      <c r="BI11" t="inlineStr">
-        <is>
-          <t>聯成</t>
-        </is>
-      </c>
-      <c r="BJ11" t="inlineStr">
-        <is>
-          <t>塑膠工業</t>
-        </is>
-      </c>
-      <c r="BK11" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BL11" t="inlineStr">
-        <is>
-          <t>0.78</t>
-        </is>
-      </c>
-      <c r="BM11" t="inlineStr">
-        <is>
-          <t>-11.96408371040724</t>
-        </is>
-      </c>
-      <c r="BN11" t="inlineStr">
-        <is>
-          <t>-13.59414944504011</t>
-        </is>
-      </c>
-      <c r="BO11" t="inlineStr">
-        <is>
-          <t>-19.633719693908</t>
-        </is>
-      </c>
-      <c r="BP11" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BQ11" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BR11" t="inlineStr">
-        <is>
-          <t>0.47</t>
-        </is>
-      </c>
-      <c r="BS11" t="inlineStr">
-        <is>
-          <t>1.56</t>
-        </is>
-      </c>
-      <c r="BT11" t="inlineStr">
-        <is>
-          <t>10.97</t>
-        </is>
-      </c>
-      <c r="BU11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BV11" t="inlineStr">
-        <is>
-          <t>0.96%</t>
-        </is>
-      </c>
-      <c r="BW11" t="inlineStr">
-        <is>
-          <t>-3.42%</t>
-        </is>
-      </c>
-      <c r="BX11" t="inlineStr">
-        <is>
-          <t>62.64</t>
-        </is>
-      </c>
-      <c r="BY11" t="inlineStr">
-        <is>
-          <t>12944</t>
-        </is>
-      </c>
-      <c r="BZ11" t="inlineStr">
-        <is>
-          <t>可塑劑(DOP)76.00%、聚氯乙烯13.00%、酸酐6.00%、其他5.00% (2024年)</t>
-        </is>
-      </c>
-      <c r="CA11" t="inlineStr">
-        <is>
-          <t>聯成-塑膠工業-上市</t>
-        </is>
-      </c>
-      <c r="CB11" t="inlineStr">
-        <is>
-          <t>塑膠工業右下上市</t>
-        </is>
-      </c>
-      <c r="CC11" t="inlineStr">
-        <is>
-          <t>10.2</t>
-        </is>
-      </c>
-      <c r="CD11" t="inlineStr">
-        <is>
-          <t>10.55</t>
-        </is>
-      </c>
-      <c r="CE11" t="inlineStr">
-        <is>
-          <t>10.15</t>
-        </is>
-      </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>10.55</t>
+          <t>10.25</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>4.41</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1707.926</t>
+          <t>1911.185</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>10.55</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-5.32</t>
+          <t>-8.43</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-4.08</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-29.56</t>
+          <t>-25.08</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-1.94</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>7.79</t>
+          <t>8.72</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,275 +5319,275 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>3939</t>
+          <t>1867</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>7.69</t>
+          <t>83.33</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>7.69</t>
+          <t>35.47</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>3.43</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-2.15</t>
+          <t>-1.78</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
+          <t>10.2</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>10.38</t>
+        </is>
+      </c>
+      <c r="AN12" t="inlineStr">
+        <is>
+          <t>10.23</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>10.13</t>
+        </is>
+      </c>
+      <c r="AP12" t="inlineStr">
+        <is>
+          <t>-96.16</t>
+        </is>
+      </c>
+      <c r="AQ12" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="AS12" t="inlineStr">
+        <is>
+          <t>0.54</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr">
+        <is>
+          <t>-95.56</t>
+        </is>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>2025/11/13</t>
+        </is>
+      </c>
+      <c r="AV12" t="inlineStr">
+        <is>
+          <t>38447782.22805756</t>
+        </is>
+      </c>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>19882656.0</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>16059833.8</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>21436958.2</t>
+        </is>
+      </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>25694765.18</t>
+        </is>
+      </c>
+      <c r="BA12" t="inlineStr">
+        <is>
+          <t>-5377124</t>
+        </is>
+      </c>
+      <c r="BB12" t="inlineStr">
+        <is>
+          <t>-2022495.703504821</t>
+        </is>
+      </c>
+      <c r="BC12" t="n">
+        <v>-2486256.04</v>
+      </c>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE12" t="inlineStr">
+        <is>
+          <t>10.5</t>
+        </is>
+      </c>
+      <c r="BF12" t="inlineStr">
+        <is>
+          <t>2025/10/14</t>
+        </is>
+      </c>
+      <c r="BG12" t="inlineStr">
+        <is>
+          <t>0.48</t>
+        </is>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>聯成</t>
+        </is>
+      </c>
+      <c r="BI12" t="inlineStr">
+        <is>
+          <t>聯成</t>
+        </is>
+      </c>
+      <c r="BJ12" t="inlineStr">
+        <is>
+          <t>塑膠工業</t>
+        </is>
+      </c>
+      <c r="BK12" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL12" t="inlineStr">
+        <is>
+          <t>0.78</t>
+        </is>
+      </c>
+      <c r="BM12" t="inlineStr">
+        <is>
+          <t>-11.96408371040724</t>
+        </is>
+      </c>
+      <c r="BN12" t="inlineStr">
+        <is>
+          <t>-13.59414944504011</t>
+        </is>
+      </c>
+      <c r="BO12" t="inlineStr">
+        <is>
+          <t>-19.633719693908</t>
+        </is>
+      </c>
+      <c r="BP12" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BQ12" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BR12" t="inlineStr">
+        <is>
+          <t>0.47</t>
+        </is>
+      </c>
+      <c r="BS12" t="inlineStr">
+        <is>
+          <t>1.54</t>
+        </is>
+      </c>
+      <c r="BT12" t="inlineStr">
+        <is>
+          <t>10.97</t>
+        </is>
+      </c>
+      <c r="BU12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BV12" t="inlineStr">
+        <is>
+          <t>0.96%</t>
+        </is>
+      </c>
+      <c r="BW12" t="inlineStr">
+        <is>
+          <t>-3.42%</t>
+        </is>
+      </c>
+      <c r="BX12" t="inlineStr">
+        <is>
+          <t>62.64</t>
+        </is>
+      </c>
+      <c r="BY12" t="inlineStr">
+        <is>
+          <t>13132</t>
+        </is>
+      </c>
+      <c r="BZ12" t="inlineStr">
+        <is>
+          <t>可塑劑(DOP)76.00%、聚氯乙烯13.00%、酸酐6.00%、其他5.00% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA12" t="inlineStr">
+        <is>
+          <t>聯成-塑膠工業-上市</t>
+        </is>
+      </c>
+      <c r="CB12" t="inlineStr">
+        <is>
+          <t>塑膠工業右下上市</t>
+        </is>
+      </c>
+      <c r="CC12" t="inlineStr">
+        <is>
+          <t>10.2</t>
+        </is>
+      </c>
+      <c r="CD12" t="inlineStr">
+        <is>
+          <t>10.55</t>
+        </is>
+      </c>
+      <c r="CE12" t="inlineStr">
+        <is>
           <t>10.15</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>10.37</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>10.23</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>10.1</t>
-        </is>
-      </c>
-      <c r="AP12" t="inlineStr">
-        <is>
-          <t>-182.94</t>
-        </is>
-      </c>
-      <c r="AQ12" t="inlineStr">
-        <is>
-          <t>-0.02</t>
-        </is>
-      </c>
-      <c r="AR12" t="inlineStr">
-        <is>
-          <t>0.03</t>
-        </is>
-      </c>
-      <c r="AS12" t="inlineStr">
-        <is>
-          <t>0.54</t>
-        </is>
-      </c>
-      <c r="AT12" t="inlineStr">
-        <is>
-          <t>-94.50</t>
-        </is>
-      </c>
-      <c r="AU12" t="inlineStr">
-        <is>
-          <t>2025/11/13</t>
-        </is>
-      </c>
-      <c r="AV12" t="inlineStr">
-        <is>
-          <t>38463741.81700289</t>
-        </is>
-      </c>
-      <c r="AW12" t="inlineStr">
-        <is>
-          <t>17105429.0</t>
-        </is>
-      </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>14639137.2</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr">
-        <is>
-          <t>20782895.4</t>
-        </is>
-      </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>25947572.9</t>
-        </is>
-      </c>
-      <c r="BA12" t="inlineStr">
-        <is>
-          <t>-6143758</t>
-        </is>
-      </c>
-      <c r="BB12" t="inlineStr">
-        <is>
-          <t>-1938175.643107979</t>
-        </is>
-      </c>
-      <c r="BC12" t="n">
-        <v>-2941112.5</v>
-      </c>
-      <c r="BD12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE12" t="inlineStr">
-        <is>
-          <t>10.5</t>
-        </is>
-      </c>
-      <c r="BF12" t="inlineStr">
-        <is>
-          <t>2025/10/14</t>
-        </is>
-      </c>
-      <c r="BG12" t="inlineStr">
-        <is>
-          <t>-3.81</t>
-        </is>
-      </c>
-      <c r="BH12" t="inlineStr">
-        <is>
-          <t>聯成</t>
-        </is>
-      </c>
-      <c r="BI12" t="inlineStr">
-        <is>
-          <t>聯成</t>
-        </is>
-      </c>
-      <c r="BJ12" t="inlineStr">
-        <is>
-          <t>塑膠工業</t>
-        </is>
-      </c>
-      <c r="BK12" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BL12" t="inlineStr">
-        <is>
-          <t>0.78</t>
-        </is>
-      </c>
-      <c r="BM12" t="inlineStr">
-        <is>
-          <t>-11.96408371040724</t>
-        </is>
-      </c>
-      <c r="BN12" t="inlineStr">
-        <is>
-          <t>-13.59414944504011</t>
-        </is>
-      </c>
-      <c r="BO12" t="inlineStr">
-        <is>
-          <t>-19.633719693908</t>
-        </is>
-      </c>
-      <c r="BP12" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BQ12" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BR12" t="inlineStr">
-        <is>
-          <t>0.45</t>
-        </is>
-      </c>
-      <c r="BS12" t="inlineStr">
-        <is>
-          <t>1.56</t>
-        </is>
-      </c>
-      <c r="BT12" t="inlineStr">
-        <is>
-          <t>10.97</t>
-        </is>
-      </c>
-      <c r="BU12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BV12" t="inlineStr">
-        <is>
-          <t>0.96%</t>
-        </is>
-      </c>
-      <c r="BW12" t="inlineStr">
-        <is>
-          <t>-3.42%</t>
-        </is>
-      </c>
-      <c r="BX12" t="inlineStr">
-        <is>
-          <t>62.64</t>
-        </is>
-      </c>
-      <c r="BY12" t="inlineStr">
-        <is>
-          <t>12944</t>
-        </is>
-      </c>
-      <c r="BZ12" t="inlineStr">
-        <is>
-          <t>可塑劑(DOP)76.00%、聚氯乙烯13.00%、酸酐6.00%、其他5.00% (2024年)</t>
-        </is>
-      </c>
-      <c r="CA12" t="inlineStr">
-        <is>
-          <t>聯成-塑膠工業-上市</t>
-        </is>
-      </c>
-      <c r="CB12" t="inlineStr">
-        <is>
-          <t>塑膠工業右下上市</t>
-        </is>
-      </c>
-      <c r="CC12" t="inlineStr">
-        <is>
-          <t>10.1</t>
-        </is>
-      </c>
-      <c r="CD12" t="inlineStr">
-        <is>
-          <t>10.15</t>
-        </is>
-      </c>
-      <c r="CE12" t="inlineStr">
-        <is>
-          <t>9.85</t>
-        </is>
-      </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>10.55</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">

--- a/Result/checksun_type/塑化劑(可塑劑).xlsx
+++ b/Result/checksun_type/塑化劑(可塑劑).xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CI12"/>
+  <dimension ref="A1:CJ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -701,165 +701,170 @@
       </c>
       <c r="BC1" s="1" t="inlineStr">
         <is>
-          <t>Volume_Price_Change_sum</t>
+          <t>VPC_MACD</t>
         </is>
       </c>
       <c r="BD1" s="1" t="inlineStr">
         <is>
+          <t>Volume_Price_Change</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
           <t>highlight_enddate</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_date收盤價</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_date</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_%</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>stock_name</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BJ1" s="1" t="inlineStr">
         <is>
           <t>Type0</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BK1" s="1" t="inlineStr">
         <is>
           <t>Type1</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BL1" s="1" t="inlineStr">
         <is>
           <t>Type2</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
+      <c r="BM1" s="1" t="inlineStr">
         <is>
           <t>貝他值</t>
         </is>
       </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="BN1" s="1" t="inlineStr">
         <is>
           <t>營業收入-上月比較增減(%)</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="BO1" s="1" t="inlineStr">
         <is>
           <t>營業收入-去年同月增減(%)</t>
         </is>
       </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="BP1" s="1" t="inlineStr">
         <is>
           <t>累計營業收入-前期比較增減(%)</t>
         </is>
       </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="BQ1" s="1" t="inlineStr">
         <is>
           <t>Full_Summary</t>
         </is>
       </c>
-      <c r="BQ1" s="1" t="inlineStr">
+      <c r="BR1" s="1" t="inlineStr">
         <is>
           <t>textdesc</t>
         </is>
       </c>
-      <c r="BR1" s="1" t="inlineStr">
+      <c r="BS1" s="1" t="inlineStr">
         <is>
           <t>淨值倍率</t>
         </is>
       </c>
-      <c r="BS1" s="1" t="inlineStr">
+      <c r="BT1" s="1" t="inlineStr">
         <is>
           <t>殖利率</t>
         </is>
       </c>
-      <c r="BT1" s="1" t="inlineStr">
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>每股營收(元)</t>
         </is>
       </c>
-      <c r="BU1" s="1" t="inlineStr">
+      <c r="BV1" s="1" t="inlineStr">
         <is>
           <t>本益比</t>
         </is>
       </c>
-      <c r="BV1" s="1" t="inlineStr">
+      <c r="BW1" s="1" t="inlineStr">
         <is>
           <t>營業毛利率</t>
         </is>
       </c>
-      <c r="BW1" s="1" t="inlineStr">
+      <c r="BX1" s="1" t="inlineStr">
         <is>
           <t>營業利益率</t>
         </is>
       </c>
-      <c r="BX1" s="1" t="inlineStr">
+      <c r="BY1" s="1" t="inlineStr">
         <is>
           <t>同業平均本益比</t>
         </is>
       </c>
-      <c r="BY1" s="1" t="inlineStr">
+      <c r="BZ1" s="1" t="inlineStr">
         <is>
           <t>總市值</t>
         </is>
       </c>
-      <c r="BZ1" s="1" t="inlineStr">
+      <c r="CA1" s="1" t="inlineStr">
         <is>
           <t>營收比重</t>
         </is>
       </c>
-      <c r="CA1" s="1" t="inlineStr">
+      <c r="CB1" s="1" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="CB1" s="1" t="inlineStr">
+      <c r="CC1" s="1" t="inlineStr">
         <is>
           <t>Typelevel</t>
         </is>
       </c>
-      <c r="CC1" s="1" t="inlineStr">
+      <c r="CD1" s="1" t="inlineStr">
         <is>
           <t>開盤價</t>
         </is>
       </c>
-      <c r="CD1" s="1" t="inlineStr">
+      <c r="CE1" s="1" t="inlineStr">
         <is>
           <t>最高價</t>
         </is>
       </c>
-      <c r="CE1" s="1" t="inlineStr">
+      <c r="CF1" s="1" t="inlineStr">
         <is>
           <t>最低價</t>
         </is>
       </c>
-      <c r="CF1" s="1" t="inlineStr">
+      <c r="CG1" s="1" t="inlineStr">
         <is>
           <t>收盤價</t>
         </is>
       </c>
-      <c r="CG1" s="1" t="inlineStr">
+      <c r="CH1" s="1" t="inlineStr">
         <is>
           <t>每股淨值(元)</t>
         </is>
       </c>
-      <c r="CH1" s="1" t="inlineStr">
+      <c r="CI1" s="1" t="inlineStr">
         <is>
           <t>desc</t>
         </is>
       </c>
-      <c r="CI1" s="1" t="inlineStr">
+      <c r="CJ1" s="1" t="inlineStr">
         <is>
           <t>flag_stat</t>
         </is>
@@ -878,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1866.918</t>
+          <t>2806.058</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>9.73</t>
+          <t>9.53</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -908,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-4.08</t>
+          <t>-4.72</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-17.77</t>
+          <t>-12.07</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -978,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-5.53</t>
+          <t>-7.48</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>8.52</t>
+          <t>12.80</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,77 +1014,77 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>1867</t>
+          <t>2806</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>15.38</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>8.89</t>
+          <t>5.13</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-2.45</t>
+          <t>-2.66</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>-3.58</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>9.974</t>
+          <t>9.790000000000001</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>10.21</t>
+          <t>10.15</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
+          <t>10.19</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
           <t>10.2</t>
         </is>
       </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>10.22</t>
-        </is>
-      </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-177.09</t>
+          <t>-141.34</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1094,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-106.90</t>
+          <t>-110.67</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,198 +1104,203 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>38447782.22805756</t>
+          <t>38450283.1012931</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>18247885.0</t>
+          <t>26792260.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>22369720.8</t>
+          <t>24442611.2</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>27203179.9</t>
+          <t>27798303.7</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>26271252.44</t>
+          <t>26345925.2</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-4833459</t>
+          <t>-3355692</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-264383.362935614</t>
-        </is>
-      </c>
-      <c r="BC2" t="n">
-        <v>27250.69</v>
-      </c>
-      <c r="BD2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-199697.2390819047</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>156076.4421134964</t>
+        </is>
+      </c>
+      <c r="BD2" t="n">
+        <v>26792260</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
           <t>10.5</t>
         </is>
       </c>
-      <c r="BF2" t="inlineStr">
+      <c r="BG2" t="inlineStr">
         <is>
           <t>2025/10/14</t>
         </is>
       </c>
-      <c r="BG2" t="inlineStr">
-        <is>
-          <t>-7.33</t>
-        </is>
-      </c>
       <c r="BH2" t="inlineStr">
         <is>
+          <t>-9.24</t>
+        </is>
+      </c>
+      <c r="BI2" t="inlineStr">
+        <is>
           <t>聯成</t>
         </is>
       </c>
-      <c r="BI2" t="inlineStr">
+      <c r="BJ2" t="inlineStr">
         <is>
           <t>聯成</t>
         </is>
       </c>
-      <c r="BJ2" t="inlineStr">
+      <c r="BK2" t="inlineStr">
         <is>
           <t>塑膠工業</t>
         </is>
       </c>
-      <c r="BK2" t="inlineStr">
+      <c r="BL2" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL2" t="inlineStr">
-        <is>
-          <t>0.78</t>
-        </is>
-      </c>
       <c r="BM2" t="inlineStr">
         <is>
+          <t>0.77</t>
+        </is>
+      </c>
+      <c r="BN2" t="inlineStr">
+        <is>
           <t>-11.96408371040724</t>
         </is>
       </c>
-      <c r="BN2" t="inlineStr">
+      <c r="BO2" t="inlineStr">
         <is>
           <t>-13.59414944504011</t>
         </is>
       </c>
-      <c r="BO2" t="inlineStr">
+      <c r="BP2" t="inlineStr">
         <is>
           <t>-19.633719693908</t>
         </is>
       </c>
-      <c r="BP2" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="BU2" t="inlineStr">
+        <is>
           <t>10.97</t>
         </is>
       </c>
-      <c r="BU2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BV2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BW2" t="inlineStr">
+        <is>
           <t>0.96%</t>
         </is>
       </c>
-      <c r="BW2" t="inlineStr">
+      <c r="BX2" t="inlineStr">
         <is>
           <t>-3.42%</t>
         </is>
       </c>
-      <c r="BX2" t="inlineStr">
-        <is>
-          <t>62.64</t>
-        </is>
-      </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>13132</t>
+          <t>62.69</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
+          <t>12863</t>
+        </is>
+      </c>
+      <c r="CA2" t="inlineStr">
+        <is>
           <t>可塑劑(DOP)76.00%、聚氯乙烯13.00%、酸酐6.00%、其他5.00% (2024年)</t>
         </is>
       </c>
-      <c r="CA2" t="inlineStr">
+      <c r="CB2" t="inlineStr">
         <is>
           <t>聯成-塑膠工業-上市</t>
         </is>
       </c>
-      <c r="CB2" t="inlineStr">
+      <c r="CC2" t="inlineStr">
         <is>
           <t>塑膠工業右下上市</t>
         </is>
       </c>
-      <c r="CC2" t="inlineStr">
-        <is>
-          <t>9.77</t>
-        </is>
-      </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>9.95</t>
+          <t>9.73</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>9.73</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>9.73</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
+          <t>9.53</t>
+        </is>
+      </c>
+      <c r="CH2" t="inlineStr">
+        <is>
           <t>22.32</t>
         </is>
       </c>
-      <c r="CH2" t="inlineStr">
+      <c r="CI2" t="inlineStr">
         <is>
           <t>** 石化及塑橡膠 - 塑化劑(可塑劑)</t>
         </is>
       </c>
-      <c r="CI2" t="inlineStr">
+      <c r="CJ2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -1309,12 +1319,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-4.1</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>3938.682</t>
+          <t>1866.918</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1334,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>9.59</t>
+          <t>9.73</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,17 +1344,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>-2.1</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-4.08</t>
+          <t>-4.72</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-2.69</t>
+          <t>-17.77</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1409,7 +1419,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-6.89</t>
+          <t>-5.53</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17.97</t>
+          <t>8.52</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-4.07</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,52 +1450,52 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>1867</t>
+          <t>2806</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>15.38</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>12.9</t>
+          <t>8.89</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-5.31</t>
+          <t>-2.45</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>10.128</t>
+          <t>9.974</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>10.25</t>
+          <t>10.21</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
@@ -1500,17 +1510,17 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-268.37</t>
+          <t>-177.09</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1530,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-103.85</t>
+          <t>-106.90</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,198 +1540,203 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>38447782.22805756</t>
+          <t>38450283.1012931</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>38346124.0</t>
+          <t>18247885.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>26631549.8</t>
+          <t>22369720.8</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>27366657.0</t>
+          <t>27203179.9</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>26177335.2</t>
+          <t>26271252.44</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-735107</t>
+          <t>-4833459</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-317407.7356947591</t>
-        </is>
-      </c>
-      <c r="BC3" t="n">
-        <v>757709.41</v>
-      </c>
-      <c r="BD3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-264383.362935614</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>27250.68723968416</t>
+        </is>
+      </c>
+      <c r="BD3" t="n">
+        <v>18247885</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
           <t>10.5</t>
         </is>
       </c>
-      <c r="BF3" t="inlineStr">
+      <c r="BG3" t="inlineStr">
         <is>
           <t>2025/10/14</t>
         </is>
       </c>
-      <c r="BG3" t="inlineStr">
-        <is>
-          <t>-8.67</t>
-        </is>
-      </c>
       <c r="BH3" t="inlineStr">
         <is>
+          <t>-7.33</t>
+        </is>
+      </c>
+      <c r="BI3" t="inlineStr">
+        <is>
           <t>聯成</t>
         </is>
       </c>
-      <c r="BI3" t="inlineStr">
+      <c r="BJ3" t="inlineStr">
         <is>
           <t>聯成</t>
         </is>
       </c>
-      <c r="BJ3" t="inlineStr">
+      <c r="BK3" t="inlineStr">
         <is>
           <t>塑膠工業</t>
         </is>
       </c>
-      <c r="BK3" t="inlineStr">
+      <c r="BL3" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL3" t="inlineStr">
-        <is>
-          <t>0.78</t>
-        </is>
-      </c>
       <c r="BM3" t="inlineStr">
         <is>
+          <t>0.77</t>
+        </is>
+      </c>
+      <c r="BN3" t="inlineStr">
+        <is>
           <t>-11.96408371040724</t>
         </is>
       </c>
-      <c r="BN3" t="inlineStr">
+      <c r="BO3" t="inlineStr">
         <is>
           <t>-13.59414944504011</t>
         </is>
       </c>
-      <c r="BO3" t="inlineStr">
+      <c r="BP3" t="inlineStr">
         <is>
           <t>-19.633719693908</t>
         </is>
       </c>
-      <c r="BP3" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
-        </is>
-      </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="BU3" t="inlineStr">
+        <is>
           <t>10.97</t>
         </is>
       </c>
-      <c r="BU3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BV3" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BW3" t="inlineStr">
+        <is>
           <t>0.96%</t>
         </is>
       </c>
-      <c r="BW3" t="inlineStr">
+      <c r="BX3" t="inlineStr">
         <is>
           <t>-3.42%</t>
         </is>
       </c>
-      <c r="BX3" t="inlineStr">
-        <is>
-          <t>62.64</t>
-        </is>
-      </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>13132</t>
+          <t>62.69</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
+          <t>12863</t>
+        </is>
+      </c>
+      <c r="CA3" t="inlineStr">
+        <is>
           <t>可塑劑(DOP)76.00%、聚氯乙烯13.00%、酸酐6.00%、其他5.00% (2024年)</t>
         </is>
       </c>
-      <c r="CA3" t="inlineStr">
+      <c r="CB3" t="inlineStr">
         <is>
           <t>聯成-塑膠工業-上市</t>
         </is>
       </c>
-      <c r="CB3" t="inlineStr">
+      <c r="CC3" t="inlineStr">
         <is>
           <t>塑膠工業右下上市</t>
         </is>
       </c>
-      <c r="CC3" t="inlineStr">
-        <is>
-          <t>9.99</t>
-        </is>
-      </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>9.99</t>
+          <t>9.77</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>9.58</t>
+          <t>9.95</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>9.59</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
+          <t>9.73</t>
+        </is>
+      </c>
+      <c r="CH3" t="inlineStr">
+        <is>
           <t>22.32</t>
         </is>
       </c>
-      <c r="CH3" t="inlineStr">
+      <c r="CI3" t="inlineStr">
         <is>
           <t>** 石化及塑橡膠 - 塑化劑(可塑劑)</t>
         </is>
       </c>
-      <c r="CI3" t="inlineStr">
+      <c r="CJ3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -1740,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-4.1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2500.445</t>
+          <t>3938.682</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1770,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>9.59</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,17 +1780,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-2.77</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-4.08</t>
+          <t>-4.72</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-2.43</t>
+          <t>-2.69</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1840,7 +1855,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-2.91</t>
+          <t>-6.89</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11.41</t>
+          <t>17.97</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-1.60</t>
+          <t>-4.07</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,57 +1886,57 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>1867</t>
+          <t>2806</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>11.29</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>40.86</t>
+          <t>12.9</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-2.72</t>
+          <t>-5.31</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>10.28</t>
+          <t>10.128</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>10.28</t>
+          <t>10.25</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>10.21</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
@@ -1931,17 +1946,17 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-293.77</t>
+          <t>-268.37</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1966,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-101.27</t>
+          <t>-103.85</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,198 +1976,203 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>38447782.22805756</t>
+          <t>38450283.1012931</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>25104257.0</t>
+          <t>38346124.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>24629573.0</t>
+          <t>26631549.8</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>25242587.5</t>
+          <t>27366657.0</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>25777972.78</t>
+          <t>26177335.2</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-613014</t>
+          <t>-735107</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-512883.5795906829</t>
-        </is>
-      </c>
-      <c r="BC4" t="n">
-        <v>-379221.94</v>
-      </c>
-      <c r="BD4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-317407.7356947591</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>757709.4057328217</t>
+        </is>
+      </c>
+      <c r="BD4" t="n">
+        <v>38346124</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
           <t>10.5</t>
         </is>
       </c>
-      <c r="BF4" t="inlineStr">
+      <c r="BG4" t="inlineStr">
         <is>
           <t>2025/10/14</t>
         </is>
       </c>
-      <c r="BG4" t="inlineStr">
-        <is>
-          <t>-4.76</t>
-        </is>
-      </c>
       <c r="BH4" t="inlineStr">
         <is>
+          <t>-8.67</t>
+        </is>
+      </c>
+      <c r="BI4" t="inlineStr">
+        <is>
           <t>聯成</t>
         </is>
       </c>
-      <c r="BI4" t="inlineStr">
+      <c r="BJ4" t="inlineStr">
         <is>
           <t>聯成</t>
         </is>
       </c>
-      <c r="BJ4" t="inlineStr">
+      <c r="BK4" t="inlineStr">
         <is>
           <t>塑膠工業</t>
         </is>
       </c>
-      <c r="BK4" t="inlineStr">
+      <c r="BL4" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL4" t="inlineStr">
-        <is>
-          <t>0.78</t>
-        </is>
-      </c>
       <c r="BM4" t="inlineStr">
         <is>
+          <t>0.77</t>
+        </is>
+      </c>
+      <c r="BN4" t="inlineStr">
+        <is>
           <t>-11.96408371040724</t>
         </is>
       </c>
-      <c r="BN4" t="inlineStr">
+      <c r="BO4" t="inlineStr">
         <is>
           <t>-13.59414944504011</t>
         </is>
       </c>
-      <c r="BO4" t="inlineStr">
+      <c r="BP4" t="inlineStr">
         <is>
           <t>-19.633719693908</t>
         </is>
       </c>
-      <c r="BP4" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="BU4" t="inlineStr">
+        <is>
           <t>10.97</t>
         </is>
       </c>
-      <c r="BU4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BV4" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BW4" t="inlineStr">
+        <is>
           <t>0.96%</t>
         </is>
       </c>
-      <c r="BW4" t="inlineStr">
+      <c r="BX4" t="inlineStr">
         <is>
           <t>-3.42%</t>
         </is>
       </c>
-      <c r="BX4" t="inlineStr">
-        <is>
-          <t>62.64</t>
-        </is>
-      </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>13132</t>
+          <t>62.69</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
+          <t>12863</t>
+        </is>
+      </c>
+      <c r="CA4" t="inlineStr">
+        <is>
           <t>可塑劑(DOP)76.00%、聚氯乙烯13.00%、酸酐6.00%、其他5.00% (2024年)</t>
         </is>
       </c>
-      <c r="CA4" t="inlineStr">
+      <c r="CB4" t="inlineStr">
         <is>
           <t>聯成-塑膠工業-上市</t>
         </is>
       </c>
-      <c r="CB4" t="inlineStr">
+      <c r="CC4" t="inlineStr">
         <is>
           <t>塑膠工業右下上市</t>
         </is>
       </c>
-      <c r="CC4" t="inlineStr">
-        <is>
-          <t>10.05</t>
-        </is>
-      </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>9.99</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>9.96</t>
+          <t>9.99</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>9.58</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
+          <t>9.59</t>
+        </is>
+      </c>
+      <c r="CH4" t="inlineStr">
+        <is>
           <t>22.32</t>
         </is>
       </c>
-      <c r="CH4" t="inlineStr">
+      <c r="CI4" t="inlineStr">
         <is>
           <t>** 石化及塑橡膠 - 塑化劑(可塑劑)</t>
         </is>
       </c>
-      <c r="CI4" t="inlineStr">
+      <c r="CJ4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -2171,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-3.35</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1335.381</t>
+          <t>2500.445</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2206,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,17 +2216,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-3.8</t>
+          <t>-4.93</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-4.08</t>
+          <t>-4.72</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>-2.43</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2271,7 +2291,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-1.94</t>
+          <t>-2.91</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,73 +2301,73 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>6.09</t>
+          <t>11.41</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-4.95</t>
+          <t>-1.60</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>1867</t>
+          <t>2806</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>27.42</t>
+          <t>11.29</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>67.74</t>
+          <t>40.86</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-2.04</t>
+          <t>-2.72</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>10.31</t>
+          <t>10.28</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>10.3</t>
+          <t>10.28</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
@@ -2362,19 +2382,19 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-185.15</t>
+          <t>-293.77</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
+          <t>-0.03</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
           <t>-0.01</t>
         </is>
       </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>-0.00</t>
-        </is>
-      </c>
       <c r="AS5" t="inlineStr">
         <is>
           <t>0.54</t>
@@ -2382,7 +2402,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-100.34</t>
+          <t>-101.27</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,198 +2412,203 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>38447782.22805756</t>
+          <t>38450283.1012931</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>13722530.0</t>
+          <t>25104257.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>24615513.2</t>
+          <t>24629573.0</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>24233663.8</t>
+          <t>25242587.5</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>25886365.74</t>
+          <t>25777972.78</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>381849</t>
+          <t>-613014</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-537185.6959741293</t>
-        </is>
-      </c>
-      <c r="BC5" t="n">
-        <v>-571094.47</v>
-      </c>
-      <c r="BD5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-512883.5795906829</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>-379221.9394817278</t>
+        </is>
+      </c>
+      <c r="BD5" t="n">
+        <v>25104257</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
           <t>10.5</t>
         </is>
       </c>
-      <c r="BF5" t="inlineStr">
+      <c r="BG5" t="inlineStr">
         <is>
           <t>2025/10/14</t>
         </is>
       </c>
-      <c r="BG5" t="inlineStr">
-        <is>
-          <t>-3.81</t>
-        </is>
-      </c>
       <c r="BH5" t="inlineStr">
         <is>
+          <t>-4.76</t>
+        </is>
+      </c>
+      <c r="BI5" t="inlineStr">
+        <is>
           <t>聯成</t>
         </is>
       </c>
-      <c r="BI5" t="inlineStr">
+      <c r="BJ5" t="inlineStr">
         <is>
           <t>聯成</t>
         </is>
       </c>
-      <c r="BJ5" t="inlineStr">
+      <c r="BK5" t="inlineStr">
         <is>
           <t>塑膠工業</t>
         </is>
       </c>
-      <c r="BK5" t="inlineStr">
+      <c r="BL5" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL5" t="inlineStr">
-        <is>
-          <t>0.78</t>
-        </is>
-      </c>
       <c r="BM5" t="inlineStr">
         <is>
+          <t>0.77</t>
+        </is>
+      </c>
+      <c r="BN5" t="inlineStr">
+        <is>
           <t>-11.96408371040724</t>
         </is>
       </c>
-      <c r="BN5" t="inlineStr">
+      <c r="BO5" t="inlineStr">
         <is>
           <t>-13.59414944504011</t>
         </is>
       </c>
-      <c r="BO5" t="inlineStr">
+      <c r="BP5" t="inlineStr">
         <is>
           <t>-19.633719693908</t>
         </is>
       </c>
-      <c r="BP5" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS5" t="inlineStr">
+        <is>
           <t>0.45</t>
         </is>
       </c>
-      <c r="BS5" t="inlineStr">
-        <is>
-          <t>1.54</t>
-        </is>
-      </c>
       <c r="BT5" t="inlineStr">
         <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="BU5" t="inlineStr">
+        <is>
           <t>10.97</t>
         </is>
       </c>
-      <c r="BU5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BV5" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BW5" t="inlineStr">
+        <is>
           <t>0.96%</t>
         </is>
       </c>
-      <c r="BW5" t="inlineStr">
+      <c r="BX5" t="inlineStr">
         <is>
           <t>-3.42%</t>
         </is>
       </c>
-      <c r="BX5" t="inlineStr">
-        <is>
-          <t>62.64</t>
-        </is>
-      </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>13132</t>
+          <t>62.69</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
+          <t>12863</t>
+        </is>
+      </c>
+      <c r="CA5" t="inlineStr">
+        <is>
           <t>可塑劑(DOP)76.00%、聚氯乙烯13.00%、酸酐6.00%、其他5.00% (2024年)</t>
         </is>
       </c>
-      <c r="CA5" t="inlineStr">
+      <c r="CB5" t="inlineStr">
         <is>
           <t>聯成-塑膠工業-上市</t>
         </is>
       </c>
-      <c r="CB5" t="inlineStr">
+      <c r="CC5" t="inlineStr">
         <is>
           <t>塑膠工業右下上市</t>
         </is>
       </c>
-      <c r="CC5" t="inlineStr">
-        <is>
-          <t>10.45</t>
-        </is>
-      </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>10.6</t>
+          <t>10.05</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>9.96</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
+          <t>10.0</t>
+        </is>
+      </c>
+      <c r="CH5" t="inlineStr">
+        <is>
           <t>22.32</t>
         </is>
       </c>
-      <c r="CH5" t="inlineStr">
+      <c r="CI5" t="inlineStr">
         <is>
           <t>** 石化及塑橡膠 - 塑化劑(可塑劑)</t>
         </is>
       </c>
-      <c r="CI5" t="inlineStr">
+      <c r="CJ5" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -2602,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-3.35</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1569.646</t>
+          <t>1335.381</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2642,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>10.45</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,17 +2652,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-7.4</t>
+          <t>-5.98</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-4.08</t>
+          <t>-4.72</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>28.41</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2702,7 +2727,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>-1.94</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,73 +2737,73 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>7.16</t>
+          <t>6.09</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-4.95</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>1867</t>
+          <t>2806</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>83.87</t>
+          <t>27.42</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>81.18</t>
+          <t>67.74</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>-2.04</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>10.276</t>
+          <t>10.31</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>10.31</t>
+          <t>10.3</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
@@ -2793,12 +2818,12 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>1372.99</t>
+          <t>-185.15</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
@@ -2813,7 +2838,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-100.18</t>
+          <t>-100.34</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,198 +2848,203 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>38447782.22805756</t>
+          <t>38450283.1012931</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>16427808.0</t>
+          <t>13722530.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>31153996.2</t>
+          <t>24615513.2</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>24262247.7</t>
+          <t>24233663.8</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>26236307.54</t>
+          <t>25886365.74</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>6891748</t>
+          <t>381849</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-531020.4642383313</t>
-        </is>
-      </c>
-      <c r="BC6" t="n">
-        <v>394668.89</v>
-      </c>
-      <c r="BD6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-537185.6959741293</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>-571094.4705210179</t>
+        </is>
+      </c>
+      <c r="BD6" t="n">
+        <v>13722530</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
           <t>10.5</t>
         </is>
       </c>
-      <c r="BF6" t="inlineStr">
+      <c r="BG6" t="inlineStr">
         <is>
           <t>2025/10/14</t>
         </is>
       </c>
-      <c r="BG6" t="inlineStr">
-        <is>
-          <t>-0.48</t>
-        </is>
-      </c>
       <c r="BH6" t="inlineStr">
         <is>
+          <t>-3.81</t>
+        </is>
+      </c>
+      <c r="BI6" t="inlineStr">
+        <is>
           <t>聯成</t>
         </is>
       </c>
-      <c r="BI6" t="inlineStr">
+      <c r="BJ6" t="inlineStr">
         <is>
           <t>聯成</t>
         </is>
       </c>
-      <c r="BJ6" t="inlineStr">
+      <c r="BK6" t="inlineStr">
         <is>
           <t>塑膠工業</t>
         </is>
       </c>
-      <c r="BK6" t="inlineStr">
+      <c r="BL6" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL6" t="inlineStr">
-        <is>
-          <t>0.78</t>
-        </is>
-      </c>
       <c r="BM6" t="inlineStr">
         <is>
+          <t>0.77</t>
+        </is>
+      </c>
+      <c r="BN6" t="inlineStr">
+        <is>
           <t>-11.96408371040724</t>
         </is>
       </c>
-      <c r="BN6" t="inlineStr">
+      <c r="BO6" t="inlineStr">
         <is>
           <t>-13.59414944504011</t>
         </is>
       </c>
-      <c r="BO6" t="inlineStr">
+      <c r="BP6" t="inlineStr">
         <is>
           <t>-19.633719693908</t>
         </is>
       </c>
-      <c r="BP6" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="BU6" t="inlineStr">
+        <is>
           <t>10.97</t>
         </is>
       </c>
-      <c r="BU6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BV6" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BW6" t="inlineStr">
+        <is>
           <t>0.96%</t>
         </is>
       </c>
-      <c r="BW6" t="inlineStr">
+      <c r="BX6" t="inlineStr">
         <is>
           <t>-3.42%</t>
         </is>
       </c>
-      <c r="BX6" t="inlineStr">
-        <is>
-          <t>62.64</t>
-        </is>
-      </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>13132</t>
+          <t>62.69</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
+          <t>12863</t>
+        </is>
+      </c>
+      <c r="CA6" t="inlineStr">
+        <is>
           <t>可塑劑(DOP)76.00%、聚氯乙烯13.00%、酸酐6.00%、其他5.00% (2024年)</t>
         </is>
       </c>
-      <c r="CA6" t="inlineStr">
+      <c r="CB6" t="inlineStr">
         <is>
           <t>聯成-塑膠工業-上市</t>
         </is>
       </c>
-      <c r="CB6" t="inlineStr">
+      <c r="CC6" t="inlineStr">
         <is>
           <t>塑膠工業右下上市</t>
         </is>
       </c>
-      <c r="CC6" t="inlineStr">
-        <is>
-          <t>10.4</t>
-        </is>
-      </c>
       <c r="CD6" t="inlineStr">
         <is>
+          <t>10.45</t>
+        </is>
+      </c>
+      <c r="CE6" t="inlineStr">
+        <is>
           <t>10.6</t>
         </is>
       </c>
-      <c r="CE6" t="inlineStr">
-        <is>
-          <t>10.3</t>
-        </is>
-      </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>10.45</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
+          <t>10.1</t>
+        </is>
+      </c>
+      <c r="CH6" t="inlineStr">
+        <is>
           <t>22.32</t>
         </is>
       </c>
-      <c r="CH6" t="inlineStr">
+      <c r="CI6" t="inlineStr">
         <is>
           <t>** 石化及塑橡膠 - 塑化劑(可塑劑)</t>
         </is>
       </c>
-      <c r="CI6" t="inlineStr">
+      <c r="CJ6" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -3033,12 +3063,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>3754.177</t>
+          <t>1569.646</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3078,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>10.5</t>
+          <t>10.45</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3088,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-7.91</t>
+          <t>-9.65</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-4.08</t>
+          <t>-4.72</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>33.22</t>
+          <t>28.41</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3163,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3173,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17.12</t>
+          <t>7.16</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,47 +3194,47 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>1867</t>
+          <t>2806</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>91.94</t>
+          <t>83.87</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>65.05</t>
+          <t>81.18</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>10.236</t>
+          <t>10.276</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
@@ -3214,29 +3244,29 @@
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>10.21</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>10.22</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>73.66</t>
+          <t>1372.99</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
           <t>-0.00</t>
         </is>
       </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>-0.00</t>
-        </is>
-      </c>
       <c r="AS7" t="inlineStr">
         <is>
           <t>0.54</t>
@@ -3244,7 +3274,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-100.80</t>
+          <t>-100.18</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,198 +3284,203 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>38447782.22805756</t>
+          <t>38450283.1012931</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>39557030.0</t>
+          <t>16427808.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>32036639.0</t>
+          <t>31153996.2</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>24048236.4</t>
+          <t>24262247.7</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>26253921.64</t>
+          <t>26236307.54</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>7988402</t>
+          <t>6891748</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-699327.6204268641</t>
-        </is>
-      </c>
-      <c r="BC7" t="n">
-        <v>1470384.31</v>
-      </c>
-      <c r="BD7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-531020.4642383313</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>394668.8947985992</t>
+        </is>
+      </c>
+      <c r="BD7" t="n">
+        <v>16427808</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
           <t>10.5</t>
         </is>
       </c>
-      <c r="BF7" t="inlineStr">
+      <c r="BG7" t="inlineStr">
         <is>
           <t>2025/10/14</t>
         </is>
       </c>
-      <c r="BG7" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
       <c r="BH7" t="inlineStr">
         <is>
+          <t>-0.48</t>
+        </is>
+      </c>
+      <c r="BI7" t="inlineStr">
+        <is>
           <t>聯成</t>
         </is>
       </c>
-      <c r="BI7" t="inlineStr">
+      <c r="BJ7" t="inlineStr">
         <is>
           <t>聯成</t>
         </is>
       </c>
-      <c r="BJ7" t="inlineStr">
+      <c r="BK7" t="inlineStr">
         <is>
           <t>塑膠工業</t>
         </is>
       </c>
-      <c r="BK7" t="inlineStr">
+      <c r="BL7" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL7" t="inlineStr">
-        <is>
-          <t>0.78</t>
-        </is>
-      </c>
       <c r="BM7" t="inlineStr">
         <is>
+          <t>0.77</t>
+        </is>
+      </c>
+      <c r="BN7" t="inlineStr">
+        <is>
           <t>-11.96408371040724</t>
         </is>
       </c>
-      <c r="BN7" t="inlineStr">
+      <c r="BO7" t="inlineStr">
         <is>
           <t>-13.59414944504011</t>
         </is>
       </c>
-      <c r="BO7" t="inlineStr">
+      <c r="BP7" t="inlineStr">
         <is>
           <t>-19.633719693908</t>
         </is>
       </c>
-      <c r="BP7" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
-        </is>
-      </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS7" t="inlineStr">
+        <is>
           <t>0.47</t>
         </is>
       </c>
-      <c r="BS7" t="inlineStr">
-        <is>
-          <t>1.54</t>
-        </is>
-      </c>
       <c r="BT7" t="inlineStr">
         <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="BU7" t="inlineStr">
+        <is>
           <t>10.97</t>
         </is>
       </c>
-      <c r="BU7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BV7" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BW7" t="inlineStr">
+        <is>
           <t>0.96%</t>
         </is>
       </c>
-      <c r="BW7" t="inlineStr">
+      <c r="BX7" t="inlineStr">
         <is>
           <t>-3.42%</t>
         </is>
       </c>
-      <c r="BX7" t="inlineStr">
-        <is>
-          <t>62.64</t>
-        </is>
-      </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>13132</t>
+          <t>62.69</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
+          <t>12863</t>
+        </is>
+      </c>
+      <c r="CA7" t="inlineStr">
+        <is>
           <t>可塑劑(DOP)76.00%、聚氯乙烯13.00%、酸酐6.00%、其他5.00% (2024年)</t>
         </is>
       </c>
-      <c r="CA7" t="inlineStr">
+      <c r="CB7" t="inlineStr">
         <is>
           <t>聯成-塑膠工業-上市</t>
         </is>
       </c>
-      <c r="CB7" t="inlineStr">
+      <c r="CC7" t="inlineStr">
         <is>
           <t>塑膠工業右下上市</t>
         </is>
       </c>
-      <c r="CC7" t="inlineStr">
+      <c r="CD7" t="inlineStr">
         <is>
           <t>10.4</t>
         </is>
       </c>
-      <c r="CD7" t="inlineStr">
-        <is>
-          <t>10.75</t>
-        </is>
-      </c>
       <c r="CE7" t="inlineStr">
         <is>
+          <t>10.6</t>
+        </is>
+      </c>
+      <c r="CF7" t="inlineStr">
+        <is>
           <t>10.3</t>
         </is>
       </c>
-      <c r="CF7" t="inlineStr">
-        <is>
-          <t>10.5</t>
-        </is>
-      </c>
       <c r="CG7" t="inlineStr">
         <is>
+          <t>10.45</t>
+        </is>
+      </c>
+      <c r="CH7" t="inlineStr">
+        <is>
           <t>22.32</t>
         </is>
       </c>
-      <c r="CH7" t="inlineStr">
+      <c r="CI7" t="inlineStr">
         <is>
           <t>** 石化及塑橡膠 - 塑化劑(可塑劑)</t>
         </is>
       </c>
-      <c r="CI7" t="inlineStr">
+      <c r="CJ7" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -3464,12 +3499,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2725.546</t>
+          <t>3754.177</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3514,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>10.35</t>
+          <t>10.5</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,17 +3524,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-6.37</t>
+          <t>-10.18</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-4.08</t>
+          <t>-4.72</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>31.50</t>
+          <t>33.22</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3564,7 +3599,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3609,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12.43</t>
+          <t>17.12</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3595,52 +3630,52 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>1867</t>
+          <t>2806</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>67.74</t>
+          <t>91.94</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>34.41</t>
+          <t>65.05</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>10.246</t>
+          <t>10.236</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>10.29</t>
+          <t>10.31</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
@@ -3650,22 +3685,22 @@
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>10.19</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-359.87</t>
+          <t>73.66</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.00</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-0.00</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3710,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-100.95</t>
+          <t>-100.80</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,198 +3720,203 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>38447782.22805756</t>
+          <t>38450283.1012931</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>28336240.0</t>
+          <t>39557030.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>28101764.2</t>
+          <t>32036639.0</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>21370450.7</t>
+          <t>24048236.4</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>26117511.38</t>
+          <t>26253921.64</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>6731313</t>
+          <t>7988402</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-1093820.699285948</t>
-        </is>
-      </c>
-      <c r="BC8" t="n">
-        <v>476475.97</v>
-      </c>
-      <c r="BD8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-699327.6204268641</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>1470384.313298099</t>
+        </is>
+      </c>
+      <c r="BD8" t="n">
+        <v>39557030</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF8" t="inlineStr">
+        <is>
           <t>10.5</t>
         </is>
       </c>
-      <c r="BF8" t="inlineStr">
+      <c r="BG8" t="inlineStr">
         <is>
           <t>2025/10/14</t>
         </is>
       </c>
-      <c r="BG8" t="inlineStr">
-        <is>
-          <t>-1.43</t>
-        </is>
-      </c>
       <c r="BH8" t="inlineStr">
         <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="BI8" t="inlineStr">
+        <is>
           <t>聯成</t>
         </is>
       </c>
-      <c r="BI8" t="inlineStr">
+      <c r="BJ8" t="inlineStr">
         <is>
           <t>聯成</t>
         </is>
       </c>
-      <c r="BJ8" t="inlineStr">
+      <c r="BK8" t="inlineStr">
         <is>
           <t>塑膠工業</t>
         </is>
       </c>
-      <c r="BK8" t="inlineStr">
+      <c r="BL8" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL8" t="inlineStr">
-        <is>
-          <t>0.78</t>
-        </is>
-      </c>
       <c r="BM8" t="inlineStr">
         <is>
+          <t>0.77</t>
+        </is>
+      </c>
+      <c r="BN8" t="inlineStr">
+        <is>
           <t>-11.96408371040724</t>
         </is>
       </c>
-      <c r="BN8" t="inlineStr">
+      <c r="BO8" t="inlineStr">
         <is>
           <t>-13.59414944504011</t>
         </is>
       </c>
-      <c r="BO8" t="inlineStr">
+      <c r="BP8" t="inlineStr">
         <is>
           <t>-19.633719693908</t>
         </is>
       </c>
-      <c r="BP8" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="BU8" t="inlineStr">
+        <is>
           <t>10.97</t>
         </is>
       </c>
-      <c r="BU8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BV8" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BW8" t="inlineStr">
+        <is>
           <t>0.96%</t>
         </is>
       </c>
-      <c r="BW8" t="inlineStr">
+      <c r="BX8" t="inlineStr">
         <is>
           <t>-3.42%</t>
         </is>
       </c>
-      <c r="BX8" t="inlineStr">
-        <is>
-          <t>62.64</t>
-        </is>
-      </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>13132</t>
+          <t>62.69</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
+          <t>12863</t>
+        </is>
+      </c>
+      <c r="CA8" t="inlineStr">
+        <is>
           <t>可塑劑(DOP)76.00%、聚氯乙烯13.00%、酸酐6.00%、其他5.00% (2024年)</t>
         </is>
       </c>
-      <c r="CA8" t="inlineStr">
+      <c r="CB8" t="inlineStr">
         <is>
           <t>聯成-塑膠工業-上市</t>
         </is>
       </c>
-      <c r="CB8" t="inlineStr">
+      <c r="CC8" t="inlineStr">
         <is>
           <t>塑膠工業右下上市</t>
         </is>
       </c>
-      <c r="CC8" t="inlineStr">
-        <is>
-          <t>10.15</t>
-        </is>
-      </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>10.6</t>
+          <t>10.4</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>10.15</t>
+          <t>10.75</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>10.35</t>
+          <t>10.3</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
+          <t>10.5</t>
+        </is>
+      </c>
+      <c r="CH8" t="inlineStr">
+        <is>
           <t>22.32</t>
         </is>
       </c>
-      <c r="CH8" t="inlineStr">
+      <c r="CI8" t="inlineStr">
         <is>
           <t>** 石化及塑橡膠 - 塑化劑(可塑劑)</t>
         </is>
       </c>
-      <c r="CI8" t="inlineStr">
+      <c r="CJ8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -3895,12 +3935,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2459.513</t>
+          <t>2725.546</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3950,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>10.15</t>
+          <t>10.35</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,17 +3960,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-4.32</t>
+          <t>-8.6</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-4.08</t>
+          <t>-4.72</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>26.88</t>
+          <t>31.50</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3995,7 +4035,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4045,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11.22</t>
+          <t>12.43</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-0.56</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,47 +4066,47 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>1867</t>
+          <t>2806</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>35.48</t>
+          <t>67.74</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>25.16</t>
+          <t>34.41</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>10.196</t>
+          <t>10.246</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
@@ -4081,22 +4121,22 @@
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>10.18</t>
+          <t>10.19</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-6995.52</t>
+          <t>-359.87</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.00</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4146,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-100.10</t>
+          <t>-100.95</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,180 +4156,180 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>38447782.22805756</t>
+          <t>38450283.1012931</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>25033958.0</t>
+          <t>28336240.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>25855602.0</t>
+          <t>28101764.2</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>20377785.6</t>
+          <t>21370450.7</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>25837516.22</t>
+          <t>26117511.38</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>5477816</t>
+          <t>6731313</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-1379329.1848641</t>
-        </is>
-      </c>
-      <c r="BC9" t="n">
-        <v>241817.41</v>
-      </c>
-      <c r="BD9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-1093820.699285948</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>476475.971393887</t>
+        </is>
+      </c>
+      <c r="BD9" t="n">
+        <v>28336240</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF9" t="inlineStr">
+        <is>
           <t>10.5</t>
         </is>
       </c>
-      <c r="BF9" t="inlineStr">
+      <c r="BG9" t="inlineStr">
         <is>
           <t>2025/10/14</t>
         </is>
       </c>
-      <c r="BG9" t="inlineStr">
-        <is>
-          <t>-3.33</t>
-        </is>
-      </c>
       <c r="BH9" t="inlineStr">
         <is>
+          <t>-1.43</t>
+        </is>
+      </c>
+      <c r="BI9" t="inlineStr">
+        <is>
           <t>聯成</t>
         </is>
       </c>
-      <c r="BI9" t="inlineStr">
+      <c r="BJ9" t="inlineStr">
         <is>
           <t>聯成</t>
         </is>
       </c>
-      <c r="BJ9" t="inlineStr">
+      <c r="BK9" t="inlineStr">
         <is>
           <t>塑膠工業</t>
         </is>
       </c>
-      <c r="BK9" t="inlineStr">
+      <c r="BL9" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL9" t="inlineStr">
-        <is>
-          <t>0.78</t>
-        </is>
-      </c>
       <c r="BM9" t="inlineStr">
         <is>
+          <t>0.77</t>
+        </is>
+      </c>
+      <c r="BN9" t="inlineStr">
+        <is>
           <t>-11.96408371040724</t>
         </is>
       </c>
-      <c r="BN9" t="inlineStr">
+      <c r="BO9" t="inlineStr">
         <is>
           <t>-13.59414944504011</t>
         </is>
       </c>
-      <c r="BO9" t="inlineStr">
+      <c r="BP9" t="inlineStr">
         <is>
           <t>-19.633719693908</t>
         </is>
       </c>
-      <c r="BP9" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="BU9" t="inlineStr">
+        <is>
           <t>10.97</t>
         </is>
       </c>
-      <c r="BU9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BV9" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BW9" t="inlineStr">
+        <is>
           <t>0.96%</t>
         </is>
       </c>
-      <c r="BW9" t="inlineStr">
+      <c r="BX9" t="inlineStr">
         <is>
           <t>-3.42%</t>
         </is>
       </c>
-      <c r="BX9" t="inlineStr">
-        <is>
-          <t>62.64</t>
-        </is>
-      </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>13132</t>
+          <t>62.69</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
+          <t>12863</t>
+        </is>
+      </c>
+      <c r="CA9" t="inlineStr">
+        <is>
           <t>可塑劑(DOP)76.00%、聚氯乙烯13.00%、酸酐6.00%、其他5.00% (2024年)</t>
         </is>
       </c>
-      <c r="CA9" t="inlineStr">
+      <c r="CB9" t="inlineStr">
         <is>
           <t>聯成-塑膠工業-上市</t>
         </is>
       </c>
-      <c r="CB9" t="inlineStr">
+      <c r="CC9" t="inlineStr">
         <is>
           <t>塑膠工業右下上市</t>
         </is>
       </c>
-      <c r="CC9" t="inlineStr">
-        <is>
-          <t>10.0</t>
-        </is>
-      </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>10.4</t>
+          <t>10.15</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>9.96</t>
+          <t>10.6</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
@@ -4299,15 +4339,20 @@
       </c>
       <c r="CG9" t="inlineStr">
         <is>
+          <t>10.35</t>
+        </is>
+      </c>
+      <c r="CH9" t="inlineStr">
+        <is>
           <t>22.32</t>
         </is>
       </c>
-      <c r="CH9" t="inlineStr">
+      <c r="CI9" t="inlineStr">
         <is>
           <t>** 石化及塑橡膠 - 塑化劑(可塑劑)</t>
         </is>
       </c>
-      <c r="CI9" t="inlineStr">
+      <c r="CJ9" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -4326,12 +4371,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-3.14</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>4676.474</t>
+          <t>2459.513</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4386,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>9.93</t>
+          <t>10.15</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4396,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-6.51</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-4.08</t>
+          <t>-4.72</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>17.89</t>
+          <t>26.88</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4426,7 +4471,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-3.59</t>
+          <t>-1.46</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,12 +4481,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>21.33</t>
+          <t>11.22</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -4457,42 +4502,42 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>1867</t>
+          <t>2806</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>35.48</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>41.11</t>
+          <t>25.16</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-2.61</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
@@ -4502,7 +4547,7 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>10.33</t>
+          <t>10.29</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
@@ -4512,22 +4557,22 @@
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>10.17</t>
+          <t>10.18</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-476.65</t>
+          <t>-6995.52</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.00</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4582,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-98.43</t>
+          <t>-100.10</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,198 +4592,203 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>38447782.22805756</t>
+          <t>38450283.1012931</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>46414945.0</t>
+          <t>25033958.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>23851814.4</t>
+          <t>25855602.0</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>20231760.7</t>
+          <t>20377785.6</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>25751255.74</t>
+          <t>25837516.22</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>3620053</t>
+          <t>5477816</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-1674083.111667096</t>
-        </is>
-      </c>
-      <c r="BC10" t="n">
-        <v>251770.49</v>
-      </c>
-      <c r="BD10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-1379329.1848641</t>
+        </is>
+      </c>
+      <c r="BC10" t="inlineStr">
+        <is>
+          <t>241817.4125523753</t>
+        </is>
+      </c>
+      <c r="BD10" t="n">
+        <v>25033958</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF10" t="inlineStr">
+        <is>
           <t>10.5</t>
         </is>
       </c>
-      <c r="BF10" t="inlineStr">
+      <c r="BG10" t="inlineStr">
         <is>
           <t>2025/10/14</t>
         </is>
       </c>
-      <c r="BG10" t="inlineStr">
-        <is>
-          <t>-5.43</t>
-        </is>
-      </c>
       <c r="BH10" t="inlineStr">
         <is>
+          <t>-3.33</t>
+        </is>
+      </c>
+      <c r="BI10" t="inlineStr">
+        <is>
           <t>聯成</t>
         </is>
       </c>
-      <c r="BI10" t="inlineStr">
+      <c r="BJ10" t="inlineStr">
         <is>
           <t>聯成</t>
         </is>
       </c>
-      <c r="BJ10" t="inlineStr">
+      <c r="BK10" t="inlineStr">
         <is>
           <t>塑膠工業</t>
         </is>
       </c>
-      <c r="BK10" t="inlineStr">
+      <c r="BL10" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL10" t="inlineStr">
-        <is>
-          <t>0.78</t>
-        </is>
-      </c>
       <c r="BM10" t="inlineStr">
         <is>
+          <t>0.77</t>
+        </is>
+      </c>
+      <c r="BN10" t="inlineStr">
+        <is>
           <t>-11.96408371040724</t>
         </is>
       </c>
-      <c r="BN10" t="inlineStr">
+      <c r="BO10" t="inlineStr">
         <is>
           <t>-13.59414944504011</t>
         </is>
       </c>
-      <c r="BO10" t="inlineStr">
+      <c r="BP10" t="inlineStr">
         <is>
           <t>-19.633719693908</t>
         </is>
       </c>
-      <c r="BP10" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ10" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR10" t="inlineStr">
+        <is>
           <t>價-量增</t>
         </is>
       </c>
-      <c r="BR10" t="inlineStr">
-        <is>
-          <t>0.44</t>
-        </is>
-      </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="BU10" t="inlineStr">
+        <is>
           <t>10.97</t>
         </is>
       </c>
-      <c r="BU10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BV10" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BW10" t="inlineStr">
+        <is>
           <t>0.96%</t>
         </is>
       </c>
-      <c r="BW10" t="inlineStr">
+      <c r="BX10" t="inlineStr">
         <is>
           <t>-3.42%</t>
         </is>
       </c>
-      <c r="BX10" t="inlineStr">
-        <is>
-          <t>62.64</t>
-        </is>
-      </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>13132</t>
+          <t>62.69</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
+          <t>12863</t>
+        </is>
+      </c>
+      <c r="CA10" t="inlineStr">
+        <is>
           <t>可塑劑(DOP)76.00%、聚氯乙烯13.00%、酸酐6.00%、其他5.00% (2024年)</t>
         </is>
       </c>
-      <c r="CA10" t="inlineStr">
+      <c r="CB10" t="inlineStr">
         <is>
           <t>聯成-塑膠工業-上市</t>
         </is>
       </c>
-      <c r="CB10" t="inlineStr">
+      <c r="CC10" t="inlineStr">
         <is>
           <t>塑膠工業右下上市</t>
         </is>
       </c>
-      <c r="CC10" t="inlineStr">
-        <is>
-          <t>10.2</t>
-        </is>
-      </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>9.72</t>
+          <t>10.4</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>9.93</t>
+          <t>9.96</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
+          <t>10.15</t>
+        </is>
+      </c>
+      <c r="CH10" t="inlineStr">
+        <is>
           <t>22.32</t>
         </is>
       </c>
-      <c r="CH10" t="inlineStr">
+      <c r="CI10" t="inlineStr">
         <is>
           <t>** 石化及塑橡膠 - 塑化劑(可塑劑)</t>
         </is>
       </c>
-      <c r="CI10" t="inlineStr">
+      <c r="CJ10" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -4757,12 +4807,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-2.9</t>
+          <t>-3.14</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2017.475</t>
+          <t>4676.474</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4822,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>10.25</t>
+          <t>9.93</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,17 +4832,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-5.34</t>
+          <t>-4.2</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-4.08</t>
+          <t>-4.72</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>17.89</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4857,7 +4907,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-3.59</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4917,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>9.20</t>
+          <t>21.33</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,77 +4938,77 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>1867</t>
+          <t>2806</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>43.68</t>
+          <t>41.11</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>-2.61</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-1.54</t>
+          <t>-1.26</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>10.22</t>
+          <t>10.196</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>10.38</t>
+          <t>10.33</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>10.21</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>10.15</t>
+          <t>10.17</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-116.74</t>
+          <t>-476.65</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.00</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +5018,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-96.57</t>
+          <t>-98.43</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,175 +5028,175 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>38447782.22805756</t>
+          <t>38450283.1012931</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>20841022.0</t>
+          <t>46414945.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>17370499.2</t>
+          <t>23851814.4</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>17407208.9</t>
+          <t>20231760.7</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>25485299.38</t>
+          <t>25751255.74</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-36709</t>
+          <t>3620053</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-2024238.312393929</t>
-        </is>
-      </c>
-      <c r="BC11" t="n">
-        <v>-2033822.66</v>
-      </c>
-      <c r="BD11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-1674083.111667096</t>
+        </is>
+      </c>
+      <c r="BC11" t="inlineStr">
+        <is>
+          <t>251770.4923304841</t>
+        </is>
+      </c>
+      <c r="BD11" t="n">
+        <v>46414945</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF11" t="inlineStr">
+        <is>
           <t>10.5</t>
         </is>
       </c>
-      <c r="BF11" t="inlineStr">
+      <c r="BG11" t="inlineStr">
         <is>
           <t>2025/10/14</t>
         </is>
       </c>
-      <c r="BG11" t="inlineStr">
-        <is>
-          <t>-2.38</t>
-        </is>
-      </c>
       <c r="BH11" t="inlineStr">
         <is>
+          <t>-5.43</t>
+        </is>
+      </c>
+      <c r="BI11" t="inlineStr">
+        <is>
           <t>聯成</t>
         </is>
       </c>
-      <c r="BI11" t="inlineStr">
+      <c r="BJ11" t="inlineStr">
         <is>
           <t>聯成</t>
         </is>
       </c>
-      <c r="BJ11" t="inlineStr">
+      <c r="BK11" t="inlineStr">
         <is>
           <t>塑膠工業</t>
         </is>
       </c>
-      <c r="BK11" t="inlineStr">
+      <c r="BL11" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL11" t="inlineStr">
-        <is>
-          <t>0.78</t>
-        </is>
-      </c>
       <c r="BM11" t="inlineStr">
         <is>
+          <t>0.77</t>
+        </is>
+      </c>
+      <c r="BN11" t="inlineStr">
+        <is>
           <t>-11.96408371040724</t>
         </is>
       </c>
-      <c r="BN11" t="inlineStr">
+      <c r="BO11" t="inlineStr">
         <is>
           <t>-13.59414944504011</t>
         </is>
       </c>
-      <c r="BO11" t="inlineStr">
+      <c r="BP11" t="inlineStr">
         <is>
           <t>-19.633719693908</t>
         </is>
       </c>
-      <c r="BP11" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ11" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR11" t="inlineStr">
+        <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="BR11" t="inlineStr">
-        <is>
-          <t>0.46</t>
-        </is>
-      </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="BU11" t="inlineStr">
+        <is>
           <t>10.97</t>
         </is>
       </c>
-      <c r="BU11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BV11" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BW11" t="inlineStr">
+        <is>
           <t>0.96%</t>
         </is>
       </c>
-      <c r="BW11" t="inlineStr">
+      <c r="BX11" t="inlineStr">
         <is>
           <t>-3.42%</t>
         </is>
       </c>
-      <c r="BX11" t="inlineStr">
-        <is>
-          <t>62.64</t>
-        </is>
-      </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>13132</t>
+          <t>62.69</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
+          <t>12863</t>
+        </is>
+      </c>
+      <c r="CA11" t="inlineStr">
+        <is>
           <t>可塑劑(DOP)76.00%、聚氯乙烯13.00%、酸酐6.00%、其他5.00% (2024年)</t>
         </is>
       </c>
-      <c r="CA11" t="inlineStr">
+      <c r="CB11" t="inlineStr">
         <is>
           <t>聯成-塑膠工業-上市</t>
         </is>
       </c>
-      <c r="CB11" t="inlineStr">
+      <c r="CC11" t="inlineStr">
         <is>
           <t>塑膠工業右下上市</t>
         </is>
       </c>
-      <c r="CC11" t="inlineStr">
-        <is>
-          <t>10.35</t>
-        </is>
-      </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>10.5</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
@@ -5156,20 +5206,25 @@
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>10.25</t>
+          <t>9.72</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
+          <t>9.93</t>
+        </is>
+      </c>
+      <c r="CH11" t="inlineStr">
+        <is>
           <t>22.32</t>
         </is>
       </c>
-      <c r="CH11" t="inlineStr">
+      <c r="CI11" t="inlineStr">
         <is>
           <t>** 石化及塑橡膠 - 塑化劑(可塑劑)</t>
         </is>
       </c>
-      <c r="CI11" t="inlineStr">
+      <c r="CJ11" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -5188,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>4.41</t>
+          <t>-2.9</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1911.185</t>
+          <t>2017.475</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,84 +5258,84 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
+          <t>10.25</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-7.56</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>-4.72</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>-0.21</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>2025-10-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>2025-10-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>2025-09-23 00:00:00</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>2025-10-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>10.65</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>10.3</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
           <t>10.55</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>-8.43</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>-4.08</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>-25.08</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>2025-10-27 00:00:00</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>2025-10-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>2025-09-23 00:00:00</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>2025-10-16 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>10.65</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>10.3</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>10.55</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>10.3</t>
-        </is>
-      </c>
       <c r="V12" t="inlineStr">
         <is>
           <t>0</t>
@@ -5288,7 +5343,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5353,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>8.72</t>
+          <t>9.20</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,288 +5374,293 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>1867</t>
+          <t>2806</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>83.33</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>35.47</t>
+          <t>43.68</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>3.43</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-1.78</t>
+          <t>-1.54</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
+          <t>10.22</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>10.38</t>
+        </is>
+      </c>
+      <c r="AN12" t="inlineStr">
+        <is>
+          <t>10.21</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>10.15</t>
+        </is>
+      </c>
+      <c r="AP12" t="inlineStr">
+        <is>
+          <t>-116.74</t>
+        </is>
+      </c>
+      <c r="AQ12" t="inlineStr">
+        <is>
+          <t>-0.00</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="AS12" t="inlineStr">
+        <is>
+          <t>0.54</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr">
+        <is>
+          <t>-96.57</t>
+        </is>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>2025/11/13</t>
+        </is>
+      </c>
+      <c r="AV12" t="inlineStr">
+        <is>
+          <t>38450283.1012931</t>
+        </is>
+      </c>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>20841022.0</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>17370499.2</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>17407208.9</t>
+        </is>
+      </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>25485299.38</t>
+        </is>
+      </c>
+      <c r="BA12" t="inlineStr">
+        <is>
+          <t>-36709</t>
+        </is>
+      </c>
+      <c r="BB12" t="inlineStr">
+        <is>
+          <t>-2024238.312393929</t>
+        </is>
+      </c>
+      <c r="BC12" t="inlineStr">
+        <is>
+          <t>-2033822.661284022</t>
+        </is>
+      </c>
+      <c r="BD12" t="n">
+        <v>20841022</v>
+      </c>
+      <c r="BE12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF12" t="inlineStr">
+        <is>
+          <t>10.5</t>
+        </is>
+      </c>
+      <c r="BG12" t="inlineStr">
+        <is>
+          <t>2025/10/14</t>
+        </is>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>-2.38</t>
+        </is>
+      </c>
+      <c r="BI12" t="inlineStr">
+        <is>
+          <t>聯成</t>
+        </is>
+      </c>
+      <c r="BJ12" t="inlineStr">
+        <is>
+          <t>聯成</t>
+        </is>
+      </c>
+      <c r="BK12" t="inlineStr">
+        <is>
+          <t>塑膠工業</t>
+        </is>
+      </c>
+      <c r="BL12" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM12" t="inlineStr">
+        <is>
+          <t>0.77</t>
+        </is>
+      </c>
+      <c r="BN12" t="inlineStr">
+        <is>
+          <t>-11.96408371040724</t>
+        </is>
+      </c>
+      <c r="BO12" t="inlineStr">
+        <is>
+          <t>-13.59414944504011</t>
+        </is>
+      </c>
+      <c r="BP12" t="inlineStr">
+        <is>
+          <t>-19.633719693908</t>
+        </is>
+      </c>
+      <c r="BQ12" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR12" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS12" t="inlineStr">
+        <is>
+          <t>0.46</t>
+        </is>
+      </c>
+      <c r="BT12" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="BU12" t="inlineStr">
+        <is>
+          <t>10.97</t>
+        </is>
+      </c>
+      <c r="BV12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BW12" t="inlineStr">
+        <is>
+          <t>0.96%</t>
+        </is>
+      </c>
+      <c r="BX12" t="inlineStr">
+        <is>
+          <t>-3.42%</t>
+        </is>
+      </c>
+      <c r="BY12" t="inlineStr">
+        <is>
+          <t>62.69</t>
+        </is>
+      </c>
+      <c r="BZ12" t="inlineStr">
+        <is>
+          <t>12863</t>
+        </is>
+      </c>
+      <c r="CA12" t="inlineStr">
+        <is>
+          <t>可塑劑(DOP)76.00%、聚氯乙烯13.00%、酸酐6.00%、其他5.00% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB12" t="inlineStr">
+        <is>
+          <t>聯成-塑膠工業-上市</t>
+        </is>
+      </c>
+      <c r="CC12" t="inlineStr">
+        <is>
+          <t>塑膠工業右下上市</t>
+        </is>
+      </c>
+      <c r="CD12" t="inlineStr">
+        <is>
+          <t>10.35</t>
+        </is>
+      </c>
+      <c r="CE12" t="inlineStr">
+        <is>
+          <t>10.5</t>
+        </is>
+      </c>
+      <c r="CF12" t="inlineStr">
+        <is>
           <t>10.2</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>10.38</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>10.23</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>10.13</t>
-        </is>
-      </c>
-      <c r="AP12" t="inlineStr">
-        <is>
-          <t>-96.16</t>
-        </is>
-      </c>
-      <c r="AQ12" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="AR12" t="inlineStr">
-        <is>
-          <t>0.02</t>
-        </is>
-      </c>
-      <c r="AS12" t="inlineStr">
-        <is>
-          <t>0.54</t>
-        </is>
-      </c>
-      <c r="AT12" t="inlineStr">
-        <is>
-          <t>-95.56</t>
-        </is>
-      </c>
-      <c r="AU12" t="inlineStr">
-        <is>
-          <t>2025/11/13</t>
-        </is>
-      </c>
-      <c r="AV12" t="inlineStr">
-        <is>
-          <t>38447782.22805756</t>
-        </is>
-      </c>
-      <c r="AW12" t="inlineStr">
-        <is>
-          <t>19882656.0</t>
-        </is>
-      </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>16059833.8</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr">
-        <is>
-          <t>21436958.2</t>
-        </is>
-      </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>25694765.18</t>
-        </is>
-      </c>
-      <c r="BA12" t="inlineStr">
-        <is>
-          <t>-5377124</t>
-        </is>
-      </c>
-      <c r="BB12" t="inlineStr">
-        <is>
-          <t>-2022495.703504821</t>
-        </is>
-      </c>
-      <c r="BC12" t="n">
-        <v>-2486256.04</v>
-      </c>
-      <c r="BD12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE12" t="inlineStr">
-        <is>
-          <t>10.5</t>
-        </is>
-      </c>
-      <c r="BF12" t="inlineStr">
-        <is>
-          <t>2025/10/14</t>
-        </is>
-      </c>
-      <c r="BG12" t="inlineStr">
-        <is>
-          <t>0.48</t>
-        </is>
-      </c>
-      <c r="BH12" t="inlineStr">
-        <is>
-          <t>聯成</t>
-        </is>
-      </c>
-      <c r="BI12" t="inlineStr">
-        <is>
-          <t>聯成</t>
-        </is>
-      </c>
-      <c r="BJ12" t="inlineStr">
-        <is>
-          <t>塑膠工業</t>
-        </is>
-      </c>
-      <c r="BK12" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BL12" t="inlineStr">
-        <is>
-          <t>0.78</t>
-        </is>
-      </c>
-      <c r="BM12" t="inlineStr">
-        <is>
-          <t>-11.96408371040724</t>
-        </is>
-      </c>
-      <c r="BN12" t="inlineStr">
-        <is>
-          <t>-13.59414944504011</t>
-        </is>
-      </c>
-      <c r="BO12" t="inlineStr">
-        <is>
-          <t>-19.633719693908</t>
-        </is>
-      </c>
-      <c r="BP12" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BQ12" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BR12" t="inlineStr">
-        <is>
-          <t>0.47</t>
-        </is>
-      </c>
-      <c r="BS12" t="inlineStr">
-        <is>
-          <t>1.54</t>
-        </is>
-      </c>
-      <c r="BT12" t="inlineStr">
-        <is>
-          <t>10.97</t>
-        </is>
-      </c>
-      <c r="BU12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BV12" t="inlineStr">
-        <is>
-          <t>0.96%</t>
-        </is>
-      </c>
-      <c r="BW12" t="inlineStr">
-        <is>
-          <t>-3.42%</t>
-        </is>
-      </c>
-      <c r="BX12" t="inlineStr">
-        <is>
-          <t>62.64</t>
-        </is>
-      </c>
-      <c r="BY12" t="inlineStr">
-        <is>
-          <t>13132</t>
-        </is>
-      </c>
-      <c r="BZ12" t="inlineStr">
-        <is>
-          <t>可塑劑(DOP)76.00%、聚氯乙烯13.00%、酸酐6.00%、其他5.00% (2024年)</t>
-        </is>
-      </c>
-      <c r="CA12" t="inlineStr">
-        <is>
-          <t>聯成-塑膠工業-上市</t>
-        </is>
-      </c>
-      <c r="CB12" t="inlineStr">
-        <is>
-          <t>塑膠工業右下上市</t>
-        </is>
-      </c>
-      <c r="CC12" t="inlineStr">
-        <is>
-          <t>10.2</t>
-        </is>
-      </c>
-      <c r="CD12" t="inlineStr">
-        <is>
-          <t>10.55</t>
-        </is>
-      </c>
-      <c r="CE12" t="inlineStr">
-        <is>
-          <t>10.15</t>
-        </is>
-      </c>
-      <c r="CF12" t="inlineStr">
-        <is>
-          <t>10.55</t>
-        </is>
-      </c>
       <c r="CG12" t="inlineStr">
         <is>
+          <t>10.25</t>
+        </is>
+      </c>
+      <c r="CH12" t="inlineStr">
+        <is>
           <t>22.32</t>
         </is>
       </c>
-      <c r="CH12" t="inlineStr">
+      <c r="CI12" t="inlineStr">
         <is>
           <t>** 石化及塑橡膠 - 塑化劑(可塑劑)</t>
         </is>
       </c>
-      <c r="CI12" t="inlineStr">
+      <c r="CJ12" t="inlineStr">
         <is>
           <t>False</t>
         </is>

--- a/Result/checksun_type/塑化劑(可塑劑).xlsx
+++ b/Result/checksun_type/塑化劑(可塑劑).xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2806.058</t>
+          <t>1859.149</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>9.53</t>
+          <t>9.39</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-4.72</t>
+          <t>-3.4</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-12.07</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-7.48</t>
+          <t>-8.83</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12.80</t>
+          <t>8.48</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-2.45</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,12 +1014,12 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>2806</t>
+          <t>1859</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1034,57 +1034,57 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-2.66</t>
+          <t>-2.67</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-3.58</t>
+          <t>-4.39</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>9.790000000000001</t>
+          <t>9.648</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>10.15</t>
+          <t>10.09</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
+          <t>10.18</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
           <t>10.19</t>
         </is>
       </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>10.2</t>
-        </is>
-      </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-141.34</t>
+          <t>-117.02</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-110.67</t>
+          <t>-115.08</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1104,46 +1104,46 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>38450283.1012931</t>
+          <t>38432997.52080344</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>26792260.0</t>
+          <t>17601489.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>24442611.2</t>
+          <t>25218403.0</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>27798303.7</t>
+          <t>24916958.1</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>26345925.2</t>
+          <t>26498584.58</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-3355692</t>
+          <t>301444</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-199697.2390819047</t>
+          <t>-237736.9354581767</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>156076.4421134964</t>
+          <t>-446955.2655276731</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>26792260</v>
+        <v>17601489</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-9.24</t>
+          <t>-10.57</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1207,7 +1207,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1247,12 +1247,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>62.69</t>
+          <t>62.96</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>12863</t>
+          <t>12674</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1272,22 +1272,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>9.73</t>
+          <t>9.55</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>9.73</t>
+          <t>9.63</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>9.38</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>9.53</t>
+          <t>9.39</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1319,12 +1319,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1866.918</t>
+          <t>2806.058</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>9.73</t>
+          <t>9.53</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1344,17 +1344,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-2.1</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-4.72</t>
+          <t>-3.4</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-17.77</t>
+          <t>-12.07</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-5.53</t>
+          <t>-7.48</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1429,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>8.52</t>
+          <t>12.80</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1450,77 +1450,77 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>2806</t>
+          <t>1859</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>15.38</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>8.89</t>
+          <t>5.13</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-2.45</t>
+          <t>-2.66</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>-3.58</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>9.974</t>
+          <t>9.790000000000001</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>10.21</t>
+          <t>10.15</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
+          <t>10.19</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
           <t>10.2</t>
         </is>
       </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>10.22</t>
-        </is>
-      </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-177.09</t>
+          <t>-141.34</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-106.90</t>
+          <t>-110.67</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1540,46 +1540,46 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>38450283.1012931</t>
+          <t>38432997.52080344</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>18247885.0</t>
+          <t>26792260.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>22369720.8</t>
+          <t>24442611.2</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>27203179.9</t>
+          <t>27798303.7</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>26271252.44</t>
+          <t>26345925.2</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-4833459</t>
+          <t>-3355692</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-264383.362935614</t>
+          <t>-199697.2390819047</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>27250.68723968416</t>
+          <t>156076.4421134964</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>18247885</v>
+        <v>26792260</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-7.33</t>
+          <t>-9.24</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1623,7 +1623,7 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
@@ -1643,22 +1643,22 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>62.69</t>
+          <t>62.96</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>12863</t>
+          <t>12674</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1708,22 +1708,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>9.77</t>
+          <t>9.73</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>9.95</t>
+          <t>9.73</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>9.73</t>
+          <t>9.53</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1755,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-4.1</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>3938.682</t>
+          <t>1866.918</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>9.59</t>
+          <t>9.73</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1780,17 +1780,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>-3.62</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-4.72</t>
+          <t>-3.4</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-2.69</t>
+          <t>-17.77</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-6.89</t>
+          <t>-5.53</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1865,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17.97</t>
+          <t>8.52</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-4.07</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1886,52 +1886,52 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>2806</t>
+          <t>1859</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>15.38</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>12.9</t>
+          <t>8.89</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-5.31</t>
+          <t>-2.45</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>10.128</t>
+          <t>9.974</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>10.25</t>
+          <t>10.21</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
@@ -1946,17 +1946,17 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-268.37</t>
+          <t>-177.09</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-103.85</t>
+          <t>-106.90</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1976,46 +1976,46 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>38450283.1012931</t>
+          <t>38432997.52080344</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>38346124.0</t>
+          <t>18247885.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>26631549.8</t>
+          <t>22369720.8</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>27366657.0</t>
+          <t>27203179.9</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>26177335.2</t>
+          <t>26271252.44</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-735107</t>
+          <t>-4833459</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-317407.7356947591</t>
+          <t>-264383.362935614</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>757709.4057328217</t>
+          <t>27250.68723968416</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>38346124</v>
+        <v>18247885</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-8.67</t>
+          <t>-7.33</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
@@ -2079,22 +2079,22 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>62.69</t>
+          <t>62.96</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>12863</t>
+          <t>12674</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2144,22 +2144,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>9.99</t>
+          <t>9.77</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>9.99</t>
+          <t>9.95</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>9.58</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>9.59</t>
+          <t>9.73</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-4.1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2500.445</t>
+          <t>3938.682</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>9.59</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2216,17 +2216,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-4.93</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-4.72</t>
+          <t>-3.4</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-2.43</t>
+          <t>-2.69</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-2.91</t>
+          <t>-6.89</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2301,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11.41</t>
+          <t>17.97</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-1.60</t>
+          <t>-4.07</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2322,57 +2322,57 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>2806</t>
+          <t>1859</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>11.29</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>40.86</t>
+          <t>12.9</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-2.72</t>
+          <t>-5.31</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>10.28</t>
+          <t>10.128</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>10.28</t>
+          <t>10.25</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>10.21</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
@@ -2382,17 +2382,17 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-293.77</t>
+          <t>-268.37</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-101.27</t>
+          <t>-103.85</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2412,46 +2412,46 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>38450283.1012931</t>
+          <t>38432997.52080344</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>25104257.0</t>
+          <t>38346124.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>24629573.0</t>
+          <t>26631549.8</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>25242587.5</t>
+          <t>27366657.0</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>25777972.78</t>
+          <t>26177335.2</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-613014</t>
+          <t>-735107</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-512883.5795906829</t>
+          <t>-317407.7356947591</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-379221.9394817278</t>
+          <t>757709.4057328217</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>25104257</v>
+        <v>38346124</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-4.76</t>
+          <t>-8.67</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2495,7 +2495,7 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
@@ -2515,22 +2515,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2555,12 +2555,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>62.69</t>
+          <t>62.96</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>12863</t>
+          <t>12674</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2580,22 +2580,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>10.05</t>
+          <t>9.99</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>9.99</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>9.96</t>
+          <t>9.58</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>9.59</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-3.35</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1335.381</t>
+          <t>2500.445</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2652,17 +2652,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-5.98</t>
+          <t>-6.5</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-4.72</t>
+          <t>-3.4</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>-2.43</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-1.94</t>
+          <t>-2.91</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2737,73 +2737,73 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>6.09</t>
+          <t>11.41</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-4.95</t>
+          <t>-1.60</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>2806</t>
+          <t>1859</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>27.42</t>
+          <t>11.29</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>67.74</t>
+          <t>40.86</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-2.04</t>
+          <t>-2.72</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>10.31</t>
+          <t>10.28</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>10.3</t>
+          <t>10.28</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
@@ -2818,19 +2818,19 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-185.15</t>
+          <t>-293.77</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
+          <t>-0.03</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
           <t>-0.01</t>
         </is>
       </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>-0.00</t>
-        </is>
-      </c>
       <c r="AS6" t="inlineStr">
         <is>
           <t>0.54</t>
@@ -2838,7 +2838,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-100.34</t>
+          <t>-101.27</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2848,46 +2848,46 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>38450283.1012931</t>
+          <t>38432997.52080344</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>13722530.0</t>
+          <t>25104257.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>24615513.2</t>
+          <t>24629573.0</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>24233663.8</t>
+          <t>25242587.5</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>25886365.74</t>
+          <t>25777972.78</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>381849</t>
+          <t>-613014</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-537185.6959741293</t>
+          <t>-512883.5795906829</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-571094.4705210179</t>
+          <t>-379221.9394817278</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>13722530</v>
+        <v>25104257</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-3.81</t>
+          <t>-4.76</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
@@ -2966,7 +2966,7 @@
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2991,12 +2991,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>62.69</t>
+          <t>62.96</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>12863</t>
+          <t>12674</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -3016,22 +3016,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>10.45</t>
+          <t>10.05</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>10.6</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>9.96</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-3.35</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1569.646</t>
+          <t>1335.381</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>10.45</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3088,17 +3088,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-9.65</t>
+          <t>-7.56</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-4.72</t>
+          <t>-3.4</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>28.41</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>-1.94</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3173,73 +3173,73 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>7.16</t>
+          <t>6.09</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-4.95</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>2806</t>
+          <t>1859</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>83.87</t>
+          <t>27.42</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>81.18</t>
+          <t>67.74</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>-2.04</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>10.276</t>
+          <t>10.31</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>10.31</t>
+          <t>10.3</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
@@ -3254,12 +3254,12 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>1372.99</t>
+          <t>-185.15</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-100.18</t>
+          <t>-100.34</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3284,46 +3284,46 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>38450283.1012931</t>
+          <t>38432997.52080344</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>16427808.0</t>
+          <t>13722530.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>31153996.2</t>
+          <t>24615513.2</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>24262247.7</t>
+          <t>24233663.8</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>26236307.54</t>
+          <t>25886365.74</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>6891748</t>
+          <t>381849</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-531020.4642383313</t>
+          <t>-537185.6959741293</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>394668.8947985992</t>
+          <t>-571094.4705210179</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>16427808</v>
+        <v>13722530</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-3.81</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3367,7 +3367,7 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
@@ -3387,22 +3387,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>62.69</t>
+          <t>62.96</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>12863</t>
+          <t>12674</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3452,7 +3452,7 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>10.4</t>
+          <t>10.45</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
@@ -3462,12 +3462,12 @@
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>10.3</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>10.45</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3499,12 +3499,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>3754.177</t>
+          <t>1569.646</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>10.5</t>
+          <t>10.45</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3524,17 +3524,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-10.18</t>
+          <t>-11.29</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-4.72</t>
+          <t>-3.4</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>33.22</t>
+          <t>28.41</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3609,17 +3609,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17.12</t>
+          <t>7.16</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3630,47 +3630,47 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>2806</t>
+          <t>1859</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>91.94</t>
+          <t>83.87</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>65.05</t>
+          <t>81.18</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>10.236</t>
+          <t>10.276</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
@@ -3680,29 +3680,29 @@
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>10.21</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>10.22</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>73.66</t>
+          <t>1372.99</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
           <t>-0.00</t>
         </is>
       </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>-0.00</t>
-        </is>
-      </c>
       <c r="AS8" t="inlineStr">
         <is>
           <t>0.54</t>
@@ -3710,7 +3710,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-100.80</t>
+          <t>-100.18</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3720,46 +3720,46 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>38450283.1012931</t>
+          <t>38432997.52080344</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>39557030.0</t>
+          <t>16427808.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>32036639.0</t>
+          <t>31153996.2</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>24048236.4</t>
+          <t>24262247.7</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>26253921.64</t>
+          <t>26236307.54</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>7988402</t>
+          <t>6891748</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-699327.6204268641</t>
+          <t>-531020.4642383313</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>1470384.313298099</t>
+          <t>394668.8947985992</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>39557030</v>
+        <v>16427808</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3803,7 +3803,7 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
@@ -3838,7 +3838,7 @@
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>62.69</t>
+          <t>62.96</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>12863</t>
+          <t>12674</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3893,7 +3893,7 @@
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>10.75</t>
+          <t>10.6</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
@@ -3903,7 +3903,7 @@
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>10.5</t>
+          <t>10.45</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3935,12 +3935,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2725.546</t>
+          <t>3754.177</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>10.35</t>
+          <t>10.5</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3960,17 +3960,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-8.6</t>
+          <t>-11.82</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-4.72</t>
+          <t>-3.4</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>31.50</t>
+          <t>33.22</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12.43</t>
+          <t>17.12</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4066,52 +4066,52 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>2806</t>
+          <t>1859</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>67.74</t>
+          <t>91.94</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>34.41</t>
+          <t>65.05</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>10.246</t>
+          <t>10.236</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>10.29</t>
+          <t>10.31</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
@@ -4121,22 +4121,22 @@
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>10.19</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-359.87</t>
+          <t>73.66</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.00</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-0.00</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-100.95</t>
+          <t>-100.80</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4156,46 +4156,46 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>38450283.1012931</t>
+          <t>38432997.52080344</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>28336240.0</t>
+          <t>39557030.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>28101764.2</t>
+          <t>32036639.0</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>21370450.7</t>
+          <t>24048236.4</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>26117511.38</t>
+          <t>26253921.64</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>6731313</t>
+          <t>7988402</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-1093820.699285948</t>
+          <t>-699327.6204268641</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>476475.971393887</t>
+          <t>1470384.313298099</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>28336240</v>
+        <v>39557030</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-1.43</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
@@ -4259,22 +4259,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>62.69</t>
+          <t>62.96</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>12863</t>
+          <t>12674</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4324,22 +4324,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>10.15</t>
+          <t>10.4</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>10.6</t>
+          <t>10.75</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>10.15</t>
+          <t>10.3</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>10.35</t>
+          <t>10.5</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4371,12 +4371,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2459.513</t>
+          <t>2725.546</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>10.15</t>
+          <t>10.35</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4396,17 +4396,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-6.51</t>
+          <t>-10.22</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-4.72</t>
+          <t>-3.4</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>26.88</t>
+          <t>31.50</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4471,7 +4471,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4481,17 +4481,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11.22</t>
+          <t>12.43</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-0.56</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4502,47 +4502,47 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>2806</t>
+          <t>1859</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>35.48</t>
+          <t>67.74</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>25.16</t>
+          <t>34.41</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>10.196</t>
+          <t>10.246</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
@@ -4557,22 +4557,22 @@
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>10.18</t>
+          <t>10.19</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-6995.52</t>
+          <t>-359.87</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.00</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-100.10</t>
+          <t>-100.95</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4592,46 +4592,46 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>38450283.1012931</t>
+          <t>38432997.52080344</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>25033958.0</t>
+          <t>28336240.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>25855602.0</t>
+          <t>28101764.2</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>20377785.6</t>
+          <t>21370450.7</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>25837516.22</t>
+          <t>26117511.38</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>5477816</t>
+          <t>6731313</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-1379329.1848641</t>
+          <t>-1093820.699285948</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>241817.4125523753</t>
+          <t>476475.971393887</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>25033958</v>
+        <v>28336240</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-3.33</t>
+          <t>-1.43</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4675,7 +4675,7 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
@@ -4695,7 +4695,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4705,12 +4705,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4735,12 +4735,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>62.69</t>
+          <t>62.96</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>12863</t>
+          <t>12674</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4760,22 +4760,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>10.15</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>10.4</t>
+          <t>10.6</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>9.96</t>
+          <t>10.15</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>10.15</t>
+          <t>10.35</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-3.14</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>4676.474</t>
+          <t>2459.513</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>9.93</t>
+          <t>10.15</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4832,17 +4832,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-4.2</t>
+          <t>-8.09</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-4.72</t>
+          <t>-3.4</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>17.89</t>
+          <t>26.88</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-3.59</t>
+          <t>-1.46</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>21.33</t>
+          <t>11.22</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -4938,42 +4938,42 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>2806</t>
+          <t>1859</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>35.48</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>41.11</t>
+          <t>25.16</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-2.61</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
@@ -4983,7 +4983,7 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>10.33</t>
+          <t>10.29</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
@@ -4993,22 +4993,22 @@
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>10.17</t>
+          <t>10.18</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-476.65</t>
+          <t>-6995.52</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.00</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-98.43</t>
+          <t>-100.10</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -5028,46 +5028,46 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>38450283.1012931</t>
+          <t>38432997.52080344</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>46414945.0</t>
+          <t>25033958.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>23851814.4</t>
+          <t>25855602.0</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>20231760.7</t>
+          <t>20377785.6</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>25751255.74</t>
+          <t>25837516.22</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>3620053</t>
+          <t>5477816</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-1674083.111667096</t>
+          <t>-1379329.1848641</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>251770.4923304841</t>
+          <t>241817.4125523753</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>46414945</v>
+        <v>25033958</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-5.43</t>
+          <t>-3.33</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5171,12 +5171,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>62.69</t>
+          <t>62.96</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>12863</t>
+          <t>12674</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5196,22 +5196,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>10.4</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>9.72</t>
+          <t>9.96</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>9.93</t>
+          <t>10.15</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-2.9</t>
+          <t>-3.14</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2017.475</t>
+          <t>4676.474</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>10.25</t>
+          <t>9.93</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5268,17 +5268,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-7.56</t>
+          <t>-5.75</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-4.72</t>
+          <t>-3.4</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>17.89</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5343,7 +5343,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-3.59</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5353,17 +5353,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>9.20</t>
+          <t>21.33</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5374,77 +5374,77 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>2806</t>
+          <t>1859</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>43.68</t>
+          <t>41.11</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>-2.61</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-1.54</t>
+          <t>-1.26</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>10.22</t>
+          <t>10.196</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>10.38</t>
+          <t>10.33</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>10.21</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>10.15</t>
+          <t>10.17</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-116.74</t>
+          <t>-476.65</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.00</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5454,7 +5454,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-96.57</t>
+          <t>-98.43</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5464,46 +5464,46 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>38450283.1012931</t>
+          <t>38432997.52080344</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>20841022.0</t>
+          <t>46414945.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>17370499.2</t>
+          <t>23851814.4</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>17407208.9</t>
+          <t>20231760.7</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>25485299.38</t>
+          <t>25751255.74</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-36709</t>
+          <t>3620053</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-2024238.312393929</t>
+          <t>-1674083.111667096</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-2033822.661284022</t>
+          <t>251770.4923304841</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>20841022</v>
+        <v>46414945</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-2.38</t>
+          <t>-5.43</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5547,7 +5547,7 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5607,12 +5607,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>62.69</t>
+          <t>62.96</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>12863</t>
+          <t>12674</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5632,22 +5632,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>10.35</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>10.5</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>9.72</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>10.25</t>
+          <t>9.93</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/塑化劑(可塑劑).xlsx
+++ b/Result/checksun_type/塑化劑(可塑劑).xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1859.149</t>
+          <t>1560.548</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>9.39</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-3.4</t>
+          <t>-3.38</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>-3.14</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-8.83</t>
+          <t>-7.77</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>8.48</t>
+          <t>7.12</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-2.45</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,77 +1014,77 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>1859</t>
+          <t>1561</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.91</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>5.13</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-2.67</t>
+          <t>-0.50</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-4.39</t>
+          <t>-5.00</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>9.648</t>
+          <t>9.548</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>10.09</t>
+          <t>10.05</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
+          <t>10.17</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
           <t>10.18</t>
         </is>
       </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>10.19</t>
-        </is>
-      </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-117.02</t>
+          <t>-87.49</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-115.08</t>
+          <t>-119.31</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1104,46 +1104,46 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>38432997.52080344</t>
+          <t>38409450.62965616</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>17601489.0</t>
+          <t>14664845.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>25218403.0</t>
+          <t>23130520.6</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>24916958.1</t>
+          <t>23880046.8</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>26498584.58</t>
+          <t>26473396.54</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>301444</t>
+          <t>-749526</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-237736.9354581767</t>
+          <t>-367031.5421935803</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-446955.2655276731</t>
+          <t>-1078151.8792383</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>17601489</v>
+        <v>14664845</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-10.57</t>
+          <t>-9.52</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1207,7 +1207,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1247,12 +1247,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>62.96</t>
+          <t>63.02</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>12674</t>
+          <t>12822</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1272,22 +1272,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
+          <t>9.46</t>
+        </is>
+      </c>
+      <c r="CE2" t="inlineStr">
+        <is>
           <t>9.55</t>
         </is>
       </c>
-      <c r="CE2" t="inlineStr">
-        <is>
-          <t>9.63</t>
-        </is>
-      </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>9.38</t>
+          <t>9.27</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>9.39</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1319,12 +1319,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2806.058</t>
+          <t>1859.149</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>9.53</t>
+          <t>9.39</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1344,17 +1344,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-3.4</t>
+          <t>-3.38</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-12.07</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-7.48</t>
+          <t>-8.83</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1429,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12.80</t>
+          <t>8.48</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-2.45</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1450,12 +1450,12 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>1859</t>
+          <t>1561</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1470,57 +1470,57 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-2.66</t>
+          <t>-2.67</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-3.58</t>
+          <t>-4.39</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>9.790000000000001</t>
+          <t>9.648</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>10.15</t>
+          <t>10.09</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
+          <t>10.18</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
           <t>10.19</t>
         </is>
       </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>10.2</t>
-        </is>
-      </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-141.34</t>
+          <t>-117.02</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-110.67</t>
+          <t>-115.08</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1540,46 +1540,46 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>38432997.52080344</t>
+          <t>38409450.62965616</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>26792260.0</t>
+          <t>17601489.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>24442611.2</t>
+          <t>25218403.0</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>27798303.7</t>
+          <t>24916958.1</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>26345925.2</t>
+          <t>26498584.58</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-3355692</t>
+          <t>301444</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-199697.2390819047</t>
+          <t>-237736.9354581767</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>156076.4421134964</t>
+          <t>-446955.2655276731</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>26792260</v>
+        <v>17601489</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-9.24</t>
+          <t>-10.57</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1643,7 +1643,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>62.96</t>
+          <t>63.02</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>12674</t>
+          <t>12822</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1708,22 +1708,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>9.73</t>
+          <t>9.55</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>9.73</t>
+          <t>9.63</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>9.38</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>9.53</t>
+          <t>9.39</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1755,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1866.918</t>
+          <t>2806.058</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>9.73</t>
+          <t>9.53</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1780,17 +1780,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-3.62</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-3.4</t>
+          <t>-3.38</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-17.77</t>
+          <t>-12.07</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-5.53</t>
+          <t>-7.48</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1865,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>8.52</t>
+          <t>12.80</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1886,77 +1886,77 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>1859</t>
+          <t>1561</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>15.38</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>8.89</t>
+          <t>5.13</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-2.45</t>
+          <t>-2.66</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>-3.58</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>9.974</t>
+          <t>9.790000000000001</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>10.21</t>
+          <t>10.15</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
+          <t>10.19</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
           <t>10.2</t>
         </is>
       </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>10.22</t>
-        </is>
-      </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-177.09</t>
+          <t>-141.34</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-106.90</t>
+          <t>-110.67</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1976,46 +1976,46 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>38432997.52080344</t>
+          <t>38409450.62965616</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>18247885.0</t>
+          <t>26792260.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>22369720.8</t>
+          <t>24442611.2</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>27203179.9</t>
+          <t>27798303.7</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>26271252.44</t>
+          <t>26345925.2</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-4833459</t>
+          <t>-3355692</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-264383.362935614</t>
+          <t>-199697.2390819047</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>27250.68723968416</t>
+          <t>156076.4421134964</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>18247885</v>
+        <v>26792260</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-7.33</t>
+          <t>-9.24</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2079,22 +2079,22 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>62.96</t>
+          <t>63.02</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>12674</t>
+          <t>12822</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2144,22 +2144,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>9.77</t>
+          <t>9.73</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>9.95</t>
+          <t>9.73</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>9.73</t>
+          <t>9.53</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-4.1</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3938.682</t>
+          <t>1866.918</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>9.59</t>
+          <t>9.73</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2216,17 +2216,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>-2.42</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-3.4</t>
+          <t>-3.38</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-2.69</t>
+          <t>-17.77</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-6.89</t>
+          <t>-5.53</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2301,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17.97</t>
+          <t>8.52</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-4.07</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2322,52 +2322,52 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>1859</t>
+          <t>1561</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>15.38</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>12.9</t>
+          <t>8.89</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-5.31</t>
+          <t>-2.45</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>10.128</t>
+          <t>9.974</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>10.25</t>
+          <t>10.21</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
@@ -2382,17 +2382,17 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-268.37</t>
+          <t>-177.09</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-103.85</t>
+          <t>-106.90</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2412,46 +2412,46 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>38432997.52080344</t>
+          <t>38409450.62965616</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>38346124.0</t>
+          <t>18247885.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>26631549.8</t>
+          <t>22369720.8</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>27366657.0</t>
+          <t>27203179.9</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>26177335.2</t>
+          <t>26271252.44</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-735107</t>
+          <t>-4833459</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-317407.7356947591</t>
+          <t>-264383.362935614</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>757709.4057328217</t>
+          <t>27250.68723968416</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>38346124</v>
+        <v>18247885</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-8.67</t>
+          <t>-7.33</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2515,22 +2515,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2555,12 +2555,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>62.96</t>
+          <t>63.02</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>12674</t>
+          <t>12822</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2580,22 +2580,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>9.99</t>
+          <t>9.77</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>9.99</t>
+          <t>9.95</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>9.58</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>9.59</t>
+          <t>9.73</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-4.1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2500.445</t>
+          <t>3938.682</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>9.59</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2652,17 +2652,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-6.5</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-3.4</t>
+          <t>-3.38</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-2.43</t>
+          <t>-2.69</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-2.91</t>
+          <t>-6.89</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2737,17 +2737,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11.41</t>
+          <t>17.97</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-1.60</t>
+          <t>-4.07</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2758,57 +2758,57 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>1859</t>
+          <t>1561</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>11.29</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>40.86</t>
+          <t>12.9</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-2.72</t>
+          <t>-5.31</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>10.28</t>
+          <t>10.128</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>10.28</t>
+          <t>10.25</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>10.21</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -2818,17 +2818,17 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-293.77</t>
+          <t>-268.37</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-101.27</t>
+          <t>-103.85</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2848,46 +2848,46 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>38432997.52080344</t>
+          <t>38409450.62965616</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>25104257.0</t>
+          <t>38346124.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>24629573.0</t>
+          <t>26631549.8</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>25242587.5</t>
+          <t>27366657.0</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>25777972.78</t>
+          <t>26177335.2</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-613014</t>
+          <t>-735107</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-512883.5795906829</t>
+          <t>-317407.7356947591</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-379221.9394817278</t>
+          <t>757709.4057328217</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>25104257</v>
+        <v>38346124</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-4.76</t>
+          <t>-8.67</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2951,22 +2951,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2991,12 +2991,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>62.96</t>
+          <t>63.02</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>12674</t>
+          <t>12822</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -3016,22 +3016,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>10.05</t>
+          <t>9.99</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>9.99</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>9.96</t>
+          <t>9.58</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>9.59</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-3.35</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1335.381</t>
+          <t>2500.445</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3088,17 +3088,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-7.56</t>
+          <t>-5.26</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-3.4</t>
+          <t>-3.38</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>-2.43</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-1.94</t>
+          <t>-2.91</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3173,73 +3173,73 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>6.09</t>
+          <t>11.41</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-4.95</t>
+          <t>-1.60</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>1859</t>
+          <t>1561</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>27.42</t>
+          <t>11.29</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>67.74</t>
+          <t>40.86</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-2.04</t>
+          <t>-2.72</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>10.31</t>
+          <t>10.28</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>10.3</t>
+          <t>10.28</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
@@ -3254,19 +3254,19 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-185.15</t>
+          <t>-293.77</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
+          <t>-0.03</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
           <t>-0.01</t>
         </is>
       </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>-0.00</t>
-        </is>
-      </c>
       <c r="AS7" t="inlineStr">
         <is>
           <t>0.54</t>
@@ -3274,7 +3274,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-100.34</t>
+          <t>-101.27</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3284,46 +3284,46 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>38432997.52080344</t>
+          <t>38409450.62965616</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>13722530.0</t>
+          <t>25104257.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>24615513.2</t>
+          <t>24629573.0</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>24233663.8</t>
+          <t>25242587.5</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>25886365.74</t>
+          <t>25777972.78</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>381849</t>
+          <t>-613014</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-537185.6959741293</t>
+          <t>-512883.5795906829</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-571094.4705210179</t>
+          <t>-379221.9394817278</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>13722530</v>
+        <v>25104257</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-3.81</t>
+          <t>-4.76</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3387,12 +3387,12 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
@@ -3402,7 +3402,7 @@
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>62.96</t>
+          <t>63.02</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>12674</t>
+          <t>12822</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3452,22 +3452,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>10.45</t>
+          <t>10.05</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>10.6</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>9.96</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3499,12 +3499,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-3.35</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1569.646</t>
+          <t>1335.381</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>10.45</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3524,17 +3524,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-11.29</t>
+          <t>-6.32</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-3.4</t>
+          <t>-3.38</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>28.41</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>-1.94</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3609,73 +3609,73 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>7.16</t>
+          <t>6.09</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-4.95</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>1859</t>
+          <t>1561</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>83.87</t>
+          <t>27.42</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>81.18</t>
+          <t>67.74</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>-2.04</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>10.276</t>
+          <t>10.31</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>10.31</t>
+          <t>10.3</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
@@ -3690,12 +3690,12 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>1372.99</t>
+          <t>-185.15</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-100.18</t>
+          <t>-100.34</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3720,46 +3720,46 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>38432997.52080344</t>
+          <t>38409450.62965616</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>16427808.0</t>
+          <t>13722530.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>31153996.2</t>
+          <t>24615513.2</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>24262247.7</t>
+          <t>24233663.8</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>26236307.54</t>
+          <t>25886365.74</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>6891748</t>
+          <t>381849</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-531020.4642383313</t>
+          <t>-537185.6959741293</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>394668.8947985992</t>
+          <t>-571094.4705210179</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>16427808</v>
+        <v>13722530</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-3.81</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3823,22 +3823,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>62.96</t>
+          <t>63.02</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>12674</t>
+          <t>12822</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3888,7 +3888,7 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>10.4</t>
+          <t>10.45</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
@@ -3898,12 +3898,12 @@
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>10.3</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>10.45</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3935,12 +3935,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>3754.177</t>
+          <t>1569.646</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>10.5</t>
+          <t>10.45</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3960,17 +3960,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-11.82</t>
+          <t>-10.0</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-3.4</t>
+          <t>-3.38</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>33.22</t>
+          <t>28.41</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17.12</t>
+          <t>7.16</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4066,47 +4066,47 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>1859</t>
+          <t>1561</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>91.94</t>
+          <t>83.87</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>65.05</t>
+          <t>81.18</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>10.236</t>
+          <t>10.276</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
@@ -4116,29 +4116,29 @@
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>10.21</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>10.22</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>73.66</t>
+          <t>1372.99</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
           <t>-0.00</t>
         </is>
       </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>-0.00</t>
-        </is>
-      </c>
       <c r="AS9" t="inlineStr">
         <is>
           <t>0.54</t>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-100.80</t>
+          <t>-100.18</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4156,46 +4156,46 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>38432997.52080344</t>
+          <t>38409450.62965616</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>39557030.0</t>
+          <t>16427808.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>32036639.0</t>
+          <t>31153996.2</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>24048236.4</t>
+          <t>24262247.7</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>26253921.64</t>
+          <t>26236307.54</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>7988402</t>
+          <t>6891748</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-699327.6204268641</t>
+          <t>-531020.4642383313</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>1470384.313298099</t>
+          <t>394668.8947985992</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>39557030</v>
+        <v>16427808</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4259,12 +4259,12 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
@@ -4274,7 +4274,7 @@
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>62.96</t>
+          <t>63.02</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>12674</t>
+          <t>12822</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4329,7 +4329,7 @@
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>10.75</t>
+          <t>10.6</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
@@ -4339,7 +4339,7 @@
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>10.5</t>
+          <t>10.45</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4371,12 +4371,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2725.546</t>
+          <t>3754.177</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>10.35</t>
+          <t>10.5</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4396,17 +4396,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-10.22</t>
+          <t>-10.53</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-3.4</t>
+          <t>-3.38</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>31.50</t>
+          <t>33.22</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4471,7 +4471,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4481,17 +4481,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12.43</t>
+          <t>17.12</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4502,52 +4502,52 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>1859</t>
+          <t>1561</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>67.74</t>
+          <t>91.94</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>34.41</t>
+          <t>65.05</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>10.246</t>
+          <t>10.236</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>10.29</t>
+          <t>10.31</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
@@ -4557,22 +4557,22 @@
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>10.19</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-359.87</t>
+          <t>73.66</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.00</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-0.00</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-100.95</t>
+          <t>-100.80</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4592,46 +4592,46 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>38432997.52080344</t>
+          <t>38409450.62965616</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>28336240.0</t>
+          <t>39557030.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>28101764.2</t>
+          <t>32036639.0</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>21370450.7</t>
+          <t>24048236.4</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>26117511.38</t>
+          <t>26253921.64</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>6731313</t>
+          <t>7988402</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-1093820.699285948</t>
+          <t>-699327.6204268641</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>476475.971393887</t>
+          <t>1470384.313298099</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>28336240</v>
+        <v>39557030</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-1.43</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4695,22 +4695,22 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4735,12 +4735,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>62.96</t>
+          <t>63.02</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>12674</t>
+          <t>12822</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4760,22 +4760,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>10.15</t>
+          <t>10.4</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>10.6</t>
+          <t>10.75</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>10.15</t>
+          <t>10.3</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>10.35</t>
+          <t>10.5</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2459.513</t>
+          <t>2725.546</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>10.15</t>
+          <t>10.35</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4832,17 +4832,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-8.09</t>
+          <t>-8.95</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-3.4</t>
+          <t>-3.38</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>26.88</t>
+          <t>31.50</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4917,17 +4917,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11.22</t>
+          <t>12.43</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-0.56</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4938,47 +4938,47 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>1859</t>
+          <t>1561</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>35.48</t>
+          <t>67.74</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>25.16</t>
+          <t>34.41</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>10.196</t>
+          <t>10.246</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
@@ -4993,22 +4993,22 @@
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>10.18</t>
+          <t>10.19</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-6995.52</t>
+          <t>-359.87</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.00</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-100.10</t>
+          <t>-100.95</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -5028,46 +5028,46 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>38432997.52080344</t>
+          <t>38409450.62965616</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>25033958.0</t>
+          <t>28336240.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>25855602.0</t>
+          <t>28101764.2</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>20377785.6</t>
+          <t>21370450.7</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>25837516.22</t>
+          <t>26117511.38</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>5477816</t>
+          <t>6731313</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-1379329.1848641</t>
+          <t>-1093820.699285948</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>241817.4125523753</t>
+          <t>476475.971393887</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>25033958</v>
+        <v>28336240</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-3.33</t>
+          <t>-1.43</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5171,12 +5171,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>62.96</t>
+          <t>63.02</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>12674</t>
+          <t>12822</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5196,22 +5196,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>10.15</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>10.4</t>
+          <t>10.6</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>9.96</t>
+          <t>10.15</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>10.15</t>
+          <t>10.35</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-3.14</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>4676.474</t>
+          <t>2459.513</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>9.93</t>
+          <t>10.15</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5268,17 +5268,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-5.75</t>
+          <t>-6.84</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-3.4</t>
+          <t>-3.38</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>17.89</t>
+          <t>26.88</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5343,7 +5343,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-3.59</t>
+          <t>-1.46</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5353,12 +5353,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>21.33</t>
+          <t>11.22</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -5374,42 +5374,42 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>1859</t>
+          <t>1561</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>35.48</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>41.11</t>
+          <t>25.16</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-2.61</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
@@ -5419,7 +5419,7 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>10.33</t>
+          <t>10.29</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
@@ -5429,22 +5429,22 @@
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>10.17</t>
+          <t>10.18</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-476.65</t>
+          <t>-6995.52</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.00</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5454,7 +5454,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-98.43</t>
+          <t>-100.10</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5464,46 +5464,46 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>38432997.52080344</t>
+          <t>38409450.62965616</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>46414945.0</t>
+          <t>25033958.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>23851814.4</t>
+          <t>25855602.0</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>20231760.7</t>
+          <t>20377785.6</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>25751255.74</t>
+          <t>25837516.22</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>3620053</t>
+          <t>5477816</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-1674083.111667096</t>
+          <t>-1379329.1848641</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>251770.4923304841</t>
+          <t>241817.4125523753</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>46414945</v>
+        <v>25033958</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-5.43</t>
+          <t>-3.33</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5607,12 +5607,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>62.96</t>
+          <t>63.02</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>12674</t>
+          <t>12822</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5632,22 +5632,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>10.4</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>9.72</t>
+          <t>9.96</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>9.93</t>
+          <t>10.15</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/塑化劑(可塑劑).xlsx
+++ b/Result/checksun_type/塑化劑(可塑劑).xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1560.548</t>
+          <t>1348.47</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-3.38</t>
+          <t>-3.1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-3.14</t>
+          <t>-19.13</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-7.77</t>
+          <t>-5.83</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>7.12</t>
+          <t>6.15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,67 +1014,67 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>1561</t>
+          <t>1348</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>9.91</t>
+          <t>29.25</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>13.05</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-0.50</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-5.00</t>
+          <t>-4.52</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-1.5</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>9.548</t>
+          <t>9.57</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>10.05</t>
+          <t>10.02</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
+          <t>10.18</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
           <t>10.17</t>
         </is>
       </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>10.18</t>
-        </is>
-      </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-87.49</t>
+          <t>-57.55</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-119.31</t>
+          <t>-122.55</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1104,46 +1104,46 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>38409450.62965616</t>
+          <t>38382599.45922747</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>14664845.0</t>
+          <t>13093655.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>23130520.6</t>
+          <t>18080026.8</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>23880046.8</t>
+          <t>22355788.3</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>26473396.54</t>
+          <t>26291263.5</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-749526</t>
+          <t>-4275761</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-367031.5421935803</t>
+          <t>-558392.068295303</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-1078151.8792383</t>
+          <t>-1610874.961854778</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>14664845</v>
+        <v>13093655</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-9.52</t>
+          <t>-7.62</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1207,12 +1207,12 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1247,12 +1247,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>63.02</t>
+          <t>63.27</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>12822</t>
+          <t>13092</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1272,22 +1272,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>9.46</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>9.55</t>
+          <t>9.88</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>9.27</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1319,12 +1319,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1859.149</t>
+          <t>1560.548</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>9.39</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1344,17 +1344,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-3.38</t>
+          <t>-3.1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>-3.14</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-8.83</t>
+          <t>-7.77</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1429,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>8.48</t>
+          <t>7.12</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-2.45</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1450,77 +1450,77 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>1561</t>
+          <t>1348</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.91</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>5.13</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-2.67</t>
+          <t>-0.50</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-4.39</t>
+          <t>-5.00</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>9.648</t>
+          <t>9.548</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>10.09</t>
+          <t>10.05</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
+          <t>10.17</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
           <t>10.18</t>
         </is>
       </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>10.19</t>
-        </is>
-      </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-117.02</t>
+          <t>-87.49</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-115.08</t>
+          <t>-119.31</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1540,46 +1540,46 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>38409450.62965616</t>
+          <t>38382599.45922747</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>17601489.0</t>
+          <t>14664845.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>25218403.0</t>
+          <t>23130520.6</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>24916958.1</t>
+          <t>23880046.8</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>26498584.58</t>
+          <t>26473396.54</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>301444</t>
+          <t>-749526</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-237736.9354581767</t>
+          <t>-367031.5421935803</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-446955.2655276731</t>
+          <t>-1078151.8792383</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>17601489</v>
+        <v>14664845</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-10.57</t>
+          <t>-9.52</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1643,7 +1643,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>63.02</t>
+          <t>63.27</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>12822</t>
+          <t>13092</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1708,22 +1708,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
+          <t>9.46</t>
+        </is>
+      </c>
+      <c r="CE3" t="inlineStr">
+        <is>
           <t>9.55</t>
         </is>
       </c>
-      <c r="CE3" t="inlineStr">
-        <is>
-          <t>9.63</t>
-        </is>
-      </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>9.38</t>
+          <t>9.27</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>9.39</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1755,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2806.058</t>
+          <t>1859.149</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>9.53</t>
+          <t>9.39</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1780,17 +1780,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-3.38</t>
+          <t>-3.1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-12.07</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-7.48</t>
+          <t>-8.83</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1865,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12.80</t>
+          <t>8.48</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-2.45</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1886,12 +1886,12 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>1561</t>
+          <t>1348</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1906,57 +1906,57 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-2.66</t>
+          <t>-2.67</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-3.58</t>
+          <t>-4.39</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>9.790000000000001</t>
+          <t>9.648</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>10.15</t>
+          <t>10.09</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
+          <t>10.18</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
           <t>10.19</t>
         </is>
       </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>10.2</t>
-        </is>
-      </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-141.34</t>
+          <t>-117.02</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-110.67</t>
+          <t>-115.08</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1976,46 +1976,46 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>38409450.62965616</t>
+          <t>38382599.45922747</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>26792260.0</t>
+          <t>17601489.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>24442611.2</t>
+          <t>25218403.0</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>27798303.7</t>
+          <t>24916958.1</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>26345925.2</t>
+          <t>26498584.58</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-3355692</t>
+          <t>301444</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-199697.2390819047</t>
+          <t>-237736.9354581767</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>156076.4421134964</t>
+          <t>-446955.2655276731</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>26792260</v>
+        <v>17601489</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-9.24</t>
+          <t>-10.57</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2079,7 +2079,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2089,12 +2089,12 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>63.02</t>
+          <t>63.27</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>12822</t>
+          <t>13092</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2144,22 +2144,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>9.73</t>
+          <t>9.55</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>9.73</t>
+          <t>9.63</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>9.38</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>9.53</t>
+          <t>9.39</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1866.918</t>
+          <t>2806.058</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>9.73</t>
+          <t>9.53</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2216,17 +2216,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-2.42</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-3.38</t>
+          <t>-3.1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-17.77</t>
+          <t>-12.07</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-5.53</t>
+          <t>-7.48</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2301,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>8.52</t>
+          <t>12.80</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2322,77 +2322,77 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>1561</t>
+          <t>1348</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>15.38</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>8.89</t>
+          <t>5.13</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-2.45</t>
+          <t>-2.66</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>-3.58</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>9.974</t>
+          <t>9.790000000000001</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>10.21</t>
+          <t>10.15</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
+          <t>10.19</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
           <t>10.2</t>
         </is>
       </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>10.22</t>
-        </is>
-      </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-177.09</t>
+          <t>-141.34</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-106.90</t>
+          <t>-110.67</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2412,46 +2412,46 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>38409450.62965616</t>
+          <t>38382599.45922747</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>18247885.0</t>
+          <t>26792260.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>22369720.8</t>
+          <t>24442611.2</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>27203179.9</t>
+          <t>27798303.7</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>26271252.44</t>
+          <t>26345925.2</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-4833459</t>
+          <t>-3355692</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-264383.362935614</t>
+          <t>-199697.2390819047</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>27250.68723968416</t>
+          <t>156076.4421134964</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>18247885</v>
+        <v>26792260</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-7.33</t>
+          <t>-9.24</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2515,22 +2515,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2555,12 +2555,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>63.02</t>
+          <t>63.27</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>12822</t>
+          <t>13092</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2580,22 +2580,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>9.77</t>
+          <t>9.73</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>9.95</t>
+          <t>9.73</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>9.73</t>
+          <t>9.53</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-4.1</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>3938.682</t>
+          <t>1866.918</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>9.59</t>
+          <t>9.73</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2652,17 +2652,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-3.38</t>
+          <t>-3.1</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-2.69</t>
+          <t>-17.77</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-6.89</t>
+          <t>-5.53</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2737,17 +2737,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17.97</t>
+          <t>8.52</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-4.07</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2758,52 +2758,52 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>1561</t>
+          <t>1348</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>15.38</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>12.9</t>
+          <t>8.89</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-5.31</t>
+          <t>-2.45</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>10.128</t>
+          <t>9.974</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>10.25</t>
+          <t>10.21</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
@@ -2818,17 +2818,17 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-268.37</t>
+          <t>-177.09</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-103.85</t>
+          <t>-106.90</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2848,46 +2848,46 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>38409450.62965616</t>
+          <t>38382599.45922747</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>38346124.0</t>
+          <t>18247885.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>26631549.8</t>
+          <t>22369720.8</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>27366657.0</t>
+          <t>27203179.9</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>26177335.2</t>
+          <t>26271252.44</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-735107</t>
+          <t>-4833459</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-317407.7356947591</t>
+          <t>-264383.362935614</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>757709.4057328217</t>
+          <t>27250.68723968416</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>38346124</v>
+        <v>18247885</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-8.67</t>
+          <t>-7.33</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2951,22 +2951,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2991,12 +2991,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>63.02</t>
+          <t>63.27</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>12822</t>
+          <t>13092</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -3016,22 +3016,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>9.99</t>
+          <t>9.77</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>9.99</t>
+          <t>9.95</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>9.58</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>9.59</t>
+          <t>9.73</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-4.1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2500.445</t>
+          <t>3938.682</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>9.59</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3088,17 +3088,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-5.26</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-3.38</t>
+          <t>-3.1</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-2.43</t>
+          <t>-2.69</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-2.91</t>
+          <t>-6.89</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3173,17 +3173,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11.41</t>
+          <t>17.97</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-1.60</t>
+          <t>-4.07</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3194,57 +3194,57 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>1561</t>
+          <t>1348</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>11.29</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>40.86</t>
+          <t>12.9</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-2.72</t>
+          <t>-5.31</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>10.28</t>
+          <t>10.128</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>10.28</t>
+          <t>10.25</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>10.21</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
@@ -3254,17 +3254,17 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-293.77</t>
+          <t>-268.37</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-101.27</t>
+          <t>-103.85</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3284,46 +3284,46 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>38409450.62965616</t>
+          <t>38382599.45922747</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>25104257.0</t>
+          <t>38346124.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>24629573.0</t>
+          <t>26631549.8</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>25242587.5</t>
+          <t>27366657.0</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>25777972.78</t>
+          <t>26177335.2</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-613014</t>
+          <t>-735107</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-512883.5795906829</t>
+          <t>-317407.7356947591</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-379221.9394817278</t>
+          <t>757709.4057328217</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>25104257</v>
+        <v>38346124</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-4.76</t>
+          <t>-8.67</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3387,22 +3387,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>63.02</t>
+          <t>63.27</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>12822</t>
+          <t>13092</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3452,22 +3452,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>10.05</t>
+          <t>9.99</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>9.99</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>9.96</t>
+          <t>9.58</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>9.59</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3499,12 +3499,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-3.35</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1335.381</t>
+          <t>2500.445</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3524,17 +3524,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-6.32</t>
+          <t>-3.09</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-3.38</t>
+          <t>-3.1</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>-2.43</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-1.94</t>
+          <t>-2.91</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3609,73 +3609,73 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>6.09</t>
+          <t>11.41</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-4.95</t>
+          <t>-1.60</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>1561</t>
+          <t>1348</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>27.42</t>
+          <t>11.29</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>67.74</t>
+          <t>40.86</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-2.04</t>
+          <t>-2.72</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>10.31</t>
+          <t>10.28</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>10.3</t>
+          <t>10.28</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
@@ -3690,19 +3690,19 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-185.15</t>
+          <t>-293.77</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
+          <t>-0.03</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
           <t>-0.01</t>
         </is>
       </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>-0.00</t>
-        </is>
-      </c>
       <c r="AS8" t="inlineStr">
         <is>
           <t>0.54</t>
@@ -3710,7 +3710,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-100.34</t>
+          <t>-101.27</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3720,46 +3720,46 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>38409450.62965616</t>
+          <t>38382599.45922747</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>13722530.0</t>
+          <t>25104257.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>24615513.2</t>
+          <t>24629573.0</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>24233663.8</t>
+          <t>25242587.5</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>25886365.74</t>
+          <t>25777972.78</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>381849</t>
+          <t>-613014</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-537185.6959741293</t>
+          <t>-512883.5795906829</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-571094.4705210179</t>
+          <t>-379221.9394817278</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>13722530</v>
+        <v>25104257</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-3.81</t>
+          <t>-4.76</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
@@ -3838,7 +3838,7 @@
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>63.02</t>
+          <t>63.27</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>12822</t>
+          <t>13092</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3888,22 +3888,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>10.45</t>
+          <t>10.05</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>10.6</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>9.96</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3935,12 +3935,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-3.35</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1569.646</t>
+          <t>1335.381</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>10.45</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3960,17 +3960,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-10.0</t>
+          <t>-4.12</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-3.38</t>
+          <t>-3.1</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>28.41</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>-1.94</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4045,73 +4045,73 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>7.16</t>
+          <t>6.09</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-4.95</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>1561</t>
+          <t>1348</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>83.87</t>
+          <t>27.42</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>81.18</t>
+          <t>67.74</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>-2.04</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>10.276</t>
+          <t>10.31</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>10.31</t>
+          <t>10.3</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>1372.99</t>
+          <t>-185.15</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-100.18</t>
+          <t>-100.34</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4156,46 +4156,46 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>38409450.62965616</t>
+          <t>38382599.45922747</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>16427808.0</t>
+          <t>13722530.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>31153996.2</t>
+          <t>24615513.2</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>24262247.7</t>
+          <t>24233663.8</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>26236307.54</t>
+          <t>25886365.74</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>6891748</t>
+          <t>381849</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-531020.4642383313</t>
+          <t>-537185.6959741293</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>394668.8947985992</t>
+          <t>-571094.4705210179</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>16427808</v>
+        <v>13722530</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-3.81</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4259,22 +4259,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>63.02</t>
+          <t>63.27</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>12822</t>
+          <t>13092</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4324,7 +4324,7 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>10.4</t>
+          <t>10.45</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
@@ -4334,12 +4334,12 @@
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>10.3</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>10.45</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4371,12 +4371,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>3754.177</t>
+          <t>1569.646</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>10.5</t>
+          <t>10.45</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4396,17 +4396,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-10.53</t>
+          <t>-7.73</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-3.38</t>
+          <t>-3.1</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>33.22</t>
+          <t>28.41</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4471,7 +4471,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4481,17 +4481,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17.12</t>
+          <t>7.16</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4502,47 +4502,47 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>1561</t>
+          <t>1348</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>91.94</t>
+          <t>83.87</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>65.05</t>
+          <t>81.18</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>10.236</t>
+          <t>10.276</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
@@ -4552,29 +4552,29 @@
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>10.21</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>10.22</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>73.66</t>
+          <t>1372.99</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
           <t>-0.00</t>
         </is>
       </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>-0.00</t>
-        </is>
-      </c>
       <c r="AS10" t="inlineStr">
         <is>
           <t>0.54</t>
@@ -4582,7 +4582,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-100.80</t>
+          <t>-100.18</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4592,46 +4592,46 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>38409450.62965616</t>
+          <t>38382599.45922747</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>39557030.0</t>
+          <t>16427808.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>32036639.0</t>
+          <t>31153996.2</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>24048236.4</t>
+          <t>24262247.7</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>26253921.64</t>
+          <t>26236307.54</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>7988402</t>
+          <t>6891748</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-699327.6204268641</t>
+          <t>-531020.4642383313</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>1470384.313298099</t>
+          <t>394668.8947985992</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>39557030</v>
+        <v>16427808</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
@@ -4710,7 +4710,7 @@
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4735,12 +4735,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>63.02</t>
+          <t>63.27</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>12822</t>
+          <t>13092</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4765,7 +4765,7 @@
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>10.75</t>
+          <t>10.6</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
@@ -4775,7 +4775,7 @@
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>10.5</t>
+          <t>10.45</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2725.546</t>
+          <t>3754.177</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>10.35</t>
+          <t>10.5</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4832,17 +4832,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-8.95</t>
+          <t>-8.25</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-3.38</t>
+          <t>-3.1</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>31.50</t>
+          <t>33.22</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4917,17 +4917,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12.43</t>
+          <t>17.12</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4938,52 +4938,52 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>1561</t>
+          <t>1348</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>67.74</t>
+          <t>91.94</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>34.41</t>
+          <t>65.05</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>10.246</t>
+          <t>10.236</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>10.29</t>
+          <t>10.31</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
@@ -4993,22 +4993,22 @@
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>10.19</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-359.87</t>
+          <t>73.66</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.00</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-0.00</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-100.95</t>
+          <t>-100.80</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -5028,46 +5028,46 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>38409450.62965616</t>
+          <t>38382599.45922747</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>28336240.0</t>
+          <t>39557030.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>28101764.2</t>
+          <t>32036639.0</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>21370450.7</t>
+          <t>24048236.4</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>26117511.38</t>
+          <t>26253921.64</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>6731313</t>
+          <t>7988402</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-1093820.699285948</t>
+          <t>-699327.6204268641</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>476475.971393887</t>
+          <t>1470384.313298099</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>28336240</v>
+        <v>39557030</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-1.43</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5171,12 +5171,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>63.02</t>
+          <t>63.27</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>12822</t>
+          <t>13092</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5196,22 +5196,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>10.15</t>
+          <t>10.4</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>10.6</t>
+          <t>10.75</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>10.15</t>
+          <t>10.3</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>10.35</t>
+          <t>10.5</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2459.513</t>
+          <t>2725.546</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>10.15</t>
+          <t>10.35</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5268,17 +5268,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-6.84</t>
+          <t>-6.7</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-3.38</t>
+          <t>-3.1</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>26.88</t>
+          <t>31.50</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5343,7 +5343,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5353,17 +5353,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11.22</t>
+          <t>12.43</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-0.56</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5374,47 +5374,47 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>1561</t>
+          <t>1348</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>35.48</t>
+          <t>67.74</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>25.16</t>
+          <t>34.41</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>10.196</t>
+          <t>10.246</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
@@ -5429,22 +5429,22 @@
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>10.18</t>
+          <t>10.19</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-6995.52</t>
+          <t>-359.87</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.00</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5454,7 +5454,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-100.10</t>
+          <t>-100.95</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5464,46 +5464,46 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>38409450.62965616</t>
+          <t>38382599.45922747</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>25033958.0</t>
+          <t>28336240.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>25855602.0</t>
+          <t>28101764.2</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>20377785.6</t>
+          <t>21370450.7</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>25837516.22</t>
+          <t>26117511.38</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>5477816</t>
+          <t>6731313</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-1379329.1848641</t>
+          <t>-1093820.699285948</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>241817.4125523753</t>
+          <t>476475.971393887</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>25033958</v>
+        <v>28336240</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-3.33</t>
+          <t>-1.43</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5607,12 +5607,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>63.02</t>
+          <t>63.27</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>12822</t>
+          <t>13092</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5632,22 +5632,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>10.15</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>10.4</t>
+          <t>10.6</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>9.96</t>
+          <t>10.15</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>10.15</t>
+          <t>10.35</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/塑化劑(可塑劑).xlsx
+++ b/Result/checksun_type/塑化劑(可塑劑).xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>9.57</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>10.02</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>10.18</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>10.02</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>10.18</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>13093655.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>18080026.8</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>18080026.8</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>22355788.3</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>26291263.5</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>26291263.5</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>-1610874.961854778</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>13093655</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>13093655.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>9.548</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>10.05</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>10.17</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>10.05</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>10.17</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>14664845.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>23130520.6</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>23130520.6</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>23880046.8</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>26473396.54</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>26473396.54</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>-1078151.8792383</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>14664845</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>14664845.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>9.648</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>10.09</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>10.18</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>10.09</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>10.18</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>17601489.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>25218403.0</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>25218403</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>24916958.1</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>26498584.58</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>26498584.58</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>-446955.2655276731</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>17601489</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>17601489.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>9.790000000000001</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>10.15</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>10.19</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>10.15</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>10.19</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>26792260.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>24442611.2</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>24442611.2</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>27798303.7</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>26345925.2</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>26345925.2</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>156076.4421134964</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>26792260</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>26792260.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>9.974</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>10.21</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>10.2</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>10.21</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>10.2</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>18247885.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>22369720.8</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>22369720.8</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>27203179.9</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>26271252.44</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>26271252.44</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>27250.68723968416</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>18247885</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>18247885.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>10.128</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>10.25</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>10.2</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>10.25</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>10.2</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>38346124.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>26631549.8</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>26631549.8</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>27366657.0</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>26177335.2</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>26177335.2</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>757709.4057328217</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>38346124</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>38346124.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>10.28</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>10.28</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>10.21</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>10.28</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>10.21</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>25104257.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>24629573.0</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>24629573</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>25242587.5</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>25777972.78</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>25777972.78</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>-379221.9394817278</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>25104257</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>25104257.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>10.31</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>10.3</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>10.21</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>10.21</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>13722530.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>24615513.2</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>24615513.2</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>24233663.8</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>25886365.74</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>25886365.74</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>-571094.4705210179</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>13722530</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>13722530.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>10.276</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>10.31</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>10.21</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>10.31</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>10.21</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>16427808.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>31153996.2</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>31153996.2</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>24262247.7</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>26236307.54</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>26236307.54</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>394668.8947985992</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>16427808</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>16427808.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,21 +4927,17 @@
           <t>10.236</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>10.31</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
+      <c r="AM11" t="n">
+        <v>10.31</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="AO11" t="inlineStr">
         <is>
           <t>10.2</t>
         </is>
       </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>10.2</t>
-        </is>
-      </c>
       <c r="AP11" t="inlineStr">
         <is>
           <t>73.66</t>
@@ -5036,20 +4978,16 @@
           <t>39557030.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>32036639.0</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>32036639</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>24048236.4</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>26253921.64</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>26253921.64</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>1470384.313298099</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>39557030</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>39557030.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>10.246</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>10.29</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>10.2</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>10.29</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>10.2</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>28336240.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>28101764.2</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>28101764.2</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>21370450.7</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>26117511.38</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>26117511.38</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>476475.971393887</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>28336240</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>28336240.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>

--- a/Result/checksun_type/塑化劑(可塑劑).xlsx
+++ b/Result/checksun_type/塑化劑(可塑劑).xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1348.47</t>
+          <t>1272.664</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>9.86</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-3.1</t>
+          <t>-3.25</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-19.13</t>
+          <t>-13.84</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-5.83</t>
+          <t>-4.27</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>6.15</t>
+          <t>5.80</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,51 +1014,51 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>1348</t>
+          <t>1273</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>29.25</t>
+          <t>66.2</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>13.05</t>
+          <t>35.12</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-4.52</t>
+          <t>-4.05</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-1.5</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>9.57</t>
+          <t>9.596</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>10.02</v>
+        <v>10</v>
       </c>
       <c r="AN2" t="n">
         <v>10.18</v>
@@ -1070,17 +1070,17 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-57.55</t>
+          <t>-31.61</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-122.55</t>
+          <t>-124.49</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>38382599.45922747</t>
+          <t>38354560.67142858</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>13093655.0</t>
+          <t>12503632.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>18080026.8</v>
+        <v>16931176.2</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>22355788.3</t>
+          <t>19650448.5</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>26291263.5</v>
+        <v>26328965.82</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-4275761</t>
+          <t>-2719272</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-558392.068295303</t>
+          <t>-778294.9763483247</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-1610874.961854778</t>
+          <t>-1987760.970639944</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>13093655.0</t>
+          <t>12503632.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-7.62</t>
+          <t>-6.10</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1211,12 +1211,12 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>63.27</t>
+          <t>63.19</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>13092</t>
+          <t>13308</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>9.76</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>9.88</t>
+          <t>9.92</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>9.73</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>9.86</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1560.548</t>
+          <t>1348.47</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-3.1</t>
+          <t>-3.25</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-3.14</t>
+          <t>-19.13</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-7.77</t>
+          <t>-5.83</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>7.12</t>
+          <t>6.15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,63 +1444,63 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>1348</t>
+          <t>1273</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>9.91</t>
+          <t>29.25</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>13.05</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-0.50</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-5.00</t>
+          <t>-4.52</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-1.5</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>9.548</t>
+          <t>9.57</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>10.05</v>
+        <v>10.02</v>
       </c>
       <c r="AN3" t="n">
-        <v>10.17</v>
+        <v>10.18</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>10.18</t>
+          <t>10.17</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-87.49</t>
+          <t>-57.55</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
@@ -1510,7 +1510,7 @@
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-119.31</t>
+          <t>-122.55</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>38382599.45922747</t>
+          <t>38354560.67142858</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>14664845.0</t>
+          <t>13093655.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>23130520.6</v>
+        <v>18080026.8</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>23880046.8</t>
+          <t>22355788.3</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>26473396.54</v>
+        <v>26291263.5</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-749526</t>
+          <t>-4275761</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-367031.5421935803</t>
+          <t>-558392.068295303</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-1078151.8792383</t>
+          <t>-1610874.961854778</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>14664845.0</t>
+          <t>13093655.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-9.52</t>
+          <t>-7.62</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,12 +1631,12 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
@@ -1646,7 +1646,7 @@
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>63.27</t>
+          <t>63.19</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>13092</t>
+          <t>13308</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>9.46</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>9.55</t>
+          <t>9.88</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>9.27</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1859.149</t>
+          <t>1560.548</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>9.39</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>3.65</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-3.1</t>
+          <t>-3.25</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>-3.14</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-8.83</t>
+          <t>-7.77</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>8.48</t>
+          <t>7.12</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-2.45</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,73 +1874,73 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>1348</t>
+          <t>1273</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.91</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>5.13</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-2.67</t>
+          <t>-0.50</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-4.39</t>
+          <t>-5.00</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>9.648</t>
+          <t>9.548</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>10.09</v>
+        <v>10.05</v>
       </c>
       <c r="AN4" t="n">
-        <v>10.18</v>
+        <v>10.17</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>10.19</t>
+          <t>10.18</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-117.02</t>
+          <t>-87.49</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-115.08</t>
+          <t>-119.31</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>38382599.45922747</t>
+          <t>38354560.67142858</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>17601489.0</t>
+          <t>14664845.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>25218403</v>
+        <v>23130520.6</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>24916958.1</t>
+          <t>23880046.8</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>26498584.58</v>
+        <v>26473396.54</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>301444</t>
+          <t>-749526</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-237736.9354581767</t>
+          <t>-367031.5421935803</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-446955.2655276731</t>
+          <t>-1078151.8792383</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>17601489.0</t>
+          <t>14664845.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-10.57</t>
+          <t>-9.52</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2071,12 +2071,12 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>63.27</t>
+          <t>63.19</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>13092</t>
+          <t>13308</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
+          <t>9.46</t>
+        </is>
+      </c>
+      <c r="CE4" t="inlineStr">
+        <is>
           <t>9.55</t>
         </is>
       </c>
-      <c r="CE4" t="inlineStr">
-        <is>
-          <t>9.63</t>
-        </is>
-      </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>9.38</t>
+          <t>9.27</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>9.39</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2806.058</t>
+          <t>1859.149</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>9.53</t>
+          <t>9.39</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>4.77</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-3.1</t>
+          <t>-3.25</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-12.07</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-7.48</t>
+          <t>-8.83</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12.80</t>
+          <t>8.48</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-2.45</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,12 +2304,12 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>1348</t>
+          <t>1273</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2324,53 +2324,53 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-2.66</t>
+          <t>-2.67</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-3.58</t>
+          <t>-4.39</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>9.790000000000001</t>
+          <t>9.648</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>10.15</v>
+        <v>10.09</v>
       </c>
       <c r="AN5" t="n">
-        <v>10.19</v>
+        <v>10.18</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>10.19</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-141.34</t>
+          <t>-117.02</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-110.67</t>
+          <t>-115.08</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>38382599.45922747</t>
+          <t>38354560.67142858</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>26792260.0</t>
+          <t>17601489.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>24442611.2</v>
+        <v>25218403</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>27798303.7</t>
+          <t>24916958.1</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>26345925.2</v>
+        <v>26498584.58</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-3355692</t>
+          <t>301444</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-199697.2390819047</t>
+          <t>-237736.9354581767</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>156076.4421134964</t>
+          <t>-446955.2655276731</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>26792260.0</t>
+          <t>17601489.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-9.24</t>
+          <t>-10.57</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2501,12 +2501,12 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>63.27</t>
+          <t>63.19</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>13092</t>
+          <t>13308</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>9.73</t>
+          <t>9.55</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>9.73</t>
+          <t>9.63</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>9.38</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>9.53</t>
+          <t>9.39</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2593,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1866.918</t>
+          <t>2806.058</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>9.73</t>
+          <t>9.53</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>3.35</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-3.1</t>
+          <t>-3.25</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-17.77</t>
+          <t>-12.07</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-5.53</t>
+          <t>-7.48</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>8.52</t>
+          <t>12.80</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,73 +2734,73 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>1348</t>
+          <t>1273</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>15.38</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>8.89</t>
+          <t>5.13</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-2.45</t>
+          <t>-2.66</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>-3.58</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>9.974</t>
+          <t>9.790000000000001</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>10.21</v>
+        <v>10.15</v>
       </c>
       <c r="AN6" t="n">
-        <v>10.2</v>
+        <v>10.19</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>10.22</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-177.09</t>
+          <t>-141.34</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-106.90</t>
+          <t>-110.67</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>38382599.45922747</t>
+          <t>38354560.67142858</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>18247885.0</t>
+          <t>26792260.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>22369720.8</v>
+        <v>24442611.2</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>27203179.9</t>
+          <t>27798303.7</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>26271252.44</v>
+        <v>26345925.2</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-4833459</t>
+          <t>-3355692</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-264383.362935614</t>
+          <t>-199697.2390819047</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>27250.68723968416</t>
+          <t>156076.4421134964</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>18247885.0</t>
+          <t>26792260.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-7.33</t>
+          <t>-9.24</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,22 +2921,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>63.27</t>
+          <t>63.19</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>13092</t>
+          <t>13308</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>9.77</t>
+          <t>9.73</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>9.95</t>
+          <t>9.73</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>9.73</t>
+          <t>9.53</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-4.1</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>3938.682</t>
+          <t>1866.918</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>9.59</t>
+          <t>9.73</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-3.1</t>
+          <t>-3.25</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-2.69</t>
+          <t>-17.77</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-6.89</t>
+          <t>-5.53</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17.97</t>
+          <t>8.52</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-4.07</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,51 +3164,51 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>1348</t>
+          <t>1273</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>15.38</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>12.9</t>
+          <t>8.89</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-5.31</t>
+          <t>-2.45</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>10.128</t>
+          <t>9.974</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>10.25</v>
+        <v>10.21</v>
       </c>
       <c r="AN7" t="n">
         <v>10.2</v>
@@ -3220,17 +3220,17 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-268.37</t>
+          <t>-177.09</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-103.85</t>
+          <t>-106.90</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>38382599.45922747</t>
+          <t>38354560.67142858</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>38346124.0</t>
+          <t>18247885.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>26631549.8</v>
+        <v>22369720.8</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>27366657.0</t>
+          <t>27203179.9</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>26177335.2</v>
+        <v>26271252.44</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-735107</t>
+          <t>-4833459</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-317407.7356947591</t>
+          <t>-264383.362935614</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>757709.4057328217</t>
+          <t>27250.68723968416</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>38346124.0</t>
+          <t>18247885.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-8.67</t>
+          <t>-7.33</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,22 +3351,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>63.27</t>
+          <t>63.19</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>13092</t>
+          <t>13308</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>9.99</t>
+          <t>9.77</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>9.99</t>
+          <t>9.95</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>9.58</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>9.59</t>
+          <t>9.73</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-4.1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2500.445</t>
+          <t>3938.682</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>9.59</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-3.09</t>
+          <t>2.74</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-3.1</t>
+          <t>-3.25</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-2.43</t>
+          <t>-2.69</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-2.91</t>
+          <t>-6.89</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11.41</t>
+          <t>17.97</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-1.60</t>
+          <t>-4.07</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,54 +3594,54 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>1348</t>
+          <t>1273</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>11.29</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>40.86</t>
+          <t>12.9</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-2.72</t>
+          <t>-5.31</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>10.28</t>
+          <t>10.128</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>10.28</v>
+        <v>10.25</v>
       </c>
       <c r="AN8" t="n">
-        <v>10.21</v>
+        <v>10.2</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3650,17 +3650,17 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-293.77</t>
+          <t>-268.37</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-101.27</t>
+          <t>-103.85</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>38382599.45922747</t>
+          <t>38354560.67142858</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>25104257.0</t>
+          <t>38346124.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>24629573</v>
+        <v>26631549.8</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>25242587.5</t>
+          <t>27366657.0</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>25777972.78</v>
+        <v>26177335.2</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-613014</t>
+          <t>-735107</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-512883.5795906829</t>
+          <t>-317407.7356947591</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-379221.9394817278</t>
+          <t>757709.4057328217</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>25104257.0</t>
+          <t>38346124.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-4.76</t>
+          <t>-8.67</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,22 +3781,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>63.27</t>
+          <t>63.19</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>13092</t>
+          <t>13308</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>10.05</t>
+          <t>9.99</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>9.99</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>9.96</t>
+          <t>9.58</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>9.59</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-3.35</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1335.381</t>
+          <t>2500.445</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-4.12</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-3.1</t>
+          <t>-3.25</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>-2.43</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-1.94</t>
+          <t>-2.91</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,72 +4003,72 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>6.09</t>
+          <t>11.41</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-4.95</t>
+          <t>-1.60</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>1348</t>
+          <t>1273</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>27.42</t>
+          <t>11.29</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>67.74</t>
+          <t>40.86</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-2.04</t>
+          <t>-2.72</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>10.31</t>
+          <t>10.28</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>10.3</v>
+        <v>10.28</v>
       </c>
       <c r="AN9" t="n">
         <v>10.21</v>
@@ -4080,19 +4080,19 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-185.15</t>
+          <t>-293.77</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
+          <t>-0.03</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
           <t>-0.01</t>
         </is>
       </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>-0.00</t>
-        </is>
-      </c>
       <c r="AS9" t="inlineStr">
         <is>
           <t>0.54</t>
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-100.34</t>
+          <t>-101.27</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>38382599.45922747</t>
+          <t>38354560.67142858</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>13722530.0</t>
+          <t>25104257.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>24615513.2</v>
+        <v>24629573</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>24233663.8</t>
+          <t>25242587.5</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>25886365.74</v>
+        <v>25777972.78</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>381849</t>
+          <t>-613014</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-537185.6959741293</t>
+          <t>-512883.5795906829</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-571094.4705210179</t>
+          <t>-379221.9394817278</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>13722530.0</t>
+          <t>25104257.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-3.81</t>
+          <t>-4.76</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,12 +4211,12 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
@@ -4226,7 +4226,7 @@
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>63.27</t>
+          <t>63.19</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>13092</t>
+          <t>13308</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>10.45</t>
+          <t>10.05</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>10.6</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>9.96</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4313,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>【b】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-3.35</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1569.646</t>
+          <t>1335.381</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>10.45</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-7.73</t>
+          <t>-2.43</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-3.1</t>
+          <t>-3.25</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>28.41</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>-1.94</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,72 +4433,72 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>7.16</t>
+          <t>6.09</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-4.95</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>1348</t>
+          <t>1273</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>83.87</t>
+          <t>27.42</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>81.18</t>
+          <t>67.74</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>-2.04</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>10.276</t>
+          <t>10.31</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>10.31</v>
+        <v>10.3</v>
       </c>
       <c r="AN10" t="n">
         <v>10.21</v>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>1372.99</t>
+          <t>-185.15</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-100.18</t>
+          <t>-100.34</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>38382599.45922747</t>
+          <t>38354560.67142858</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>16427808.0</t>
+          <t>13722530.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>31153996.2</v>
+        <v>24615513.2</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>24262247.7</t>
+          <t>24233663.8</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>26236307.54</v>
+        <v>25886365.74</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>6891748</t>
+          <t>381849</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-531020.4642383313</t>
+          <t>-537185.6959741293</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>394668.8947985992</t>
+          <t>-571094.4705210179</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>16427808.0</t>
+          <t>13722530.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-3.81</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>63.27</t>
+          <t>63.19</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>13092</t>
+          <t>13308</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,7 +4706,7 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>10.4</t>
+          <t>10.45</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
@@ -4716,12 +4716,12 @@
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>10.3</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>10.45</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>3754.177</t>
+          <t>1569.646</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>10.5</t>
+          <t>10.45</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-8.25</t>
+          <t>-5.98</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-3.1</t>
+          <t>-3.25</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>33.22</t>
+          <t>28.41</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17.12</t>
+          <t>7.16</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,75 +4884,75 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>1348</t>
+          <t>1273</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>91.94</t>
+          <t>83.87</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>65.05</t>
+          <t>81.18</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>10.236</t>
+          <t>10.276</t>
         </is>
       </c>
       <c r="AM11" t="n">
         <v>10.31</v>
       </c>
       <c r="AN11" t="n">
-        <v>10.2</v>
+        <v>10.21</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>10.22</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>73.66</t>
+          <t>1372.99</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
           <t>-0.00</t>
         </is>
       </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>-0.00</t>
-        </is>
-      </c>
       <c r="AS11" t="inlineStr">
         <is>
           <t>0.54</t>
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-100.80</t>
+          <t>-100.18</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>38382599.45922747</t>
+          <t>38354560.67142858</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>39557030.0</t>
+          <t>16427808.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>32036639</v>
+        <v>31153996.2</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>24048236.4</t>
+          <t>24262247.7</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>26253921.64</v>
+        <v>26236307.54</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>7988402</t>
+          <t>6891748</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-699327.6204268641</t>
+          <t>-531020.4642383313</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>1470384.313298099</t>
+          <t>394668.8947985992</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>39557030.0</t>
+          <t>16427808.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>63.27</t>
+          <t>63.19</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>13092</t>
+          <t>13308</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>10.75</t>
+          <t>10.6</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>10.5</t>
+          <t>10.45</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5173,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2725.546</t>
+          <t>3754.177</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>10.35</t>
+          <t>10.5</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-6.7</t>
+          <t>-6.49</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-3.1</t>
+          <t>-3.25</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>31.50</t>
+          <t>33.22</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12.43</t>
+          <t>17.12</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,73 +5314,73 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>1348</t>
+          <t>1273</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>67.74</t>
+          <t>91.94</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>34.41</t>
+          <t>65.05</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>10.246</t>
+          <t>10.236</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>10.29</v>
+        <v>10.31</v>
       </c>
       <c r="AN12" t="n">
         <v>10.2</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>10.19</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-359.87</t>
+          <t>73.66</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.00</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-0.00</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-100.95</t>
+          <t>-100.80</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>38382599.45922747</t>
+          <t>38354560.67142858</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>28336240.0</t>
+          <t>39557030.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>28101764.2</v>
+        <v>32036639</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>21370450.7</t>
+          <t>24048236.4</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>26117511.38</v>
+        <v>26253921.64</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>6731313</t>
+          <t>7988402</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-1093820.699285948</t>
+          <t>-699327.6204268641</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>476475.971393887</t>
+          <t>1470384.313298099</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>28336240.0</t>
+          <t>39557030.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-1.43</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>63.27</t>
+          <t>63.19</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>13092</t>
+          <t>13308</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>10.15</t>
+          <t>10.4</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>10.6</t>
+          <t>10.75</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>10.15</t>
+          <t>10.3</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>10.35</t>
+          <t>10.5</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/塑化劑(可塑劑).xlsx
+++ b/Result/checksun_type/塑化劑(可塑劑).xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>4.95</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1272.664</t>
+          <t>4353.738</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>9.86</t>
+          <t>10.35</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-3.25</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-13.84</t>
+          <t>-8.98</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-4.27</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>5.80</t>
+          <t>19.86</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>4.65</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,68 +1014,68 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>1273</t>
+          <t>4354</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>66.2</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>35.12</t>
+          <t>65.15</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>6.05</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-4.05</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>9.596</t>
+          <t>9.76</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>10</v>
+        <v>10.01</v>
       </c>
       <c r="AN2" t="n">
-        <v>10.18</v>
+        <v>10.19</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>10.17</t>
+          <t>10.18</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-31.61</t>
+          <t>8.30</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
@@ -1090,53 +1090,53 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-124.49</t>
+          <t>-123.99</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>2025/11/13</t>
+          <t>2025/11/28</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>38354560.67142858</t>
+          <t>38394436.85092725</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>12503632.0</t>
+          <t>44205175.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>16931176.2</v>
+        <v>20413759.2</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>19650448.5</t>
+          <t>22428185.2</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>26328965.82</v>
+        <v>27064322.42</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-2719272</t>
+          <t>-2014426</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-778294.9763483247</t>
+          <t>-631522.122682977</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-1987760.970639944</t>
+          <t>175728.5724764355</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>12503632.0</t>
+          <t>44205175.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-6.10</t>
+          <t>-1.43</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,22 +1201,22 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>63.19</t>
+          <t>63.18</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>13308</t>
+          <t>13969</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>9.76</t>
+          <t>9.89</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>9.92</t>
+          <t>10.35</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>9.73</t>
+          <t>9.89</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>9.86</t>
+          <t>10.35</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1348.47</t>
+          <t>1272.664</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>9.86</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>4.73</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-3.25</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-19.13</t>
+          <t>-13.84</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1358,7 +1358,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-5.83</t>
+          <t>-4.27</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>6.15</t>
+          <t>5.80</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,51 +1444,51 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>1273</t>
+          <t>4354</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>29.25</t>
+          <t>66.2</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>13.05</t>
+          <t>35.12</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-4.52</t>
+          <t>-4.05</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-1.5</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>9.57</t>
+          <t>9.596</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>10.02</v>
+        <v>10</v>
       </c>
       <c r="AN3" t="n">
         <v>10.18</v>
@@ -1500,17 +1500,17 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-57.55</t>
+          <t>-31.61</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,53 +1520,53 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-122.55</t>
+          <t>-124.49</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>2025/11/13</t>
+          <t>2025/11/28</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>38354560.67142858</t>
+          <t>38394436.85092725</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>13093655.0</t>
+          <t>12503632.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>18080026.8</v>
+        <v>16931176.2</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>22355788.3</t>
+          <t>19650448.5</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>26291263.5</v>
+        <v>26328965.82</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-4275761</t>
+          <t>-2719272</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-558392.068295303</t>
+          <t>-778294.9763483247</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-1610874.961854778</t>
+          <t>-1987760.970639944</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>13093655.0</t>
+          <t>12503632.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-7.62</t>
+          <t>-6.10</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1641,12 +1641,12 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>63.19</t>
+          <t>63.18</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>13308</t>
+          <t>13969</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>9.76</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>9.88</t>
+          <t>9.92</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>9.73</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>9.86</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1560.548</t>
+          <t>1348.47</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>3.65</t>
+          <t>6.28</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-3.25</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-3.14</t>
+          <t>-19.13</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1788,7 +1788,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-7.77</t>
+          <t>-5.83</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>7.12</t>
+          <t>6.15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,63 +1874,63 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>1273</t>
+          <t>4354</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>9.91</t>
+          <t>29.25</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>13.05</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-0.50</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-5.00</t>
+          <t>-4.52</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-1.5</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>9.548</t>
+          <t>9.57</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>10.05</v>
+        <v>10.02</v>
       </c>
       <c r="AN4" t="n">
-        <v>10.17</v>
+        <v>10.18</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>10.18</t>
+          <t>10.17</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-87.49</t>
+          <t>-57.55</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
@@ -1940,7 +1940,7 @@
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,53 +1950,53 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-119.31</t>
+          <t>-122.55</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>2025/11/13</t>
+          <t>2025/11/28</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>38354560.67142858</t>
+          <t>38394436.85092725</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>14664845.0</t>
+          <t>13093655.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>23130520.6</v>
+        <v>18080026.8</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>23880046.8</t>
+          <t>22355788.3</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>26473396.54</v>
+        <v>26291263.5</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-749526</t>
+          <t>-4275761</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-367031.5421935803</t>
+          <t>-558392.068295303</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-1078151.8792383</t>
+          <t>-1610874.961854778</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>14664845.0</t>
+          <t>13093655.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-9.52</t>
+          <t>-7.62</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
@@ -2076,7 +2076,7 @@
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>63.19</t>
+          <t>63.18</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>13308</t>
+          <t>13969</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>9.46</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>9.55</t>
+          <t>9.88</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>9.27</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1859.149</t>
+          <t>1560.548</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>9.39</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>4.77</t>
+          <t>8.21</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-3.25</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>-3.14</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2218,7 +2218,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-8.83</t>
+          <t>-7.77</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>8.48</t>
+          <t>7.12</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-2.45</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,73 +2304,73 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>1273</t>
+          <t>4354</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.91</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>5.13</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-2.67</t>
+          <t>-0.50</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-4.39</t>
+          <t>-5.00</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>9.648</t>
+          <t>9.548</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>10.09</v>
+        <v>10.05</v>
       </c>
       <c r="AN5" t="n">
-        <v>10.18</v>
+        <v>10.17</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>10.19</t>
+          <t>10.18</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-117.02</t>
+          <t>-87.49</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,53 +2380,53 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-115.08</t>
+          <t>-119.31</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>2025/11/13</t>
+          <t>2025/11/28</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>38354560.67142858</t>
+          <t>38394436.85092725</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>17601489.0</t>
+          <t>14664845.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>25218403</v>
+        <v>23130520.6</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>24916958.1</t>
+          <t>23880046.8</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>26498584.58</v>
+        <v>26473396.54</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>301444</t>
+          <t>-749526</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-237736.9354581767</t>
+          <t>-367031.5421935803</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-446955.2655276731</t>
+          <t>-1078151.8792383</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>17601489.0</t>
+          <t>14664845.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-10.57</t>
+          <t>-9.52</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2501,12 +2501,12 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>63.19</t>
+          <t>63.18</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>13308</t>
+          <t>13969</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
+          <t>9.46</t>
+        </is>
+      </c>
+      <c r="CE5" t="inlineStr">
+        <is>
           <t>9.55</t>
         </is>
       </c>
-      <c r="CE5" t="inlineStr">
-        <is>
-          <t>9.63</t>
-        </is>
-      </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>9.38</t>
+          <t>9.27</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>9.39</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2806.058</t>
+          <t>1859.149</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>9.53</t>
+          <t>9.39</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>3.35</t>
+          <t>9.28</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-3.25</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-12.07</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2648,7 +2648,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-7.48</t>
+          <t>-8.83</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12.80</t>
+          <t>8.48</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-2.45</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,12 +2734,12 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>1273</t>
+          <t>4354</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2754,53 +2754,53 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-2.66</t>
+          <t>-2.67</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-3.58</t>
+          <t>-4.39</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>9.790000000000001</t>
+          <t>9.648</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>10.15</v>
+        <v>10.09</v>
       </c>
       <c r="AN6" t="n">
-        <v>10.19</v>
+        <v>10.18</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>10.19</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-141.34</t>
+          <t>-117.02</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,53 +2810,53 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-110.67</t>
+          <t>-115.08</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>2025/11/13</t>
+          <t>2025/11/28</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>38354560.67142858</t>
+          <t>38394436.85092725</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>26792260.0</t>
+          <t>17601489.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>24442611.2</v>
+        <v>25218403</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>27798303.7</t>
+          <t>24916958.1</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>26345925.2</v>
+        <v>26498584.58</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-3355692</t>
+          <t>301444</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-199697.2390819047</t>
+          <t>-237736.9354581767</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>156076.4421134964</t>
+          <t>-446955.2655276731</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>26792260.0</t>
+          <t>17601489.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-9.24</t>
+          <t>-10.57</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2931,12 +2931,12 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>63.19</t>
+          <t>63.18</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>13308</t>
+          <t>13969</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>9.73</t>
+          <t>9.55</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>9.73</t>
+          <t>9.63</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>9.38</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>9.53</t>
+          <t>9.39</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3023,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1866.918</t>
+          <t>2806.058</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>9.73</t>
+          <t>9.53</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>7.92</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-3.25</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-17.77</t>
+          <t>-12.07</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-5.53</t>
+          <t>-7.48</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>8.52</t>
+          <t>12.80</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,73 +3164,73 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>1273</t>
+          <t>4354</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>15.38</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>8.89</t>
+          <t>5.13</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-2.45</t>
+          <t>-2.66</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>-3.58</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>9.974</t>
+          <t>9.790000000000001</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>10.21</v>
+        <v>10.15</v>
       </c>
       <c r="AN7" t="n">
-        <v>10.2</v>
+        <v>10.19</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>10.22</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-177.09</t>
+          <t>-141.34</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,53 +3240,53 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-106.90</t>
+          <t>-110.67</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>2025/11/13</t>
+          <t>2025/11/28</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>38354560.67142858</t>
+          <t>38394436.85092725</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>18247885.0</t>
+          <t>26792260.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>22369720.8</v>
+        <v>24442611.2</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>27203179.9</t>
+          <t>27798303.7</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>26271252.44</v>
+        <v>26345925.2</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-4833459</t>
+          <t>-3355692</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-264383.362935614</t>
+          <t>-199697.2390819047</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>27250.68723968416</t>
+          <t>156076.4421134964</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>18247885.0</t>
+          <t>26792260.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-7.33</t>
+          <t>-9.24</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,22 +3351,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>63.19</t>
+          <t>63.18</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>13308</t>
+          <t>13969</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>9.77</t>
+          <t>9.73</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>9.95</t>
+          <t>9.73</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>9.73</t>
+          <t>9.53</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-4.1</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>3938.682</t>
+          <t>1866.918</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>9.59</t>
+          <t>9.73</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2.74</t>
+          <t>5.99</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-3.25</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-2.69</t>
+          <t>-17.77</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-6.89</t>
+          <t>-5.53</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17.97</t>
+          <t>8.52</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-4.07</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,51 +3594,51 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>1273</t>
+          <t>4354</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>15.38</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>12.9</t>
+          <t>8.89</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-5.31</t>
+          <t>-2.45</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>10.128</t>
+          <t>9.974</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>10.25</v>
+        <v>10.21</v>
       </c>
       <c r="AN8" t="n">
         <v>10.2</v>
@@ -3650,17 +3650,17 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-268.37</t>
+          <t>-177.09</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,53 +3670,53 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-103.85</t>
+          <t>-106.90</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>2025/11/13</t>
+          <t>2025/11/28</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>38354560.67142858</t>
+          <t>38394436.85092725</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>38346124.0</t>
+          <t>18247885.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>26631549.8</v>
+        <v>22369720.8</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>27366657.0</t>
+          <t>27203179.9</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>26177335.2</v>
+        <v>26271252.44</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-735107</t>
+          <t>-4833459</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-317407.7356947591</t>
+          <t>-264383.362935614</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>757709.4057328217</t>
+          <t>27250.68723968416</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>38346124.0</t>
+          <t>18247885.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-8.67</t>
+          <t>-7.33</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,22 +3781,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>63.19</t>
+          <t>63.18</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>13308</t>
+          <t>13969</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>9.99</t>
+          <t>9.77</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>9.99</t>
+          <t>9.95</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>9.58</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>9.59</t>
+          <t>9.73</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-4.1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2500.445</t>
+          <t>3938.682</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>9.59</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>7.34</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-3.25</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-2.43</t>
+          <t>-2.69</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3938,7 +3938,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-2.91</t>
+          <t>-6.89</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11.41</t>
+          <t>17.97</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-1.60</t>
+          <t>-4.07</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,54 +4024,54 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>1273</t>
+          <t>4354</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>11.29</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>40.86</t>
+          <t>12.9</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-2.72</t>
+          <t>-5.31</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>10.28</t>
+          <t>10.128</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>10.28</v>
+        <v>10.25</v>
       </c>
       <c r="AN9" t="n">
-        <v>10.21</v>
+        <v>10.2</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4080,17 +4080,17 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-293.77</t>
+          <t>-268.37</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,53 +4100,53 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-101.27</t>
+          <t>-103.85</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>2025/11/13</t>
+          <t>2025/11/28</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>38354560.67142858</t>
+          <t>38394436.85092725</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>25104257.0</t>
+          <t>38346124.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>24629573</v>
+        <v>26631549.8</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>25242587.5</t>
+          <t>27366657.0</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>25777972.78</v>
+        <v>26177335.2</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-613014</t>
+          <t>-735107</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-512883.5795906829</t>
+          <t>-317407.7356947591</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-379221.9394817278</t>
+          <t>757709.4057328217</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>25104257.0</t>
+          <t>38346124.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-4.76</t>
+          <t>-8.67</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,22 +4211,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>63.19</t>
+          <t>63.18</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>13308</t>
+          <t>13969</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>10.05</t>
+          <t>9.99</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>9.99</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>9.96</t>
+          <t>9.58</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>9.59</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-3.35</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1335.381</t>
+          <t>2500.445</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,19 +4348,19 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
+          <t>3.38</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>-1.64</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>-2.43</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>-3.25</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>1.58</t>
-        </is>
-      </c>
       <c r="K10" t="inlineStr">
         <is>
           <t>0</t>
@@ -4368,7 +4368,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-1.94</t>
+          <t>-2.91</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,72 +4433,72 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>6.09</t>
+          <t>11.41</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-4.95</t>
+          <t>-1.60</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>1273</t>
+          <t>4354</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>27.42</t>
+          <t>11.29</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>67.74</t>
+          <t>40.86</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-2.04</t>
+          <t>-2.72</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>10.31</t>
+          <t>10.28</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>10.3</v>
+        <v>10.28</v>
       </c>
       <c r="AN10" t="n">
         <v>10.21</v>
@@ -4510,19 +4510,19 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-185.15</t>
+          <t>-293.77</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
+          <t>-0.03</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
           <t>-0.01</t>
         </is>
       </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>-0.00</t>
-        </is>
-      </c>
       <c r="AS10" t="inlineStr">
         <is>
           <t>0.54</t>
@@ -4530,53 +4530,53 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-100.34</t>
+          <t>-101.27</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>2025/11/13</t>
+          <t>2025/11/28</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>38354560.67142858</t>
+          <t>38394436.85092725</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>13722530.0</t>
+          <t>25104257.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>24615513.2</v>
+        <v>24629573</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>24233663.8</t>
+          <t>25242587.5</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>25886365.74</v>
+        <v>25777972.78</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>381849</t>
+          <t>-613014</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-537185.6959741293</t>
+          <t>-512883.5795906829</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-571094.4705210179</t>
+          <t>-379221.9394817278</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>13722530.0</t>
+          <t>25104257.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-3.81</t>
+          <t>-4.76</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,12 +4641,12 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
@@ -4656,7 +4656,7 @@
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>63.19</t>
+          <t>63.18</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>13308</t>
+          <t>13969</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>10.45</t>
+          <t>10.05</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>10.6</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>9.96</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4743,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>【b】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-3.35</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1569.646</t>
+          <t>1335.381</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>10.45</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-5.98</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-3.25</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>28.41</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4798,7 +4798,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>-1.94</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,72 +4863,72 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>7.16</t>
+          <t>6.09</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-4.95</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>1273</t>
+          <t>4354</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>83.87</t>
+          <t>27.42</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>81.18</t>
+          <t>67.74</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>-2.04</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>10.276</t>
+          <t>10.31</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>10.31</v>
+        <v>10.3</v>
       </c>
       <c r="AN11" t="n">
         <v>10.21</v>
@@ -4940,12 +4940,12 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>1372.99</t>
+          <t>-185.15</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
@@ -4960,53 +4960,53 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-100.18</t>
+          <t>-100.34</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>2025/11/13</t>
+          <t>2025/11/28</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>38354560.67142858</t>
+          <t>38394436.85092725</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>16427808.0</t>
+          <t>13722530.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>31153996.2</v>
+        <v>24615513.2</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>24262247.7</t>
+          <t>24233663.8</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>26236307.54</v>
+        <v>25886365.74</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>6891748</t>
+          <t>381849</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-531020.4642383313</t>
+          <t>-537185.6959741293</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>394668.8947985992</t>
+          <t>-571094.4705210179</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>16427808.0</t>
+          <t>13722530.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-3.81</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>63.19</t>
+          <t>63.18</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>13308</t>
+          <t>13969</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,7 +5136,7 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>10.4</t>
+          <t>10.45</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
@@ -5146,12 +5146,12 @@
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>10.3</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>10.45</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>3754.177</t>
+          <t>1569.646</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>10.5</t>
+          <t>10.45</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-6.49</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-3.25</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>33.22</t>
+          <t>28.41</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5228,7 +5228,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17.12</t>
+          <t>7.16</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,75 +5314,75 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>1273</t>
+          <t>4354</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>91.94</t>
+          <t>83.87</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>65.05</t>
+          <t>81.18</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>10.236</t>
+          <t>10.276</t>
         </is>
       </c>
       <c r="AM12" t="n">
         <v>10.31</v>
       </c>
       <c r="AN12" t="n">
-        <v>10.2</v>
+        <v>10.21</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>10.22</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>73.66</t>
+          <t>1372.99</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
           <t>-0.00</t>
         </is>
       </c>
-      <c r="AR12" t="inlineStr">
-        <is>
-          <t>-0.00</t>
-        </is>
-      </c>
       <c r="AS12" t="inlineStr">
         <is>
           <t>0.54</t>
@@ -5390,53 +5390,53 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-100.80</t>
+          <t>-100.18</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>2025/11/13</t>
+          <t>2025/11/28</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>38354560.67142858</t>
+          <t>38394436.85092725</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>39557030.0</t>
+          <t>16427808.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>32036639</v>
+        <v>31153996.2</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>24048236.4</t>
+          <t>24262247.7</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>26253921.64</v>
+        <v>26236307.54</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>7988402</t>
+          <t>6891748</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-699327.6204268641</t>
+          <t>-531020.4642383313</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>1470384.313298099</t>
+          <t>394668.8947985992</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>39557030.0</t>
+          <t>16427808.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5516,7 +5516,7 @@
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>63.19</t>
+          <t>63.18</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>13308</t>
+          <t>13969</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5571,7 +5571,7 @@
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>10.75</t>
+          <t>10.6</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
@@ -5581,7 +5581,7 @@
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>10.5</t>
+          <t>10.45</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/塑化劑(可塑劑).xlsx
+++ b/Result/checksun_type/塑化劑(可塑劑).xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>4.95</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>4353.738</t>
+          <t>6273.16</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>10.35</t>
+          <t>10.7</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-8.98</t>
+          <t>9.10</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>3.88</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>19.86</t>
+          <t>28.61</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>4.65</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,12 +1014,12 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>33</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>4354</t>
+          <t>6273</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1029,58 +1029,58 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>65.15</t>
+          <t>88.73</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>6.05</t>
+          <t>6.77</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-1.69</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>9.76</t>
+          <t>10.022</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>10.01</v>
+        <v>10.04</v>
       </c>
       <c r="AN2" t="n">
-        <v>10.19</v>
+        <v>10.22</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>10.18</t>
+          <t>10.19</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>8.30</t>
+          <t>59.14</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-123.99</t>
+          <t>-120.90</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>38394436.85092725</t>
+          <t>38482598.88247863</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>44205175.0</t>
+          <t>66856122.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>20413759.2</v>
+        <v>30264685.8</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>22428185.2</t>
+          <t>27741544.4</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>27064322.42</v>
+        <v>28239844.66</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-2014426</t>
+          <t>2523141</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-631522.122682977</t>
+          <t>-13657.32483236655</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>175728.5724764355</t>
+          <t>3384599.063345991</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>44205175.0</t>
+          <t>66856122.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-1.43</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1206,17 +1206,17 @@
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>63.18</t>
+          <t>63.27</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>13969</t>
+          <t>14442</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>9.89</t>
+          <t>10.3</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>10.35</t>
+          <t>10.8</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>9.89</t>
+          <t>10.3</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>10.35</t>
+          <t>10.7</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1296,14 +1296,14 @@
       </c>
       <c r="CJ2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>4.95</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1272.664</t>
+          <t>4353.738</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>9.86</t>
+          <t>10.35</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>4.73</t>
+          <t>3.27</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-13.84</t>
+          <t>-8.98</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1358,7 +1358,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-4.27</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>5.80</t>
+          <t>19.86</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>4.65</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,68 +1444,68 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>33</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>4354</t>
+          <t>6273</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>66.2</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>35.12</t>
+          <t>65.15</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>6.05</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-4.05</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>9.596</t>
+          <t>9.76</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>10</v>
+        <v>10.01</v>
       </c>
       <c r="AN3" t="n">
-        <v>10.18</v>
+        <v>10.19</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>10.17</t>
+          <t>10.18</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-31.61</t>
+          <t>8.30</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-124.49</t>
+          <t>-123.99</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>38394436.85092725</t>
+          <t>38482598.88247863</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>12503632.0</t>
+          <t>44205175.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>16931176.2</v>
+        <v>20413759.2</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>19650448.5</t>
+          <t>22428185.2</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>26328965.82</v>
+        <v>27064322.42</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-2719272</t>
+          <t>-2014426</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-778294.9763483247</t>
+          <t>-631522.122682977</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-1987760.970639944</t>
+          <t>175728.5724764355</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>12503632.0</t>
+          <t>44205175.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-6.10</t>
+          <t>-1.43</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,22 +1631,22 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>63.18</t>
+          <t>63.27</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>13969</t>
+          <t>14442</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>9.76</t>
+          <t>9.89</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>9.92</t>
+          <t>10.35</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>9.73</t>
+          <t>9.89</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>9.86</t>
+          <t>10.35</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1726,7 +1726,7 @@
       </c>
       <c r="CJ3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1348.47</t>
+          <t>1272.664</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>9.86</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>6.28</t>
+          <t>7.85</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-19.13</t>
+          <t>-13.84</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1788,7 +1788,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-5.83</t>
+          <t>-4.27</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>6.15</t>
+          <t>5.80</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,51 +1874,51 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>33</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>4354</t>
+          <t>6273</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>29.25</t>
+          <t>66.2</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>13.05</t>
+          <t>35.12</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-4.52</t>
+          <t>-4.05</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-1.5</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>9.57</t>
+          <t>9.596</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>10.02</v>
+        <v>10</v>
       </c>
       <c r="AN4" t="n">
         <v>10.18</v>
@@ -1930,17 +1930,17 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-57.55</t>
+          <t>-31.61</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-122.55</t>
+          <t>-124.49</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>38394436.85092725</t>
+          <t>38482598.88247863</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>13093655.0</t>
+          <t>12503632.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>18080026.8</v>
+        <v>16931176.2</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>22355788.3</t>
+          <t>19650448.5</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>26291263.5</v>
+        <v>26328965.82</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-4275761</t>
+          <t>-2719272</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-558392.068295303</t>
+          <t>-778294.9763483247</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-1610874.961854778</t>
+          <t>-1987760.970639944</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>13093655.0</t>
+          <t>12503632.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-7.62</t>
+          <t>-6.10</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2071,12 +2071,12 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>63.18</t>
+          <t>63.27</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>13969</t>
+          <t>14442</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>9.76</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>9.88</t>
+          <t>9.92</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>9.73</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>9.86</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2156,7 +2156,7 @@
       </c>
       <c r="CJ4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1560.548</t>
+          <t>1348.47</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>8.21</t>
+          <t>9.35</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-3.14</t>
+          <t>-19.13</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2218,7 +2218,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-7.77</t>
+          <t>-5.83</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>7.12</t>
+          <t>6.15</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,63 +2304,63 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>33</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>4354</t>
+          <t>6273</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>9.91</t>
+          <t>29.25</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>13.05</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-0.50</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-5.00</t>
+          <t>-4.52</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-1.5</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>9.548</t>
+          <t>9.57</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>10.05</v>
+        <v>10.02</v>
       </c>
       <c r="AN5" t="n">
-        <v>10.17</v>
+        <v>10.18</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>10.18</t>
+          <t>10.17</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-87.49</t>
+          <t>-57.55</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
@@ -2370,7 +2370,7 @@
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-119.31</t>
+          <t>-122.55</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>38394436.85092725</t>
+          <t>38482598.88247863</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>14664845.0</t>
+          <t>13093655.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>23130520.6</v>
+        <v>18080026.8</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>23880046.8</t>
+          <t>22355788.3</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>26473396.54</v>
+        <v>26291263.5</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-749526</t>
+          <t>-4275761</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-367031.5421935803</t>
+          <t>-558392.068295303</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-1078151.8792383</t>
+          <t>-1610874.961854778</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>14664845.0</t>
+          <t>13093655.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-9.52</t>
+          <t>-7.62</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,12 +2491,12 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
@@ -2506,7 +2506,7 @@
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>63.18</t>
+          <t>63.27</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>13969</t>
+          <t>14442</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>9.46</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>9.55</t>
+          <t>9.88</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>9.27</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="CJ5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1859.149</t>
+          <t>1560.548</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>9.39</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>9.28</t>
+          <t>11.21</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>-3.14</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2648,7 +2648,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-8.83</t>
+          <t>-7.77</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>8.48</t>
+          <t>7.12</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-2.45</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,73 +2734,73 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>33</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>4354</t>
+          <t>6273</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.91</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>5.13</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-2.67</t>
+          <t>-0.50</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-4.39</t>
+          <t>-5.00</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>9.648</t>
+          <t>9.548</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>10.09</v>
+        <v>10.05</v>
       </c>
       <c r="AN6" t="n">
-        <v>10.18</v>
+        <v>10.17</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>10.19</t>
+          <t>10.18</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-117.02</t>
+          <t>-87.49</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-115.08</t>
+          <t>-119.31</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>38394436.85092725</t>
+          <t>38482598.88247863</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>17601489.0</t>
+          <t>14664845.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>25218403</v>
+        <v>23130520.6</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>24916958.1</t>
+          <t>23880046.8</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>26498584.58</v>
+        <v>26473396.54</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>301444</t>
+          <t>-749526</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-237736.9354581767</t>
+          <t>-367031.5421935803</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-446955.2655276731</t>
+          <t>-1078151.8792383</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>17601489.0</t>
+          <t>14664845.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-10.57</t>
+          <t>-9.52</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2931,12 +2931,12 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>63.18</t>
+          <t>63.27</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>13969</t>
+          <t>14442</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
+          <t>9.46</t>
+        </is>
+      </c>
+      <c r="CE6" t="inlineStr">
+        <is>
           <t>9.55</t>
         </is>
       </c>
-      <c r="CE6" t="inlineStr">
-        <is>
-          <t>9.63</t>
-        </is>
-      </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>9.38</t>
+          <t>9.27</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>9.39</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="CJ6" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2806.058</t>
+          <t>1859.149</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>9.53</t>
+          <t>9.39</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>7.92</t>
+          <t>12.24</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-12.07</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-7.48</t>
+          <t>-8.83</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12.80</t>
+          <t>8.48</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-2.45</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,12 +3164,12 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>33</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>4354</t>
+          <t>6273</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3184,53 +3184,53 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-2.66</t>
+          <t>-2.67</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-3.58</t>
+          <t>-4.39</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>9.790000000000001</t>
+          <t>9.648</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>10.15</v>
+        <v>10.09</v>
       </c>
       <c r="AN7" t="n">
-        <v>10.19</v>
+        <v>10.18</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>10.19</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-141.34</t>
+          <t>-117.02</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-110.67</t>
+          <t>-115.08</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>38394436.85092725</t>
+          <t>38482598.88247863</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>26792260.0</t>
+          <t>17601489.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>24442611.2</v>
+        <v>25218403</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>27798303.7</t>
+          <t>24916958.1</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>26345925.2</v>
+        <v>26498584.58</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-3355692</t>
+          <t>301444</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-199697.2390819047</t>
+          <t>-237736.9354581767</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>156076.4421134964</t>
+          <t>-446955.2655276731</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>26792260.0</t>
+          <t>17601489.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-9.24</t>
+          <t>-10.57</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,7 +3351,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3361,12 +3361,12 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>63.18</t>
+          <t>63.27</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>13969</t>
+          <t>14442</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>9.73</t>
+          <t>9.55</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>9.73</t>
+          <t>9.63</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>9.38</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>9.53</t>
+          <t>9.39</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3446,14 +3446,14 @@
       </c>
       <c r="CJ7" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1866.918</t>
+          <t>2806.058</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>9.73</t>
+          <t>9.53</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>5.99</t>
+          <t>10.93</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-17.77</t>
+          <t>-12.07</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-5.53</t>
+          <t>-7.48</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>8.52</t>
+          <t>12.80</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,73 +3594,73 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>33</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>4354</t>
+          <t>6273</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>15.38</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>8.89</t>
+          <t>5.13</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-2.45</t>
+          <t>-2.66</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>-3.58</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>9.974</t>
+          <t>9.790000000000001</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>10.21</v>
+        <v>10.15</v>
       </c>
       <c r="AN8" t="n">
-        <v>10.2</v>
+        <v>10.19</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>10.22</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-177.09</t>
+          <t>-141.34</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-106.90</t>
+          <t>-110.67</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>38394436.85092725</t>
+          <t>38482598.88247863</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>18247885.0</t>
+          <t>26792260.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>22369720.8</v>
+        <v>24442611.2</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>27203179.9</t>
+          <t>27798303.7</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>26271252.44</v>
+        <v>26345925.2</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-4833459</t>
+          <t>-3355692</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-264383.362935614</t>
+          <t>-199697.2390819047</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>27250.68723968416</t>
+          <t>156076.4421134964</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>18247885.0</t>
+          <t>26792260.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-7.33</t>
+          <t>-9.24</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,22 +3781,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>63.18</t>
+          <t>63.27</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>13969</t>
+          <t>14442</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>9.77</t>
+          <t>9.73</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>9.95</t>
+          <t>9.73</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>9.73</t>
+          <t>9.53</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3876,7 +3876,7 @@
       </c>
       <c r="CJ8" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-4.1</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>3938.682</t>
+          <t>1866.918</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>9.59</t>
+          <t>9.73</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>7.34</t>
+          <t>9.07</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-2.69</t>
+          <t>-17.77</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3938,7 +3938,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-6.89</t>
+          <t>-5.53</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17.97</t>
+          <t>8.52</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-4.07</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,51 +4024,51 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>33</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>4354</t>
+          <t>6273</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>15.38</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>12.9</t>
+          <t>8.89</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-5.31</t>
+          <t>-2.45</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>10.128</t>
+          <t>9.974</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>10.25</v>
+        <v>10.21</v>
       </c>
       <c r="AN9" t="n">
         <v>10.2</v>
@@ -4080,17 +4080,17 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-268.37</t>
+          <t>-177.09</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-103.85</t>
+          <t>-106.90</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>38394436.85092725</t>
+          <t>38482598.88247863</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>38346124.0</t>
+          <t>18247885.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>26631549.8</v>
+        <v>22369720.8</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>27366657.0</t>
+          <t>27203179.9</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>26177335.2</v>
+        <v>26271252.44</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-735107</t>
+          <t>-4833459</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-317407.7356947591</t>
+          <t>-264383.362935614</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>757709.4057328217</t>
+          <t>27250.68723968416</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>38346124.0</t>
+          <t>18247885.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-8.67</t>
+          <t>-7.33</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,22 +4211,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>63.18</t>
+          <t>63.27</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>13969</t>
+          <t>14442</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>9.99</t>
+          <t>9.77</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>9.99</t>
+          <t>9.95</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>9.58</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>9.59</t>
+          <t>9.73</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4306,7 +4306,7 @@
       </c>
       <c r="CJ9" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-4.1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2500.445</t>
+          <t>3938.682</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>9.59</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>3.38</t>
+          <t>10.37</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-2.43</t>
+          <t>-2.69</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4368,7 +4368,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-2.91</t>
+          <t>-6.89</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11.41</t>
+          <t>17.97</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-1.60</t>
+          <t>-4.07</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,54 +4454,54 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>33</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>4354</t>
+          <t>6273</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>11.29</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>40.86</t>
+          <t>12.9</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-2.72</t>
+          <t>-5.31</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>10.28</t>
+          <t>10.128</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>10.28</v>
+        <v>10.25</v>
       </c>
       <c r="AN10" t="n">
-        <v>10.21</v>
+        <v>10.2</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4510,17 +4510,17 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-293.77</t>
+          <t>-268.37</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-101.27</t>
+          <t>-103.85</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>38394436.85092725</t>
+          <t>38482598.88247863</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>25104257.0</t>
+          <t>38346124.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>24629573</v>
+        <v>26631549.8</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>25242587.5</t>
+          <t>27366657.0</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>25777972.78</v>
+        <v>26177335.2</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-613014</t>
+          <t>-735107</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-512883.5795906829</t>
+          <t>-317407.7356947591</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-379221.9394817278</t>
+          <t>757709.4057328217</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>25104257.0</t>
+          <t>38346124.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-4.76</t>
+          <t>-8.67</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>63.18</t>
+          <t>63.27</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>13969</t>
+          <t>14442</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>10.05</t>
+          <t>9.99</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>9.99</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>9.96</t>
+          <t>9.58</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>9.59</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4736,7 +4736,7 @@
       </c>
       <c r="CJ10" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-3.35</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1335.381</t>
+          <t>2500.445</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>6.54</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>-2.43</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4798,7 +4798,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-1.94</t>
+          <t>-2.91</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,72 +4863,72 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>6.09</t>
+          <t>11.41</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-4.95</t>
+          <t>-1.60</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>33</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>4354</t>
+          <t>6273</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>27.42</t>
+          <t>11.29</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>67.74</t>
+          <t>40.86</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-2.04</t>
+          <t>-2.72</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>10.31</t>
+          <t>10.28</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>10.3</v>
+        <v>10.28</v>
       </c>
       <c r="AN11" t="n">
         <v>10.21</v>
@@ -4940,19 +4940,19 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-185.15</t>
+          <t>-293.77</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
+          <t>-0.03</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
           <t>-0.01</t>
         </is>
       </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>-0.00</t>
-        </is>
-      </c>
       <c r="AS11" t="inlineStr">
         <is>
           <t>0.54</t>
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-100.34</t>
+          <t>-101.27</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>38394436.85092725</t>
+          <t>38482598.88247863</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>13722530.0</t>
+          <t>25104257.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>24615513.2</v>
+        <v>24629573</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>24233663.8</t>
+          <t>25242587.5</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>25886365.74</v>
+        <v>25777972.78</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>381849</t>
+          <t>-613014</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-537185.6959741293</t>
+          <t>-512883.5795906829</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-571094.4705210179</t>
+          <t>-379221.9394817278</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>13722530.0</t>
+          <t>25104257.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-3.81</t>
+          <t>-4.76</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>63.18</t>
+          <t>63.27</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>13969</t>
+          <t>14442</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>10.45</t>
+          <t>10.05</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>10.6</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>9.96</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5166,14 +5166,14 @@
       </c>
       <c r="CJ11" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>【b】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-3.35</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1569.646</t>
+          <t>1335.381</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>10.45</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>5.61</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>28.41</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5228,7 +5228,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>-1.94</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,72 +5293,72 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>7.16</t>
+          <t>6.09</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-4.95</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>33</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>4354</t>
+          <t>6273</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>83.87</t>
+          <t>27.42</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>81.18</t>
+          <t>67.74</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>-2.04</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>10.276</t>
+          <t>10.31</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>10.31</v>
+        <v>10.3</v>
       </c>
       <c r="AN12" t="n">
         <v>10.21</v>
@@ -5370,12 +5370,12 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>1372.99</t>
+          <t>-185.15</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-100.18</t>
+          <t>-100.34</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>38394436.85092725</t>
+          <t>38482598.88247863</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>16427808.0</t>
+          <t>13722530.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>31153996.2</v>
+        <v>24615513.2</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>24262247.7</t>
+          <t>24233663.8</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>26236307.54</v>
+        <v>25886365.74</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>6891748</t>
+          <t>381849</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-531020.4642383313</t>
+          <t>-537185.6959741293</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>394668.8947985992</t>
+          <t>-571094.4705210179</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>16427808.0</t>
+          <t>13722530.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-3.81</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>63.18</t>
+          <t>63.27</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>13969</t>
+          <t>14442</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,7 +5566,7 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>10.4</t>
+          <t>10.45</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>10.3</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>10.45</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5596,7 +5596,7 @@
       </c>
       <c r="CJ12" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>

--- a/Result/checksun_type/塑化劑(可塑劑).xlsx
+++ b/Result/checksun_type/塑化劑(可塑劑).xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>5.61</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>6273.16</t>
+          <t>34269.781</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>10.7</t>
+          <t>11.3</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>9.10</t>
+          <t>64.03</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>3.88</t>
+          <t>9.71</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>28.61</t>
+          <t>100.00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2.95</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,12 +1014,12 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>105</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>6273</t>
+          <t>34270</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1029,58 +1029,58 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>88.73</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>6.77</t>
+          <t>8.84</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-1.69</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>10.022</t>
+          <t>10.382</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>10.04</v>
+        <v>10.1</v>
       </c>
       <c r="AN2" t="n">
-        <v>10.22</v>
+        <v>10.25</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>10.19</t>
+          <t>10.21</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>59.14</t>
+          <t>175.85</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-120.90</t>
+          <t>-114.52</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>38482598.88247863</t>
+          <t>39261700.86913229</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>66856122.0</t>
+          <t>390794197.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>30264685.8</v>
+        <v>105490556.2</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>27741544.4</t>
+          <t>64310538.4</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>28239844.66</v>
+        <v>35931629.66</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>2523141</t>
+          <t>41180017</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-13657.32483236655</t>
+          <t>4579451.34904508</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>3384599.063345991</t>
+          <t>29841549.05537103</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>66856122.0</t>
+          <t>390794197.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>7.62</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1201,22 +1201,22 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>63.27</t>
+          <t>63.54</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>14442</t>
+          <t>15251</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1261,27 +1261,27 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>塑膠工業右下上市</t>
+          <t>塑膠工業平上市</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>10.3</t>
+          <t>10.7</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>10.8</t>
+          <t>11.75</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>10.3</t>
+          <t>10.7</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>10.7</t>
+          <t>11.3</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>4.95</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>4353.738</t>
+          <t>6273.16</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>10.35</t>
+          <t>10.7</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>3.27</t>
+          <t>5.31</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-8.98</t>
+          <t>9.10</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1358,7 +1358,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>3.88</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>19.86</t>
+          <t>18.31</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>4.65</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,12 +1444,12 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>105</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>6273</t>
+          <t>34270</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1459,58 +1459,58 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>65.15</t>
+          <t>88.73</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>6.05</t>
+          <t>6.77</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-1.69</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>9.76</t>
+          <t>10.022</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>10.01</v>
+        <v>10.04</v>
       </c>
       <c r="AN3" t="n">
-        <v>10.19</v>
+        <v>10.22</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>10.18</t>
+          <t>10.19</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>8.30</t>
+          <t>59.14</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-123.99</t>
+          <t>-120.90</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>38482598.88247863</t>
+          <t>39261700.86913229</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>44205175.0</t>
+          <t>66856122.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>20413759.2</v>
+        <v>30264685.8</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>22428185.2</t>
+          <t>27741544.4</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>27064322.42</v>
+        <v>28239844.66</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-2014426</t>
+          <t>2523141</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-631522.122682977</t>
+          <t>-13657.32483236655</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>175728.5724764355</t>
+          <t>3384599.063345991</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>44205175.0</t>
+          <t>66856122.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-1.43</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
@@ -1636,17 +1636,17 @@
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>63.27</t>
+          <t>63.54</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>14442</t>
+          <t>15251</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1691,27 +1691,27 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>塑膠工業右下上市</t>
+          <t>塑膠工業平上市</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>9.89</t>
+          <t>10.3</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>10.35</t>
+          <t>10.8</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>9.89</t>
+          <t>10.3</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>10.35</t>
+          <t>10.7</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1733,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>4.95</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1272.664</t>
+          <t>4353.738</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>9.86</t>
+          <t>10.35</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>7.85</t>
+          <t>8.41</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-13.84</t>
+          <t>-8.98</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1788,7 +1788,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-4.27</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>5.80</t>
+          <t>12.70</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>4.65</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,68 +1874,68 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>105</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>6273</t>
+          <t>34270</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>66.2</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>35.12</t>
+          <t>65.15</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>6.05</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-4.05</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>9.596</t>
+          <t>9.76</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>10</v>
+        <v>10.01</v>
       </c>
       <c r="AN4" t="n">
-        <v>10.18</v>
+        <v>10.19</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>10.17</t>
+          <t>10.18</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-31.61</t>
+          <t>8.30</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-124.49</t>
+          <t>-123.99</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>38482598.88247863</t>
+          <t>39261700.86913229</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>12503632.0</t>
+          <t>44205175.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>16931176.2</v>
+        <v>20413759.2</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>19650448.5</t>
+          <t>22428185.2</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>26328965.82</v>
+        <v>27064322.42</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-2719272</t>
+          <t>-2014426</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-778294.9763483247</t>
+          <t>-631522.122682977</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-1987760.970639944</t>
+          <t>175728.5724764355</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>12503632.0</t>
+          <t>44205175.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-6.10</t>
+          <t>-1.43</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
@@ -2061,22 +2061,22 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>63.27</t>
+          <t>63.54</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>14442</t>
+          <t>15251</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2121,27 +2121,27 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>塑膠工業右下上市</t>
+          <t>塑膠工業平上市</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>9.76</t>
+          <t>9.89</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>9.92</t>
+          <t>10.35</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>9.73</t>
+          <t>9.89</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>9.86</t>
+          <t>10.35</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1348.47</t>
+          <t>1272.664</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>9.86</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>9.35</t>
+          <t>12.74</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-19.13</t>
+          <t>-13.84</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2218,7 +2218,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-5.83</t>
+          <t>-4.27</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>6.15</t>
+          <t>3.71</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,51 +2304,51 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>105</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>6273</t>
+          <t>34270</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>29.25</t>
+          <t>66.2</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>13.05</t>
+          <t>35.12</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-4.52</t>
+          <t>-4.05</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-1.5</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>9.57</t>
+          <t>9.596</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>10.02</v>
+        <v>10</v>
       </c>
       <c r="AN5" t="n">
         <v>10.18</v>
@@ -2360,17 +2360,17 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-57.55</t>
+          <t>-31.61</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-122.55</t>
+          <t>-124.49</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>38482598.88247863</t>
+          <t>39261700.86913229</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>13093655.0</t>
+          <t>12503632.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>18080026.8</v>
+        <v>16931176.2</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>22355788.3</t>
+          <t>19650448.5</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>26291263.5</v>
+        <v>26328965.82</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-4275761</t>
+          <t>-2719272</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-558392.068295303</t>
+          <t>-778294.9763483247</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-1610874.961854778</t>
+          <t>-1987760.970639944</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>13093655.0</t>
+          <t>12503632.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-7.62</t>
+          <t>-6.10</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2501,12 +2501,12 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>63.27</t>
+          <t>63.54</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>14442</t>
+          <t>15251</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2551,27 +2551,27 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>塑膠工業右下上市</t>
+          <t>塑膠工業平上市</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>9.76</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>9.88</t>
+          <t>9.92</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>9.73</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>9.86</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1560.548</t>
+          <t>1348.47</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>11.21</t>
+          <t>14.16</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-3.14</t>
+          <t>-19.13</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2648,7 +2648,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-7.77</t>
+          <t>-5.83</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>7.12</t>
+          <t>3.93</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,63 +2734,63 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>105</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>6273</t>
+          <t>34270</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>9.91</t>
+          <t>29.25</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>13.05</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-0.50</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-5.00</t>
+          <t>-4.52</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-1.5</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>9.548</t>
+          <t>9.57</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>10.05</v>
+        <v>10.02</v>
       </c>
       <c r="AN6" t="n">
-        <v>10.17</v>
+        <v>10.18</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>10.18</t>
+          <t>10.17</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-87.49</t>
+          <t>-57.55</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-119.31</t>
+          <t>-122.55</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>38482598.88247863</t>
+          <t>39261700.86913229</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>14664845.0</t>
+          <t>13093655.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>23130520.6</v>
+        <v>18080026.8</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>23880046.8</t>
+          <t>22355788.3</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>26473396.54</v>
+        <v>26291263.5</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-749526</t>
+          <t>-4275761</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-367031.5421935803</t>
+          <t>-558392.068295303</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-1078151.8792383</t>
+          <t>-1610874.961854778</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>14664845.0</t>
+          <t>13093655.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-9.52</t>
+          <t>-7.62</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -2921,12 +2921,12 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>63.27</t>
+          <t>63.54</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>14442</t>
+          <t>15251</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2981,27 +2981,27 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>塑膠工業右下上市</t>
+          <t>塑膠工業平上市</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>9.46</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>9.55</t>
+          <t>9.88</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>9.27</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1859.149</t>
+          <t>1560.548</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>9.39</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>12.24</t>
+          <t>15.93</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>-3.14</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-8.83</t>
+          <t>-7.77</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>8.48</t>
+          <t>4.55</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-2.45</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,73 +3164,73 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>105</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>6273</t>
+          <t>34270</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.91</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>5.13</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-2.67</t>
+          <t>-0.50</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-4.39</t>
+          <t>-5.00</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>9.648</t>
+          <t>9.548</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>10.09</v>
+        <v>10.05</v>
       </c>
       <c r="AN7" t="n">
-        <v>10.18</v>
+        <v>10.17</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>10.19</t>
+          <t>10.18</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-117.02</t>
+          <t>-87.49</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-115.08</t>
+          <t>-119.31</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>38482598.88247863</t>
+          <t>39261700.86913229</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>17601489.0</t>
+          <t>14664845.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>25218403</v>
+        <v>23130520.6</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>24916958.1</t>
+          <t>23880046.8</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>26498584.58</v>
+        <v>26473396.54</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>301444</t>
+          <t>-749526</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-237736.9354581767</t>
+          <t>-367031.5421935803</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-446955.2655276731</t>
+          <t>-1078151.8792383</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>17601489.0</t>
+          <t>14664845.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-10.57</t>
+          <t>-9.52</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
@@ -3351,7 +3351,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3361,12 +3361,12 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>63.27</t>
+          <t>63.54</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>14442</t>
+          <t>15251</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3411,27 +3411,27 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>塑膠工業右下上市</t>
+          <t>塑膠工業平上市</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
+          <t>9.46</t>
+        </is>
+      </c>
+      <c r="CE7" t="inlineStr">
+        <is>
           <t>9.55</t>
         </is>
       </c>
-      <c r="CE7" t="inlineStr">
-        <is>
-          <t>9.63</t>
-        </is>
-      </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>9.38</t>
+          <t>9.27</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>9.39</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2806.058</t>
+          <t>1859.149</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>9.53</t>
+          <t>9.39</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>10.93</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-12.07</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-7.48</t>
+          <t>-8.83</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12.80</t>
+          <t>5.43</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-2.45</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,12 +3594,12 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>105</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>6273</t>
+          <t>34270</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3614,53 +3614,53 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-2.66</t>
+          <t>-2.67</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-3.58</t>
+          <t>-4.39</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>9.790000000000001</t>
+          <t>9.648</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>10.15</v>
+        <v>10.09</v>
       </c>
       <c r="AN8" t="n">
-        <v>10.19</v>
+        <v>10.18</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>10.19</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-141.34</t>
+          <t>-117.02</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-110.67</t>
+          <t>-115.08</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>38482598.88247863</t>
+          <t>39261700.86913229</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>26792260.0</t>
+          <t>17601489.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>24442611.2</v>
+        <v>25218403</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>27798303.7</t>
+          <t>24916958.1</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>26345925.2</v>
+        <v>26498584.58</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-3355692</t>
+          <t>301444</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-199697.2390819047</t>
+          <t>-237736.9354581767</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>156076.4421134964</t>
+          <t>-446955.2655276731</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>26792260.0</t>
+          <t>17601489.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-9.24</t>
+          <t>-10.57</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3761,7 +3761,7 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
@@ -3781,7 +3781,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3791,12 +3791,12 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>63.27</t>
+          <t>63.54</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>14442</t>
+          <t>15251</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3841,27 +3841,27 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>塑膠工業右下上市</t>
+          <t>塑膠工業平上市</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>9.73</t>
+          <t>9.55</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>9.73</t>
+          <t>9.63</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>9.38</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>9.53</t>
+          <t>9.39</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3883,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1866.918</t>
+          <t>2806.058</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>9.73</t>
+          <t>9.53</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>9.07</t>
+          <t>15.66</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-17.77</t>
+          <t>-12.07</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3938,7 +3938,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-5.53</t>
+          <t>-7.48</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>8.52</t>
+          <t>8.19</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,73 +4024,73 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>105</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>6273</t>
+          <t>34270</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>15.38</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>8.89</t>
+          <t>5.13</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-2.45</t>
+          <t>-2.66</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>-3.58</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>9.974</t>
+          <t>9.790000000000001</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>10.21</v>
+        <v>10.15</v>
       </c>
       <c r="AN9" t="n">
-        <v>10.2</v>
+        <v>10.19</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>10.22</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-177.09</t>
+          <t>-141.34</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-106.90</t>
+          <t>-110.67</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>38482598.88247863</t>
+          <t>39261700.86913229</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>18247885.0</t>
+          <t>26792260.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>22369720.8</v>
+        <v>24442611.2</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>27203179.9</t>
+          <t>27798303.7</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>26271252.44</v>
+        <v>26345925.2</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-4833459</t>
+          <t>-3355692</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-264383.362935614</t>
+          <t>-199697.2390819047</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>27250.68723968416</t>
+          <t>156076.4421134964</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>18247885.0</t>
+          <t>26792260.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-7.33</t>
+          <t>-9.24</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4191,7 +4191,7 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
@@ -4211,22 +4211,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>63.27</t>
+          <t>63.54</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>14442</t>
+          <t>15251</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4271,27 +4271,27 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>塑膠工業右下上市</t>
+          <t>塑膠工業平上市</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>9.77</t>
+          <t>9.73</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>9.95</t>
+          <t>9.73</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>9.73</t>
+          <t>9.53</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-4.1</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>3938.682</t>
+          <t>1866.918</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>9.59</t>
+          <t>9.73</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>10.37</t>
+          <t>13.89</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-2.69</t>
+          <t>-17.77</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4368,7 +4368,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-6.89</t>
+          <t>-5.53</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17.97</t>
+          <t>5.45</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-4.07</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,51 +4454,51 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>105</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>6273</t>
+          <t>34270</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>15.38</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>12.9</t>
+          <t>8.89</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-5.31</t>
+          <t>-2.45</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>10.128</t>
+          <t>9.974</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>10.25</v>
+        <v>10.21</v>
       </c>
       <c r="AN10" t="n">
         <v>10.2</v>
@@ -4510,17 +4510,17 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-268.37</t>
+          <t>-177.09</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-103.85</t>
+          <t>-106.90</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>38482598.88247863</t>
+          <t>39261700.86913229</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>38346124.0</t>
+          <t>18247885.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>26631549.8</v>
+        <v>22369720.8</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>27366657.0</t>
+          <t>27203179.9</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>26177335.2</v>
+        <v>26271252.44</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-735107</t>
+          <t>-4833459</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-317407.7356947591</t>
+          <t>-264383.362935614</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>757709.4057328217</t>
+          <t>27250.68723968416</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>38346124.0</t>
+          <t>18247885.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-8.67</t>
+          <t>-7.33</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4621,7 +4621,7 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
@@ -4641,22 +4641,22 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>63.27</t>
+          <t>63.54</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>14442</t>
+          <t>15251</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4701,27 +4701,27 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>塑膠工業右下上市</t>
+          <t>塑膠工業平上市</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>9.99</t>
+          <t>9.77</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>9.99</t>
+          <t>9.95</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>9.58</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>9.59</t>
+          <t>9.73</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-4.1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2500.445</t>
+          <t>3938.682</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>9.59</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>6.54</t>
+          <t>15.13</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-2.43</t>
+          <t>-2.69</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4798,7 +4798,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-2.91</t>
+          <t>-6.89</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11.41</t>
+          <t>11.49</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-1.60</t>
+          <t>-4.07</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,54 +4884,54 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>105</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>6273</t>
+          <t>34270</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>11.29</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>40.86</t>
+          <t>12.9</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-2.72</t>
+          <t>-5.31</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>10.28</t>
+          <t>10.128</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>10.28</v>
+        <v>10.25</v>
       </c>
       <c r="AN11" t="n">
-        <v>10.21</v>
+        <v>10.2</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -4940,17 +4940,17 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-293.77</t>
+          <t>-268.37</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-101.27</t>
+          <t>-103.85</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>38482598.88247863</t>
+          <t>39261700.86913229</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>25104257.0</t>
+          <t>38346124.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>24629573</v>
+        <v>26631549.8</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>25242587.5</t>
+          <t>27366657.0</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>25777972.78</v>
+        <v>26177335.2</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-613014</t>
+          <t>-735107</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-512883.5795906829</t>
+          <t>-317407.7356947591</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-379221.9394817278</t>
+          <t>757709.4057328217</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>25104257.0</t>
+          <t>38346124.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-4.76</t>
+          <t>-8.67</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5051,7 +5051,7 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>63.27</t>
+          <t>63.54</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>14442</t>
+          <t>15251</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5131,27 +5131,27 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>塑膠工業右下上市</t>
+          <t>塑膠工業平上市</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>10.05</t>
+          <t>9.99</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>9.99</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>9.96</t>
+          <t>9.58</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>9.59</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-3.35</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1335.381</t>
+          <t>2500.445</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>5.61</t>
+          <t>11.5</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>-2.43</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5228,7 +5228,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-1.94</t>
+          <t>-2.91</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,72 +5293,72 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>6.09</t>
+          <t>7.30</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-4.95</t>
+          <t>-1.60</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>105</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>6273</t>
+          <t>34270</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>27.42</t>
+          <t>11.29</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>67.74</t>
+          <t>40.86</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-2.04</t>
+          <t>-2.72</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>10.31</t>
+          <t>10.28</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>10.3</v>
+        <v>10.28</v>
       </c>
       <c r="AN12" t="n">
         <v>10.21</v>
@@ -5370,19 +5370,19 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-185.15</t>
+          <t>-293.77</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
+          <t>-0.03</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
           <t>-0.01</t>
         </is>
       </c>
-      <c r="AR12" t="inlineStr">
-        <is>
-          <t>-0.00</t>
-        </is>
-      </c>
       <c r="AS12" t="inlineStr">
         <is>
           <t>0.54</t>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-100.34</t>
+          <t>-101.27</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>38482598.88247863</t>
+          <t>39261700.86913229</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>13722530.0</t>
+          <t>25104257.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>24615513.2</v>
+        <v>24629573</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>24233663.8</t>
+          <t>25242587.5</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>25886365.74</v>
+        <v>25777972.78</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>381849</t>
+          <t>-613014</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-537185.6959741293</t>
+          <t>-512883.5795906829</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-571094.4705210179</t>
+          <t>-379221.9394817278</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>13722530.0</t>
+          <t>25104257.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-3.81</t>
+          <t>-4.76</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5516,7 +5516,7 @@
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>63.27</t>
+          <t>63.54</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>14442</t>
+          <t>15251</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5561,27 +5561,27 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>塑膠工業右下上市</t>
+          <t>塑膠工業平上市</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>10.45</t>
+          <t>10.05</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>10.6</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>9.96</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/塑化劑(可塑劑).xlsx
+++ b/Result/checksun_type/塑化劑(可塑劑).xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>5.61</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>34269.781</t>
+          <t>10514.261</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>64.03</t>
+          <t>75.06</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>100.00</t>
+          <t>30.68</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>-2.16</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,12 +1014,12 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>34270</t>
+          <t>10514</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1034,53 +1034,53 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>8.84</t>
+          <t>5.59</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>5.32</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-1.45</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>10.382</t>
+          <t>10.702</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>10.1</v>
+        <v>10.16</v>
       </c>
       <c r="AN2" t="n">
-        <v>10.25</v>
+        <v>10.28</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>10.21</t>
+          <t>10.23</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>175.85</t>
+          <t>511.12</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-114.52</t>
+          <t>-106.37</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>39261700.86913229</t>
+          <t>39462022.65553977</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>390794197.0</t>
+          <t>120192159.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>105490556.2</v>
+        <v>126910257</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>64310538.4</t>
+          <t>72495141.9</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>35931629.66</v>
+        <v>37850914.22</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>41180017</t>
+          <t>54415115</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>4579451.34904508</t>
+          <t>8078031.522023421</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>29841549.05537103</t>
+          <t>27320222.47340429</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>390794197.0</t>
+          <t>120192159.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
@@ -1241,7 +1241,7 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>63.54</t>
+          <t>63.5</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1266,17 +1266,17 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>10.7</t>
+          <t>11.15</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>11.75</t>
+          <t>11.8</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>10.7</t>
+          <t>11.05</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>5.61</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>6273.16</t>
+          <t>34269.781</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>10.7</t>
+          <t>11.3</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>5.31</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>9.10</t>
+          <t>64.03</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>3.88</t>
+          <t>9.71</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>18.31</t>
+          <t>100.00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2.95</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,12 +1444,12 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>34270</t>
+          <t>10514</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1459,58 +1459,58 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>88.73</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>6.77</t>
+          <t>8.84</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-1.69</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>10.022</t>
+          <t>10.382</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>10.04</v>
+        <v>10.1</v>
       </c>
       <c r="AN3" t="n">
-        <v>10.22</v>
+        <v>10.25</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>10.19</t>
+          <t>10.21</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>59.14</t>
+          <t>175.85</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-120.90</t>
+          <t>-114.52</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>39261700.86913229</t>
+          <t>39462022.65553977</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>66856122.0</t>
+          <t>390794197.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>30264685.8</v>
+        <v>105490556.2</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>27741544.4</t>
+          <t>64310538.4</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>28239844.66</v>
+        <v>35931629.66</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>2523141</t>
+          <t>41180017</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-13657.32483236655</t>
+          <t>4579451.34904508</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>3384599.063345991</t>
+          <t>29841549.05537103</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>66856122.0</t>
+          <t>390794197.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>7.62</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
@@ -1631,17 +1631,17 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1671,7 +1671,7 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>63.54</t>
+          <t>63.5</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>10.3</t>
+          <t>10.7</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>10.8</t>
+          <t>11.75</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>10.3</t>
+          <t>10.7</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>10.7</t>
+          <t>11.3</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>4.95</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>4353.738</t>
+          <t>6273.16</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>10.35</t>
+          <t>10.7</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>8.41</t>
+          <t>5.31</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-8.98</t>
+          <t>9.10</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>3.88</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12.70</t>
+          <t>18.31</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>4.65</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,12 +1874,12 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>34270</t>
+          <t>10514</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1889,58 +1889,58 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>65.15</t>
+          <t>88.73</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>6.05</t>
+          <t>6.77</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-1.69</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>9.76</t>
+          <t>10.022</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>10.01</v>
+        <v>10.04</v>
       </c>
       <c r="AN4" t="n">
-        <v>10.19</v>
+        <v>10.22</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>10.18</t>
+          <t>10.19</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>8.30</t>
+          <t>59.14</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-123.99</t>
+          <t>-120.90</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>39261700.86913229</t>
+          <t>39462022.65553977</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>44205175.0</t>
+          <t>66856122.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>20413759.2</v>
+        <v>30264685.8</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>22428185.2</t>
+          <t>27741544.4</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>27064322.42</v>
+        <v>28239844.66</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-2014426</t>
+          <t>2523141</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-631522.122682977</t>
+          <t>-13657.32483236655</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>175728.5724764355</t>
+          <t>3384599.063345991</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>44205175.0</t>
+          <t>66856122.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-1.43</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2101,7 +2101,7 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>63.54</t>
+          <t>63.5</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>9.89</t>
+          <t>10.3</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>10.35</t>
+          <t>10.8</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>9.89</t>
+          <t>10.3</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>10.35</t>
+          <t>10.7</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2163,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>4.95</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1272.664</t>
+          <t>4353.738</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>9.86</t>
+          <t>10.35</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>12.74</t>
+          <t>8.41</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-13.84</t>
+          <t>-8.98</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-4.27</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>3.71</t>
+          <t>12.70</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>4.65</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,68 +2304,68 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>34270</t>
+          <t>10514</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>66.2</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>35.12</t>
+          <t>65.15</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>6.05</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-4.05</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>9.596</t>
+          <t>9.76</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>10</v>
+        <v>10.01</v>
       </c>
       <c r="AN5" t="n">
-        <v>10.18</v>
+        <v>10.19</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>10.17</t>
+          <t>10.18</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-31.61</t>
+          <t>8.30</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-124.49</t>
+          <t>-123.99</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>39261700.86913229</t>
+          <t>39462022.65553977</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>12503632.0</t>
+          <t>44205175.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>16931176.2</v>
+        <v>20413759.2</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>19650448.5</t>
+          <t>22428185.2</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>26328965.82</v>
+        <v>27064322.42</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-2719272</t>
+          <t>-2014426</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-778294.9763483247</t>
+          <t>-631522.122682977</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-1987760.970639944</t>
+          <t>175728.5724764355</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>12503632.0</t>
+          <t>44205175.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-6.10</t>
+          <t>-1.43</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
@@ -2491,17 +2491,17 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2531,7 +2531,7 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>63.54</t>
+          <t>63.5</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>9.76</t>
+          <t>9.89</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>9.92</t>
+          <t>10.35</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>9.73</t>
+          <t>9.89</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>9.86</t>
+          <t>10.35</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1348.47</t>
+          <t>1272.664</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>9.86</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>14.16</t>
+          <t>12.74</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-19.13</t>
+          <t>-13.84</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-5.83</t>
+          <t>-4.27</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>3.93</t>
+          <t>3.71</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,51 +2734,51 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>34270</t>
+          <t>10514</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>29.25</t>
+          <t>66.2</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>13.05</t>
+          <t>35.12</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-4.52</t>
+          <t>-4.05</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-1.5</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>9.57</t>
+          <t>9.596</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>10.02</v>
+        <v>10</v>
       </c>
       <c r="AN6" t="n">
         <v>10.18</v>
@@ -2790,17 +2790,17 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-57.55</t>
+          <t>-31.61</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-122.55</t>
+          <t>-124.49</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>39261700.86913229</t>
+          <t>39462022.65553977</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>13093655.0</t>
+          <t>12503632.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>18080026.8</v>
+        <v>16931176.2</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>22355788.3</t>
+          <t>19650448.5</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>26291263.5</v>
+        <v>26328965.82</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-4275761</t>
+          <t>-2719272</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-558392.068295303</t>
+          <t>-778294.9763483247</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-1610874.961854778</t>
+          <t>-1987760.970639944</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>13093655.0</t>
+          <t>12503632.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-7.62</t>
+          <t>-6.10</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2961,7 +2961,7 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>63.54</t>
+          <t>63.5</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>9.76</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>9.88</t>
+          <t>9.92</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>9.73</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>9.86</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1560.548</t>
+          <t>1348.47</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>15.93</t>
+          <t>14.16</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-3.14</t>
+          <t>-19.13</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-7.77</t>
+          <t>-5.83</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>4.55</t>
+          <t>3.93</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,63 +3164,63 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>34270</t>
+          <t>10514</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>9.91</t>
+          <t>29.25</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>13.05</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-0.50</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-5.00</t>
+          <t>-4.52</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-1.5</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>9.548</t>
+          <t>9.57</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>10.05</v>
+        <v>10.02</v>
       </c>
       <c r="AN7" t="n">
-        <v>10.17</v>
+        <v>10.18</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>10.18</t>
+          <t>10.17</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-87.49</t>
+          <t>-57.55</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
@@ -3230,7 +3230,7 @@
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-119.31</t>
+          <t>-122.55</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>39261700.86913229</t>
+          <t>39462022.65553977</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>14664845.0</t>
+          <t>13093655.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>23130520.6</v>
+        <v>18080026.8</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>23880046.8</t>
+          <t>22355788.3</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>26473396.54</v>
+        <v>26291263.5</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-749526</t>
+          <t>-4275761</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-367031.5421935803</t>
+          <t>-558392.068295303</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-1078151.8792383</t>
+          <t>-1610874.961854778</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>14664845.0</t>
+          <t>13093655.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-9.52</t>
+          <t>-7.62</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
@@ -3351,12 +3351,12 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>63.54</t>
+          <t>63.5</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>9.46</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>9.55</t>
+          <t>9.88</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>9.27</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1859.149</t>
+          <t>1560.548</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>9.39</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>15.93</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>-3.14</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-8.83</t>
+          <t>-7.77</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>5.43</t>
+          <t>4.55</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-2.45</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,73 +3594,73 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>34270</t>
+          <t>10514</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.91</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>5.13</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-2.67</t>
+          <t>-0.50</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-4.39</t>
+          <t>-5.00</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>9.648</t>
+          <t>9.548</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>10.09</v>
+        <v>10.05</v>
       </c>
       <c r="AN8" t="n">
-        <v>10.18</v>
+        <v>10.17</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>10.19</t>
+          <t>10.18</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-117.02</t>
+          <t>-87.49</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-115.08</t>
+          <t>-119.31</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>39261700.86913229</t>
+          <t>39462022.65553977</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>17601489.0</t>
+          <t>14664845.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>25218403</v>
+        <v>23130520.6</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>24916958.1</t>
+          <t>23880046.8</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>26498584.58</v>
+        <v>26473396.54</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>301444</t>
+          <t>-749526</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-237736.9354581767</t>
+          <t>-367031.5421935803</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-446955.2655276731</t>
+          <t>-1078151.8792383</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>17601489.0</t>
+          <t>14664845.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-10.57</t>
+          <t>-9.52</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3761,7 +3761,7 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
@@ -3781,7 +3781,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3791,7 +3791,7 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>63.54</t>
+          <t>63.5</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
+          <t>9.46</t>
+        </is>
+      </c>
+      <c r="CE8" t="inlineStr">
+        <is>
           <t>9.55</t>
         </is>
       </c>
-      <c r="CE8" t="inlineStr">
-        <is>
-          <t>9.63</t>
-        </is>
-      </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>9.38</t>
+          <t>9.27</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>9.39</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2806.058</t>
+          <t>1859.149</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>9.53</t>
+          <t>9.39</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>15.66</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-12.07</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-7.48</t>
+          <t>-8.83</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>8.19</t>
+          <t>5.43</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-2.45</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,12 +4024,12 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>34270</t>
+          <t>10514</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -4044,53 +4044,53 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-2.66</t>
+          <t>-2.67</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-3.58</t>
+          <t>-4.39</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>9.790000000000001</t>
+          <t>9.648</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>10.15</v>
+        <v>10.09</v>
       </c>
       <c r="AN9" t="n">
-        <v>10.19</v>
+        <v>10.18</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>10.19</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-141.34</t>
+          <t>-117.02</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-110.67</t>
+          <t>-115.08</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>39261700.86913229</t>
+          <t>39462022.65553977</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>26792260.0</t>
+          <t>17601489.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>24442611.2</v>
+        <v>25218403</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>27798303.7</t>
+          <t>24916958.1</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>26345925.2</v>
+        <v>26498584.58</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-3355692</t>
+          <t>301444</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-199697.2390819047</t>
+          <t>-237736.9354581767</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>156076.4421134964</t>
+          <t>-446955.2655276731</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>26792260.0</t>
+          <t>17601489.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-9.24</t>
+          <t>-10.57</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4191,7 +4191,7 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
@@ -4211,7 +4211,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4221,7 +4221,7 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4251,7 +4251,7 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>63.54</t>
+          <t>63.5</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>9.73</t>
+          <t>9.55</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>9.73</t>
+          <t>9.63</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>9.38</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>9.53</t>
+          <t>9.39</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4313,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1866.918</t>
+          <t>2806.058</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>9.73</t>
+          <t>9.53</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>13.89</t>
+          <t>15.66</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-17.77</t>
+          <t>-12.07</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-5.53</t>
+          <t>-7.48</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>5.45</t>
+          <t>8.19</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,73 +4454,73 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>34270</t>
+          <t>10514</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>15.38</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>8.89</t>
+          <t>5.13</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-2.45</t>
+          <t>-2.66</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>-3.58</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>9.974</t>
+          <t>9.790000000000001</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>10.21</v>
+        <v>10.15</v>
       </c>
       <c r="AN10" t="n">
-        <v>10.2</v>
+        <v>10.19</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>10.22</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-177.09</t>
+          <t>-141.34</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-106.90</t>
+          <t>-110.67</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>39261700.86913229</t>
+          <t>39462022.65553977</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>18247885.0</t>
+          <t>26792260.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>22369720.8</v>
+        <v>24442611.2</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>27203179.9</t>
+          <t>27798303.7</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>26271252.44</v>
+        <v>26345925.2</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-4833459</t>
+          <t>-3355692</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-264383.362935614</t>
+          <t>-199697.2390819047</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>27250.68723968416</t>
+          <t>156076.4421134964</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>18247885.0</t>
+          <t>26792260.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-7.33</t>
+          <t>-9.24</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4621,7 +4621,7 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
@@ -4641,17 +4641,17 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4681,7 +4681,7 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>63.54</t>
+          <t>63.5</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>9.77</t>
+          <t>9.73</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>9.95</t>
+          <t>9.73</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>9.73</t>
+          <t>9.53</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-4.1</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>3938.682</t>
+          <t>1866.918</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>9.59</t>
+          <t>9.73</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>15.13</t>
+          <t>13.89</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-2.69</t>
+          <t>-17.77</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-6.89</t>
+          <t>-5.53</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11.49</t>
+          <t>5.45</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-4.07</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,51 +4884,51 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>34270</t>
+          <t>10514</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>15.38</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>12.9</t>
+          <t>8.89</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-5.31</t>
+          <t>-2.45</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>10.128</t>
+          <t>9.974</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>10.25</v>
+        <v>10.21</v>
       </c>
       <c r="AN11" t="n">
         <v>10.2</v>
@@ -4940,17 +4940,17 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-268.37</t>
+          <t>-177.09</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-103.85</t>
+          <t>-106.90</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>39261700.86913229</t>
+          <t>39462022.65553977</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>38346124.0</t>
+          <t>18247885.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>26631549.8</v>
+        <v>22369720.8</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>27366657.0</t>
+          <t>27203179.9</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>26177335.2</v>
+        <v>26271252.44</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-735107</t>
+          <t>-4833459</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-317407.7356947591</t>
+          <t>-264383.362935614</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>757709.4057328217</t>
+          <t>27250.68723968416</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>38346124.0</t>
+          <t>18247885.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-8.67</t>
+          <t>-7.33</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5051,7 +5051,7 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>63.54</t>
+          <t>63.5</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>9.99</t>
+          <t>9.77</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>9.99</t>
+          <t>9.95</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>9.58</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>9.59</t>
+          <t>9.73</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-4.1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2500.445</t>
+          <t>3938.682</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>9.59</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>11.5</t>
+          <t>15.13</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-2.43</t>
+          <t>-2.69</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-2.91</t>
+          <t>-6.89</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>7.30</t>
+          <t>11.49</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-1.60</t>
+          <t>-4.07</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,54 +5314,54 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>34270</t>
+          <t>10514</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>11.29</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>40.86</t>
+          <t>12.9</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-2.72</t>
+          <t>-5.31</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>10.28</t>
+          <t>10.128</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>10.28</v>
+        <v>10.25</v>
       </c>
       <c r="AN12" t="n">
-        <v>10.21</v>
+        <v>10.2</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5370,17 +5370,17 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-293.77</t>
+          <t>-268.37</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-101.27</t>
+          <t>-103.85</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>39261700.86913229</t>
+          <t>39462022.65553977</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>25104257.0</t>
+          <t>38346124.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>24629573</v>
+        <v>26631549.8</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>25242587.5</t>
+          <t>27366657.0</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>25777972.78</v>
+        <v>26177335.2</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-613014</t>
+          <t>-735107</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-512883.5795906829</t>
+          <t>-317407.7356947591</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-379221.9394817278</t>
+          <t>757709.4057328217</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>25104257.0</t>
+          <t>38346124.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-4.76</t>
+          <t>-8.67</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5541,7 +5541,7 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>63.54</t>
+          <t>63.5</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>10.05</t>
+          <t>9.99</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>9.99</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>9.96</t>
+          <t>9.58</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>9.59</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/塑化劑(可塑劑).xlsx
+++ b/Result/checksun_type/塑化劑(可塑劑).xlsx
@@ -883,42 +883,42 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>1.32</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>4488.958</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>11.45</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>10514.261</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>11.3</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>75.06</t>
+          <t>77.66</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>9.71</t>
+          <t>11.17</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>30.68</t>
+          <t>13.10</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-2.16</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,12 +1014,12 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>10514</t>
+          <t>4489</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1034,53 +1034,53 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>5.59</t>
+          <t>3.90</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>5.32</t>
+          <t>7.97</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>10.702</t>
+          <t>11.02</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>10.16</v>
+        <v>10.21</v>
       </c>
       <c r="AN2" t="n">
-        <v>10.28</v>
+        <v>10.31</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>10.23</t>
+          <t>10.25</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>511.12</t>
+          <t>1276.76</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-106.37</t>
+          <t>-97.09</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>39462022.65553977</t>
+          <t>39515005.27446809</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>120192159.0</t>
+          <t>51209846.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>126910257</v>
+        <v>134651499.8</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>72495141.9</t>
+          <t>75791338.0</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>37850914.22</v>
+        <v>38375557.84</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>54415115</t>
+          <t>58860161</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>8078031.522023421</t>
+          <t>9865813.569280198</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>27320222.47340429</t>
+          <t>19698614.82919247</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>120192159.0</t>
+          <t>51209846.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>7.62</t>
+          <t>9.05</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
@@ -1216,7 +1216,7 @@
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>63.5</t>
+          <t>63.47</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>15251</t>
+          <t>15454</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
+          <t>11.4</t>
+        </is>
+      </c>
+      <c r="CE2" t="inlineStr">
+        <is>
+          <t>11.6</t>
+        </is>
+      </c>
+      <c r="CF2" t="inlineStr">
+        <is>
           <t>11.15</t>
         </is>
       </c>
-      <c r="CE2" t="inlineStr">
-        <is>
-          <t>11.8</t>
-        </is>
-      </c>
-      <c r="CF2" t="inlineStr">
-        <is>
-          <t>11.05</t>
-        </is>
-      </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>11.3</t>
+          <t>11.45</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>5.61</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>34269.781</t>
+          <t>10514.261</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>64.03</t>
+          <t>75.06</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>100.00</t>
+          <t>30.68</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>-2.16</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,12 +1444,12 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>10514</t>
+          <t>4489</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1464,53 +1464,53 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>8.84</t>
+          <t>5.59</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>5.32</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-1.45</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>10.382</t>
+          <t>10.702</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>10.1</v>
+        <v>10.16</v>
       </c>
       <c r="AN3" t="n">
-        <v>10.25</v>
+        <v>10.28</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>10.21</t>
+          <t>10.23</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>175.85</t>
+          <t>511.12</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-114.52</t>
+          <t>-106.37</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>39462022.65553977</t>
+          <t>39515005.27446809</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>390794197.0</t>
+          <t>120192159.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>105490556.2</v>
+        <v>126910257</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>64310538.4</t>
+          <t>72495141.9</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>35931629.66</v>
+        <v>37850914.22</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>41180017</t>
+          <t>54415115</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>4579451.34904508</t>
+          <t>8078031.522023421</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>29841549.05537103</t>
+          <t>27320222.47340429</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>390794197.0</t>
+          <t>120192159.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
@@ -1631,12 +1631,12 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
@@ -1646,7 +1646,7 @@
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>63.5</t>
+          <t>63.47</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>15251</t>
+          <t>15454</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,17 +1696,17 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>10.7</t>
+          <t>11.15</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>11.75</t>
+          <t>11.8</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>10.7</t>
+          <t>11.05</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>5.61</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>6273.16</t>
+          <t>34269.781</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>10.7</t>
+          <t>11.3</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>5.31</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>9.10</t>
+          <t>64.03</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>3.88</t>
+          <t>9.71</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>18.31</t>
+          <t>100.00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2.95</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,12 +1874,12 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>10514</t>
+          <t>4489</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1889,58 +1889,58 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>88.73</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>6.77</t>
+          <t>8.84</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-1.69</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>10.022</t>
+          <t>10.382</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>10.04</v>
+        <v>10.1</v>
       </c>
       <c r="AN4" t="n">
-        <v>10.22</v>
+        <v>10.25</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>10.19</t>
+          <t>10.21</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>59.14</t>
+          <t>175.85</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-120.90</t>
+          <t>-114.52</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>39462022.65553977</t>
+          <t>39515005.27446809</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>66856122.0</t>
+          <t>390794197.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>30264685.8</v>
+        <v>105490556.2</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>27741544.4</t>
+          <t>64310538.4</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>28239844.66</v>
+        <v>35931629.66</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>2523141</t>
+          <t>41180017</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-13657.32483236655</t>
+          <t>4579451.34904508</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>3384599.063345991</t>
+          <t>29841549.05537103</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>66856122.0</t>
+          <t>390794197.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>7.62</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
@@ -2061,22 +2061,22 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>63.5</t>
+          <t>63.47</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>15251</t>
+          <t>15454</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>10.3</t>
+          <t>10.7</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>10.8</t>
+          <t>11.75</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>10.3</t>
+          <t>10.7</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>10.7</t>
+          <t>11.3</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>4.95</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>4353.738</t>
+          <t>6273.16</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>10.35</t>
+          <t>10.7</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>8.41</t>
+          <t>6.55</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-8.98</t>
+          <t>9.10</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>3.88</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12.70</t>
+          <t>18.31</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>4.65</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,12 +2304,12 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>10514</t>
+          <t>4489</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2319,58 +2319,58 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>65.15</t>
+          <t>88.73</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>6.05</t>
+          <t>6.77</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-1.69</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>9.76</t>
+          <t>10.022</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>10.01</v>
+        <v>10.04</v>
       </c>
       <c r="AN5" t="n">
-        <v>10.19</v>
+        <v>10.22</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>10.18</t>
+          <t>10.19</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>8.30</t>
+          <t>59.14</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-123.99</t>
+          <t>-120.90</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>39462022.65553977</t>
+          <t>39515005.27446809</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>44205175.0</t>
+          <t>66856122.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>20413759.2</v>
+        <v>30264685.8</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>22428185.2</t>
+          <t>27741544.4</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>27064322.42</v>
+        <v>28239844.66</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-2014426</t>
+          <t>2523141</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-631522.122682977</t>
+          <t>-13657.32483236655</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>175728.5724764355</t>
+          <t>3384599.063345991</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>44205175.0</t>
+          <t>66856122.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-1.43</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
@@ -2496,17 +2496,17 @@
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>63.5</t>
+          <t>63.47</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>15251</t>
+          <t>15454</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>9.89</t>
+          <t>10.3</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>10.35</t>
+          <t>10.8</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>9.89</t>
+          <t>10.3</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>10.35</t>
+          <t>10.7</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2593,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>4.95</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1272.664</t>
+          <t>4353.738</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>9.86</t>
+          <t>10.35</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>12.74</t>
+          <t>9.61</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-13.84</t>
+          <t>-8.98</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-4.27</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>3.71</t>
+          <t>12.70</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>4.65</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,68 +2734,68 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>10514</t>
+          <t>4489</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>66.2</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>35.12</t>
+          <t>65.15</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>6.05</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-4.05</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>9.596</t>
+          <t>9.76</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>10</v>
+        <v>10.01</v>
       </c>
       <c r="AN6" t="n">
-        <v>10.18</v>
+        <v>10.19</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>10.17</t>
+          <t>10.18</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-31.61</t>
+          <t>8.30</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-124.49</t>
+          <t>-123.99</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>39462022.65553977</t>
+          <t>39515005.27446809</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>12503632.0</t>
+          <t>44205175.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>16931176.2</v>
+        <v>20413759.2</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>19650448.5</t>
+          <t>22428185.2</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>26328965.82</v>
+        <v>27064322.42</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-2719272</t>
+          <t>-2014426</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-778294.9763483247</t>
+          <t>-631522.122682977</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-1987760.970639944</t>
+          <t>175728.5724764355</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>12503632.0</t>
+          <t>44205175.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-6.10</t>
+          <t>-1.43</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -2921,22 +2921,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>63.5</t>
+          <t>63.47</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>15251</t>
+          <t>15454</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>9.76</t>
+          <t>9.89</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>9.92</t>
+          <t>10.35</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>9.73</t>
+          <t>9.89</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>9.86</t>
+          <t>10.35</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1348.47</t>
+          <t>1272.664</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>9.86</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>14.16</t>
+          <t>13.89</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-19.13</t>
+          <t>-13.84</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-5.83</t>
+          <t>-4.27</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>3.93</t>
+          <t>3.71</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,51 +3164,51 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>10514</t>
+          <t>4489</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>29.25</t>
+          <t>66.2</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>13.05</t>
+          <t>35.12</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-4.52</t>
+          <t>-4.05</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-1.5</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>9.57</t>
+          <t>9.596</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>10.02</v>
+        <v>10</v>
       </c>
       <c r="AN7" t="n">
         <v>10.18</v>
@@ -3220,17 +3220,17 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-57.55</t>
+          <t>-31.61</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-122.55</t>
+          <t>-124.49</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>39462022.65553977</t>
+          <t>39515005.27446809</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>13093655.0</t>
+          <t>12503632.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>18080026.8</v>
+        <v>16931176.2</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>22355788.3</t>
+          <t>19650448.5</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>26291263.5</v>
+        <v>26328965.82</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-4275761</t>
+          <t>-2719272</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-558392.068295303</t>
+          <t>-778294.9763483247</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-1610874.961854778</t>
+          <t>-1987760.970639944</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>13093655.0</t>
+          <t>12503632.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-7.62</t>
+          <t>-6.10</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
@@ -3351,7 +3351,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3361,12 +3361,12 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>63.5</t>
+          <t>63.47</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>15251</t>
+          <t>15454</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>9.76</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>9.88</t>
+          <t>9.92</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>9.73</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>9.86</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1560.548</t>
+          <t>1348.47</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>15.93</t>
+          <t>15.28</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-3.14</t>
+          <t>-19.13</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-7.77</t>
+          <t>-5.83</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>4.55</t>
+          <t>3.93</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,63 +3594,63 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>10514</t>
+          <t>4489</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>9.91</t>
+          <t>29.25</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>13.05</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-0.50</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-5.00</t>
+          <t>-4.52</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-1.5</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>9.548</t>
+          <t>9.57</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>10.05</v>
+        <v>10.02</v>
       </c>
       <c r="AN8" t="n">
-        <v>10.17</v>
+        <v>10.18</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>10.18</t>
+          <t>10.17</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-87.49</t>
+          <t>-57.55</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
@@ -3660,7 +3660,7 @@
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-119.31</t>
+          <t>-122.55</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>39462022.65553977</t>
+          <t>39515005.27446809</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>14664845.0</t>
+          <t>13093655.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>23130520.6</v>
+        <v>18080026.8</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>23880046.8</t>
+          <t>22355788.3</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>26473396.54</v>
+        <v>26291263.5</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-749526</t>
+          <t>-4275761</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-367031.5421935803</t>
+          <t>-558392.068295303</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-1078151.8792383</t>
+          <t>-1610874.961854778</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>14664845.0</t>
+          <t>13093655.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-9.52</t>
+          <t>-7.62</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3761,7 +3761,7 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
@@ -3796,7 +3796,7 @@
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>63.5</t>
+          <t>63.47</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>15251</t>
+          <t>15454</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>9.46</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>9.55</t>
+          <t>9.88</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>9.27</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1859.149</t>
+          <t>1560.548</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>9.39</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>17.03</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>-3.14</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-8.83</t>
+          <t>-7.77</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>5.43</t>
+          <t>4.55</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-2.45</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,73 +4024,73 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>10514</t>
+          <t>4489</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.91</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>5.13</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-2.67</t>
+          <t>-0.50</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-4.39</t>
+          <t>-5.00</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>9.648</t>
+          <t>9.548</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>10.09</v>
+        <v>10.05</v>
       </c>
       <c r="AN9" t="n">
-        <v>10.18</v>
+        <v>10.17</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>10.19</t>
+          <t>10.18</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-117.02</t>
+          <t>-87.49</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-115.08</t>
+          <t>-119.31</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>39462022.65553977</t>
+          <t>39515005.27446809</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>17601489.0</t>
+          <t>14664845.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>25218403</v>
+        <v>23130520.6</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>24916958.1</t>
+          <t>23880046.8</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>26498584.58</v>
+        <v>26473396.54</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>301444</t>
+          <t>-749526</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-237736.9354581767</t>
+          <t>-367031.5421935803</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-446955.2655276731</t>
+          <t>-1078151.8792383</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>17601489.0</t>
+          <t>14664845.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-10.57</t>
+          <t>-9.52</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4191,7 +4191,7 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
@@ -4211,7 +4211,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>63.5</t>
+          <t>63.47</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>15251</t>
+          <t>15454</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
+          <t>9.46</t>
+        </is>
+      </c>
+      <c r="CE9" t="inlineStr">
+        <is>
           <t>9.55</t>
         </is>
       </c>
-      <c r="CE9" t="inlineStr">
-        <is>
-          <t>9.63</t>
-        </is>
-      </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>9.38</t>
+          <t>9.27</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>9.39</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2806.058</t>
+          <t>1859.149</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>9.53</t>
+          <t>9.39</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>15.66</t>
+          <t>17.99</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-12.07</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-7.48</t>
+          <t>-8.83</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>8.19</t>
+          <t>5.43</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-2.45</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,12 +4454,12 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>10514</t>
+          <t>4489</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -4474,53 +4474,53 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-2.66</t>
+          <t>-2.67</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-3.58</t>
+          <t>-4.39</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>9.790000000000001</t>
+          <t>9.648</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>10.15</v>
+        <v>10.09</v>
       </c>
       <c r="AN10" t="n">
-        <v>10.19</v>
+        <v>10.18</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>10.19</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-141.34</t>
+          <t>-117.02</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-110.67</t>
+          <t>-115.08</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>39462022.65553977</t>
+          <t>39515005.27446809</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>26792260.0</t>
+          <t>17601489.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>24442611.2</v>
+        <v>25218403</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>27798303.7</t>
+          <t>24916958.1</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>26345925.2</v>
+        <v>26498584.58</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-3355692</t>
+          <t>301444</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-199697.2390819047</t>
+          <t>-237736.9354581767</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>156076.4421134964</t>
+          <t>-446955.2655276731</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>26792260.0</t>
+          <t>17601489.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-9.24</t>
+          <t>-10.57</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4621,7 +4621,7 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
@@ -4641,22 +4641,22 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>63.5</t>
+          <t>63.47</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>15251</t>
+          <t>15454</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>9.73</t>
+          <t>9.55</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>9.73</t>
+          <t>9.63</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>9.38</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>9.53</t>
+          <t>9.39</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4743,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1866.918</t>
+          <t>2806.058</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>9.73</t>
+          <t>9.53</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>13.89</t>
+          <t>16.77</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-17.77</t>
+          <t>-12.07</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-5.53</t>
+          <t>-7.48</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>5.45</t>
+          <t>8.19</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,73 +4884,73 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>10514</t>
+          <t>4489</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>15.38</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>8.89</t>
+          <t>5.13</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-2.45</t>
+          <t>-2.66</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>-3.58</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>9.974</t>
+          <t>9.790000000000001</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>10.21</v>
+        <v>10.15</v>
       </c>
       <c r="AN11" t="n">
-        <v>10.2</v>
+        <v>10.19</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>10.22</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-177.09</t>
+          <t>-141.34</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-106.90</t>
+          <t>-110.67</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>39462022.65553977</t>
+          <t>39515005.27446809</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>18247885.0</t>
+          <t>26792260.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>22369720.8</v>
+        <v>24442611.2</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>27203179.9</t>
+          <t>27798303.7</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>26271252.44</v>
+        <v>26345925.2</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-4833459</t>
+          <t>-3355692</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-264383.362935614</t>
+          <t>-199697.2390819047</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>27250.68723968416</t>
+          <t>156076.4421134964</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>18247885.0</t>
+          <t>26792260.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-7.33</t>
+          <t>-9.24</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5051,7 +5051,7 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>63.5</t>
+          <t>63.47</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>15251</t>
+          <t>15454</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>9.77</t>
+          <t>9.73</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>9.95</t>
+          <t>9.73</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>9.73</t>
+          <t>9.53</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-4.1</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>3938.682</t>
+          <t>1866.918</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>9.59</t>
+          <t>9.73</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>15.13</t>
+          <t>15.02</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-2.69</t>
+          <t>-17.77</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-6.89</t>
+          <t>-5.53</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11.49</t>
+          <t>5.45</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-4.07</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,51 +5314,51 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>10514</t>
+          <t>4489</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>15.38</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>12.9</t>
+          <t>8.89</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-5.31</t>
+          <t>-2.45</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>10.128</t>
+          <t>9.974</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>10.25</v>
+        <v>10.21</v>
       </c>
       <c r="AN12" t="n">
         <v>10.2</v>
@@ -5370,17 +5370,17 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-268.37</t>
+          <t>-177.09</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-103.85</t>
+          <t>-106.90</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>39462022.65553977</t>
+          <t>39515005.27446809</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>38346124.0</t>
+          <t>18247885.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>26631549.8</v>
+        <v>22369720.8</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>27366657.0</t>
+          <t>27203179.9</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>26177335.2</v>
+        <v>26271252.44</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-735107</t>
+          <t>-4833459</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-317407.7356947591</t>
+          <t>-264383.362935614</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>757709.4057328217</t>
+          <t>27250.68723968416</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>38346124.0</t>
+          <t>18247885.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-8.67</t>
+          <t>-7.33</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>63.5</t>
+          <t>63.47</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>15251</t>
+          <t>15454</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>9.99</t>
+          <t>9.77</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>9.99</t>
+          <t>9.95</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>9.58</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>9.59</t>
+          <t>9.73</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/塑化劑(可塑劑).xlsx
+++ b/Result/checksun_type/塑化劑(可塑劑).xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【d1】;【d2】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>-3.08</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>4488.958</t>
+          <t>4250.244</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>11.45</t>
+          <t>11.1</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>77.66</t>
+          <t>73.78</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>11.17</t>
+          <t>7.77</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13.10</t>
+          <t>12.40</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,83 +1014,75 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>4489</t>
+          <t>4250</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>82.05</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>3.90</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>7.97</t>
-        </is>
+          <t>94.02</t>
+        </is>
+      </c>
+      <c r="AH2" t="n">
+        <v>-0.63</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>8.99</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
+          <t>0.56</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>11.17</t>
+        </is>
+      </c>
+      <c r="AM2" t="n">
+        <v>10.25</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>10.33</v>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>10.27</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>297.70</t>
+        </is>
+      </c>
+      <c r="AQ2" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
           <t>0.54</t>
         </is>
       </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>11.02</t>
-        </is>
-      </c>
-      <c r="AM2" t="n">
-        <v>10.21</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>10.31</v>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>10.25</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>1276.76</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>0.22</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>0.02</t>
-        </is>
-      </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>0.54</t>
-        </is>
-      </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-97.09</t>
+          <t>-88.63</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1092,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>39515005.27446809</t>
+          <t>39559567.71883853</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>51209846.0</t>
+          <t>47317394.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>134651499.8</v>
+        <v>135273943.6</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>75791338.0</t>
+          <t>77843851.4</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>38375557.84</v>
+        <v>38862439.4</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>58860161</t>
+          <t>57430092</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>9865813.569280198</t>
+          <t>10437086.8982393</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>19698614.82919247</t>
+          <t>13579090.20751438</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>51209846.0</t>
+          <t>47317394.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1148,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>9.05</t>
+          <t>5.71</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1181,7 +1173,7 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1201,22 +1193,22 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1241,12 +1233,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>63.47</t>
+          <t>63.25</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>15454</t>
+          <t>14982</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1258,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>11.4</t>
+          <t>11.35</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>11.6</t>
+          <t>11.35</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>11.15</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>11.45</t>
+          <t>11.1</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1303,7 +1295,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【d1】;【d2】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1313,12 +1305,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>10514.261</t>
+          <t>4488.958</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1320,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>11.3</t>
+          <t>11.45</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1330,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>-3.15</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>75.06</t>
+          <t>77.66</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1405,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>9.71</t>
+          <t>11.17</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1415,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>30.68</t>
+          <t>13.10</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-2.16</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,12 +1436,12 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>4489</t>
+          <t>4250</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1462,56 +1454,48 @@
           <t>100.0</t>
         </is>
       </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>5.59</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>5.32</t>
-        </is>
+      <c r="AH3" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>7.97</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>10.702</t>
+          <t>11.02</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>10.16</v>
+        <v>10.21</v>
       </c>
       <c r="AN3" t="n">
-        <v>10.28</v>
+        <v>10.31</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>10.23</t>
+          <t>10.25</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>511.12</t>
-        </is>
-      </c>
-      <c r="AQ3" t="inlineStr">
-        <is>
-          <t>0.14</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>-0.03</t>
-        </is>
+          <t>1276.76</t>
+        </is>
+      </c>
+      <c r="AQ3" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>0.02</v>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
@@ -1520,7 +1504,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-106.37</t>
+          <t>-97.09</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1514,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>39515005.27446809</t>
+          <t>39559567.71883853</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>120192159.0</t>
+          <t>51209846.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>126910257</v>
+        <v>134651499.8</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>72495141.9</t>
+          <t>75791338.0</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>37850914.22</v>
+        <v>38375557.84</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>54415115</t>
+          <t>58860161</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>8078031.522023421</t>
+          <t>9865813.569280198</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>27320222.47340429</t>
+          <t>19698614.82919247</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>120192159.0</t>
+          <t>51209846.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1570,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>7.62</t>
+          <t>9.05</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1611,7 +1595,7 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
@@ -1631,12 +1615,12 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
@@ -1646,7 +1630,7 @@
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1671,12 +1655,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>63.47</t>
+          <t>63.25</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>15454</t>
+          <t>14982</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1680,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
+          <t>11.4</t>
+        </is>
+      </c>
+      <c r="CE3" t="inlineStr">
+        <is>
+          <t>11.6</t>
+        </is>
+      </c>
+      <c r="CF3" t="inlineStr">
+        <is>
           <t>11.15</t>
         </is>
       </c>
-      <c r="CE3" t="inlineStr">
-        <is>
-          <t>11.8</t>
-        </is>
-      </c>
-      <c r="CF3" t="inlineStr">
-        <is>
-          <t>11.05</t>
-        </is>
-      </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>11.3</t>
+          <t>11.45</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1733,7 +1717,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【d1】;【d2】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1743,12 +1727,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>5.61</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>34269.781</t>
+          <t>10514.261</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1768,17 +1752,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>-1.8</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>64.03</t>
+          <t>75.06</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1853,17 +1837,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>100.00</t>
+          <t>30.68</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>-2.16</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,12 +1858,12 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>4489</t>
+          <t>4250</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1892,56 +1876,48 @@
           <t>100.0</t>
         </is>
       </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>8.84</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>2.78</t>
-        </is>
+      <c r="AH4" t="n">
+        <v>5.59</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>5.32</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-1.45</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>10.382</t>
+          <t>10.702</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>10.1</v>
+        <v>10.16</v>
       </c>
       <c r="AN4" t="n">
-        <v>10.25</v>
+        <v>10.28</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>10.21</t>
+          <t>10.23</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>175.85</t>
-        </is>
-      </c>
-      <c r="AQ4" t="inlineStr">
-        <is>
-          <t>0.06</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>-0.08</t>
-        </is>
+          <t>511.12</t>
+        </is>
+      </c>
+      <c r="AQ4" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>-0.03</v>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
@@ -1950,7 +1926,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-114.52</t>
+          <t>-106.37</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1936,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>39515005.27446809</t>
+          <t>39559567.71883853</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>390794197.0</t>
+          <t>120192159.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>105490556.2</v>
+        <v>126910257</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>64310538.4</t>
+          <t>72495141.9</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>35931629.66</v>
+        <v>37850914.22</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>41180017</t>
+          <t>54415115</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>4579451.34904508</t>
+          <t>8078031.522023421</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>29841549.05537103</t>
+          <t>27320222.47340429</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>390794197.0</t>
+          <t>120192159.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2041,7 +2017,7 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
@@ -2061,12 +2037,12 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
@@ -2076,7 +2052,7 @@
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2101,12 +2077,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>63.47</t>
+          <t>63.25</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>15454</t>
+          <t>14982</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,17 +2102,17 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>10.7</t>
+          <t>11.15</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>11.75</t>
+          <t>11.8</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>10.7</t>
+          <t>11.05</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2163,7 +2139,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【d1】;【d2】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2173,12 +2149,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>5.61</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>6273.16</t>
+          <t>34269.781</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2164,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>10.7</t>
+          <t>11.3</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2174,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>6.55</t>
+          <t>-1.8</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>9.10</t>
+          <t>64.03</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2249,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>3.88</t>
+          <t>9.71</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2259,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>18.31</t>
+          <t>100.00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2.95</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,12 +2280,12 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>4489</t>
+          <t>4250</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2319,59 +2295,51 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>88.73</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>6.77</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>-0.22</t>
-        </is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="AH5" t="n">
+        <v>8.84</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>2.78</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-1.69</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>10.022</t>
+          <t>10.382</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>10.04</v>
+        <v>10.1</v>
       </c>
       <c r="AN5" t="n">
-        <v>10.22</v>
+        <v>10.25</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>10.19</t>
+          <t>10.21</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>59.14</t>
-        </is>
-      </c>
-      <c r="AQ5" t="inlineStr">
-        <is>
-          <t>-0.05</t>
-        </is>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>-0.11</t>
-        </is>
+          <t>175.85</t>
+        </is>
+      </c>
+      <c r="AQ5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>-0.08</v>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
@@ -2380,7 +2348,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-120.90</t>
+          <t>-114.52</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2358,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>39515005.27446809</t>
+          <t>39559567.71883853</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>66856122.0</t>
+          <t>390794197.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>30264685.8</v>
+        <v>105490556.2</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>27741544.4</t>
+          <t>64310538.4</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>28239844.66</v>
+        <v>35931629.66</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>2523141</t>
+          <t>41180017</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-13657.32483236655</t>
+          <t>4579451.34904508</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>3384599.063345991</t>
+          <t>29841549.05537103</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>66856122.0</t>
+          <t>390794197.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2414,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>7.62</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2471,7 +2439,7 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
@@ -2491,22 +2459,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2531,12 +2499,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>63.47</t>
+          <t>63.25</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>15454</t>
+          <t>14982</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2524,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>10.3</t>
+          <t>10.7</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>10.8</t>
+          <t>11.75</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>10.3</t>
+          <t>10.7</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>10.7</t>
+          <t>11.3</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2591,11 +2559,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>【d】</t>
-        </is>
-      </c>
+      <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
           <t>1313</t>
@@ -2603,12 +2567,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>4.95</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>4353.738</t>
+          <t>6273.16</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2582,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>10.35</t>
+          <t>10.7</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2592,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>9.61</t>
+          <t>3.6</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-8.98</t>
+          <t>9.10</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2667,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>3.88</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2677,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12.70</t>
+          <t>18.31</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>4.65</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,12 +2698,12 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>4489</t>
+          <t>4250</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2749,59 +2713,51 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>65.15</t>
-        </is>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>6.05</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>-2.51</t>
-        </is>
+          <t>88.73</t>
+        </is>
+      </c>
+      <c r="AH6" t="n">
+        <v>6.77</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>-0.22</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-1.69</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>9.76</t>
+          <t>10.022</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>10.01</v>
+        <v>10.04</v>
       </c>
       <c r="AN6" t="n">
-        <v>10.19</v>
+        <v>10.22</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>10.18</t>
+          <t>10.19</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>8.30</t>
-        </is>
-      </c>
-      <c r="AQ6" t="inlineStr">
-        <is>
-          <t>-0.12</t>
-        </is>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>-0.13</t>
-        </is>
+          <t>59.14</t>
+        </is>
+      </c>
+      <c r="AQ6" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>-0.11</v>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
@@ -2810,7 +2766,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-123.99</t>
+          <t>-120.90</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2776,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>39515005.27446809</t>
+          <t>39559567.71883853</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>44205175.0</t>
+          <t>66856122.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>20413759.2</v>
+        <v>30264685.8</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>22428185.2</t>
+          <t>27741544.4</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>27064322.42</v>
+        <v>28239844.66</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-2014426</t>
+          <t>2523141</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-631522.122682977</t>
+          <t>-13657.32483236655</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>175728.5724764355</t>
+          <t>3384599.063345991</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>44205175.0</t>
+          <t>66856122.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2832,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-1.43</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2901,7 +2857,7 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -2926,17 +2882,17 @@
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2961,12 +2917,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>63.47</t>
+          <t>63.25</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>15454</t>
+          <t>14982</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2942,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>9.89</t>
+          <t>10.3</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>10.35</t>
+          <t>10.8</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>9.89</t>
+          <t>10.3</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>10.35</t>
+          <t>10.7</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3021,11 +2977,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>【e】</t>
-        </is>
-      </c>
+      <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
           <t>1313</t>
@@ -3033,12 +2985,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>4.95</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1272.664</t>
+          <t>4353.738</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3000,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>9.86</t>
+          <t>10.35</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3010,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>13.89</t>
+          <t>6.76</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-13.84</t>
+          <t>-8.98</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3085,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-4.27</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3095,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>3.71</t>
+          <t>12.70</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>4.65</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,74 +3116,66 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>4489</t>
+          <t>4250</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>66.2</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>35.12</t>
-        </is>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>-4.05</t>
-        </is>
+          <t>65.15</t>
+        </is>
+      </c>
+      <c r="AH7" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>-2.51</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>9.596</t>
+          <t>9.76</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>10</v>
+        <v>10.01</v>
       </c>
       <c r="AN7" t="n">
-        <v>10.18</v>
+        <v>10.19</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>10.17</t>
+          <t>10.18</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-31.61</t>
-        </is>
-      </c>
-      <c r="AQ7" t="inlineStr">
-        <is>
-          <t>-0.17</t>
-        </is>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>-0.13</t>
-        </is>
+          <t>8.30</t>
+        </is>
+      </c>
+      <c r="AQ7" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>-0.13</v>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
@@ -3240,7 +3184,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-124.49</t>
+          <t>-123.99</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3194,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>39515005.27446809</t>
+          <t>39559567.71883853</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>12503632.0</t>
+          <t>44205175.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>16931176.2</v>
+        <v>20413759.2</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>19650448.5</t>
+          <t>22428185.2</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>26328965.82</v>
+        <v>27064322.42</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-2719272</t>
+          <t>-2014426</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-778294.9763483247</t>
+          <t>-631522.122682977</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-1987760.970639944</t>
+          <t>175728.5724764355</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>12503632.0</t>
+          <t>44205175.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3250,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-6.10</t>
+          <t>-1.43</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3331,7 +3275,7 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
@@ -3351,22 +3295,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3391,12 +3335,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>63.47</t>
+          <t>63.25</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>15454</t>
+          <t>14982</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3360,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>9.76</t>
+          <t>9.89</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>9.92</t>
+          <t>10.35</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>9.73</t>
+          <t>9.89</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>9.86</t>
+          <t>10.35</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3407,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1348.47</t>
+          <t>1272.664</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3422,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>9.86</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3432,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>15.28</t>
+          <t>11.17</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-19.13</t>
+          <t>-13.84</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3507,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-5.83</t>
+          <t>-4.27</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3517,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>3.93</t>
+          <t>3.71</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,51 +3538,47 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>4489</t>
+          <t>4250</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>29.25</t>
+          <t>66.2</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>13.05</t>
-        </is>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>1.36</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>-4.52</t>
-        </is>
+          <t>35.12</t>
+        </is>
+      </c>
+      <c r="AH8" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>-4.05</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-1.5</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>9.57</t>
+          <t>9.596</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>10.02</v>
+        <v>10</v>
       </c>
       <c r="AN8" t="n">
         <v>10.18</v>
@@ -3650,18 +3590,14 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-57.55</t>
-        </is>
-      </c>
-      <c r="AQ8" t="inlineStr">
-        <is>
-          <t>-0.19</t>
-        </is>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>-0.12</t>
-        </is>
+          <t>-31.61</t>
+        </is>
+      </c>
+      <c r="AQ8" t="n">
+        <v>-0.17</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>-0.13</v>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
@@ -3670,7 +3606,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-122.55</t>
+          <t>-124.49</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3616,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>39515005.27446809</t>
+          <t>39559567.71883853</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>13093655.0</t>
+          <t>12503632.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>18080026.8</v>
+        <v>16931176.2</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>22355788.3</t>
+          <t>19650448.5</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>26291263.5</v>
+        <v>26328965.82</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-4275761</t>
+          <t>-2719272</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-558392.068295303</t>
+          <t>-778294.9763483247</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-1610874.961854778</t>
+          <t>-1987760.970639944</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>13093655.0</t>
+          <t>12503632.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3672,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-7.62</t>
+          <t>-6.10</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3761,7 +3697,7 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
@@ -3781,7 +3717,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3791,12 +3727,12 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3821,12 +3757,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>63.47</t>
+          <t>63.25</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>15454</t>
+          <t>14982</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3782,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>9.76</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>9.88</t>
+          <t>9.92</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>9.73</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>9.86</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3829,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1560.548</t>
+          <t>1348.47</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3844,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3854,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>17.03</t>
+          <t>12.61</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-3.14</t>
+          <t>-19.13</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3929,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-7.77</t>
+          <t>-5.83</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +3939,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>4.55</t>
+          <t>3.93</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,74 +3960,66 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>4489</t>
+          <t>4250</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>9.91</t>
+          <t>29.25</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>3.3</t>
-        </is>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>-0.50</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>-5.00</t>
-        </is>
+          <t>13.05</t>
+        </is>
+      </c>
+      <c r="AH9" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>-4.52</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-1.5</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>9.548</t>
+          <t>9.57</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>10.05</v>
+        <v>10.02</v>
       </c>
       <c r="AN9" t="n">
-        <v>10.17</v>
+        <v>10.18</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>10.18</t>
+          <t>10.17</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-87.49</t>
-        </is>
-      </c>
-      <c r="AQ9" t="inlineStr">
-        <is>
-          <t>-0.19</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>-0.10</t>
-        </is>
+          <t>-57.55</t>
+        </is>
+      </c>
+      <c r="AQ9" t="n">
+        <v>-0.19</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>-0.12</v>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
@@ -4100,7 +4028,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-119.31</t>
+          <t>-122.55</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4038,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>39515005.27446809</t>
+          <t>39559567.71883853</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>14664845.0</t>
+          <t>13093655.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>23130520.6</v>
+        <v>18080026.8</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>23880046.8</t>
+          <t>22355788.3</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>26473396.54</v>
+        <v>26291263.5</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-749526</t>
+          <t>-4275761</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-367031.5421935803</t>
+          <t>-558392.068295303</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-1078151.8792383</t>
+          <t>-1610874.961854778</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>14664845.0</t>
+          <t>13093655.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4094,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-9.52</t>
+          <t>-7.62</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4191,7 +4119,7 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
@@ -4211,12 +4139,12 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
@@ -4226,7 +4154,7 @@
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4251,12 +4179,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>63.47</t>
+          <t>63.25</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>15454</t>
+          <t>14982</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4204,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>9.46</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>9.55</t>
+          <t>9.88</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>9.27</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4251,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1859.149</t>
+          <t>1560.548</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4266,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>9.39</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4276,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>17.99</t>
+          <t>14.41</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>-3.14</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4351,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-8.83</t>
+          <t>-7.77</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4361,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>5.43</t>
+          <t>4.55</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-2.45</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,74 +4382,66 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>4489</t>
+          <t>4250</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.91</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>5.13</t>
-        </is>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>-2.67</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>-4.39</t>
-        </is>
+          <t>3.3</t>
+        </is>
+      </c>
+      <c r="AH10" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>-5</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>9.648</t>
+          <t>9.548</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>10.09</v>
+        <v>10.05</v>
       </c>
       <c r="AN10" t="n">
-        <v>10.18</v>
+        <v>10.17</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>10.19</t>
+          <t>10.18</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-117.02</t>
-        </is>
-      </c>
-      <c r="AQ10" t="inlineStr">
-        <is>
-          <t>-0.18</t>
-        </is>
-      </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>-0.08</t>
-        </is>
+          <t>-87.49</t>
+        </is>
+      </c>
+      <c r="AQ10" t="n">
+        <v>-0.19</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>-0.1</v>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
@@ -4530,7 +4450,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-115.08</t>
+          <t>-119.31</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4460,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>39515005.27446809</t>
+          <t>39559567.71883853</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>17601489.0</t>
+          <t>14664845.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>25218403</v>
+        <v>23130520.6</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>24916958.1</t>
+          <t>23880046.8</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>26498584.58</v>
+        <v>26473396.54</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>301444</t>
+          <t>-749526</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-237736.9354581767</t>
+          <t>-367031.5421935803</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-446955.2655276731</t>
+          <t>-1078151.8792383</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>17601489.0</t>
+          <t>14664845.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4516,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-10.57</t>
+          <t>-9.52</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4621,7 +4541,7 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
@@ -4641,7 +4561,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4651,12 +4571,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4681,12 +4601,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>63.47</t>
+          <t>63.25</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>15454</t>
+          <t>14982</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4626,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
+          <t>9.46</t>
+        </is>
+      </c>
+      <c r="CE10" t="inlineStr">
+        <is>
           <t>9.55</t>
         </is>
       </c>
-      <c r="CE10" t="inlineStr">
-        <is>
-          <t>9.63</t>
-        </is>
-      </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>9.38</t>
+          <t>9.27</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>9.39</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4673,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2806.058</t>
+          <t>1859.149</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4688,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>9.53</t>
+          <t>9.39</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4698,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>16.77</t>
+          <t>15.41</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-12.07</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4773,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-7.48</t>
+          <t>-8.83</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4783,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>8.19</t>
+          <t>5.43</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-2.45</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,12 +4804,12 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>4489</t>
+          <t>4250</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4902,56 +4822,48 @@
           <t>5.13</t>
         </is>
       </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>-2.66</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>-3.58</t>
-        </is>
+      <c r="AH11" t="n">
+        <v>-2.67</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>-4.39</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>9.790000000000001</t>
+          <t>9.648</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>10.15</v>
+        <v>10.09</v>
       </c>
       <c r="AN11" t="n">
-        <v>10.19</v>
+        <v>10.18</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>10.19</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-141.34</t>
-        </is>
-      </c>
-      <c r="AQ11" t="inlineStr">
-        <is>
-          <t>-0.14</t>
-        </is>
-      </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>-0.06</t>
-        </is>
+          <t>-117.02</t>
+        </is>
+      </c>
+      <c r="AQ11" t="n">
+        <v>-0.18</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>-0.08</v>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
@@ -4960,7 +4872,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-110.67</t>
+          <t>-115.08</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4882,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>39515005.27446809</t>
+          <t>39559567.71883853</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>26792260.0</t>
+          <t>17601489.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>24442611.2</v>
+        <v>25218403</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>27798303.7</t>
+          <t>24916958.1</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>26345925.2</v>
+        <v>26498584.58</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-3355692</t>
+          <t>301444</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-199697.2390819047</t>
+          <t>-237736.9354581767</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>156076.4421134964</t>
+          <t>-446955.2655276731</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>26792260.0</t>
+          <t>17601489.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +4938,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-9.24</t>
+          <t>-10.57</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5051,7 +4963,7 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
@@ -5071,7 +4983,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,12 +4993,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5111,12 +5023,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>63.47</t>
+          <t>63.25</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>15454</t>
+          <t>14982</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5048,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>9.73</t>
+          <t>9.55</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>9.73</t>
+          <t>9.63</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>9.38</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>9.53</t>
+          <t>9.39</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5173,7 +5085,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5183,12 +5095,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1866.918</t>
+          <t>2806.058</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5110,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>9.73</t>
+          <t>9.53</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5120,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>15.02</t>
+          <t>14.14</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-17.77</t>
+          <t>-12.07</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5195,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-5.53</t>
+          <t>-7.48</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5205,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>5.45</t>
+          <t>8.19</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,74 +5226,66 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>4489</t>
+          <t>4250</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>15.38</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>8.89</t>
-        </is>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>-2.45</t>
-        </is>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>-2.34</t>
-        </is>
+          <t>5.13</t>
+        </is>
+      </c>
+      <c r="AH12" t="n">
+        <v>-2.66</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>-3.58</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>9.974</t>
+          <t>9.790000000000001</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>10.21</v>
+        <v>10.15</v>
       </c>
       <c r="AN12" t="n">
-        <v>10.2</v>
+        <v>10.19</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>10.22</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-177.09</t>
-        </is>
-      </c>
-      <c r="AQ12" t="inlineStr">
-        <is>
-          <t>-0.10</t>
-        </is>
-      </c>
-      <c r="AR12" t="inlineStr">
-        <is>
-          <t>-0.04</t>
-        </is>
+          <t>-141.34</t>
+        </is>
+      </c>
+      <c r="AQ12" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>-0.06</v>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
@@ -5390,7 +5294,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-106.90</t>
+          <t>-110.67</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5304,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>39515005.27446809</t>
+          <t>39559567.71883853</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>18247885.0</t>
+          <t>26792260.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>22369720.8</v>
+        <v>24442611.2</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>27203179.9</t>
+          <t>27798303.7</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>26271252.44</v>
+        <v>26345925.2</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-4833459</t>
+          <t>-3355692</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-264383.362935614</t>
+          <t>-199697.2390819047</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>27250.68723968416</t>
+          <t>156076.4421134964</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>18247885.0</t>
+          <t>26792260.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5360,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-7.33</t>
+          <t>-9.24</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5481,7 +5385,7 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
@@ -5501,7 +5405,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,12 +5415,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5541,12 +5445,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>63.47</t>
+          <t>63.25</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>15454</t>
+          <t>14982</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5470,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>9.77</t>
+          <t>9.73</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>9.95</t>
+          <t>9.73</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>9.73</t>
+          <t>9.53</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/塑化劑(可塑劑).xlsx
+++ b/Result/checksun_type/塑化劑(可塑劑).xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-3.08</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>4250.244</t>
+          <t>3380.77</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>11.05</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,17 +913,17 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>4.83</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>73.78</t>
+          <t>62.06</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -933,77 +933,77 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
+          <t>2025-12-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>2025-12-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
           <t>2025-10-27 00:00:00</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>2025-10-28 00:00:00</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>2025-09-23 00:00:00</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>2025-10-16 00:00:00</t>
-        </is>
-      </c>
       <c r="Q2" t="inlineStr">
         <is>
+          <t>11.05</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>11.05</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
           <t>10.65</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>10.3</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>10.55</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>10.3</t>
-        </is>
-      </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>7.77</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>7.28</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12.40</t>
+          <t>9.87</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>2.82</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,66 +1014,66 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>4250</t>
+          <t>3381</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>82.05</t>
+          <t>77.14</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>94.02</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="AH2" t="n">
-        <v>-0.63</v>
+        <v>-1.69</v>
       </c>
       <c r="AI2" t="n">
-        <v>8.99</v>
+        <v>9.07</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>11.17</t>
+          <t>11.24</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>10.25</v>
+        <v>10.3</v>
       </c>
       <c r="AN2" t="n">
-        <v>10.33</v>
+        <v>10.34</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>10.27</t>
+          <t>10.28</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>297.70</t>
+          <t>156.80</t>
         </is>
       </c>
       <c r="AQ2" t="n">
-        <v>0.24</v>
+        <v>0.26</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.06</v>
+        <v>0.1</v>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-88.63</t>
+          <t>-81.30</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1092,48 +1092,48 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>39559567.71883853</t>
+          <t>39581766.4115983</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>47317394.0</t>
+          <t>36836029.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>135273943.6</v>
+        <v>129269925</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>77843851.4</t>
+          <t>79767305.4</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>38862439.4</v>
+        <v>38038480.18</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>57430092</t>
+          <t>49502619</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>10437086.8982393</t>
+          <t>10088280.19730277</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>13579090.20751438</t>
+          <t>8169843.34215185</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>47317394.0</t>
+          <t>36836029.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="BF2" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>5.71</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1193,12 +1193,12 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>63.25</t>
+          <t>63.12</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>14982</t>
+          <t>14914</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1258,22 +1258,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>11.35</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>11.35</t>
+          <t>11.1</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>10.7</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>11.05</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1295,7 +1295,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1305,12 +1305,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>-3.08</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>4488.958</t>
+          <t>4250.244</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>11.45</t>
+          <t>11.1</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1330,17 +1330,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-3.15</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>4.83</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>77.66</t>
+          <t>73.78</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1355,49 +1355,49 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
+          <t>2025-12-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2025-12-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
           <t>2025-10-27 00:00:00</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>2025-10-28 00:00:00</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>2025-09-23 00:00:00</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>2025-10-16 00:00:00</t>
-        </is>
-      </c>
       <c r="Q3" t="inlineStr">
         <is>
+          <t>11.05</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
           <t>10.65</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>10.3</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>10.55</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>10.3</t>
-        </is>
-      </c>
       <c r="V3" t="inlineStr">
         <is>
           <t>0</t>
@@ -1405,27 +1405,27 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>11.17</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>7.28</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13.10</t>
+          <t>12.40</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1436,75 +1436,75 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>4250</t>
+          <t>3381</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>82.05</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>94.02</t>
         </is>
       </c>
       <c r="AH3" t="n">
-        <v>3.9</v>
+        <v>-0.63</v>
       </c>
       <c r="AI3" t="n">
-        <v>7.97</v>
+        <v>8.99</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
+          <t>0.56</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>11.17</t>
+        </is>
+      </c>
+      <c r="AM3" t="n">
+        <v>10.25</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>10.33</v>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>10.27</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>297.70</t>
+        </is>
+      </c>
+      <c r="AQ3" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
           <t>0.54</t>
         </is>
       </c>
-      <c r="AL3" t="inlineStr">
-        <is>
-          <t>11.02</t>
-        </is>
-      </c>
-      <c r="AM3" t="n">
-        <v>10.21</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>10.31</v>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>10.25</t>
-        </is>
-      </c>
-      <c r="AP3" t="inlineStr">
-        <is>
-          <t>1276.76</t>
-        </is>
-      </c>
-      <c r="AQ3" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="AS3" t="inlineStr">
-        <is>
-          <t>0.54</t>
-        </is>
-      </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-97.09</t>
+          <t>-88.63</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1514,43 +1514,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>39559567.71883853</t>
+          <t>39581766.4115983</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>51209846.0</t>
+          <t>47317394.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>134651499.8</v>
+        <v>135273943.6</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>75791338.0</t>
+          <t>77843851.4</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>38375557.84</v>
+        <v>38862439.4</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>58860161</t>
+          <t>57430092</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>9865813.569280198</t>
+          <t>10437086.8982393</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>19698614.82919247</t>
+          <t>13579090.20751438</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>51209846.0</t>
+          <t>47317394.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>9.05</t>
+          <t>5.71</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1615,22 +1615,22 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>63.25</t>
+          <t>63.12</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>14982</t>
+          <t>14914</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1680,22 +1680,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>11.4</t>
+          <t>11.35</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>11.6</t>
+          <t>11.35</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>11.15</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>11.45</t>
+          <t>11.1</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1717,7 +1717,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>10514.261</t>
+          <t>4488.958</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>11.3</t>
+          <t>11.45</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1752,17 +1752,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-1.8</t>
+          <t>-3.62</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>4.83</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>75.06</t>
+          <t>77.66</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1777,49 +1777,49 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
+          <t>2025-12-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2025-12-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
           <t>2025-10-27 00:00:00</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>2025-10-28 00:00:00</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>2025-09-23 00:00:00</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>2025-10-16 00:00:00</t>
-        </is>
-      </c>
       <c r="Q4" t="inlineStr">
         <is>
+          <t>11.05</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
           <t>10.65</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>10.3</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>10.55</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>10.3</t>
-        </is>
-      </c>
       <c r="V4" t="inlineStr">
         <is>
           <t>0</t>
@@ -1827,27 +1827,27 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>9.71</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>7.28</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>30.68</t>
+          <t>13.10</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-2.16</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1858,12 +1858,12 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>4250</t>
+          <t>3381</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1877,47 +1877,47 @@
         </is>
       </c>
       <c r="AH4" t="n">
-        <v>5.59</v>
+        <v>3.9</v>
       </c>
       <c r="AI4" t="n">
-        <v>5.32</v>
+        <v>7.97</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>10.702</t>
+          <t>11.02</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>10.16</v>
+        <v>10.21</v>
       </c>
       <c r="AN4" t="n">
-        <v>10.28</v>
+        <v>10.31</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>10.23</t>
+          <t>10.25</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>511.12</t>
+          <t>1276.76</t>
         </is>
       </c>
       <c r="AQ4" t="n">
-        <v>0.14</v>
+        <v>0.22</v>
       </c>
       <c r="AR4" t="n">
-        <v>-0.03</v>
+        <v>0.02</v>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-106.37</t>
+          <t>-97.09</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1936,43 +1936,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>39559567.71883853</t>
+          <t>39581766.4115983</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>120192159.0</t>
+          <t>51209846.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>126910257</v>
+        <v>134651499.8</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>72495141.9</t>
+          <t>75791338.0</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>37850914.22</v>
+        <v>38375557.84</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>54415115</t>
+          <t>58860161</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>8078031.522023421</t>
+          <t>9865813.569280198</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>27320222.47340429</t>
+          <t>19698614.82919247</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>120192159.0</t>
+          <t>51209846.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>7.62</t>
+          <t>9.05</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2037,12 +2037,12 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2077,12 +2077,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>63.25</t>
+          <t>63.12</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>14982</t>
+          <t>14914</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2102,22 +2102,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
+          <t>11.4</t>
+        </is>
+      </c>
+      <c r="CE4" t="inlineStr">
+        <is>
+          <t>11.6</t>
+        </is>
+      </c>
+      <c r="CF4" t="inlineStr">
+        <is>
           <t>11.15</t>
         </is>
       </c>
-      <c r="CE4" t="inlineStr">
-        <is>
-          <t>11.8</t>
-        </is>
-      </c>
-      <c r="CF4" t="inlineStr">
-        <is>
-          <t>11.05</t>
-        </is>
-      </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>11.3</t>
+          <t>11.45</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2139,7 +2139,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2149,12 +2149,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>5.61</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>34269.781</t>
+          <t>10514.261</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2174,17 +2174,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-1.8</t>
+          <t>-2.26</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>4.83</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>64.03</t>
+          <t>75.06</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2199,49 +2199,49 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
+          <t>2025-12-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2025-12-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
           <t>2025-10-27 00:00:00</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>2025-10-28 00:00:00</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>2025-09-23 00:00:00</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>2025-10-16 00:00:00</t>
-        </is>
-      </c>
       <c r="Q5" t="inlineStr">
         <is>
+          <t>11.05</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
           <t>10.65</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>10.3</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>10.55</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>10.3</t>
-        </is>
-      </c>
       <c r="V5" t="inlineStr">
         <is>
           <t>0</t>
@@ -2249,27 +2249,27 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>9.71</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>7.28</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>100.00</t>
+          <t>30.68</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>-2.16</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2280,12 +2280,12 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>4250</t>
+          <t>3381</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2299,47 +2299,47 @@
         </is>
       </c>
       <c r="AH5" t="n">
-        <v>8.84</v>
+        <v>5.59</v>
       </c>
       <c r="AI5" t="n">
-        <v>2.78</v>
+        <v>5.32</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-1.45</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>10.382</t>
+          <t>10.702</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>10.1</v>
+        <v>10.16</v>
       </c>
       <c r="AN5" t="n">
-        <v>10.25</v>
+        <v>10.28</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>10.21</t>
+          <t>10.23</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>175.85</t>
+          <t>511.12</t>
         </is>
       </c>
       <c r="AQ5" t="n">
-        <v>0.06</v>
+        <v>0.14</v>
       </c>
       <c r="AR5" t="n">
-        <v>-0.08</v>
+        <v>-0.03</v>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-114.52</t>
+          <t>-106.37</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2358,43 +2358,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>39559567.71883853</t>
+          <t>39581766.4115983</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>390794197.0</t>
+          <t>120192159.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>105490556.2</v>
+        <v>126910257</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>64310538.4</t>
+          <t>72495141.9</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>35931629.66</v>
+        <v>37850914.22</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>41180017</t>
+          <t>54415115</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>4579451.34904508</t>
+          <t>8078031.522023421</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>29841549.05537103</t>
+          <t>27320222.47340429</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>390794197.0</t>
+          <t>120192159.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2459,12 +2459,12 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>63.25</t>
+          <t>63.12</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>14982</t>
+          <t>14914</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2524,17 +2524,17 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>10.7</t>
+          <t>11.15</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>11.75</t>
+          <t>11.8</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>10.7</t>
+          <t>11.05</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2559,7 +2559,11 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr"/>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>【d1】</t>
+        </is>
+      </c>
       <c r="B6" t="inlineStr">
         <is>
           <t>1313</t>
@@ -2567,12 +2571,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>5.61</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>6273.16</t>
+          <t>34269.781</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2582,7 +2586,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>10.7</t>
+          <t>11.3</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2592,17 +2596,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t>-2.26</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>4.83</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>9.10</t>
+          <t>64.03</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2617,49 +2621,49 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
+          <t>2025-12-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2025-12-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
           <t>2025-10-27 00:00:00</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>2025-10-28 00:00:00</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>2025-09-23 00:00:00</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>2025-10-16 00:00:00</t>
-        </is>
-      </c>
       <c r="Q6" t="inlineStr">
         <is>
+          <t>11.05</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
           <t>10.65</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>10.3</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>10.55</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>10.3</t>
-        </is>
-      </c>
       <c r="V6" t="inlineStr">
         <is>
           <t>0</t>
@@ -2667,27 +2671,27 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>3.88</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>7.28</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>18.31</t>
+          <t>100.00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2.95</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2698,12 +2702,12 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>4250</t>
+          <t>3381</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2713,51 +2717,51 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>88.73</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH6" t="n">
-        <v>6.77</v>
+        <v>8.84</v>
       </c>
       <c r="AI6" t="n">
-        <v>-0.22</v>
+        <v>2.78</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-1.69</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>10.022</t>
+          <t>10.382</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>10.04</v>
+        <v>10.1</v>
       </c>
       <c r="AN6" t="n">
-        <v>10.22</v>
+        <v>10.25</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>10.19</t>
+          <t>10.21</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>59.14</t>
+          <t>175.85</t>
         </is>
       </c>
       <c r="AQ6" t="n">
-        <v>-0.05</v>
+        <v>0.06</v>
       </c>
       <c r="AR6" t="n">
-        <v>-0.11</v>
+        <v>-0.08</v>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
@@ -2766,7 +2770,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-120.90</t>
+          <t>-114.52</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2776,43 +2780,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>39559567.71883853</t>
+          <t>39581766.4115983</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>66856122.0</t>
+          <t>390794197.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>30264685.8</v>
+        <v>105490556.2</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>27741544.4</t>
+          <t>64310538.4</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>28239844.66</v>
+        <v>35931629.66</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>2523141</t>
+          <t>41180017</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-13657.32483236655</t>
+          <t>4579451.34904508</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>3384599.063345991</t>
+          <t>29841549.05537103</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>66856122.0</t>
+          <t>390794197.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2832,7 +2836,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>7.62</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2877,22 +2881,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2917,12 +2921,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>63.25</t>
+          <t>63.12</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>14982</t>
+          <t>14914</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2942,22 +2946,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>10.3</t>
+          <t>10.7</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>10.8</t>
+          <t>11.75</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>10.3</t>
+          <t>10.7</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>10.7</t>
+          <t>11.3</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -2977,7 +2981,11 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr"/>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B7" t="inlineStr">
         <is>
           <t>1313</t>
@@ -2985,12 +2993,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>4.95</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>4353.738</t>
+          <t>6273.16</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3000,7 +3008,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>10.35</t>
+          <t>10.7</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3010,17 +3018,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>6.76</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>4.83</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-8.98</t>
+          <t>9.10</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3035,49 +3043,49 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
+          <t>2025-12-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2025-12-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
           <t>2025-10-27 00:00:00</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>2025-10-28 00:00:00</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>2025-09-23 00:00:00</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>2025-10-16 00:00:00</t>
-        </is>
-      </c>
       <c r="Q7" t="inlineStr">
         <is>
+          <t>11.05</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
           <t>10.65</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>10.3</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>10.55</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>10.3</t>
-        </is>
-      </c>
       <c r="V7" t="inlineStr">
         <is>
           <t>0</t>
@@ -3085,27 +3093,27 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>7.28</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12.70</t>
+          <t>18.31</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>4.65</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3116,12 +3124,12 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>4250</t>
+          <t>3381</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3131,51 +3139,51 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>65.15</t>
+          <t>88.73</t>
         </is>
       </c>
       <c r="AH7" t="n">
-        <v>6.05</v>
+        <v>6.77</v>
       </c>
       <c r="AI7" t="n">
-        <v>-2.51</v>
+        <v>-0.22</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-1.69</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>9.76</t>
+          <t>10.022</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>10.01</v>
+        <v>10.04</v>
       </c>
       <c r="AN7" t="n">
-        <v>10.19</v>
+        <v>10.22</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>10.18</t>
+          <t>10.19</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>8.30</t>
+          <t>59.14</t>
         </is>
       </c>
       <c r="AQ7" t="n">
-        <v>-0.12</v>
+        <v>-0.05</v>
       </c>
       <c r="AR7" t="n">
-        <v>-0.13</v>
+        <v>-0.11</v>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
@@ -3184,7 +3192,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-123.99</t>
+          <t>-120.90</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3194,43 +3202,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>39559567.71883853</t>
+          <t>39581766.4115983</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>44205175.0</t>
+          <t>66856122.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>20413759.2</v>
+        <v>30264685.8</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>22428185.2</t>
+          <t>27741544.4</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>27064322.42</v>
+        <v>28239844.66</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-2014426</t>
+          <t>2523141</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-631522.122682977</t>
+          <t>-13657.32483236655</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>175728.5724764355</t>
+          <t>3384599.063345991</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>44205175.0</t>
+          <t>66856122.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3250,7 +3258,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-1.43</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3300,17 +3308,17 @@
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3335,12 +3343,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>63.25</t>
+          <t>63.12</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>14982</t>
+          <t>14914</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3360,22 +3368,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>9.89</t>
+          <t>10.3</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>10.35</t>
+          <t>10.8</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>9.89</t>
+          <t>10.3</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>10.35</t>
+          <t>10.7</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3397,7 +3405,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3407,12 +3415,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>4.95</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1272.664</t>
+          <t>4353.738</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3422,7 +3430,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>9.86</t>
+          <t>10.35</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3432,17 +3440,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>11.17</t>
+          <t>6.33</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>4.83</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-13.84</t>
+          <t>-8.98</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3457,49 +3465,49 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
+          <t>2025-12-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>2025-12-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
           <t>2025-10-27 00:00:00</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>2025-10-28 00:00:00</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>2025-09-23 00:00:00</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>2025-10-16 00:00:00</t>
-        </is>
-      </c>
       <c r="Q8" t="inlineStr">
         <is>
+          <t>11.05</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
           <t>10.65</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>10.3</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>10.55</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>10.3</t>
-        </is>
-      </c>
       <c r="V8" t="inlineStr">
         <is>
           <t>0</t>
@@ -3507,27 +3515,27 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-4.27</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>7.28</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>3.71</t>
+          <t>12.70</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>4.65</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3538,63 +3546,63 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>4250</t>
+          <t>3381</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>66.2</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>35.12</t>
+          <t>65.15</t>
         </is>
       </c>
       <c r="AH8" t="n">
-        <v>2.75</v>
+        <v>6.05</v>
       </c>
       <c r="AI8" t="n">
-        <v>-4.05</v>
+        <v>-2.51</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>9.596</t>
+          <t>9.76</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>10</v>
+        <v>10.01</v>
       </c>
       <c r="AN8" t="n">
-        <v>10.18</v>
+        <v>10.19</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>10.17</t>
+          <t>10.18</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-31.61</t>
+          <t>8.30</t>
         </is>
       </c>
       <c r="AQ8" t="n">
-        <v>-0.17</v>
+        <v>-0.12</v>
       </c>
       <c r="AR8" t="n">
         <v>-0.13</v>
@@ -3606,7 +3614,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-124.49</t>
+          <t>-123.99</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3616,43 +3624,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>39559567.71883853</t>
+          <t>39581766.4115983</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>12503632.0</t>
+          <t>44205175.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>16931176.2</v>
+        <v>20413759.2</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>19650448.5</t>
+          <t>22428185.2</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>26328965.82</v>
+        <v>27064322.42</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-2719272</t>
+          <t>-2014426</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-778294.9763483247</t>
+          <t>-631522.122682977</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-1987760.970639944</t>
+          <t>175728.5724764355</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>12503632.0</t>
+          <t>44205175.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3672,7 +3680,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-6.10</t>
+          <t>-1.43</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3717,22 +3725,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3757,12 +3765,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>63.25</t>
+          <t>63.12</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>14982</t>
+          <t>14914</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3782,22 +3790,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>9.76</t>
+          <t>9.89</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>9.92</t>
+          <t>10.35</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>9.73</t>
+          <t>9.89</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>9.86</t>
+          <t>10.35</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3829,12 +3837,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1348.47</t>
+          <t>1272.664</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3844,7 +3852,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>9.86</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3854,17 +3862,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>12.61</t>
+          <t>10.77</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>4.83</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-19.13</t>
+          <t>-13.84</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3879,49 +3887,49 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
+          <t>2025-12-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>2025-12-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
           <t>2025-10-27 00:00:00</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>2025-10-28 00:00:00</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>2025-09-23 00:00:00</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>2025-10-16 00:00:00</t>
-        </is>
-      </c>
       <c r="Q9" t="inlineStr">
         <is>
+          <t>11.05</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
           <t>10.65</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>10.3</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>10.55</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>10.3</t>
-        </is>
-      </c>
       <c r="V9" t="inlineStr">
         <is>
           <t>0</t>
@@ -3929,27 +3937,27 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-5.83</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>7.28</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>3.93</t>
+          <t>3.71</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -3960,47 +3968,47 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>4250</t>
+          <t>3381</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>29.25</t>
+          <t>66.2</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>13.05</t>
+          <t>35.12</t>
         </is>
       </c>
       <c r="AH9" t="n">
-        <v>1.36</v>
+        <v>2.75</v>
       </c>
       <c r="AI9" t="n">
-        <v>-4.52</v>
+        <v>-4.05</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-1.5</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>9.57</t>
+          <t>9.596</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>10.02</v>
+        <v>10</v>
       </c>
       <c r="AN9" t="n">
         <v>10.18</v>
@@ -4012,14 +4020,14 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-57.55</t>
+          <t>-31.61</t>
         </is>
       </c>
       <c r="AQ9" t="n">
-        <v>-0.19</v>
+        <v>-0.17</v>
       </c>
       <c r="AR9" t="n">
-        <v>-0.12</v>
+        <v>-0.13</v>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
@@ -4028,7 +4036,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-122.55</t>
+          <t>-124.49</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4038,43 +4046,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>39559567.71883853</t>
+          <t>39581766.4115983</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>13093655.0</t>
+          <t>12503632.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>18080026.8</v>
+        <v>16931176.2</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>22355788.3</t>
+          <t>19650448.5</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>26291263.5</v>
+        <v>26328965.82</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-4275761</t>
+          <t>-2719272</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-558392.068295303</t>
+          <t>-778294.9763483247</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-1610874.961854778</t>
+          <t>-1987760.970639944</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>13093655.0</t>
+          <t>12503632.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4094,7 +4102,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-7.62</t>
+          <t>-6.10</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4139,7 +4147,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4149,12 +4157,12 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4179,12 +4187,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>63.25</t>
+          <t>63.12</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>14982</t>
+          <t>14914</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4204,22 +4212,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>9.76</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>9.88</t>
+          <t>9.92</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>9.73</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>9.86</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4251,12 +4259,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1560.548</t>
+          <t>1348.47</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4266,7 +4274,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4276,17 +4284,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>14.41</t>
+          <t>12.22</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>4.83</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-3.14</t>
+          <t>-19.13</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4301,49 +4309,49 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
+          <t>2025-12-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>2025-12-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
           <t>2025-10-27 00:00:00</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>2025-10-28 00:00:00</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>2025-09-23 00:00:00</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>2025-10-16 00:00:00</t>
-        </is>
-      </c>
       <c r="Q10" t="inlineStr">
         <is>
+          <t>11.05</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
           <t>10.65</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>10.3</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>10.55</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>10.3</t>
-        </is>
-      </c>
       <c r="V10" t="inlineStr">
         <is>
           <t>0</t>
@@ -4351,27 +4359,27 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-7.77</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>7.28</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>4.55</t>
+          <t>3.93</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4382,66 +4390,66 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>4250</t>
+          <t>3381</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>9.91</t>
+          <t>29.25</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>13.05</t>
         </is>
       </c>
       <c r="AH10" t="n">
-        <v>-0.5</v>
+        <v>1.36</v>
       </c>
       <c r="AI10" t="n">
-        <v>-5</v>
+        <v>-4.52</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-1.5</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>9.548</t>
+          <t>9.57</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>10.05</v>
+        <v>10.02</v>
       </c>
       <c r="AN10" t="n">
-        <v>10.17</v>
+        <v>10.18</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>10.18</t>
+          <t>10.17</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-87.49</t>
+          <t>-57.55</t>
         </is>
       </c>
       <c r="AQ10" t="n">
         <v>-0.19</v>
       </c>
       <c r="AR10" t="n">
-        <v>-0.1</v>
+        <v>-0.12</v>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
@@ -4450,7 +4458,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-119.31</t>
+          <t>-122.55</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4460,43 +4468,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>39559567.71883853</t>
+          <t>39581766.4115983</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>14664845.0</t>
+          <t>13093655.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>23130520.6</v>
+        <v>18080026.8</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>23880046.8</t>
+          <t>22355788.3</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>26473396.54</v>
+        <v>26291263.5</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-749526</t>
+          <t>-4275761</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-367031.5421935803</t>
+          <t>-558392.068295303</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-1078151.8792383</t>
+          <t>-1610874.961854778</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>14664845.0</t>
+          <t>13093655.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4516,7 +4524,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-9.52</t>
+          <t>-7.62</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4561,7 +4569,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4576,7 +4584,7 @@
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4601,12 +4609,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>63.25</t>
+          <t>63.12</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>14982</t>
+          <t>14914</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4626,22 +4634,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>9.46</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>9.55</t>
+          <t>9.88</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>9.27</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4673,12 +4681,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1859.149</t>
+          <t>1560.548</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4688,7 +4696,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>9.39</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4698,17 +4706,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>15.41</t>
+          <t>14.03</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>4.83</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>-3.14</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4723,49 +4731,49 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
+          <t>2025-12-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2025-12-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
           <t>2025-10-27 00:00:00</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>2025-10-28 00:00:00</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>2025-09-23 00:00:00</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>2025-10-16 00:00:00</t>
-        </is>
-      </c>
       <c r="Q11" t="inlineStr">
         <is>
+          <t>11.05</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
           <t>10.65</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>10.3</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>10.55</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>10.3</t>
-        </is>
-      </c>
       <c r="V11" t="inlineStr">
         <is>
           <t>0</t>
@@ -4773,27 +4781,27 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-8.83</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>7.28</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>5.43</t>
+          <t>4.55</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-2.45</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4804,66 +4812,66 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>4250</t>
+          <t>3381</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.91</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>5.13</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="AH11" t="n">
-        <v>-2.67</v>
+        <v>-0.5</v>
       </c>
       <c r="AI11" t="n">
-        <v>-4.39</v>
+        <v>-5</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>9.648</t>
+          <t>9.548</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>10.09</v>
+        <v>10.05</v>
       </c>
       <c r="AN11" t="n">
-        <v>10.18</v>
+        <v>10.17</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>10.19</t>
+          <t>10.18</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-117.02</t>
+          <t>-87.49</t>
         </is>
       </c>
       <c r="AQ11" t="n">
-        <v>-0.18</v>
+        <v>-0.19</v>
       </c>
       <c r="AR11" t="n">
-        <v>-0.08</v>
+        <v>-0.1</v>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
@@ -4872,7 +4880,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-115.08</t>
+          <t>-119.31</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4882,43 +4890,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>39559567.71883853</t>
+          <t>39581766.4115983</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>17601489.0</t>
+          <t>14664845.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>25218403</v>
+        <v>23130520.6</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>24916958.1</t>
+          <t>23880046.8</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>26498584.58</v>
+        <v>26473396.54</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>301444</t>
+          <t>-749526</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-237736.9354581767</t>
+          <t>-367031.5421935803</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-446955.2655276731</t>
+          <t>-1078151.8792383</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>17601489.0</t>
+          <t>14664845.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -4938,7 +4946,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-10.57</t>
+          <t>-9.52</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -4983,7 +4991,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -4993,12 +5001,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5023,12 +5031,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>63.25</t>
+          <t>63.12</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>14982</t>
+          <t>14914</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5048,22 +5056,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
+          <t>9.46</t>
+        </is>
+      </c>
+      <c r="CE11" t="inlineStr">
+        <is>
           <t>9.55</t>
         </is>
       </c>
-      <c r="CE11" t="inlineStr">
-        <is>
-          <t>9.63</t>
-        </is>
-      </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>9.38</t>
+          <t>9.27</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>9.39</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5095,12 +5103,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2806.058</t>
+          <t>1859.149</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5110,7 +5118,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>9.53</t>
+          <t>9.39</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5120,17 +5128,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>14.14</t>
+          <t>15.02</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>4.83</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-12.07</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5145,49 +5153,49 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
+          <t>2025-12-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>2025-12-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
           <t>2025-10-27 00:00:00</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>2025-10-28 00:00:00</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>2025-09-23 00:00:00</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>2025-10-16 00:00:00</t>
-        </is>
-      </c>
       <c r="Q12" t="inlineStr">
         <is>
+          <t>11.05</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
           <t>10.65</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>10.3</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>10.55</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>10.3</t>
-        </is>
-      </c>
       <c r="V12" t="inlineStr">
         <is>
           <t>0</t>
@@ -5195,27 +5203,27 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-7.48</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>7.28</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>8.19</t>
+          <t>5.43</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-2.45</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5226,12 +5234,12 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>4250</t>
+          <t>3381</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5245,47 +5253,47 @@
         </is>
       </c>
       <c r="AH12" t="n">
-        <v>-2.66</v>
+        <v>-2.67</v>
       </c>
       <c r="AI12" t="n">
-        <v>-3.58</v>
+        <v>-4.39</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>9.790000000000001</t>
+          <t>9.648</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>10.15</v>
+        <v>10.09</v>
       </c>
       <c r="AN12" t="n">
-        <v>10.19</v>
+        <v>10.18</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>10.19</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-141.34</t>
+          <t>-117.02</t>
         </is>
       </c>
       <c r="AQ12" t="n">
-        <v>-0.14</v>
+        <v>-0.18</v>
       </c>
       <c r="AR12" t="n">
-        <v>-0.06</v>
+        <v>-0.08</v>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
@@ -5294,7 +5302,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-110.67</t>
+          <t>-115.08</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5304,43 +5312,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>39559567.71883853</t>
+          <t>39581766.4115983</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>26792260.0</t>
+          <t>17601489.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>24442611.2</v>
+        <v>25218403</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>27798303.7</t>
+          <t>24916958.1</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>26345925.2</v>
+        <v>26498584.58</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-3355692</t>
+          <t>301444</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-199697.2390819047</t>
+          <t>-237736.9354581767</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>156076.4421134964</t>
+          <t>-446955.2655276731</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>26792260.0</t>
+          <t>17601489.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5360,7 +5368,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-9.24</t>
+          <t>-10.57</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5405,7 +5413,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5415,12 +5423,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5445,12 +5453,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>63.25</t>
+          <t>63.12</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>14982</t>
+          <t>14914</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5470,22 +5478,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>9.73</t>
+          <t>9.55</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>9.73</t>
+          <t>9.63</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>9.38</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>9.53</t>
+          <t>9.39</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/塑化劑(可塑劑).xlsx
+++ b/Result/checksun_type/塑化劑(可塑劑).xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>3380.77</t>
+          <t>4587.903</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,74 +898,74 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>11.2</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2.27</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>-26.61</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>2025-12-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>2025-12-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>2025-10-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>2025-10-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
           <t>11.05</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>4.83</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>62.06</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>2025-12-08</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>2025-12-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>2025-12-09 00:00:00</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>2025-10-27 00:00:00</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>2025-10-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
         <is>
           <t>11.05</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>11.05</t>
-        </is>
-      </c>
       <c r="T2" t="inlineStr">
         <is>
           <t>10.65</t>
@@ -978,7 +978,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>9.87</t>
+          <t>13.39</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2.82</t>
+          <t>5.71</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,75 +1014,75 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>3381</t>
+          <t>4588</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>77.14</t>
+          <t>84.28</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>86.4</t>
+          <t>81.16</t>
         </is>
       </c>
       <c r="AH2" t="n">
-        <v>-1.69</v>
+        <v>-0.18</v>
       </c>
       <c r="AI2" t="n">
-        <v>9.07</v>
+        <v>8.33</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
+          <t>0.62</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>11.22</t>
+        </is>
+      </c>
+      <c r="AM2" t="n">
+        <v>10.36</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>10.36</v>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>10.29</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>104.81</t>
+        </is>
+      </c>
+      <c r="AQ2" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
           <t>0.54</t>
         </is>
       </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>11.24</t>
-        </is>
-      </c>
-      <c r="AM2" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>10.34</v>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>10.28</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>156.80</t>
-        </is>
-      </c>
-      <c r="AQ2" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>0.54</t>
-        </is>
-      </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-81.30</t>
+          <t>-74.66</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1092,48 +1092,48 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>39581766.4115983</t>
+          <t>39632180.51906779</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>36836029.0</t>
+          <t>50183303.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>129269925</v>
+        <v>61147746.2</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>79767305.4</t>
+          <t>83319151.2</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>38038480.18</v>
+        <v>38351204.62</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>49502619</t>
+          <t>-22171405</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>10088280.19730277</t>
+          <t>9333186.321232235</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>8169843.34215185</t>
+          <t>5180170.002844289</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>36836029.0</t>
+          <t>50183303.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="BF2" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>6.67</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1193,12 +1193,12 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>63.12</t>
+          <t>63.09</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>14914</t>
+          <t>15117</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1263,17 +1263,17 @@
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>11.25</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>10.7</t>
+          <t>10.55</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>11.05</t>
+          <t>11.2</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1305,12 +1305,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-3.08</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>4250.244</t>
+          <t>3380.77</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>11.05</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1330,22 +1330,22 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>4.83</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>73.78</t>
+          <t>62.06</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -1360,7 +1360,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2025-12-09 00:00:00</t>
+          <t>2025-12-10 00:00:00</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1385,7 +1385,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>11.05</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -1415,17 +1415,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12.40</t>
+          <t>9.87</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>2.82</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1436,66 +1436,66 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>3381</t>
+          <t>4588</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>82.05</t>
+          <t>77.14</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>94.02</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="AH3" t="n">
-        <v>-0.63</v>
+        <v>-1.69</v>
       </c>
       <c r="AI3" t="n">
-        <v>8.99</v>
+        <v>9.07</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>11.17</t>
+          <t>11.24</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>10.25</v>
+        <v>10.3</v>
       </c>
       <c r="AN3" t="n">
-        <v>10.33</v>
+        <v>10.34</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>10.27</t>
+          <t>10.28</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>297.70</t>
+          <t>156.80</t>
         </is>
       </c>
       <c r="AQ3" t="n">
-        <v>0.24</v>
+        <v>0.26</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.06</v>
+        <v>0.1</v>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-88.63</t>
+          <t>-81.30</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1514,48 +1514,48 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>39581766.4115983</t>
+          <t>39632180.51906779</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>47317394.0</t>
+          <t>36836029.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>135273943.6</v>
+        <v>129269925</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>77843851.4</t>
+          <t>79767305.4</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>38862439.4</v>
+        <v>38038480.18</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>57430092</t>
+          <t>49502619</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>10437086.8982393</t>
+          <t>10088280.19730277</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>13579090.20751438</t>
+          <t>8169843.34215185</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>47317394.0</t>
+          <t>36836029.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="BF3" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>5.71</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1615,12 +1615,12 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>63.12</t>
+          <t>63.09</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>14914</t>
+          <t>15117</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1680,22 +1680,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>11.35</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>11.35</t>
+          <t>11.1</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>10.7</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>11.05</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>-3.08</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>4488.958</t>
+          <t>4250.244</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>11.45</t>
+          <t>11.1</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1752,17 +1752,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-3.62</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>4.83</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>77.66</t>
+          <t>73.78</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2025-12-09 00:00:00</t>
+          <t>2025-12-10 00:00:00</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -1837,17 +1837,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13.10</t>
+          <t>12.40</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1858,75 +1858,75 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>3381</t>
+          <t>4588</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>82.05</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>94.02</t>
         </is>
       </c>
       <c r="AH4" t="n">
-        <v>3.9</v>
+        <v>-0.63</v>
       </c>
       <c r="AI4" t="n">
-        <v>7.97</v>
+        <v>8.99</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
+          <t>0.56</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>11.17</t>
+        </is>
+      </c>
+      <c r="AM4" t="n">
+        <v>10.25</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>10.33</v>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>10.27</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>297.70</t>
+        </is>
+      </c>
+      <c r="AQ4" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
           <t>0.54</t>
         </is>
       </c>
-      <c r="AL4" t="inlineStr">
-        <is>
-          <t>11.02</t>
-        </is>
-      </c>
-      <c r="AM4" t="n">
-        <v>10.21</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>10.31</v>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>10.25</t>
-        </is>
-      </c>
-      <c r="AP4" t="inlineStr">
-        <is>
-          <t>1276.76</t>
-        </is>
-      </c>
-      <c r="AQ4" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="AS4" t="inlineStr">
-        <is>
-          <t>0.54</t>
-        </is>
-      </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-97.09</t>
+          <t>-88.63</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1936,43 +1936,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>39581766.4115983</t>
+          <t>39632180.51906779</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>51209846.0</t>
+          <t>47317394.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>134651499.8</v>
+        <v>135273943.6</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>75791338.0</t>
+          <t>77843851.4</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>38375557.84</v>
+        <v>38862439.4</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>58860161</t>
+          <t>57430092</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>9865813.569280198</t>
+          <t>10437086.8982393</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>19698614.82919247</t>
+          <t>13579090.20751438</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>51209846.0</t>
+          <t>47317394.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>9.05</t>
+          <t>5.71</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2037,22 +2037,22 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2077,12 +2077,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>63.12</t>
+          <t>63.09</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>14914</t>
+          <t>15117</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2102,22 +2102,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>11.4</t>
+          <t>11.35</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>11.6</t>
+          <t>11.35</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>11.15</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>11.45</t>
+          <t>11.1</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2149,12 +2149,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>10514.261</t>
+          <t>4488.958</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>11.3</t>
+          <t>11.45</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2174,17 +2174,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-2.26</t>
+          <t>-2.23</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>4.83</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>75.06</t>
+          <t>77.66</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2204,7 +2204,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2025-12-09 00:00:00</t>
+          <t>2025-12-10 00:00:00</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -2259,17 +2259,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>30.68</t>
+          <t>13.10</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-2.16</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2280,12 +2280,12 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>3381</t>
+          <t>4588</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2299,47 +2299,47 @@
         </is>
       </c>
       <c r="AH5" t="n">
-        <v>5.59</v>
+        <v>3.9</v>
       </c>
       <c r="AI5" t="n">
-        <v>5.32</v>
+        <v>7.97</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>10.702</t>
+          <t>11.02</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>10.16</v>
+        <v>10.21</v>
       </c>
       <c r="AN5" t="n">
-        <v>10.28</v>
+        <v>10.31</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>10.23</t>
+          <t>10.25</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>511.12</t>
+          <t>1276.76</t>
         </is>
       </c>
       <c r="AQ5" t="n">
-        <v>0.14</v>
+        <v>0.22</v>
       </c>
       <c r="AR5" t="n">
-        <v>-0.03</v>
+        <v>0.02</v>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-106.37</t>
+          <t>-97.09</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2358,43 +2358,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>39581766.4115983</t>
+          <t>39632180.51906779</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>120192159.0</t>
+          <t>51209846.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>126910257</v>
+        <v>134651499.8</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>72495141.9</t>
+          <t>75791338.0</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>37850914.22</v>
+        <v>38375557.84</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>54415115</t>
+          <t>58860161</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>8078031.522023421</t>
+          <t>9865813.569280198</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>27320222.47340429</t>
+          <t>19698614.82919247</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>120192159.0</t>
+          <t>51209846.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>7.62</t>
+          <t>9.05</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2459,12 +2459,12 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>63.12</t>
+          <t>63.09</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>14914</t>
+          <t>15117</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2524,22 +2524,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
+          <t>11.4</t>
+        </is>
+      </c>
+      <c r="CE5" t="inlineStr">
+        <is>
+          <t>11.6</t>
+        </is>
+      </c>
+      <c r="CF5" t="inlineStr">
+        <is>
           <t>11.15</t>
         </is>
       </c>
-      <c r="CE5" t="inlineStr">
-        <is>
-          <t>11.8</t>
-        </is>
-      </c>
-      <c r="CF5" t="inlineStr">
-        <is>
-          <t>11.05</t>
-        </is>
-      </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>11.3</t>
+          <t>11.45</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>5.61</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>34269.781</t>
+          <t>10514.261</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2596,17 +2596,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-2.26</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>4.83</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>64.03</t>
+          <t>75.06</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2025-12-09 00:00:00</t>
+          <t>2025-12-10 00:00:00</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -2681,17 +2681,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>100.00</t>
+          <t>30.68</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>-2.16</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2702,12 +2702,12 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>3381</t>
+          <t>4588</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2721,47 +2721,47 @@
         </is>
       </c>
       <c r="AH6" t="n">
-        <v>8.84</v>
+        <v>5.59</v>
       </c>
       <c r="AI6" t="n">
-        <v>2.78</v>
+        <v>5.32</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-1.45</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>10.382</t>
+          <t>10.702</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>10.1</v>
+        <v>10.16</v>
       </c>
       <c r="AN6" t="n">
-        <v>10.25</v>
+        <v>10.28</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>10.21</t>
+          <t>10.23</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>175.85</t>
+          <t>511.12</t>
         </is>
       </c>
       <c r="AQ6" t="n">
-        <v>0.06</v>
+        <v>0.14</v>
       </c>
       <c r="AR6" t="n">
-        <v>-0.08</v>
+        <v>-0.03</v>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
@@ -2770,7 +2770,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-114.52</t>
+          <t>-106.37</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2780,43 +2780,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>39581766.4115983</t>
+          <t>39632180.51906779</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>390794197.0</t>
+          <t>120192159.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>105490556.2</v>
+        <v>126910257</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>64310538.4</t>
+          <t>72495141.9</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>35931629.66</v>
+        <v>37850914.22</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>41180017</t>
+          <t>54415115</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>4579451.34904508</t>
+          <t>8078031.522023421</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>29841549.05537103</t>
+          <t>27320222.47340429</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>390794197.0</t>
+          <t>120192159.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2881,12 +2881,12 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
@@ -2896,7 +2896,7 @@
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2921,12 +2921,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>63.12</t>
+          <t>63.09</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>14914</t>
+          <t>15117</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2946,17 +2946,17 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>10.7</t>
+          <t>11.15</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>11.75</t>
+          <t>11.8</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>10.7</t>
+          <t>11.05</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -2983,7 +2983,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2993,12 +2993,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>5.61</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>6273.16</t>
+          <t>34269.781</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>10.7</t>
+          <t>11.3</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3018,17 +3018,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>4.83</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>9.10</t>
+          <t>64.03</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2025-12-09 00:00:00</t>
+          <t>2025-12-10 00:00:00</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -3103,17 +3103,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>18.31</t>
+          <t>100.00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2.95</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3124,12 +3124,12 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>3381</t>
+          <t>4588</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3139,51 +3139,51 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>88.73</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH7" t="n">
-        <v>6.77</v>
+        <v>8.84</v>
       </c>
       <c r="AI7" t="n">
-        <v>-0.22</v>
+        <v>2.78</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-1.69</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>10.022</t>
+          <t>10.382</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>10.04</v>
+        <v>10.1</v>
       </c>
       <c r="AN7" t="n">
-        <v>10.22</v>
+        <v>10.25</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>10.19</t>
+          <t>10.21</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>59.14</t>
+          <t>175.85</t>
         </is>
       </c>
       <c r="AQ7" t="n">
-        <v>-0.05</v>
+        <v>0.06</v>
       </c>
       <c r="AR7" t="n">
-        <v>-0.11</v>
+        <v>-0.08</v>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
@@ -3192,7 +3192,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-120.90</t>
+          <t>-114.52</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3202,43 +3202,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>39581766.4115983</t>
+          <t>39632180.51906779</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>66856122.0</t>
+          <t>390794197.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>30264685.8</v>
+        <v>105490556.2</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>27741544.4</t>
+          <t>64310538.4</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>28239844.66</v>
+        <v>35931629.66</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>2523141</t>
+          <t>41180017</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-13657.32483236655</t>
+          <t>4579451.34904508</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>3384599.063345991</t>
+          <t>29841549.05537103</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>66856122.0</t>
+          <t>390794197.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>7.62</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3303,22 +3303,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3343,12 +3343,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>63.12</t>
+          <t>63.09</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>14914</t>
+          <t>15117</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3368,22 +3368,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>10.3</t>
+          <t>10.7</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>10.8</t>
+          <t>11.75</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>10.3</t>
+          <t>10.7</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>10.7</t>
+          <t>11.3</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>4.95</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>4353.738</t>
+          <t>6273.16</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3430,7 +3430,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>10.35</t>
+          <t>10.7</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3440,17 +3440,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>6.33</t>
+          <t>4.46</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>4.83</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-8.98</t>
+          <t>9.10</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3470,7 +3470,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2025-12-09 00:00:00</t>
+          <t>2025-12-10 00:00:00</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -3525,17 +3525,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12.70</t>
+          <t>18.31</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>4.65</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3546,12 +3546,12 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>3381</t>
+          <t>4588</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3561,51 +3561,51 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>65.15</t>
+          <t>88.73</t>
         </is>
       </c>
       <c r="AH8" t="n">
-        <v>6.05</v>
+        <v>6.77</v>
       </c>
       <c r="AI8" t="n">
-        <v>-2.51</v>
+        <v>-0.22</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-1.69</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>9.76</t>
+          <t>10.022</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>10.01</v>
+        <v>10.04</v>
       </c>
       <c r="AN8" t="n">
-        <v>10.19</v>
+        <v>10.22</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>10.18</t>
+          <t>10.19</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>8.30</t>
+          <t>59.14</t>
         </is>
       </c>
       <c r="AQ8" t="n">
-        <v>-0.12</v>
+        <v>-0.05</v>
       </c>
       <c r="AR8" t="n">
-        <v>-0.13</v>
+        <v>-0.11</v>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-123.99</t>
+          <t>-120.90</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3624,43 +3624,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>39581766.4115983</t>
+          <t>39632180.51906779</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>44205175.0</t>
+          <t>66856122.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>20413759.2</v>
+        <v>30264685.8</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>22428185.2</t>
+          <t>27741544.4</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>27064322.42</v>
+        <v>28239844.66</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-2014426</t>
+          <t>2523141</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-631522.122682977</t>
+          <t>-13657.32483236655</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>175728.5724764355</t>
+          <t>3384599.063345991</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>44205175.0</t>
+          <t>66856122.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3680,7 +3680,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-1.43</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3730,17 +3730,17 @@
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>63.12</t>
+          <t>63.09</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>14914</t>
+          <t>15117</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3790,22 +3790,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>9.89</t>
+          <t>10.3</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>10.35</t>
+          <t>10.8</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>9.89</t>
+          <t>10.3</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>10.35</t>
+          <t>10.7</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3827,7 +3827,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>4.95</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1272.664</t>
+          <t>4353.738</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3852,7 +3852,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>9.86</t>
+          <t>10.35</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3862,17 +3862,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>10.77</t>
+          <t>7.59</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>4.83</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-13.84</t>
+          <t>-8.98</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3892,7 +3892,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2025-12-09 00:00:00</t>
+          <t>2025-12-10 00:00:00</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -3947,17 +3947,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>3.71</t>
+          <t>12.70</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>4.65</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -3968,63 +3968,63 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>3381</t>
+          <t>4588</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>66.2</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>35.12</t>
+          <t>65.15</t>
         </is>
       </c>
       <c r="AH9" t="n">
-        <v>2.75</v>
+        <v>6.05</v>
       </c>
       <c r="AI9" t="n">
-        <v>-4.05</v>
+        <v>-2.51</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>9.596</t>
+          <t>9.76</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>10</v>
+        <v>10.01</v>
       </c>
       <c r="AN9" t="n">
-        <v>10.18</v>
+        <v>10.19</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>10.17</t>
+          <t>10.18</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-31.61</t>
+          <t>8.30</t>
         </is>
       </c>
       <c r="AQ9" t="n">
-        <v>-0.17</v>
+        <v>-0.12</v>
       </c>
       <c r="AR9" t="n">
         <v>-0.13</v>
@@ -4036,7 +4036,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-124.49</t>
+          <t>-123.99</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4046,43 +4046,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>39581766.4115983</t>
+          <t>39632180.51906779</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>12503632.0</t>
+          <t>44205175.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>16931176.2</v>
+        <v>20413759.2</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>19650448.5</t>
+          <t>22428185.2</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>26328965.82</v>
+        <v>27064322.42</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-2719272</t>
+          <t>-2014426</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-778294.9763483247</t>
+          <t>-631522.122682977</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-1987760.970639944</t>
+          <t>175728.5724764355</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>12503632.0</t>
+          <t>44205175.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-6.10</t>
+          <t>-1.43</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4147,22 +4147,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4187,12 +4187,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>63.12</t>
+          <t>63.09</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>14914</t>
+          <t>15117</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4212,22 +4212,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>9.76</t>
+          <t>9.89</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>9.92</t>
+          <t>10.35</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>9.73</t>
+          <t>9.89</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>9.86</t>
+          <t>10.35</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4259,12 +4259,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1348.47</t>
+          <t>1272.664</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4274,7 +4274,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>9.86</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4284,17 +4284,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>12.22</t>
+          <t>11.96</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>4.83</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-19.13</t>
+          <t>-13.84</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4314,7 +4314,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2025-12-09 00:00:00</t>
+          <t>2025-12-10 00:00:00</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -4369,17 +4369,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>3.93</t>
+          <t>3.71</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4390,47 +4390,47 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>3381</t>
+          <t>4588</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>29.25</t>
+          <t>66.2</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>13.05</t>
+          <t>35.12</t>
         </is>
       </c>
       <c r="AH10" t="n">
-        <v>1.36</v>
+        <v>2.75</v>
       </c>
       <c r="AI10" t="n">
-        <v>-4.52</v>
+        <v>-4.05</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-1.5</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>9.57</t>
+          <t>9.596</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>10.02</v>
+        <v>10</v>
       </c>
       <c r="AN10" t="n">
         <v>10.18</v>
@@ -4442,14 +4442,14 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-57.55</t>
+          <t>-31.61</t>
         </is>
       </c>
       <c r="AQ10" t="n">
-        <v>-0.19</v>
+        <v>-0.17</v>
       </c>
       <c r="AR10" t="n">
-        <v>-0.12</v>
+        <v>-0.13</v>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-122.55</t>
+          <t>-124.49</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4468,43 +4468,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>39581766.4115983</t>
+          <t>39632180.51906779</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>13093655.0</t>
+          <t>12503632.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>18080026.8</v>
+        <v>16931176.2</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>22355788.3</t>
+          <t>19650448.5</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>26291263.5</v>
+        <v>26328965.82</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-4275761</t>
+          <t>-2719272</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-558392.068295303</t>
+          <t>-778294.9763483247</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-1610874.961854778</t>
+          <t>-1987760.970639944</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>13093655.0</t>
+          <t>12503632.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4524,7 +4524,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-7.62</t>
+          <t>-6.10</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4569,22 +4569,22 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4609,12 +4609,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>63.12</t>
+          <t>63.09</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>14914</t>
+          <t>15117</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4634,22 +4634,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>9.76</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>9.88</t>
+          <t>9.92</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>9.73</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>9.86</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1560.548</t>
+          <t>1348.47</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4706,17 +4706,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>14.03</t>
+          <t>13.39</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>4.83</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-3.14</t>
+          <t>-19.13</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4736,7 +4736,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2025-12-09 00:00:00</t>
+          <t>2025-12-10 00:00:00</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -4791,17 +4791,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>4.55</t>
+          <t>3.93</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4812,66 +4812,66 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>3381</t>
+          <t>4588</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>9.91</t>
+          <t>29.25</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>13.05</t>
         </is>
       </c>
       <c r="AH11" t="n">
-        <v>-0.5</v>
+        <v>1.36</v>
       </c>
       <c r="AI11" t="n">
-        <v>-5</v>
+        <v>-4.52</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-1.5</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>9.548</t>
+          <t>9.57</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>10.05</v>
+        <v>10.02</v>
       </c>
       <c r="AN11" t="n">
-        <v>10.17</v>
+        <v>10.18</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>10.18</t>
+          <t>10.17</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-87.49</t>
+          <t>-57.55</t>
         </is>
       </c>
       <c r="AQ11" t="n">
         <v>-0.19</v>
       </c>
       <c r="AR11" t="n">
-        <v>-0.1</v>
+        <v>-0.12</v>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
@@ -4880,7 +4880,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-119.31</t>
+          <t>-122.55</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4890,43 +4890,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>39581766.4115983</t>
+          <t>39632180.51906779</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>14664845.0</t>
+          <t>13093655.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>23130520.6</v>
+        <v>18080026.8</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>23880046.8</t>
+          <t>22355788.3</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>26473396.54</v>
+        <v>26291263.5</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-749526</t>
+          <t>-4275761</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-367031.5421935803</t>
+          <t>-558392.068295303</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-1078151.8792383</t>
+          <t>-1610874.961854778</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>14664845.0</t>
+          <t>13093655.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -4946,7 +4946,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-9.52</t>
+          <t>-7.62</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -4991,7 +4991,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5006,7 +5006,7 @@
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5031,12 +5031,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>63.12</t>
+          <t>63.09</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>14914</t>
+          <t>15117</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5056,22 +5056,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>9.46</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>9.55</t>
+          <t>9.88</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>9.27</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5103,12 +5103,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1859.149</t>
+          <t>1560.548</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5118,7 +5118,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>9.39</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5128,17 +5128,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>15.02</t>
+          <t>15.18</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>4.83</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>-3.14</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5158,7 +5158,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2025-12-09 00:00:00</t>
+          <t>2025-12-10 00:00:00</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>5.43</t>
+          <t>4.55</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-2.45</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5234,66 +5234,66 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>3381</t>
+          <t>4588</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.91</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>5.13</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="AH12" t="n">
-        <v>-2.67</v>
+        <v>-0.5</v>
       </c>
       <c r="AI12" t="n">
-        <v>-4.39</v>
+        <v>-5</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>9.648</t>
+          <t>9.548</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>10.09</v>
+        <v>10.05</v>
       </c>
       <c r="AN12" t="n">
-        <v>10.18</v>
+        <v>10.17</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>10.19</t>
+          <t>10.18</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-117.02</t>
+          <t>-87.49</t>
         </is>
       </c>
       <c r="AQ12" t="n">
-        <v>-0.18</v>
+        <v>-0.19</v>
       </c>
       <c r="AR12" t="n">
-        <v>-0.08</v>
+        <v>-0.1</v>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
@@ -5302,7 +5302,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-115.08</t>
+          <t>-119.31</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5312,43 +5312,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>39581766.4115983</t>
+          <t>39632180.51906779</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>17601489.0</t>
+          <t>14664845.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>25218403</v>
+        <v>23130520.6</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>24916958.1</t>
+          <t>23880046.8</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>26498584.58</v>
+        <v>26473396.54</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>301444</t>
+          <t>-749526</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-237736.9354581767</t>
+          <t>-367031.5421935803</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-446955.2655276731</t>
+          <t>-1078151.8792383</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>17601489.0</t>
+          <t>14664845.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-10.57</t>
+          <t>-9.52</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5423,12 +5423,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5453,12 +5453,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>63.12</t>
+          <t>63.09</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>14914</t>
+          <t>15117</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5478,22 +5478,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
+          <t>9.46</t>
+        </is>
+      </c>
+      <c r="CE12" t="inlineStr">
+        <is>
           <t>9.55</t>
         </is>
       </c>
-      <c r="CE12" t="inlineStr">
-        <is>
-          <t>9.63</t>
-        </is>
-      </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>9.38</t>
+          <t>9.27</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>9.39</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/塑化劑(可塑劑).xlsx
+++ b/Result/checksun_type/塑化劑(可塑劑).xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>【d1】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>-5.36</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>4587.903</t>
+          <t>4746.574</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>11.2</t>
+          <t>10.6</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-26.61</t>
+          <t>-45.68</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2025-12-10 00:00:00</t>
+          <t>2025-12-11 00:00:00</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>-4.07</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13.39</t>
+          <t>13.85</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>5.71</t>
+          <t>-5.19</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1019,61 +1019,61 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>4588</t>
+          <t>4747</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>84.28</t>
+          <t>22.73</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>81.16</t>
+          <t>61.38</t>
         </is>
       </c>
       <c r="AH2" t="n">
-        <v>-0.18</v>
+        <v>-4.33</v>
       </c>
       <c r="AI2" t="n">
-        <v>8.33</v>
+        <v>6.85</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>11.22</t>
+          <t>11.08</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>10.36</v>
+        <v>10.37</v>
       </c>
       <c r="AN2" t="n">
         <v>10.36</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>10.29</t>
+          <t>10.3</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>104.81</t>
+          <t>54.76</t>
         </is>
       </c>
       <c r="AQ2" t="n">
-        <v>0.28</v>
+        <v>0.24</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.14</v>
+        <v>0.16</v>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-74.66</t>
+          <t>-70.64</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1092,63 +1092,63 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>39632180.51906779</t>
+          <t>39684266.11354019</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>50183303.0</t>
+          <t>51040578.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>61147746.2</v>
+        <v>47317430</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>83319151.2</t>
+          <t>87113843.5</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>38351204.62</v>
+        <v>38674174.84</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-22171405</t>
+          <t>-39796413</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>9333186.321232235</t>
+          <t>8362263.81646695</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>5180170.002844289</t>
+          <t>3022190.040257879</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>50183303.0</t>
+          <t>51040578.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>10.5</t>
+          <t>10.6</t>
         </is>
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>2025/10/14</t>
+          <t>2025/12/10</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>6.67</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1193,7 +1193,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>63.09</t>
+          <t>63.01</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>15117</t>
+          <t>14307</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1253,17 +1253,17 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>塑膠工業平上市</t>
+          <t>塑膠工業右下上市</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>11.2</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>11.25</t>
+          <t>11.2</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>11.2</t>
+          <t>10.6</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1305,12 +1305,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>3380.77</t>
+          <t>4587.903</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1320,74 +1320,74 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>11.2</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-5.66</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>-0.81</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>-26.61</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>-50.0</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2025-12-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2025-12-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>2025-10-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2025-10-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
           <t>11.05</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>1.34</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2.27</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>62.06</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>2025-12-08</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>2025-12-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>2025-12-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>2025-10-27 00:00:00</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>2025-10-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>11.05</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>11.05</t>
-        </is>
-      </c>
       <c r="T3" t="inlineStr">
         <is>
           <t>10.65</t>
@@ -1400,7 +1400,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -1415,17 +1415,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>9.87</t>
+          <t>13.39</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2.82</t>
+          <t>5.71</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1441,70 +1441,70 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>4588</t>
+          <t>4747</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>77.14</t>
+          <t>84.28</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>86.4</t>
+          <t>81.16</t>
         </is>
       </c>
       <c r="AH3" t="n">
-        <v>-1.69</v>
+        <v>-0.18</v>
       </c>
       <c r="AI3" t="n">
-        <v>9.07</v>
+        <v>8.33</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
+          <t>0.62</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>11.22</t>
+        </is>
+      </c>
+      <c r="AM3" t="n">
+        <v>10.36</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>10.36</v>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>10.29</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>104.81</t>
+        </is>
+      </c>
+      <c r="AQ3" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
           <t>0.54</t>
         </is>
       </c>
-      <c r="AL3" t="inlineStr">
-        <is>
-          <t>11.24</t>
-        </is>
-      </c>
-      <c r="AM3" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>10.34</v>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>10.28</t>
-        </is>
-      </c>
-      <c r="AP3" t="inlineStr">
-        <is>
-          <t>156.80</t>
-        </is>
-      </c>
-      <c r="AQ3" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="AS3" t="inlineStr">
-        <is>
-          <t>0.54</t>
-        </is>
-      </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-81.30</t>
+          <t>-74.66</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1514,63 +1514,63 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>39632180.51906779</t>
+          <t>39684266.11354019</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>36836029.0</t>
+          <t>50183303.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>129269925</v>
+        <v>61147746.2</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>79767305.4</t>
+          <t>83319151.2</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>38038480.18</v>
+        <v>38351204.62</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>49502619</t>
+          <t>-22171405</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>10088280.19730277</t>
+          <t>9333186.321232235</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>8169843.34215185</t>
+          <t>5180170.002844289</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>36836029.0</t>
+          <t>50183303.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>10.5</t>
+          <t>10.6</t>
         </is>
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>2025/10/14</t>
+          <t>2025/12/10</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>5.66</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1615,12 +1615,12 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>63.09</t>
+          <t>63.01</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>15117</t>
+          <t>14307</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>塑膠工業平上市</t>
+          <t>塑膠工業右下上市</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
@@ -1685,17 +1685,17 @@
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>11.25</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>10.7</t>
+          <t>10.55</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>11.05</t>
+          <t>11.2</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-3.08</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>4250.244</t>
+          <t>3380.77</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>11.05</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1752,27 +1752,27 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>-4.25</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>73.78</t>
+          <t>62.06</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2025-12-10 00:00:00</t>
+          <t>2025-12-11 00:00:00</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -1807,7 +1807,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>11.05</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1822,7 +1822,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1837,17 +1837,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12.40</t>
+          <t>9.87</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>2.82</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1863,61 +1863,61 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>4588</t>
+          <t>4747</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>82.05</t>
+          <t>77.14</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>94.02</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="AH4" t="n">
-        <v>-0.63</v>
+        <v>-1.69</v>
       </c>
       <c r="AI4" t="n">
-        <v>8.99</v>
+        <v>9.07</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>11.17</t>
+          <t>11.24</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>10.25</v>
+        <v>10.3</v>
       </c>
       <c r="AN4" t="n">
-        <v>10.33</v>
+        <v>10.34</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>10.27</t>
+          <t>10.28</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>297.70</t>
+          <t>156.80</t>
         </is>
       </c>
       <c r="AQ4" t="n">
-        <v>0.24</v>
+        <v>0.26</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.06</v>
+        <v>0.1</v>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-88.63</t>
+          <t>-81.30</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1936,63 +1936,63 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>39632180.51906779</t>
+          <t>39684266.11354019</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>47317394.0</t>
+          <t>36836029.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>135273943.6</v>
+        <v>129269925</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>77843851.4</t>
+          <t>79767305.4</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>38862439.4</v>
+        <v>38038480.18</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>57430092</t>
+          <t>49502619</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>10437086.8982393</t>
+          <t>10088280.19730277</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>13579090.20751438</t>
+          <t>8169843.34215185</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>47317394.0</t>
+          <t>36836029.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>10.5</t>
+          <t>10.6</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>2025/10/14</t>
+          <t>2025/12/10</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>5.71</t>
+          <t>4.25</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2037,12 +2037,12 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2077,12 +2077,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>63.09</t>
+          <t>63.01</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>15117</t>
+          <t>14307</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2097,27 +2097,27 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>塑膠工業平上市</t>
+          <t>塑膠工業右下上市</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>11.35</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>11.35</t>
+          <t>11.1</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>10.7</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>11.05</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2149,12 +2149,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>-3.08</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>4488.958</t>
+          <t>4250.244</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>11.45</t>
+          <t>11.1</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2174,17 +2174,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-2.23</t>
+          <t>-4.72</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>77.66</t>
+          <t>73.78</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2194,7 +2194,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2204,7 +2204,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2025-12-10 00:00:00</t>
+          <t>2025-12-11 00:00:00</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -2259,17 +2259,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13.10</t>
+          <t>12.40</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2285,70 +2285,70 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>4588</t>
+          <t>4747</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>82.05</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>94.02</t>
         </is>
       </c>
       <c r="AH5" t="n">
-        <v>3.9</v>
+        <v>-0.63</v>
       </c>
       <c r="AI5" t="n">
-        <v>7.97</v>
+        <v>8.99</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
+          <t>0.56</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>11.17</t>
+        </is>
+      </c>
+      <c r="AM5" t="n">
+        <v>10.25</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>10.33</v>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>10.27</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>297.70</t>
+        </is>
+      </c>
+      <c r="AQ5" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
           <t>0.54</t>
         </is>
       </c>
-      <c r="AL5" t="inlineStr">
-        <is>
-          <t>11.02</t>
-        </is>
-      </c>
-      <c r="AM5" t="n">
-        <v>10.21</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>10.31</v>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>10.25</t>
-        </is>
-      </c>
-      <c r="AP5" t="inlineStr">
-        <is>
-          <t>1276.76</t>
-        </is>
-      </c>
-      <c r="AQ5" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="AS5" t="inlineStr">
-        <is>
-          <t>0.54</t>
-        </is>
-      </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-97.09</t>
+          <t>-88.63</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2358,43 +2358,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>39632180.51906779</t>
+          <t>39684266.11354019</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>51209846.0</t>
+          <t>47317394.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>134651499.8</v>
+        <v>135273943.6</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>75791338.0</t>
+          <t>77843851.4</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>38375557.84</v>
+        <v>38862439.4</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>58860161</t>
+          <t>57430092</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>9865813.569280198</t>
+          <t>10437086.8982393</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>19698614.82919247</t>
+          <t>13579090.20751438</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>51209846.0</t>
+          <t>47317394.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2404,17 +2404,17 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>10.5</t>
+          <t>10.6</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>2025/10/14</t>
+          <t>2025/12/10</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>9.05</t>
+          <t>4.72</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2459,22 +2459,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>63.09</t>
+          <t>63.01</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>15117</t>
+          <t>14307</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2519,27 +2519,27 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>塑膠工業平上市</t>
+          <t>塑膠工業右下上市</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>11.4</t>
+          <t>11.35</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>11.6</t>
+          <t>11.35</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>11.15</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>11.45</t>
+          <t>11.1</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>10514.261</t>
+          <t>4488.958</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>11.3</t>
+          <t>11.45</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2596,17 +2596,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>-8.02</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>75.06</t>
+          <t>77.66</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2616,7 +2616,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2025-12-10 00:00:00</t>
+          <t>2025-12-11 00:00:00</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -2681,17 +2681,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>30.68</t>
+          <t>13.10</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-2.16</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2707,7 +2707,7 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>4588</t>
+          <t>4747</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2721,47 +2721,47 @@
         </is>
       </c>
       <c r="AH6" t="n">
-        <v>5.59</v>
+        <v>3.9</v>
       </c>
       <c r="AI6" t="n">
-        <v>5.32</v>
+        <v>7.97</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>10.702</t>
+          <t>11.02</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>10.16</v>
+        <v>10.21</v>
       </c>
       <c r="AN6" t="n">
-        <v>10.28</v>
+        <v>10.31</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>10.23</t>
+          <t>10.25</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>511.12</t>
+          <t>1276.76</t>
         </is>
       </c>
       <c r="AQ6" t="n">
-        <v>0.14</v>
+        <v>0.22</v>
       </c>
       <c r="AR6" t="n">
-        <v>-0.03</v>
+        <v>0.02</v>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
@@ -2770,7 +2770,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-106.37</t>
+          <t>-97.09</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2780,43 +2780,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>39632180.51906779</t>
+          <t>39684266.11354019</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>120192159.0</t>
+          <t>51209846.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>126910257</v>
+        <v>134651499.8</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>72495141.9</t>
+          <t>75791338.0</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>37850914.22</v>
+        <v>38375557.84</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>54415115</t>
+          <t>58860161</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>8078031.522023421</t>
+          <t>9865813.569280198</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>27320222.47340429</t>
+          <t>19698614.82919247</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>120192159.0</t>
+          <t>51209846.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2826,17 +2826,17 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>10.5</t>
+          <t>10.6</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>2025/10/14</t>
+          <t>2025/12/10</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>7.62</t>
+          <t>8.02</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2881,12 +2881,12 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
@@ -2896,7 +2896,7 @@
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2921,12 +2921,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>63.09</t>
+          <t>63.01</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>15117</t>
+          <t>14307</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2941,27 +2941,27 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>塑膠工業平上市</t>
+          <t>塑膠工業右下上市</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
+          <t>11.4</t>
+        </is>
+      </c>
+      <c r="CE6" t="inlineStr">
+        <is>
+          <t>11.6</t>
+        </is>
+      </c>
+      <c r="CF6" t="inlineStr">
+        <is>
           <t>11.15</t>
         </is>
       </c>
-      <c r="CE6" t="inlineStr">
-        <is>
-          <t>11.8</t>
-        </is>
-      </c>
-      <c r="CF6" t="inlineStr">
-        <is>
-          <t>11.05</t>
-        </is>
-      </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>11.3</t>
+          <t>11.45</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -2993,12 +2993,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>5.61</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>34269.781</t>
+          <t>10514.261</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3018,17 +3018,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>-6.6</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>64.03</t>
+          <t>75.06</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3038,7 +3038,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2025-12-10 00:00:00</t>
+          <t>2025-12-11 00:00:00</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -3103,17 +3103,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>100.00</t>
+          <t>30.68</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>-2.16</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3129,7 +3129,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>4588</t>
+          <t>4747</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3143,47 +3143,47 @@
         </is>
       </c>
       <c r="AH7" t="n">
-        <v>8.84</v>
+        <v>5.59</v>
       </c>
       <c r="AI7" t="n">
-        <v>2.78</v>
+        <v>5.32</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-1.45</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>10.382</t>
+          <t>10.702</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>10.1</v>
+        <v>10.16</v>
       </c>
       <c r="AN7" t="n">
-        <v>10.25</v>
+        <v>10.28</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>10.21</t>
+          <t>10.23</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>175.85</t>
+          <t>511.12</t>
         </is>
       </c>
       <c r="AQ7" t="n">
-        <v>0.06</v>
+        <v>0.14</v>
       </c>
       <c r="AR7" t="n">
-        <v>-0.08</v>
+        <v>-0.03</v>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
@@ -3192,7 +3192,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-114.52</t>
+          <t>-106.37</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3202,43 +3202,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>39632180.51906779</t>
+          <t>39684266.11354019</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>390794197.0</t>
+          <t>120192159.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>105490556.2</v>
+        <v>126910257</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>64310538.4</t>
+          <t>72495141.9</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>35931629.66</v>
+        <v>37850914.22</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>41180017</t>
+          <t>54415115</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>4579451.34904508</t>
+          <t>8078031.522023421</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>29841549.05537103</t>
+          <t>27320222.47340429</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>390794197.0</t>
+          <t>120192159.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3248,17 +3248,17 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>10.5</t>
+          <t>10.6</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>2025/10/14</t>
+          <t>2025/12/10</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>7.62</t>
+          <t>6.60</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3303,12 +3303,12 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
@@ -3318,7 +3318,7 @@
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3343,12 +3343,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>63.09</t>
+          <t>63.01</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>15117</t>
+          <t>14307</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3363,22 +3363,22 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>塑膠工業平上市</t>
+          <t>塑膠工業右下上市</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>10.7</t>
+          <t>11.15</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>11.75</t>
+          <t>11.8</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>10.7</t>
+          <t>11.05</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3405,7 +3405,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>5.61</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>6273.16</t>
+          <t>34269.781</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3430,7 +3430,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>10.7</t>
+          <t>11.3</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3440,17 +3440,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>4.46</t>
+          <t>-6.6</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>9.10</t>
+          <t>64.03</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3460,7 +3460,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3470,7 +3470,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2025-12-10 00:00:00</t>
+          <t>2025-12-11 00:00:00</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -3525,17 +3525,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>18.31</t>
+          <t>100.00</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2.95</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3551,7 +3551,7 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>4588</t>
+          <t>4747</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3561,51 +3561,51 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>88.73</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH8" t="n">
-        <v>6.77</v>
+        <v>8.84</v>
       </c>
       <c r="AI8" t="n">
-        <v>-0.22</v>
+        <v>2.78</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-1.69</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>10.022</t>
+          <t>10.382</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>10.04</v>
+        <v>10.1</v>
       </c>
       <c r="AN8" t="n">
-        <v>10.22</v>
+        <v>10.25</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>10.19</t>
+          <t>10.21</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>59.14</t>
+          <t>175.85</t>
         </is>
       </c>
       <c r="AQ8" t="n">
-        <v>-0.05</v>
+        <v>0.06</v>
       </c>
       <c r="AR8" t="n">
-        <v>-0.11</v>
+        <v>-0.08</v>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-120.90</t>
+          <t>-114.52</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3624,43 +3624,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>39632180.51906779</t>
+          <t>39684266.11354019</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>66856122.0</t>
+          <t>390794197.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>30264685.8</v>
+        <v>105490556.2</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>27741544.4</t>
+          <t>64310538.4</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>28239844.66</v>
+        <v>35931629.66</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>2523141</t>
+          <t>41180017</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-13657.32483236655</t>
+          <t>4579451.34904508</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>3384599.063345991</t>
+          <t>29841549.05537103</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>66856122.0</t>
+          <t>390794197.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3670,17 +3670,17 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>10.5</t>
+          <t>10.6</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>2025/10/14</t>
+          <t>2025/12/10</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>6.60</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3725,22 +3725,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>63.09</t>
+          <t>63.01</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>15117</t>
+          <t>14307</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3785,27 +3785,27 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>塑膠工業平上市</t>
+          <t>塑膠工業右下上市</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>10.3</t>
+          <t>10.7</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>10.8</t>
+          <t>11.75</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>10.3</t>
+          <t>10.7</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>10.7</t>
+          <t>11.3</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>4.95</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>4353.738</t>
+          <t>6273.16</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3852,7 +3852,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>10.35</t>
+          <t>10.7</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3862,17 +3862,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>7.59</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-8.98</t>
+          <t>9.10</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3882,7 +3882,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -3892,7 +3892,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2025-12-10 00:00:00</t>
+          <t>2025-12-11 00:00:00</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -3947,17 +3947,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12.70</t>
+          <t>18.31</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>4.65</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -3973,7 +3973,7 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>4588</t>
+          <t>4747</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -3983,51 +3983,51 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>65.15</t>
+          <t>88.73</t>
         </is>
       </c>
       <c r="AH9" t="n">
-        <v>6.05</v>
+        <v>6.77</v>
       </c>
       <c r="AI9" t="n">
-        <v>-2.51</v>
+        <v>-0.22</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-1.69</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>9.76</t>
+          <t>10.022</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>10.01</v>
+        <v>10.04</v>
       </c>
       <c r="AN9" t="n">
-        <v>10.19</v>
+        <v>10.22</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>10.18</t>
+          <t>10.19</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>8.30</t>
+          <t>59.14</t>
         </is>
       </c>
       <c r="AQ9" t="n">
-        <v>-0.12</v>
+        <v>-0.05</v>
       </c>
       <c r="AR9" t="n">
-        <v>-0.13</v>
+        <v>-0.11</v>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-123.99</t>
+          <t>-120.90</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4046,43 +4046,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>39632180.51906779</t>
+          <t>39684266.11354019</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>44205175.0</t>
+          <t>66856122.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>20413759.2</v>
+        <v>30264685.8</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>22428185.2</t>
+          <t>27741544.4</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>27064322.42</v>
+        <v>28239844.66</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-2014426</t>
+          <t>2523141</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-631522.122682977</t>
+          <t>-13657.32483236655</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>175728.5724764355</t>
+          <t>3384599.063345991</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>44205175.0</t>
+          <t>66856122.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4092,17 +4092,17 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>10.5</t>
+          <t>10.6</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>2025/10/14</t>
+          <t>2025/12/10</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-1.43</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4152,17 +4152,17 @@
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4187,12 +4187,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>63.09</t>
+          <t>63.01</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>15117</t>
+          <t>14307</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4207,27 +4207,27 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>塑膠工業平上市</t>
+          <t>塑膠工業右下上市</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>9.89</t>
+          <t>10.3</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>10.35</t>
+          <t>10.8</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>9.89</t>
+          <t>10.3</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>10.35</t>
+          <t>10.7</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4249,7 +4249,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4259,12 +4259,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>4.95</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1272.664</t>
+          <t>4353.738</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4274,7 +4274,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>9.86</t>
+          <t>10.35</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4284,17 +4284,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>11.96</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-13.84</t>
+          <t>-8.98</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4304,7 +4304,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4314,7 +4314,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2025-12-10 00:00:00</t>
+          <t>2025-12-11 00:00:00</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -4369,17 +4369,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>3.71</t>
+          <t>12.70</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>4.65</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4395,58 +4395,58 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>4588</t>
+          <t>4747</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>66.2</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>35.12</t>
+          <t>65.15</t>
         </is>
       </c>
       <c r="AH10" t="n">
-        <v>2.75</v>
+        <v>6.05</v>
       </c>
       <c r="AI10" t="n">
-        <v>-4.05</v>
+        <v>-2.51</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>9.596</t>
+          <t>9.76</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>10</v>
+        <v>10.01</v>
       </c>
       <c r="AN10" t="n">
-        <v>10.18</v>
+        <v>10.19</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>10.17</t>
+          <t>10.18</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-31.61</t>
+          <t>8.30</t>
         </is>
       </c>
       <c r="AQ10" t="n">
-        <v>-0.17</v>
+        <v>-0.12</v>
       </c>
       <c r="AR10" t="n">
         <v>-0.13</v>
@@ -4458,7 +4458,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-124.49</t>
+          <t>-123.99</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4468,43 +4468,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>39632180.51906779</t>
+          <t>39684266.11354019</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>12503632.0</t>
+          <t>44205175.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>16931176.2</v>
+        <v>20413759.2</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>19650448.5</t>
+          <t>22428185.2</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>26328965.82</v>
+        <v>27064322.42</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-2719272</t>
+          <t>-2014426</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-778294.9763483247</t>
+          <t>-631522.122682977</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-1987760.970639944</t>
+          <t>175728.5724764355</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>12503632.0</t>
+          <t>44205175.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4514,17 +4514,17 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>10.5</t>
+          <t>10.6</t>
         </is>
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>2025/10/14</t>
+          <t>2025/12/10</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-6.10</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4569,7 +4569,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4609,12 +4609,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>63.09</t>
+          <t>63.01</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>15117</t>
+          <t>14307</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4629,27 +4629,27 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>塑膠工業平上市</t>
+          <t>塑膠工業右下上市</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>9.76</t>
+          <t>9.89</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>9.92</t>
+          <t>10.35</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>9.73</t>
+          <t>9.89</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>9.86</t>
+          <t>10.35</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1348.47</t>
+          <t>1272.664</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>9.86</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4706,17 +4706,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>13.39</t>
+          <t>6.98</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-19.13</t>
+          <t>-13.84</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4726,7 +4726,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -4736,7 +4736,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2025-12-10 00:00:00</t>
+          <t>2025-12-11 00:00:00</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -4791,17 +4791,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>3.93</t>
+          <t>3.71</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4817,42 +4817,42 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>4588</t>
+          <t>4747</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>29.25</t>
+          <t>66.2</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>13.05</t>
+          <t>35.12</t>
         </is>
       </c>
       <c r="AH11" t="n">
-        <v>1.36</v>
+        <v>2.75</v>
       </c>
       <c r="AI11" t="n">
-        <v>-4.52</v>
+        <v>-4.05</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-1.5</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>9.57</t>
+          <t>9.596</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>10.02</v>
+        <v>10</v>
       </c>
       <c r="AN11" t="n">
         <v>10.18</v>
@@ -4864,14 +4864,14 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-57.55</t>
+          <t>-31.61</t>
         </is>
       </c>
       <c r="AQ11" t="n">
-        <v>-0.19</v>
+        <v>-0.17</v>
       </c>
       <c r="AR11" t="n">
-        <v>-0.12</v>
+        <v>-0.13</v>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
@@ -4880,7 +4880,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-122.55</t>
+          <t>-124.49</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4890,43 +4890,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>39632180.51906779</t>
+          <t>39684266.11354019</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>13093655.0</t>
+          <t>12503632.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>18080026.8</v>
+        <v>16931176.2</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>22355788.3</t>
+          <t>19650448.5</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>26291263.5</v>
+        <v>26328965.82</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-4275761</t>
+          <t>-2719272</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-558392.068295303</t>
+          <t>-778294.9763483247</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-1610874.961854778</t>
+          <t>-1987760.970639944</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>13093655.0</t>
+          <t>12503632.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -4936,17 +4936,17 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>10.5</t>
+          <t>10.6</t>
         </is>
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>2025/10/14</t>
+          <t>2025/12/10</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-7.62</t>
+          <t>-6.98</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -4991,7 +4991,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5001,12 +5001,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5031,12 +5031,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>63.09</t>
+          <t>63.01</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>15117</t>
+          <t>14307</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5051,27 +5051,27 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>塑膠工業平上市</t>
+          <t>塑膠工業右下上市</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>9.76</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>9.88</t>
+          <t>9.92</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>9.73</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>9.86</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5103,12 +5103,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1560.548</t>
+          <t>1348.47</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5118,7 +5118,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5128,17 +5128,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>15.18</t>
+          <t>8.49</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-3.14</t>
+          <t>-19.13</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5148,7 +5148,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5158,7 +5158,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2025-12-10 00:00:00</t>
+          <t>2025-12-11 00:00:00</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>4.55</t>
+          <t>3.93</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5239,61 +5239,61 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>4588</t>
+          <t>4747</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>9.91</t>
+          <t>29.25</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>13.05</t>
         </is>
       </c>
       <c r="AH12" t="n">
-        <v>-0.5</v>
+        <v>1.36</v>
       </c>
       <c r="AI12" t="n">
-        <v>-5</v>
+        <v>-4.52</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-1.5</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>9.548</t>
+          <t>9.57</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>10.05</v>
+        <v>10.02</v>
       </c>
       <c r="AN12" t="n">
-        <v>10.17</v>
+        <v>10.18</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>10.18</t>
+          <t>10.17</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-87.49</t>
+          <t>-57.55</t>
         </is>
       </c>
       <c r="AQ12" t="n">
         <v>-0.19</v>
       </c>
       <c r="AR12" t="n">
-        <v>-0.1</v>
+        <v>-0.12</v>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
@@ -5302,7 +5302,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-119.31</t>
+          <t>-122.55</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5312,43 +5312,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>39632180.51906779</t>
+          <t>39684266.11354019</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>14664845.0</t>
+          <t>13093655.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>23130520.6</v>
+        <v>18080026.8</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>23880046.8</t>
+          <t>22355788.3</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>26473396.54</v>
+        <v>26291263.5</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-749526</t>
+          <t>-4275761</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-367031.5421935803</t>
+          <t>-558392.068295303</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-1078151.8792383</t>
+          <t>-1610874.961854778</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>14664845.0</t>
+          <t>13093655.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5358,17 +5358,17 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>10.5</t>
+          <t>10.6</t>
         </is>
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>2025/10/14</t>
+          <t>2025/12/10</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-9.52</t>
+          <t>-8.49</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5428,7 +5428,7 @@
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5453,12 +5453,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>63.09</t>
+          <t>63.01</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>15117</t>
+          <t>14307</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5473,27 +5473,27 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>塑膠工業平上市</t>
+          <t>塑膠工業右下上市</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>9.46</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>9.55</t>
+          <t>9.88</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>9.27</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/塑化劑(可塑劑).xlsx
+++ b/Result/checksun_type/塑化劑(可塑劑).xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-5.36</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>4746.574</t>
+          <t>1950.665</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>10.6</t>
+          <t>10.85</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-45.68</t>
+          <t>-53.07</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2025-12-11 00:00:00</t>
+          <t>2025-12-12 00:00:00</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>-4.07</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13.85</t>
+          <t>5.69</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-5.19</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,66 +1014,66 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>4747</t>
+          <t>1951</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>22.73</t>
+          <t>29.41</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>61.38</t>
+          <t>45.47</t>
         </is>
       </c>
       <c r="AH2" t="n">
-        <v>-4.33</v>
+        <v>-1</v>
       </c>
       <c r="AI2" t="n">
-        <v>6.85</v>
+        <v>5.51</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>11.08</t>
+          <t>10.96</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>10.37</v>
+        <v>10.39</v>
       </c>
       <c r="AN2" t="n">
         <v>10.36</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>10.3</t>
+          <t>10.31</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>54.76</t>
+          <t>35.30</t>
         </is>
       </c>
       <c r="AQ2" t="n">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-70.64</t>
+          <t>-67.80</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1092,48 +1092,48 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>39684266.11354019</t>
+          <t>39672805.50211267</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>51040578.0</t>
+          <t>21031488.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>47317430</v>
+        <v>41281758.4</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>87113843.5</t>
+          <t>87966629.1</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>38674174.84</v>
+        <v>38425696.6</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-39796413</t>
+          <t>-46684870</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>8362263.81646695</t>
+          <t>6950433.624001412</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>3022190.040257879</t>
+          <t>-814632.4345590472</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>51040578.0</t>
+          <t>21031488.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="BF2" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1173,7 +1173,7 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1193,22 +1193,22 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>63.01</t>
+          <t>63.14</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>14307</t>
+          <t>14644</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1258,22 +1258,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>11.2</t>
+          <t>10.6</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>11.2</t>
+          <t>10.95</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>10.55</t>
+          <t>10.6</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>10.6</t>
+          <t>10.85</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1295,7 +1295,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>【d1】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1305,12 +1305,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>-5.36</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>4587.903</t>
+          <t>4746.574</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>11.2</t>
+          <t>10.6</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1330,17 +1330,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-5.66</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-26.61</t>
+          <t>-45.68</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1360,7 +1360,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2025-12-11 00:00:00</t>
+          <t>2025-12-12 00:00:00</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>-4.07</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -1415,17 +1415,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13.39</t>
+          <t>13.85</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>5.71</t>
+          <t>-5.19</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1436,66 +1436,66 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>4747</t>
+          <t>1951</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>84.28</t>
+          <t>22.73</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>81.16</t>
+          <t>61.38</t>
         </is>
       </c>
       <c r="AH3" t="n">
-        <v>-0.18</v>
+        <v>-4.33</v>
       </c>
       <c r="AI3" t="n">
-        <v>8.33</v>
+        <v>6.85</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>11.22</t>
+          <t>11.08</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>10.36</v>
+        <v>10.37</v>
       </c>
       <c r="AN3" t="n">
         <v>10.36</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>10.29</t>
+          <t>10.3</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>104.81</t>
+          <t>54.76</t>
         </is>
       </c>
       <c r="AQ3" t="n">
-        <v>0.28</v>
+        <v>0.24</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.14</v>
+        <v>0.16</v>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-74.66</t>
+          <t>-70.64</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1514,48 +1514,48 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>39684266.11354019</t>
+          <t>39672805.50211267</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>50183303.0</t>
+          <t>51040578.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>61147746.2</v>
+        <v>47317430</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>83319151.2</t>
+          <t>87113843.5</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>38351204.62</v>
+        <v>38674174.84</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-22171405</t>
+          <t>-39796413</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>9333186.321232235</t>
+          <t>8362263.81646695</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>5180170.002844289</t>
+          <t>3022190.040257879</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>50183303.0</t>
+          <t>51040578.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="BF3" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>5.66</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1625,12 +1625,12 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>63.01</t>
+          <t>63.14</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>14307</t>
+          <t>14644</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>11.2</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>11.25</t>
+          <t>11.2</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
@@ -1695,7 +1695,7 @@
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>11.2</t>
+          <t>10.6</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>3380.77</t>
+          <t>4587.903</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1742,74 +1742,74 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>11.2</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-3.23</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>0.92</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>-26.61</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>-50.0</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2025-12-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2025-12-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>2025-10-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>2025-10-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
           <t>11.05</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>-4.25</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>-0.81</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>62.06</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>2025-12-08</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>-50.0</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>2025-12-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>2025-12-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>2025-10-27 00:00:00</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>2025-10-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>11.05</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>11.05</t>
-        </is>
-      </c>
       <c r="T4" t="inlineStr">
         <is>
           <t>10.65</t>
@@ -1822,7 +1822,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1837,17 +1837,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>9.87</t>
+          <t>13.39</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2.82</t>
+          <t>5.71</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1858,75 +1858,75 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>4747</t>
+          <t>1951</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>77.14</t>
+          <t>84.28</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>86.4</t>
+          <t>81.16</t>
         </is>
       </c>
       <c r="AH4" t="n">
-        <v>-1.69</v>
+        <v>-0.18</v>
       </c>
       <c r="AI4" t="n">
-        <v>9.07</v>
+        <v>8.33</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
+          <t>0.62</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>11.22</t>
+        </is>
+      </c>
+      <c r="AM4" t="n">
+        <v>10.36</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>10.36</v>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>10.29</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>104.81</t>
+        </is>
+      </c>
+      <c r="AQ4" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
           <t>0.54</t>
         </is>
       </c>
-      <c r="AL4" t="inlineStr">
-        <is>
-          <t>11.24</t>
-        </is>
-      </c>
-      <c r="AM4" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>10.34</v>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>10.28</t>
-        </is>
-      </c>
-      <c r="AP4" t="inlineStr">
-        <is>
-          <t>156.80</t>
-        </is>
-      </c>
-      <c r="AQ4" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="AS4" t="inlineStr">
-        <is>
-          <t>0.54</t>
-        </is>
-      </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-81.30</t>
+          <t>-74.66</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1936,48 +1936,48 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>39684266.11354019</t>
+          <t>39672805.50211267</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>36836029.0</t>
+          <t>50183303.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>129269925</v>
+        <v>61147746.2</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>79767305.4</t>
+          <t>83319151.2</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>38038480.18</v>
+        <v>38351204.62</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>49502619</t>
+          <t>-22171405</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>10088280.19730277</t>
+          <t>9333186.321232235</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>8169843.34215185</t>
+          <t>5180170.002844289</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>36836029.0</t>
+          <t>50183303.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>4.25</t>
+          <t>5.66</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2017,7 +2017,7 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
@@ -2037,12 +2037,12 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2077,12 +2077,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>63.01</t>
+          <t>63.14</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>14307</t>
+          <t>14644</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2107,17 +2107,17 @@
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>11.25</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>10.7</t>
+          <t>10.55</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>11.05</t>
+          <t>11.2</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2149,12 +2149,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-3.08</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>4250.244</t>
+          <t>3380.77</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>11.05</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2174,22 +2174,22 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-4.72</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>73.78</t>
+          <t>62.06</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -2204,7 +2204,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2025-12-11 00:00:00</t>
+          <t>2025-12-12 00:00:00</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -2229,7 +2229,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>11.05</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -2244,7 +2244,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -2259,17 +2259,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12.40</t>
+          <t>9.87</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>2.82</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2280,66 +2280,66 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>4747</t>
+          <t>1951</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>82.05</t>
+          <t>77.14</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>94.02</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="AH5" t="n">
-        <v>-0.63</v>
+        <v>-1.69</v>
       </c>
       <c r="AI5" t="n">
-        <v>8.99</v>
+        <v>9.07</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>11.17</t>
+          <t>11.24</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>10.25</v>
+        <v>10.3</v>
       </c>
       <c r="AN5" t="n">
-        <v>10.33</v>
+        <v>10.34</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>10.27</t>
+          <t>10.28</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>297.70</t>
+          <t>156.80</t>
         </is>
       </c>
       <c r="AQ5" t="n">
-        <v>0.24</v>
+        <v>0.26</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.06</v>
+        <v>0.1</v>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-88.63</t>
+          <t>-81.30</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2358,48 +2358,48 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>39684266.11354019</t>
+          <t>39672805.50211267</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>47317394.0</t>
+          <t>36836029.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>135273943.6</v>
+        <v>129269925</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>77843851.4</t>
+          <t>79767305.4</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>38862439.4</v>
+        <v>38038480.18</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>57430092</t>
+          <t>49502619</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>10437086.8982393</t>
+          <t>10088280.19730277</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>13579090.20751438</t>
+          <t>8169843.34215185</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>47317394.0</t>
+          <t>36836029.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>4.72</t>
+          <t>4.25</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
@@ -2459,12 +2459,12 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>63.01</t>
+          <t>63.14</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>14307</t>
+          <t>14644</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2524,22 +2524,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>11.35</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>11.35</t>
+          <t>11.1</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>10.7</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>11.05</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>-3.08</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>4488.958</t>
+          <t>4250.244</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>11.45</t>
+          <t>11.1</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2596,17 +2596,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-8.02</t>
+          <t>-2.3</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>77.66</t>
+          <t>73.78</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2025-12-11 00:00:00</t>
+          <t>2025-12-12 00:00:00</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -2681,17 +2681,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13.10</t>
+          <t>12.40</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2702,75 +2702,75 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>4747</t>
+          <t>1951</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>82.05</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>94.02</t>
         </is>
       </c>
       <c r="AH6" t="n">
-        <v>3.9</v>
+        <v>-0.63</v>
       </c>
       <c r="AI6" t="n">
-        <v>7.97</v>
+        <v>8.99</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
+          <t>0.56</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>11.17</t>
+        </is>
+      </c>
+      <c r="AM6" t="n">
+        <v>10.25</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>10.33</v>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>10.27</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>297.70</t>
+        </is>
+      </c>
+      <c r="AQ6" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
           <t>0.54</t>
         </is>
       </c>
-      <c r="AL6" t="inlineStr">
-        <is>
-          <t>11.02</t>
-        </is>
-      </c>
-      <c r="AM6" t="n">
-        <v>10.21</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>10.31</v>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>10.25</t>
-        </is>
-      </c>
-      <c r="AP6" t="inlineStr">
-        <is>
-          <t>1276.76</t>
-        </is>
-      </c>
-      <c r="AQ6" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="AS6" t="inlineStr">
-        <is>
-          <t>0.54</t>
-        </is>
-      </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-97.09</t>
+          <t>-88.63</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2780,43 +2780,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>39684266.11354019</t>
+          <t>39672805.50211267</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>51209846.0</t>
+          <t>47317394.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>134651499.8</v>
+        <v>135273943.6</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>75791338.0</t>
+          <t>77843851.4</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>38375557.84</v>
+        <v>38862439.4</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>58860161</t>
+          <t>57430092</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>9865813.569280198</t>
+          <t>10437086.8982393</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>19698614.82919247</t>
+          <t>13579090.20751438</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>51209846.0</t>
+          <t>47317394.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2836,7 +2836,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>8.02</t>
+          <t>4.72</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2861,7 +2861,7 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -2881,22 +2881,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2921,12 +2921,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>63.01</t>
+          <t>63.14</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>14307</t>
+          <t>14644</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2946,22 +2946,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>11.4</t>
+          <t>11.35</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>11.6</t>
+          <t>11.35</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>11.15</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>11.45</t>
+          <t>11.1</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -2993,12 +2993,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>10514.261</t>
+          <t>4488.958</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>11.3</t>
+          <t>11.45</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3018,17 +3018,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-6.6</t>
+          <t>-5.53</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>75.06</t>
+          <t>77.66</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2025-12-11 00:00:00</t>
+          <t>2025-12-12 00:00:00</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -3103,17 +3103,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>30.68</t>
+          <t>13.10</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-2.16</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3124,12 +3124,12 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>4747</t>
+          <t>1951</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3143,47 +3143,47 @@
         </is>
       </c>
       <c r="AH7" t="n">
-        <v>5.59</v>
+        <v>3.9</v>
       </c>
       <c r="AI7" t="n">
-        <v>5.32</v>
+        <v>7.97</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>10.702</t>
+          <t>11.02</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>10.16</v>
+        <v>10.21</v>
       </c>
       <c r="AN7" t="n">
-        <v>10.28</v>
+        <v>10.31</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>10.23</t>
+          <t>10.25</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>511.12</t>
+          <t>1276.76</t>
         </is>
       </c>
       <c r="AQ7" t="n">
-        <v>0.14</v>
+        <v>0.22</v>
       </c>
       <c r="AR7" t="n">
-        <v>-0.03</v>
+        <v>0.02</v>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
@@ -3192,7 +3192,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-106.37</t>
+          <t>-97.09</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3202,43 +3202,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>39684266.11354019</t>
+          <t>39672805.50211267</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>120192159.0</t>
+          <t>51209846.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>126910257</v>
+        <v>134651499.8</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>72495141.9</t>
+          <t>75791338.0</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>37850914.22</v>
+        <v>38375557.84</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>54415115</t>
+          <t>58860161</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>8078031.522023421</t>
+          <t>9865813.569280198</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>27320222.47340429</t>
+          <t>19698614.82919247</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>120192159.0</t>
+          <t>51209846.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>6.60</t>
+          <t>8.02</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
@@ -3303,12 +3303,12 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
@@ -3318,7 +3318,7 @@
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3343,12 +3343,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>63.01</t>
+          <t>63.14</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>14307</t>
+          <t>14644</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3368,22 +3368,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
+          <t>11.4</t>
+        </is>
+      </c>
+      <c r="CE7" t="inlineStr">
+        <is>
+          <t>11.6</t>
+        </is>
+      </c>
+      <c r="CF7" t="inlineStr">
+        <is>
           <t>11.15</t>
         </is>
       </c>
-      <c r="CE7" t="inlineStr">
-        <is>
-          <t>11.8</t>
-        </is>
-      </c>
-      <c r="CF7" t="inlineStr">
-        <is>
-          <t>11.05</t>
-        </is>
-      </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>11.3</t>
+          <t>11.45</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>5.61</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>34269.781</t>
+          <t>10514.261</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3440,17 +3440,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-6.6</t>
+          <t>-4.15</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>64.03</t>
+          <t>75.06</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3470,7 +3470,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2025-12-11 00:00:00</t>
+          <t>2025-12-12 00:00:00</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -3525,17 +3525,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>100.00</t>
+          <t>30.68</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>-2.16</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3546,12 +3546,12 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>4747</t>
+          <t>1951</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3565,47 +3565,47 @@
         </is>
       </c>
       <c r="AH8" t="n">
-        <v>8.84</v>
+        <v>5.59</v>
       </c>
       <c r="AI8" t="n">
-        <v>2.78</v>
+        <v>5.32</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-1.45</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>10.382</t>
+          <t>10.702</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>10.1</v>
+        <v>10.16</v>
       </c>
       <c r="AN8" t="n">
-        <v>10.25</v>
+        <v>10.28</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>10.21</t>
+          <t>10.23</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>175.85</t>
+          <t>511.12</t>
         </is>
       </c>
       <c r="AQ8" t="n">
-        <v>0.06</v>
+        <v>0.14</v>
       </c>
       <c r="AR8" t="n">
-        <v>-0.08</v>
+        <v>-0.03</v>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-114.52</t>
+          <t>-106.37</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3624,43 +3624,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>39684266.11354019</t>
+          <t>39672805.50211267</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>390794197.0</t>
+          <t>120192159.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>105490556.2</v>
+        <v>126910257</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>64310538.4</t>
+          <t>72495141.9</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>35931629.66</v>
+        <v>37850914.22</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>41180017</t>
+          <t>54415115</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>4579451.34904508</t>
+          <t>8078031.522023421</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>29841549.05537103</t>
+          <t>27320222.47340429</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>390794197.0</t>
+          <t>120192159.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3705,7 +3705,7 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
@@ -3725,12 +3725,12 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
@@ -3740,7 +3740,7 @@
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>63.01</t>
+          <t>63.14</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>14307</t>
+          <t>14644</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3790,17 +3790,17 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>10.7</t>
+          <t>11.15</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>11.75</t>
+          <t>11.8</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>10.7</t>
+          <t>11.05</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3827,7 +3827,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>5.61</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>6273.16</t>
+          <t>34269.781</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3852,7 +3852,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>10.7</t>
+          <t>11.3</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3862,17 +3862,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-4.15</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>9.10</t>
+          <t>64.03</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3892,7 +3892,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2025-12-11 00:00:00</t>
+          <t>2025-12-12 00:00:00</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -3947,17 +3947,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>18.31</t>
+          <t>100.00</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2.95</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -3968,12 +3968,12 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>4747</t>
+          <t>1951</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -3983,51 +3983,51 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>88.73</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH9" t="n">
-        <v>6.77</v>
+        <v>8.84</v>
       </c>
       <c r="AI9" t="n">
-        <v>-0.22</v>
+        <v>2.78</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-1.69</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>10.022</t>
+          <t>10.382</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>10.04</v>
+        <v>10.1</v>
       </c>
       <c r="AN9" t="n">
-        <v>10.22</v>
+        <v>10.25</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>10.19</t>
+          <t>10.21</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>59.14</t>
+          <t>175.85</t>
         </is>
       </c>
       <c r="AQ9" t="n">
-        <v>-0.05</v>
+        <v>0.06</v>
       </c>
       <c r="AR9" t="n">
-        <v>-0.11</v>
+        <v>-0.08</v>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-120.90</t>
+          <t>-114.52</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4046,43 +4046,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>39684266.11354019</t>
+          <t>39672805.50211267</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>66856122.0</t>
+          <t>390794197.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>30264685.8</v>
+        <v>105490556.2</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>27741544.4</t>
+          <t>64310538.4</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>28239844.66</v>
+        <v>35931629.66</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>2523141</t>
+          <t>41180017</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-13657.32483236655</t>
+          <t>4579451.34904508</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>3384599.063345991</t>
+          <t>29841549.05537103</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>66856122.0</t>
+          <t>390794197.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>6.60</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4127,7 +4127,7 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
@@ -4147,22 +4147,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4187,12 +4187,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>63.01</t>
+          <t>63.14</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>14307</t>
+          <t>14644</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4212,22 +4212,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>10.3</t>
+          <t>10.7</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>10.8</t>
+          <t>11.75</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>10.3</t>
+          <t>10.7</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>10.7</t>
+          <t>11.3</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4259,12 +4259,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>4.95</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>4353.738</t>
+          <t>6273.16</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4274,7 +4274,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>10.35</t>
+          <t>10.7</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4284,17 +4284,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-8.98</t>
+          <t>9.10</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4314,7 +4314,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2025-12-11 00:00:00</t>
+          <t>2025-12-12 00:00:00</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -4369,17 +4369,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12.70</t>
+          <t>18.31</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>4.65</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4390,12 +4390,12 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>4747</t>
+          <t>1951</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -4405,51 +4405,51 @@
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>65.15</t>
+          <t>88.73</t>
         </is>
       </c>
       <c r="AH10" t="n">
-        <v>6.05</v>
+        <v>6.77</v>
       </c>
       <c r="AI10" t="n">
-        <v>-2.51</v>
+        <v>-0.22</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-1.69</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>9.76</t>
+          <t>10.022</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>10.01</v>
+        <v>10.04</v>
       </c>
       <c r="AN10" t="n">
-        <v>10.19</v>
+        <v>10.22</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>10.18</t>
+          <t>10.19</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>8.30</t>
+          <t>59.14</t>
         </is>
       </c>
       <c r="AQ10" t="n">
-        <v>-0.12</v>
+        <v>-0.05</v>
       </c>
       <c r="AR10" t="n">
-        <v>-0.13</v>
+        <v>-0.11</v>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-123.99</t>
+          <t>-120.90</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4468,43 +4468,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>39684266.11354019</t>
+          <t>39672805.50211267</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>44205175.0</t>
+          <t>66856122.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>20413759.2</v>
+        <v>30264685.8</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>22428185.2</t>
+          <t>27741544.4</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>27064322.42</v>
+        <v>28239844.66</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-2014426</t>
+          <t>2523141</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-631522.122682977</t>
+          <t>-13657.32483236655</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>175728.5724764355</t>
+          <t>3384599.063345991</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>44205175.0</t>
+          <t>66856122.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4524,7 +4524,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4549,7 +4549,7 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4609,12 +4609,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>63.01</t>
+          <t>63.14</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>14307</t>
+          <t>14644</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4634,22 +4634,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>9.89</t>
+          <t>10.3</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>10.35</t>
+          <t>10.8</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>9.89</t>
+          <t>10.3</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>10.35</t>
+          <t>10.7</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4671,7 +4671,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>4.95</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1272.664</t>
+          <t>4353.738</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>9.86</t>
+          <t>10.35</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4706,17 +4706,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>6.98</t>
+          <t>4.61</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-13.84</t>
+          <t>-8.98</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4736,7 +4736,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2025-12-11 00:00:00</t>
+          <t>2025-12-12 00:00:00</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -4791,17 +4791,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>3.71</t>
+          <t>12.70</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>4.65</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4812,63 +4812,63 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>4747</t>
+          <t>1951</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>66.2</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>35.12</t>
+          <t>65.15</t>
         </is>
       </c>
       <c r="AH11" t="n">
-        <v>2.75</v>
+        <v>6.05</v>
       </c>
       <c r="AI11" t="n">
-        <v>-4.05</v>
+        <v>-2.51</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>9.596</t>
+          <t>9.76</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>10</v>
+        <v>10.01</v>
       </c>
       <c r="AN11" t="n">
-        <v>10.18</v>
+        <v>10.19</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>10.17</t>
+          <t>10.18</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-31.61</t>
+          <t>8.30</t>
         </is>
       </c>
       <c r="AQ11" t="n">
-        <v>-0.17</v>
+        <v>-0.12</v>
       </c>
       <c r="AR11" t="n">
         <v>-0.13</v>
@@ -4880,7 +4880,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-124.49</t>
+          <t>-123.99</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4890,43 +4890,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>39684266.11354019</t>
+          <t>39672805.50211267</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>12503632.0</t>
+          <t>44205175.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>16931176.2</v>
+        <v>20413759.2</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>19650448.5</t>
+          <t>22428185.2</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>26328965.82</v>
+        <v>27064322.42</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-2719272</t>
+          <t>-2014426</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-778294.9763483247</t>
+          <t>-631522.122682977</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-1987760.970639944</t>
+          <t>175728.5724764355</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>12503632.0</t>
+          <t>44205175.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -4946,7 +4946,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-6.98</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -4971,7 +4971,7 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
@@ -4991,7 +4991,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5001,12 +5001,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5031,12 +5031,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>63.01</t>
+          <t>63.14</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>14307</t>
+          <t>14644</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5056,22 +5056,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>9.76</t>
+          <t>9.89</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>9.92</t>
+          <t>10.35</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>9.73</t>
+          <t>9.89</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>9.86</t>
+          <t>10.35</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5103,12 +5103,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1348.47</t>
+          <t>1272.664</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5118,7 +5118,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>9.86</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5128,17 +5128,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>8.49</t>
+          <t>9.12</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-19.13</t>
+          <t>-13.84</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5158,7 +5158,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2025-12-11 00:00:00</t>
+          <t>2025-12-12 00:00:00</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>3.93</t>
+          <t>3.71</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5234,47 +5234,47 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>4747</t>
+          <t>1951</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>29.25</t>
+          <t>66.2</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>13.05</t>
+          <t>35.12</t>
         </is>
       </c>
       <c r="AH12" t="n">
-        <v>1.36</v>
+        <v>2.75</v>
       </c>
       <c r="AI12" t="n">
-        <v>-4.52</v>
+        <v>-4.05</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-1.5</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>9.57</t>
+          <t>9.596</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>10.02</v>
+        <v>10</v>
       </c>
       <c r="AN12" t="n">
         <v>10.18</v>
@@ -5286,14 +5286,14 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-57.55</t>
+          <t>-31.61</t>
         </is>
       </c>
       <c r="AQ12" t="n">
-        <v>-0.19</v>
+        <v>-0.17</v>
       </c>
       <c r="AR12" t="n">
-        <v>-0.12</v>
+        <v>-0.13</v>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
@@ -5302,7 +5302,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-122.55</t>
+          <t>-124.49</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5312,43 +5312,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>39684266.11354019</t>
+          <t>39672805.50211267</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>13093655.0</t>
+          <t>12503632.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>18080026.8</v>
+        <v>16931176.2</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>22355788.3</t>
+          <t>19650448.5</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>26291263.5</v>
+        <v>26328965.82</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-4275761</t>
+          <t>-2719272</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-558392.068295303</t>
+          <t>-778294.9763483247</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-1610874.961854778</t>
+          <t>-1987760.970639944</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>13093655.0</t>
+          <t>12503632.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-8.49</t>
+          <t>-6.98</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5393,7 +5393,7 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5423,12 +5423,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5453,12 +5453,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>63.01</t>
+          <t>63.14</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>14307</t>
+          <t>14644</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5478,22 +5478,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>9.76</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>9.88</t>
+          <t>9.92</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>9.73</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>9.86</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/塑化劑(可塑劑).xlsx
+++ b/Result/checksun_type/塑化劑(可塑劑).xlsx
@@ -923,12 +923,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1904.815</t>
+          <t>1703.083</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -953,12 +953,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-57.99</t>
+          <t>-60.06</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2025-12-15 00:00:00</t>
+          <t>2025-12-16 00:00:00</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -1068,22 +1068,22 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>5.56</t>
+          <t>4.97</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-5.16</t>
+          <t>-1.40</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
@@ -1094,12 +1094,12 @@
       <c r="AK2" t="inlineStr"/>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>1905</t>
+          <t>1703</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
@@ -1109,32 +1109,32 @@
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>19.34</t>
+          <t>13.73</t>
         </is>
       </c>
       <c r="AP2" t="n">
-        <v>-2.02</v>
+        <v>-1.3</v>
       </c>
       <c r="AQ2" t="n">
-        <v>4.54</v>
+        <v>3.5</v>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>10.87</t>
+          <t>10.79</t>
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>10.4</v>
+        <v>10.42</v>
       </c>
       <c r="AV2" t="n">
         <v>10.37</v>
@@ -1146,11 +1146,11 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>15.38</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="AY2" t="n">
-        <v>0.21</v>
+        <v>0.18</v>
       </c>
       <c r="AZ2" t="n">
         <v>0.18</v>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-66.51</t>
+          <t>-66.34</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
@@ -1172,48 +1172,48 @@
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>39660797.71097046</t>
+          <t>39643582.14396068</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>20756844.0</t>
+          <t>18268876.0</t>
         </is>
       </c>
       <c r="BF2" t="n">
-        <v>35969648.4</v>
+        <v>32256217.8</v>
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>85621796.0</t>
+          <t>80763071.4</t>
         </is>
       </c>
       <c r="BH2" t="n">
-        <v>38506172.98</v>
+        <v>38610965.58</v>
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>-49652147</t>
+          <t>-48506853</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>5342576.042452438</t>
+          <t>3677575.421348871</t>
         </is>
       </c>
       <c r="BK2" t="inlineStr">
         <is>
-          <t>-3500640.656066917</t>
+          <t>-5479927.99472075</t>
         </is>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>20756844.0</t>
+          <t>18268876.0</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>63.31</t>
+          <t>63.44</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>10.95</t>
+          <t>10.6</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
         <is>
-          <t>11.2</t>
+          <t>10.9</t>
         </is>
       </c>
       <c r="CN2" t="inlineStr">
         <is>
-          <t>10.65</t>
+          <t>10.55</t>
         </is>
       </c>
       <c r="CO2" t="inlineStr">
@@ -1385,12 +1385,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1950.665</t>
+          <t>1904.815</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>10.85</t>
+          <t>10.65</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1410,17 +1410,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-53.07</t>
+          <t>-57.99</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1440,7 +1440,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2025-12-15 00:00:00</t>
+          <t>2025-12-16 00:00:00</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1480,7 +1480,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>-3.62</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -1535,17 +1535,17 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>5.69</t>
+          <t>5.56</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>-5.16</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
@@ -1556,66 +1556,66 @@
       <c r="AK3" t="inlineStr"/>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>1905</t>
+          <t>1703</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>29.41</t>
+          <t>5.88</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>45.47</t>
+          <t>19.34</t>
         </is>
       </c>
       <c r="AP3" t="n">
-        <v>-1</v>
+        <v>-2.02</v>
       </c>
       <c r="AQ3" t="n">
-        <v>5.51</v>
+        <v>4.54</v>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>10.96</t>
+          <t>10.87</t>
         </is>
       </c>
       <c r="AU3" t="n">
-        <v>10.39</v>
+        <v>10.4</v>
       </c>
       <c r="AV3" t="n">
-        <v>10.36</v>
+        <v>10.37</v>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>10.31</t>
+          <t>10.3</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>35.30</t>
+          <t>15.38</t>
         </is>
       </c>
       <c r="AY3" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-67.80</t>
+          <t>-66.51</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
@@ -1634,48 +1634,48 @@
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>39660797.71097046</t>
+          <t>39643582.14396068</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>21031488.0</t>
+          <t>20756844.0</t>
         </is>
       </c>
       <c r="BF3" t="n">
-        <v>41281758.4</v>
+        <v>35969648.4</v>
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>87966629.1</t>
+          <t>85621796.0</t>
         </is>
       </c>
       <c r="BH3" t="n">
-        <v>38425696.6</v>
+        <v>38506172.98</v>
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>-46684870</t>
+          <t>-49652147</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
         <is>
-          <t>6950433.624001412</t>
+          <t>5342576.042452438</t>
         </is>
       </c>
       <c r="BK3" t="inlineStr">
         <is>
-          <t>-814632.4345590472</t>
+          <t>-3500640.656066917</t>
         </is>
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>21031488.0</t>
+          <t>20756844.0</t>
         </is>
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
@@ -1690,7 +1690,7 @@
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
@@ -1715,7 +1715,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1735,17 +1735,17 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="CB3" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>63.31</t>
+          <t>63.44</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1800,22 +1800,22 @@
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>10.6</t>
+          <t>10.95</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
         <is>
-          <t>10.95</t>
+          <t>11.2</t>
         </is>
       </c>
       <c r="CN3" t="inlineStr">
         <is>
-          <t>10.6</t>
+          <t>10.65</t>
         </is>
       </c>
       <c r="CO3" t="inlineStr">
         <is>
-          <t>10.85</t>
+          <t>10.65</t>
         </is>
       </c>
       <c r="CP3" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-5.36</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>4746.574</t>
+          <t>1950.665</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1862,7 +1862,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>10.6</t>
+          <t>10.85</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1872,17 +1872,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-45.68</t>
+          <t>-53.07</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1902,7 +1902,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2025-12-15 00:00:00</t>
+          <t>2025-12-16 00:00:00</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -1942,7 +1942,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>-4.07</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1992,22 +1992,22 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>13.85</t>
+          <t>5.69</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-5.19</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
@@ -2018,66 +2018,66 @@
       <c r="AK4" t="inlineStr"/>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>1905</t>
+          <t>1703</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>22.73</t>
+          <t>29.41</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>61.38</t>
+          <t>45.47</t>
         </is>
       </c>
       <c r="AP4" t="n">
-        <v>-4.33</v>
+        <v>-1</v>
       </c>
       <c r="AQ4" t="n">
-        <v>6.85</v>
+        <v>5.51</v>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>11.08</t>
+          <t>10.96</t>
         </is>
       </c>
       <c r="AU4" t="n">
-        <v>10.37</v>
+        <v>10.39</v>
       </c>
       <c r="AV4" t="n">
         <v>10.36</v>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>10.3</t>
+          <t>10.31</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>54.76</t>
+          <t>35.30</t>
         </is>
       </c>
       <c r="AY4" t="n">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-70.64</t>
+          <t>-67.80</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
@@ -2096,48 +2096,48 @@
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>39660797.71097046</t>
+          <t>39643582.14396068</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>51040578.0</t>
+          <t>21031488.0</t>
         </is>
       </c>
       <c r="BF4" t="n">
-        <v>47317430</v>
+        <v>41281758.4</v>
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>87113843.5</t>
+          <t>87966629.1</t>
         </is>
       </c>
       <c r="BH4" t="n">
-        <v>38674174.84</v>
+        <v>38425696.6</v>
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>-39796413</t>
+          <t>-46684870</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>8362263.81646695</t>
+          <t>6950433.624001412</t>
         </is>
       </c>
       <c r="BK4" t="inlineStr">
         <is>
-          <t>3022190.040257879</t>
+          <t>-814632.4345590472</t>
         </is>
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>51040578.0</t>
+          <t>21031488.0</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
@@ -2152,7 +2152,7 @@
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
@@ -2177,7 +2177,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2197,17 +2197,17 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="CB4" t="inlineStr">
@@ -2237,7 +2237,7 @@
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>63.31</t>
+          <t>63.44</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2262,22 +2262,22 @@
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>11.2</t>
+          <t>10.6</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
         <is>
-          <t>11.2</t>
+          <t>10.95</t>
         </is>
       </c>
       <c r="CN4" t="inlineStr">
         <is>
-          <t>10.55</t>
+          <t>10.6</t>
         </is>
       </c>
       <c r="CO4" t="inlineStr">
         <is>
-          <t>10.6</t>
+          <t>10.85</t>
         </is>
       </c>
       <c r="CP4" t="inlineStr">
@@ -2299,7 +2299,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>【d1】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2309,12 +2309,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>-5.36</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>4587.903</t>
+          <t>4746.574</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2324,7 +2324,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>11.2</t>
+          <t>10.6</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2334,17 +2334,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-5.16</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-26.61</t>
+          <t>-45.68</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2364,7 +2364,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2025-12-15 00:00:00</t>
+          <t>2025-12-16 00:00:00</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>-4.07</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -2454,22 +2454,22 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>13.39</t>
+          <t>13.85</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>5.71</t>
+          <t>-5.19</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
@@ -2480,66 +2480,66 @@
       <c r="AK5" t="inlineStr"/>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>1905</t>
+          <t>1703</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>84.28</t>
+          <t>22.73</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>81.16</t>
+          <t>61.38</t>
         </is>
       </c>
       <c r="AP5" t="n">
-        <v>-0.18</v>
+        <v>-4.33</v>
       </c>
       <c r="AQ5" t="n">
-        <v>8.33</v>
+        <v>6.85</v>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>11.22</t>
+          <t>11.08</t>
         </is>
       </c>
       <c r="AU5" t="n">
-        <v>10.36</v>
+        <v>10.37</v>
       </c>
       <c r="AV5" t="n">
         <v>10.36</v>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>10.29</t>
+          <t>10.3</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>104.81</t>
+          <t>54.76</t>
         </is>
       </c>
       <c r="AY5" t="n">
-        <v>0.28</v>
+        <v>0.24</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.14</v>
+        <v>0.16</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2548,7 +2548,7 @@
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-74.66</t>
+          <t>-70.64</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
@@ -2558,48 +2558,48 @@
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>39660797.71097046</t>
+          <t>39643582.14396068</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>50183303.0</t>
+          <t>51040578.0</t>
         </is>
       </c>
       <c r="BF5" t="n">
-        <v>61147746.2</v>
+        <v>47317430</v>
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>83319151.2</t>
+          <t>87113843.5</t>
         </is>
       </c>
       <c r="BH5" t="n">
-        <v>38351204.62</v>
+        <v>38674174.84</v>
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>-22171405</t>
+          <t>-39796413</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>9333186.321232235</t>
+          <t>8362263.81646695</t>
         </is>
       </c>
       <c r="BK5" t="inlineStr">
         <is>
-          <t>5180170.002844289</t>
+          <t>3022190.040257879</t>
         </is>
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>50183303.0</t>
+          <t>51040578.0</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
@@ -2614,7 +2614,7 @@
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>5.66</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
@@ -2639,7 +2639,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2669,7 +2669,7 @@
       </c>
       <c r="CA5" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="CB5" t="inlineStr">
@@ -2699,7 +2699,7 @@
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>63.31</t>
+          <t>63.44</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2724,12 +2724,12 @@
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>11.2</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
         <is>
-          <t>11.25</t>
+          <t>11.2</t>
         </is>
       </c>
       <c r="CN5" t="inlineStr">
@@ -2739,7 +2739,7 @@
       </c>
       <c r="CO5" t="inlineStr">
         <is>
-          <t>11.2</t>
+          <t>10.6</t>
         </is>
       </c>
       <c r="CP5" t="inlineStr">
@@ -2771,12 +2771,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>3380.77</t>
+          <t>4587.903</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2786,74 +2786,74 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>11.2</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-5.16</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>0.18</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>-26.61</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>-50.0</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>2025-12-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2025-12-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>2025-10-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>2025-10-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
           <t>11.05</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>-3.76</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>-0.65</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>62.06</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>2025-12-08</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>-50.0</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>2025-12-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>2025-12-15 00:00:00</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>2025-10-27 00:00:00</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>2025-10-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
         <is>
           <t>11.05</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>11.05</t>
-        </is>
-      </c>
       <c r="T6" t="inlineStr">
         <is>
           <t>10.65</t>
@@ -2866,7 +2866,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -2916,22 +2916,22 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>9.87</t>
+          <t>13.39</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>2.82</t>
+          <t>5.71</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -2942,75 +2942,75 @@
       <c r="AK6" t="inlineStr"/>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>1905</t>
+          <t>1703</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>77.14</t>
+          <t>84.28</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>86.4</t>
+          <t>81.16</t>
         </is>
       </c>
       <c r="AP6" t="n">
-        <v>-1.69</v>
+        <v>-0.18</v>
       </c>
       <c r="AQ6" t="n">
-        <v>9.07</v>
+        <v>8.33</v>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
+          <t>0.62</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>11.22</t>
+        </is>
+      </c>
+      <c r="AU6" t="n">
+        <v>10.36</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>10.36</v>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>10.29</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>104.81</t>
+        </is>
+      </c>
+      <c r="AY6" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="BA6" t="inlineStr">
+        <is>
           <t>0.54</t>
         </is>
       </c>
-      <c r="AT6" t="inlineStr">
-        <is>
-          <t>11.24</t>
-        </is>
-      </c>
-      <c r="AU6" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>10.34</v>
-      </c>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>10.28</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>156.80</t>
-        </is>
-      </c>
-      <c r="AY6" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="BA6" t="inlineStr">
-        <is>
-          <t>0.54</t>
-        </is>
-      </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-81.30</t>
+          <t>-74.66</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
@@ -3020,48 +3020,48 @@
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>39660797.71097046</t>
+          <t>39643582.14396068</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>36836029.0</t>
+          <t>50183303.0</t>
         </is>
       </c>
       <c r="BF6" t="n">
-        <v>129269925</v>
+        <v>61147746.2</v>
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>79767305.4</t>
+          <t>83319151.2</t>
         </is>
       </c>
       <c r="BH6" t="n">
-        <v>38038480.18</v>
+        <v>38351204.62</v>
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>49502619</t>
+          <t>-22171405</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
         <is>
-          <t>10088280.19730277</t>
+          <t>9333186.321232235</t>
         </is>
       </c>
       <c r="BK6" t="inlineStr">
         <is>
-          <t>8169843.34215185</t>
+          <t>5180170.002844289</t>
         </is>
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>36836029.0</t>
+          <t>50183303.0</t>
         </is>
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>4.25</t>
+          <t>5.66</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
@@ -3101,7 +3101,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -3121,12 +3121,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -3161,7 +3161,7 @@
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>63.31</t>
+          <t>63.44</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3191,17 +3191,17 @@
       </c>
       <c r="CM6" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>11.25</t>
         </is>
       </c>
       <c r="CN6" t="inlineStr">
         <is>
-          <t>10.7</t>
+          <t>10.55</t>
         </is>
       </c>
       <c r="CO6" t="inlineStr">
         <is>
-          <t>11.05</t>
+          <t>11.2</t>
         </is>
       </c>
       <c r="CP6" t="inlineStr">
@@ -3233,12 +3233,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-3.08</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>4250.244</t>
+          <t>3380.77</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3248,7 +3248,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>11.05</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3258,22 +3258,22 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-4.23</t>
+          <t>-3.76</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>73.78</t>
+          <t>62.06</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -3288,7 +3288,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2025-12-15 00:00:00</t>
+          <t>2025-12-16 00:00:00</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -3313,7 +3313,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>11.05</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -3328,7 +3328,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -3383,17 +3383,17 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>12.40</t>
+          <t>9.87</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>2.82</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
@@ -3404,66 +3404,66 @@
       <c r="AK7" t="inlineStr"/>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>1905</t>
+          <t>1703</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>82.05</t>
+          <t>77.14</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>94.02</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="AP7" t="n">
-        <v>-0.63</v>
+        <v>-1.69</v>
       </c>
       <c r="AQ7" t="n">
-        <v>8.99</v>
+        <v>9.07</v>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>11.17</t>
+          <t>11.24</t>
         </is>
       </c>
       <c r="AU7" t="n">
-        <v>10.25</v>
+        <v>10.3</v>
       </c>
       <c r="AV7" t="n">
-        <v>10.33</v>
+        <v>10.34</v>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>10.27</t>
+          <t>10.28</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>297.70</t>
+          <t>156.80</t>
         </is>
       </c>
       <c r="AY7" t="n">
-        <v>0.24</v>
+        <v>0.26</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.06</v>
+        <v>0.1</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3472,7 +3472,7 @@
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-88.63</t>
+          <t>-81.30</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
@@ -3482,48 +3482,48 @@
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>39660797.71097046</t>
+          <t>39643582.14396068</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>47317394.0</t>
+          <t>36836029.0</t>
         </is>
       </c>
       <c r="BF7" t="n">
-        <v>135273943.6</v>
+        <v>129269925</v>
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>77843851.4</t>
+          <t>79767305.4</t>
         </is>
       </c>
       <c r="BH7" t="n">
-        <v>38862439.4</v>
+        <v>38038480.18</v>
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>57430092</t>
+          <t>49502619</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
         <is>
-          <t>10437086.8982393</t>
+          <t>10088280.19730277</t>
         </is>
       </c>
       <c r="BK7" t="inlineStr">
         <is>
-          <t>13579090.20751438</t>
+          <t>8169843.34215185</t>
         </is>
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>47317394.0</t>
+          <t>36836029.0</t>
         </is>
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
@@ -3538,7 +3538,7 @@
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>4.72</t>
+          <t>4.25</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3583,12 +3583,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3623,7 +3623,7 @@
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>63.31</t>
+          <t>63.44</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3648,22 +3648,22 @@
       </c>
       <c r="CL7" t="inlineStr">
         <is>
-          <t>11.35</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="CM7" t="inlineStr">
         <is>
-          <t>11.35</t>
+          <t>11.1</t>
         </is>
       </c>
       <c r="CN7" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>10.7</t>
         </is>
       </c>
       <c r="CO7" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>11.05</t>
         </is>
       </c>
       <c r="CP7" t="inlineStr">
@@ -3695,12 +3695,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>-3.08</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>4488.958</t>
+          <t>4250.244</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>11.45</t>
+          <t>11.1</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3720,17 +3720,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-7.51</t>
+          <t>-4.23</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>77.66</t>
+          <t>73.78</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3750,7 +3750,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2025-12-15 00:00:00</t>
+          <t>2025-12-16 00:00:00</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -3840,22 +3840,22 @@
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>13.10</t>
+          <t>12.40</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
@@ -3866,75 +3866,75 @@
       <c r="AK8" t="inlineStr"/>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>1905</t>
+          <t>1703</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>82.05</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>94.02</t>
         </is>
       </c>
       <c r="AP8" t="n">
-        <v>3.9</v>
+        <v>-0.63</v>
       </c>
       <c r="AQ8" t="n">
-        <v>7.97</v>
+        <v>8.99</v>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
+          <t>0.56</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr">
+        <is>
+          <t>11.17</t>
+        </is>
+      </c>
+      <c r="AU8" t="n">
+        <v>10.25</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>10.33</v>
+      </c>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>10.27</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>297.70</t>
+        </is>
+      </c>
+      <c r="AY8" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="BA8" t="inlineStr">
+        <is>
           <t>0.54</t>
         </is>
       </c>
-      <c r="AT8" t="inlineStr">
-        <is>
-          <t>11.02</t>
-        </is>
-      </c>
-      <c r="AU8" t="n">
-        <v>10.21</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>10.31</v>
-      </c>
-      <c r="AW8" t="inlineStr">
-        <is>
-          <t>10.25</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>1276.76</t>
-        </is>
-      </c>
-      <c r="AY8" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="BA8" t="inlineStr">
-        <is>
-          <t>0.54</t>
-        </is>
-      </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-97.09</t>
+          <t>-88.63</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
@@ -3944,43 +3944,43 @@
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>39660797.71097046</t>
+          <t>39643582.14396068</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>51209846.0</t>
+          <t>47317394.0</t>
         </is>
       </c>
       <c r="BF8" t="n">
-        <v>134651499.8</v>
+        <v>135273943.6</v>
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>75791338.0</t>
+          <t>77843851.4</t>
         </is>
       </c>
       <c r="BH8" t="n">
-        <v>38375557.84</v>
+        <v>38862439.4</v>
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>58860161</t>
+          <t>57430092</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
         <is>
-          <t>9865813.569280198</t>
+          <t>10437086.8982393</t>
         </is>
       </c>
       <c r="BK8" t="inlineStr">
         <is>
-          <t>19698614.82919247</t>
+          <t>13579090.20751438</t>
         </is>
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>51209846.0</t>
+          <t>47317394.0</t>
         </is>
       </c>
       <c r="BM8" t="inlineStr">
@@ -4000,7 +4000,7 @@
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>8.02</t>
+          <t>4.72</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
@@ -4025,7 +4025,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="CB8" t="inlineStr">
@@ -4085,7 +4085,7 @@
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>63.31</t>
+          <t>63.44</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -4110,22 +4110,22 @@
       </c>
       <c r="CL8" t="inlineStr">
         <is>
-          <t>11.4</t>
+          <t>11.35</t>
         </is>
       </c>
       <c r="CM8" t="inlineStr">
         <is>
-          <t>11.6</t>
+          <t>11.35</t>
         </is>
       </c>
       <c r="CN8" t="inlineStr">
         <is>
-          <t>11.15</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="CO8" t="inlineStr">
         <is>
-          <t>11.45</t>
+          <t>11.1</t>
         </is>
       </c>
       <c r="CP8" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>10514.261</t>
+          <t>4488.958</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4172,7 +4172,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>11.3</t>
+          <t>11.45</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -4182,17 +4182,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-6.1</t>
+          <t>-7.51</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>75.06</t>
+          <t>77.66</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4212,7 +4212,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2025-12-15 00:00:00</t>
+          <t>2025-12-16 00:00:00</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -4302,22 +4302,22 @@
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>30.68</t>
+          <t>13.10</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-2.16</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -4328,12 +4328,12 @@
       <c r="AK9" t="inlineStr"/>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>1905</t>
+          <t>1703</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
@@ -4347,47 +4347,47 @@
         </is>
       </c>
       <c r="AP9" t="n">
-        <v>5.59</v>
+        <v>3.9</v>
       </c>
       <c r="AQ9" t="n">
-        <v>5.32</v>
+        <v>7.97</v>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>10.702</t>
+          <t>11.02</t>
         </is>
       </c>
       <c r="AU9" t="n">
-        <v>10.16</v>
+        <v>10.21</v>
       </c>
       <c r="AV9" t="n">
-        <v>10.28</v>
+        <v>10.31</v>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>10.23</t>
+          <t>10.25</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>511.12</t>
+          <t>1276.76</t>
         </is>
       </c>
       <c r="AY9" t="n">
-        <v>0.14</v>
+        <v>0.22</v>
       </c>
       <c r="AZ9" t="n">
-        <v>-0.03</v>
+        <v>0.02</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-106.37</t>
+          <t>-97.09</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
@@ -4406,43 +4406,43 @@
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>39660797.71097046</t>
+          <t>39643582.14396068</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
-          <t>120192159.0</t>
+          <t>51209846.0</t>
         </is>
       </c>
       <c r="BF9" t="n">
-        <v>126910257</v>
+        <v>134651499.8</v>
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>72495141.9</t>
+          <t>75791338.0</t>
         </is>
       </c>
       <c r="BH9" t="n">
-        <v>37850914.22</v>
+        <v>38375557.84</v>
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>54415115</t>
+          <t>58860161</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
         <is>
-          <t>8078031.522023421</t>
+          <t>9865813.569280198</t>
         </is>
       </c>
       <c r="BK9" t="inlineStr">
         <is>
-          <t>27320222.47340429</t>
+          <t>19698614.82919247</t>
         </is>
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>120192159.0</t>
+          <t>51209846.0</t>
         </is>
       </c>
       <c r="BM9" t="inlineStr">
@@ -4462,7 +4462,7 @@
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>6.60</t>
+          <t>8.02</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
@@ -4487,7 +4487,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4507,12 +4507,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4547,7 +4547,7 @@
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>63.31</t>
+          <t>63.44</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4572,22 +4572,22 @@
       </c>
       <c r="CL9" t="inlineStr">
         <is>
+          <t>11.4</t>
+        </is>
+      </c>
+      <c r="CM9" t="inlineStr">
+        <is>
+          <t>11.6</t>
+        </is>
+      </c>
+      <c r="CN9" t="inlineStr">
+        <is>
           <t>11.15</t>
         </is>
       </c>
-      <c r="CM9" t="inlineStr">
-        <is>
-          <t>11.8</t>
-        </is>
-      </c>
-      <c r="CN9" t="inlineStr">
-        <is>
-          <t>11.05</t>
-        </is>
-      </c>
       <c r="CO9" t="inlineStr">
         <is>
-          <t>11.3</t>
+          <t>11.45</t>
         </is>
       </c>
       <c r="CP9" t="inlineStr">
@@ -4619,12 +4619,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>5.61</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>34269.781</t>
+          <t>10514.261</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4649,12 +4649,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>64.03</t>
+          <t>75.06</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4674,7 +4674,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2025-12-15 00:00:00</t>
+          <t>2025-12-16 00:00:00</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -4764,22 +4764,22 @@
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>100.00</t>
+          <t>30.68</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>-2.16</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -4790,12 +4790,12 @@
       <c r="AK10" t="inlineStr"/>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>1905</t>
+          <t>1703</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
@@ -4809,47 +4809,47 @@
         </is>
       </c>
       <c r="AP10" t="n">
-        <v>8.84</v>
+        <v>5.59</v>
       </c>
       <c r="AQ10" t="n">
-        <v>2.78</v>
+        <v>5.32</v>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-1.45</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>10.382</t>
+          <t>10.702</t>
         </is>
       </c>
       <c r="AU10" t="n">
-        <v>10.1</v>
+        <v>10.16</v>
       </c>
       <c r="AV10" t="n">
-        <v>10.25</v>
+        <v>10.28</v>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>10.21</t>
+          <t>10.23</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>175.85</t>
+          <t>511.12</t>
         </is>
       </c>
       <c r="AY10" t="n">
-        <v>0.06</v>
+        <v>0.14</v>
       </c>
       <c r="AZ10" t="n">
-        <v>-0.08</v>
+        <v>-0.03</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4858,7 +4858,7 @@
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-114.52</t>
+          <t>-106.37</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
@@ -4868,43 +4868,43 @@
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>39660797.71097046</t>
+          <t>39643582.14396068</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
-          <t>390794197.0</t>
+          <t>120192159.0</t>
         </is>
       </c>
       <c r="BF10" t="n">
-        <v>105490556.2</v>
+        <v>126910257</v>
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>64310538.4</t>
+          <t>72495141.9</t>
         </is>
       </c>
       <c r="BH10" t="n">
-        <v>35931629.66</v>
+        <v>37850914.22</v>
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>41180017</t>
+          <t>54415115</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
         <is>
-          <t>4579451.34904508</t>
+          <t>8078031.522023421</t>
         </is>
       </c>
       <c r="BK10" t="inlineStr">
         <is>
-          <t>29841549.05537103</t>
+          <t>27320222.47340429</t>
         </is>
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>390794197.0</t>
+          <t>120192159.0</t>
         </is>
       </c>
       <c r="BM10" t="inlineStr">
@@ -4949,7 +4949,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -4969,7 +4969,7 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -5009,7 +5009,7 @@
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>63.31</t>
+          <t>63.44</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -5034,17 +5034,17 @@
       </c>
       <c r="CL10" t="inlineStr">
         <is>
-          <t>10.7</t>
+          <t>11.15</t>
         </is>
       </c>
       <c r="CM10" t="inlineStr">
         <is>
-          <t>11.75</t>
+          <t>11.8</t>
         </is>
       </c>
       <c r="CN10" t="inlineStr">
         <is>
-          <t>10.7</t>
+          <t>11.05</t>
         </is>
       </c>
       <c r="CO10" t="inlineStr">
@@ -5071,7 +5071,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>5.61</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>6273.16</t>
+          <t>34269.781</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>10.7</t>
+          <t>11.3</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -5106,17 +5106,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>-6.1</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>9.10</t>
+          <t>64.03</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -5136,7 +5136,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2025-12-15 00:00:00</t>
+          <t>2025-12-16 00:00:00</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -5226,22 +5226,22 @@
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>18.31</t>
+          <t>100.00</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>2.95</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
@@ -5252,12 +5252,12 @@
       <c r="AK11" t="inlineStr"/>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>1905</t>
+          <t>1703</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
@@ -5267,51 +5267,51 @@
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>88.73</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AP11" t="n">
-        <v>6.77</v>
+        <v>8.84</v>
       </c>
       <c r="AQ11" t="n">
-        <v>-0.22</v>
+        <v>2.78</v>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-1.69</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>10.022</t>
+          <t>10.382</t>
         </is>
       </c>
       <c r="AU11" t="n">
-        <v>10.04</v>
+        <v>10.1</v>
       </c>
       <c r="AV11" t="n">
-        <v>10.22</v>
+        <v>10.25</v>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>10.19</t>
+          <t>10.21</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>59.14</t>
+          <t>175.85</t>
         </is>
       </c>
       <c r="AY11" t="n">
-        <v>-0.05</v>
+        <v>0.06</v>
       </c>
       <c r="AZ11" t="n">
-        <v>-0.11</v>
+        <v>-0.08</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5320,7 +5320,7 @@
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-120.90</t>
+          <t>-114.52</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
@@ -5330,43 +5330,43 @@
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>39660797.71097046</t>
+          <t>39643582.14396068</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
-          <t>66856122.0</t>
+          <t>390794197.0</t>
         </is>
       </c>
       <c r="BF11" t="n">
-        <v>30264685.8</v>
+        <v>105490556.2</v>
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>27741544.4</t>
+          <t>64310538.4</t>
         </is>
       </c>
       <c r="BH11" t="n">
-        <v>28239844.66</v>
+        <v>35931629.66</v>
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>2523141</t>
+          <t>41180017</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
         <is>
-          <t>-13657.32483236655</t>
+          <t>4579451.34904508</t>
         </is>
       </c>
       <c r="BK11" t="inlineStr">
         <is>
-          <t>3384599.063345991</t>
+          <t>29841549.05537103</t>
         </is>
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>66856122.0</t>
+          <t>390794197.0</t>
         </is>
       </c>
       <c r="BM11" t="inlineStr">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>6.60</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5411,7 +5411,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5441,7 +5441,7 @@
       </c>
       <c r="CA11" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="CB11" t="inlineStr">
@@ -5471,7 +5471,7 @@
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>63.31</t>
+          <t>63.44</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5496,22 +5496,22 @@
       </c>
       <c r="CL11" t="inlineStr">
         <is>
-          <t>10.3</t>
+          <t>10.7</t>
         </is>
       </c>
       <c r="CM11" t="inlineStr">
         <is>
-          <t>10.8</t>
+          <t>11.75</t>
         </is>
       </c>
       <c r="CN11" t="inlineStr">
         <is>
-          <t>10.3</t>
+          <t>10.7</t>
         </is>
       </c>
       <c r="CO11" t="inlineStr">
         <is>
-          <t>10.7</t>
+          <t>11.3</t>
         </is>
       </c>
       <c r="CP11" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>4.95</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>4353.738</t>
+          <t>6273.16</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5558,7 +5558,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>10.35</t>
+          <t>10.7</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5568,17 +5568,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2.82</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-8.98</t>
+          <t>9.10</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5598,7 +5598,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2025-12-15 00:00:00</t>
+          <t>2025-12-16 00:00:00</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -5688,22 +5688,22 @@
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>12.70</t>
+          <t>18.31</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>4.65</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -5714,12 +5714,12 @@
       <c r="AK12" t="inlineStr"/>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>1905</t>
+          <t>1703</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
@@ -5729,51 +5729,51 @@
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>65.15</t>
+          <t>88.73</t>
         </is>
       </c>
       <c r="AP12" t="n">
-        <v>6.05</v>
+        <v>6.77</v>
       </c>
       <c r="AQ12" t="n">
-        <v>-2.51</v>
+        <v>-0.22</v>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-1.69</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>9.76</t>
+          <t>10.022</t>
         </is>
       </c>
       <c r="AU12" t="n">
-        <v>10.01</v>
+        <v>10.04</v>
       </c>
       <c r="AV12" t="n">
-        <v>10.19</v>
+        <v>10.22</v>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>10.18</t>
+          <t>10.19</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>8.30</t>
+          <t>59.14</t>
         </is>
       </c>
       <c r="AY12" t="n">
-        <v>-0.12</v>
+        <v>-0.05</v>
       </c>
       <c r="AZ12" t="n">
-        <v>-0.13</v>
+        <v>-0.11</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-123.99</t>
+          <t>-120.90</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
@@ -5792,43 +5792,43 @@
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>39660797.71097046</t>
+          <t>39643582.14396068</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
-          <t>44205175.0</t>
+          <t>66856122.0</t>
         </is>
       </c>
       <c r="BF12" t="n">
-        <v>20413759.2</v>
+        <v>30264685.8</v>
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>22428185.2</t>
+          <t>27741544.4</t>
         </is>
       </c>
       <c r="BH12" t="n">
-        <v>27064322.42</v>
+        <v>28239844.66</v>
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>-2014426</t>
+          <t>2523141</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
         <is>
-          <t>-631522.122682977</t>
+          <t>-13657.32483236655</t>
         </is>
       </c>
       <c r="BK12" t="inlineStr">
         <is>
-          <t>175728.5724764355</t>
+          <t>3384599.063345991</t>
         </is>
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>44205175.0</t>
+          <t>66856122.0</t>
         </is>
       </c>
       <c r="BM12" t="inlineStr">
@@ -5848,7 +5848,7 @@
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5873,7 +5873,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -5903,7 +5903,7 @@
       </c>
       <c r="CA12" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="CB12" t="inlineStr">
@@ -5933,7 +5933,7 @@
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>63.31</t>
+          <t>63.44</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5958,22 +5958,22 @@
       </c>
       <c r="CL12" t="inlineStr">
         <is>
-          <t>9.89</t>
+          <t>10.3</t>
         </is>
       </c>
       <c r="CM12" t="inlineStr">
         <is>
-          <t>10.35</t>
+          <t>10.8</t>
         </is>
       </c>
       <c r="CN12" t="inlineStr">
         <is>
-          <t>9.89</t>
+          <t>10.3</t>
         </is>
       </c>
       <c r="CO12" t="inlineStr">
         <is>
-          <t>10.35</t>
+          <t>10.7</t>
         </is>
       </c>
       <c r="CP12" t="inlineStr">

--- a/Result/checksun_type/塑化劑(可塑劑).xlsx
+++ b/Result/checksun_type/塑化劑(可塑劑).xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CR12"/>
+  <dimension ref="A1:CV12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -566,345 +566,365 @@
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
+          <t>MACD_hist_diff</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
           <t>MA_death_cross_d</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>MA_death_cross_d收盤價</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>MA_death_cross_d2</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>MA_death_cross_d2收盤價</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>MACD_hist_diff</t>
-        </is>
-      </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
+          <t>MACD_death_cross_d</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>MACD_death_cross_d收盤價</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>MACD_death_cross_d2</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>MACD_death_cross_d2收盤價</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>量能</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>價能</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>cond_entry</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>text_desc</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>盤後量</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>成交量</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>%K</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>%D</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>MA5_%</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>均價_%</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>均價long_%</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>均價longlong_%</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>MA_short</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>MA_long</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>MA_longlong</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>MA_longlonglong</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>MACD_%</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>MACD</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>MACD-SL</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>MACD-SL_max</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>MACDSL_%</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>MACD_last_cross_date</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>成交金額平均</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>成交金額</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BJ1" s="1" t="inlineStr">
         <is>
           <t>Volume_MA_short</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BK1" s="1" t="inlineStr">
         <is>
           <t>Volume_MA_long</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BL1" s="1" t="inlineStr">
         <is>
           <t>Volume_MA_long50</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BM1" s="1" t="inlineStr">
         <is>
           <t>Volume_Oscillator</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BN1" s="1" t="inlineStr">
         <is>
           <t>volume_threshold</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BO1" s="1" t="inlineStr">
         <is>
           <t>VPC_MACD</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
+      <c r="BP1" s="1" t="inlineStr">
         <is>
           <t>Volume_Price_Change</t>
         </is>
       </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="BQ1" s="1" t="inlineStr">
         <is>
           <t>highlight_enddate</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="BR1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_date收盤價</t>
         </is>
       </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="BS1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_date</t>
         </is>
       </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="BT1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_%</t>
         </is>
       </c>
-      <c r="BQ1" s="1" t="inlineStr">
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>stock_name</t>
         </is>
       </c>
-      <c r="BR1" s="1" t="inlineStr">
+      <c r="BV1" s="1" t="inlineStr">
         <is>
           <t>Type0</t>
         </is>
       </c>
-      <c r="BS1" s="1" t="inlineStr">
+      <c r="BW1" s="1" t="inlineStr">
         <is>
           <t>Type1</t>
         </is>
       </c>
-      <c r="BT1" s="1" t="inlineStr">
+      <c r="BX1" s="1" t="inlineStr">
         <is>
           <t>Type2</t>
         </is>
       </c>
-      <c r="BU1" s="1" t="inlineStr">
+      <c r="BY1" s="1" t="inlineStr">
         <is>
           <t>貝他值</t>
         </is>
       </c>
-      <c r="BV1" s="1" t="inlineStr">
+      <c r="BZ1" s="1" t="inlineStr">
         <is>
           <t>營業收入-上月比較增減(%)</t>
         </is>
       </c>
-      <c r="BW1" s="1" t="inlineStr">
+      <c r="CA1" s="1" t="inlineStr">
         <is>
           <t>營業收入-去年同月增減(%)</t>
         </is>
       </c>
-      <c r="BX1" s="1" t="inlineStr">
+      <c r="CB1" s="1" t="inlineStr">
         <is>
           <t>累計營業收入-前期比較增減(%)</t>
         </is>
       </c>
-      <c r="BY1" s="1" t="inlineStr">
+      <c r="CC1" s="1" t="inlineStr">
         <is>
           <t>Full_Summary</t>
         </is>
       </c>
-      <c r="BZ1" s="1" t="inlineStr">
+      <c r="CD1" s="1" t="inlineStr">
         <is>
           <t>textdesc</t>
         </is>
       </c>
-      <c r="CA1" s="1" t="inlineStr">
+      <c r="CE1" s="1" t="inlineStr">
         <is>
           <t>淨值倍率</t>
         </is>
       </c>
-      <c r="CB1" s="1" t="inlineStr">
+      <c r="CF1" s="1" t="inlineStr">
         <is>
           <t>殖利率</t>
         </is>
       </c>
-      <c r="CC1" s="1" t="inlineStr">
+      <c r="CG1" s="1" t="inlineStr">
         <is>
           <t>每股營收(元)</t>
         </is>
       </c>
-      <c r="CD1" s="1" t="inlineStr">
+      <c r="CH1" s="1" t="inlineStr">
         <is>
           <t>本益比</t>
         </is>
       </c>
-      <c r="CE1" s="1" t="inlineStr">
+      <c r="CI1" s="1" t="inlineStr">
         <is>
           <t>營業毛利率</t>
         </is>
       </c>
-      <c r="CF1" s="1" t="inlineStr">
+      <c r="CJ1" s="1" t="inlineStr">
         <is>
           <t>營業利益率</t>
         </is>
       </c>
-      <c r="CG1" s="1" t="inlineStr">
+      <c r="CK1" s="1" t="inlineStr">
         <is>
           <t>同業平均本益比</t>
         </is>
       </c>
-      <c r="CH1" s="1" t="inlineStr">
+      <c r="CL1" s="1" t="inlineStr">
         <is>
           <t>總市值</t>
         </is>
       </c>
-      <c r="CI1" s="1" t="inlineStr">
+      <c r="CM1" s="1" t="inlineStr">
         <is>
           <t>營收比重</t>
         </is>
       </c>
-      <c r="CJ1" s="1" t="inlineStr">
+      <c r="CN1" s="1" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="CK1" s="1" t="inlineStr">
+      <c r="CO1" s="1" t="inlineStr">
         <is>
           <t>Typelevel</t>
         </is>
       </c>
-      <c r="CL1" s="1" t="inlineStr">
+      <c r="CP1" s="1" t="inlineStr">
         <is>
           <t>開盤價</t>
         </is>
       </c>
-      <c r="CM1" s="1" t="inlineStr">
+      <c r="CQ1" s="1" t="inlineStr">
         <is>
           <t>最高價</t>
         </is>
       </c>
-      <c r="CN1" s="1" t="inlineStr">
+      <c r="CR1" s="1" t="inlineStr">
         <is>
           <t>最低價</t>
         </is>
       </c>
-      <c r="CO1" s="1" t="inlineStr">
+      <c r="CS1" s="1" t="inlineStr">
         <is>
           <t>收盤價</t>
         </is>
       </c>
-      <c r="CP1" s="1" t="inlineStr">
+      <c r="CT1" s="1" t="inlineStr">
         <is>
           <t>每股淨值(元)</t>
         </is>
       </c>
-      <c r="CQ1" s="1" t="inlineStr">
+      <c r="CU1" s="1" t="inlineStr">
         <is>
           <t>desc</t>
         </is>
       </c>
-      <c r="CR1" s="1" t="inlineStr">
+      <c r="CV1" s="1" t="inlineStr">
         <is>
           <t>flag_stat</t>
         </is>
@@ -1048,325 +1068,345 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
+          <t>-0.02</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
           <t>2025/11/21</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>9.53</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>2025/09/22</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
         <is>
           <t>10.15</t>
         </is>
       </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>-0.02</t>
-        </is>
-      </c>
       <c r="AG2" t="inlineStr">
         <is>
+          <t>2025/11/17</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>10.1</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>2025/10/28</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>10.3</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
           <t>2025-12-15</t>
         </is>
       </c>
-      <c r="AH2" t="inlineStr">
+      <c r="AL2" t="inlineStr">
         <is>
           <t>4.97</t>
         </is>
       </c>
-      <c r="AI2" t="inlineStr">
+      <c r="AM2" t="inlineStr">
         <is>
           <t>-1.40</t>
         </is>
       </c>
-      <c r="AJ2" t="inlineStr">
+      <c r="AN2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK2" t="inlineStr"/>
-      <c r="AL2" t="inlineStr">
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
+      <c r="AQ2" t="inlineStr">
         <is>
           <t>1703</t>
         </is>
       </c>
-      <c r="AN2" t="inlineStr">
+      <c r="AR2" t="inlineStr">
         <is>
           <t>5.88</t>
         </is>
       </c>
-      <c r="AO2" t="inlineStr">
+      <c r="AS2" t="inlineStr">
         <is>
           <t>13.73</t>
         </is>
       </c>
-      <c r="AP2" t="n">
+      <c r="AT2" t="n">
         <v>-1.3</v>
       </c>
-      <c r="AQ2" t="n">
+      <c r="AU2" t="n">
         <v>3.5</v>
       </c>
-      <c r="AR2" t="inlineStr">
+      <c r="AV2" t="inlineStr">
         <is>
           <t>0.49</t>
         </is>
       </c>
-      <c r="AS2" t="inlineStr">
+      <c r="AW2" t="inlineStr">
         <is>
           <t>0.73</t>
         </is>
       </c>
-      <c r="AT2" t="inlineStr">
+      <c r="AX2" t="inlineStr">
         <is>
           <t>10.79</t>
         </is>
       </c>
-      <c r="AU2" t="n">
+      <c r="AY2" t="n">
         <v>10.42</v>
       </c>
-      <c r="AV2" t="n">
+      <c r="AZ2" t="n">
         <v>10.37</v>
       </c>
-      <c r="AW2" t="inlineStr">
+      <c r="BA2" t="inlineStr">
         <is>
           <t>10.3</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="BB2" t="inlineStr">
         <is>
           <t>2.01</t>
         </is>
       </c>
-      <c r="AY2" t="n">
+      <c r="BC2" t="n">
         <v>0.18</v>
       </c>
-      <c r="AZ2" t="n">
+      <c r="BD2" t="n">
         <v>0.18</v>
       </c>
-      <c r="BA2" t="inlineStr">
+      <c r="BE2" t="inlineStr">
         <is>
           <t>0.54</t>
         </is>
       </c>
-      <c r="BB2" t="inlineStr">
+      <c r="BF2" t="inlineStr">
         <is>
           <t>-66.34</t>
         </is>
       </c>
-      <c r="BC2" t="inlineStr">
+      <c r="BG2" t="inlineStr">
         <is>
           <t>2025/11/28</t>
         </is>
       </c>
-      <c r="BD2" t="inlineStr">
+      <c r="BH2" t="inlineStr">
         <is>
           <t>39643582.14396068</t>
         </is>
       </c>
-      <c r="BE2" t="inlineStr">
+      <c r="BI2" t="inlineStr">
         <is>
           <t>18268876.0</t>
         </is>
       </c>
-      <c r="BF2" t="n">
+      <c r="BJ2" t="n">
         <v>32256217.8</v>
       </c>
-      <c r="BG2" t="inlineStr">
+      <c r="BK2" t="inlineStr">
         <is>
           <t>80763071.4</t>
         </is>
       </c>
-      <c r="BH2" t="n">
+      <c r="BL2" t="n">
         <v>38610965.58</v>
       </c>
-      <c r="BI2" t="inlineStr">
+      <c r="BM2" t="inlineStr">
         <is>
           <t>-48506853</t>
         </is>
       </c>
-      <c r="BJ2" t="inlineStr">
+      <c r="BN2" t="inlineStr">
         <is>
           <t>3677575.421348871</t>
         </is>
       </c>
-      <c r="BK2" t="inlineStr">
+      <c r="BO2" t="inlineStr">
         <is>
           <t>-5479927.99472075</t>
         </is>
       </c>
-      <c r="BL2" t="inlineStr">
+      <c r="BP2" t="inlineStr">
         <is>
           <t>18268876.0</t>
         </is>
       </c>
-      <c r="BM2" t="inlineStr">
+      <c r="BQ2" t="inlineStr">
         <is>
           <t>2025-12-16</t>
         </is>
       </c>
-      <c r="BN2" t="inlineStr">
+      <c r="BR2" t="inlineStr">
         <is>
           <t>10.6</t>
         </is>
       </c>
-      <c r="BO2" t="inlineStr">
+      <c r="BS2" t="inlineStr">
         <is>
           <t>2025/12/10</t>
         </is>
       </c>
-      <c r="BP2" t="inlineStr">
+      <c r="BT2" t="inlineStr">
         <is>
           <t>0.47</t>
         </is>
       </c>
-      <c r="BQ2" t="inlineStr">
+      <c r="BU2" t="inlineStr">
         <is>
           <t>聯成</t>
         </is>
       </c>
-      <c r="BR2" t="inlineStr">
+      <c r="BV2" t="inlineStr">
         <is>
           <t>聯成</t>
         </is>
       </c>
-      <c r="BS2" t="inlineStr">
+      <c r="BW2" t="inlineStr">
         <is>
           <t>塑膠工業</t>
         </is>
       </c>
-      <c r="BT2" t="inlineStr">
+      <c r="BX2" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BU2" t="inlineStr">
+      <c r="BY2" t="inlineStr">
         <is>
           <t>0.76</t>
         </is>
       </c>
-      <c r="BV2" t="inlineStr">
+      <c r="BZ2" t="inlineStr">
         <is>
           <t>-11.96408371040724</t>
         </is>
       </c>
-      <c r="BW2" t="inlineStr">
+      <c r="CA2" t="inlineStr">
         <is>
           <t>-13.59414944504011</t>
         </is>
       </c>
-      <c r="BX2" t="inlineStr">
+      <c r="CB2" t="inlineStr">
         <is>
           <t>-19.633719693908</t>
         </is>
       </c>
-      <c r="BY2" t="inlineStr">
+      <c r="CC2" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ2" t="inlineStr">
+      <c r="CD2" t="inlineStr">
         <is>
           <t>價漲量-</t>
         </is>
       </c>
-      <c r="CA2" t="inlineStr">
+      <c r="CE2" t="inlineStr">
         <is>
           <t>0.48</t>
         </is>
       </c>
-      <c r="CB2" t="inlineStr">
+      <c r="CF2" t="inlineStr">
         <is>
           <t>1.41</t>
         </is>
       </c>
-      <c r="CC2" t="inlineStr">
+      <c r="CG2" t="inlineStr">
         <is>
           <t>10.97</t>
         </is>
       </c>
-      <c r="CD2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CE2" t="inlineStr">
+      <c r="CH2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CI2" t="inlineStr">
         <is>
           <t>0.96%</t>
         </is>
       </c>
-      <c r="CF2" t="inlineStr">
+      <c r="CJ2" t="inlineStr">
         <is>
           <t>-3.42%</t>
         </is>
       </c>
-      <c r="CG2" t="inlineStr">
+      <c r="CK2" t="inlineStr">
         <is>
           <t>63.44</t>
         </is>
       </c>
-      <c r="CH2" t="inlineStr">
+      <c r="CL2" t="inlineStr">
         <is>
           <t>14374</t>
         </is>
       </c>
-      <c r="CI2" t="inlineStr">
+      <c r="CM2" t="inlineStr">
         <is>
           <t>可塑劑(DOP)76.00%、聚氯乙烯13.00%、酸酐6.00%、其他5.00% (2024年)</t>
         </is>
       </c>
-      <c r="CJ2" t="inlineStr">
+      <c r="CN2" t="inlineStr">
         <is>
           <t>聯成-塑膠工業-上市</t>
         </is>
       </c>
-      <c r="CK2" t="inlineStr">
+      <c r="CO2" t="inlineStr">
         <is>
           <t>塑膠工業右下上市</t>
         </is>
       </c>
-      <c r="CL2" t="inlineStr">
+      <c r="CP2" t="inlineStr">
         <is>
           <t>10.6</t>
         </is>
       </c>
-      <c r="CM2" t="inlineStr">
+      <c r="CQ2" t="inlineStr">
         <is>
           <t>10.9</t>
         </is>
       </c>
-      <c r="CN2" t="inlineStr">
+      <c r="CR2" t="inlineStr">
         <is>
           <t>10.55</t>
         </is>
       </c>
-      <c r="CO2" t="inlineStr">
+      <c r="CS2" t="inlineStr">
         <is>
           <t>10.65</t>
         </is>
       </c>
-      <c r="CP2" t="inlineStr">
+      <c r="CT2" t="inlineStr">
         <is>
           <t>22.32</t>
         </is>
       </c>
-      <c r="CQ2" t="inlineStr">
+      <c r="CU2" t="inlineStr">
         <is>
           <t>** 石化及塑橡膠 - 塑化劑(可塑劑)</t>
         </is>
       </c>
-      <c r="CR2" t="inlineStr">
+      <c r="CV2" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -1510,325 +1550,345 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
+          <t>-0.03</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
           <t>2025/11/21</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>9.53</t>
         </is>
       </c>
-      <c r="AD3" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>2025/09/22</t>
         </is>
       </c>
-      <c r="AE3" t="inlineStr">
+      <c r="AF3" t="inlineStr">
         <is>
           <t>10.15</t>
         </is>
       </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>-0.03</t>
-        </is>
-      </c>
       <c r="AG3" t="inlineStr">
         <is>
+          <t>2025/11/17</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>10.1</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>2025/10/28</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>10.3</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
           <t>2025-12-12</t>
         </is>
       </c>
-      <c r="AH3" t="inlineStr">
+      <c r="AL3" t="inlineStr">
         <is>
           <t>5.56</t>
         </is>
       </c>
-      <c r="AI3" t="inlineStr">
+      <c r="AM3" t="inlineStr">
         <is>
           <t>-5.16</t>
         </is>
       </c>
-      <c r="AJ3" t="inlineStr">
+      <c r="AN3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK3" t="inlineStr"/>
-      <c r="AL3" t="inlineStr">
+      <c r="AO3" t="inlineStr"/>
+      <c r="AP3" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
+      <c r="AQ3" t="inlineStr">
         <is>
           <t>1703</t>
         </is>
       </c>
-      <c r="AN3" t="inlineStr">
+      <c r="AR3" t="inlineStr">
         <is>
           <t>5.88</t>
         </is>
       </c>
-      <c r="AO3" t="inlineStr">
+      <c r="AS3" t="inlineStr">
         <is>
           <t>19.34</t>
         </is>
       </c>
-      <c r="AP3" t="n">
+      <c r="AT3" t="n">
         <v>-2.02</v>
       </c>
-      <c r="AQ3" t="n">
+      <c r="AU3" t="n">
         <v>4.54</v>
       </c>
-      <c r="AR3" t="inlineStr">
+      <c r="AV3" t="inlineStr">
         <is>
           <t>0.29</t>
         </is>
       </c>
-      <c r="AS3" t="inlineStr">
+      <c r="AW3" t="inlineStr">
         <is>
           <t>0.62</t>
         </is>
       </c>
-      <c r="AT3" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>10.87</t>
         </is>
       </c>
-      <c r="AU3" t="n">
+      <c r="AY3" t="n">
         <v>10.4</v>
       </c>
-      <c r="AV3" t="n">
+      <c r="AZ3" t="n">
         <v>10.37</v>
       </c>
-      <c r="AW3" t="inlineStr">
+      <c r="BA3" t="inlineStr">
         <is>
           <t>10.3</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="BB3" t="inlineStr">
         <is>
           <t>15.38</t>
         </is>
       </c>
-      <c r="AY3" t="n">
+      <c r="BC3" t="n">
         <v>0.21</v>
       </c>
-      <c r="AZ3" t="n">
+      <c r="BD3" t="n">
         <v>0.18</v>
       </c>
-      <c r="BA3" t="inlineStr">
+      <c r="BE3" t="inlineStr">
         <is>
           <t>0.54</t>
         </is>
       </c>
-      <c r="BB3" t="inlineStr">
+      <c r="BF3" t="inlineStr">
         <is>
           <t>-66.51</t>
         </is>
       </c>
-      <c r="BC3" t="inlineStr">
+      <c r="BG3" t="inlineStr">
         <is>
           <t>2025/11/28</t>
         </is>
       </c>
-      <c r="BD3" t="inlineStr">
+      <c r="BH3" t="inlineStr">
         <is>
           <t>39643582.14396068</t>
         </is>
       </c>
-      <c r="BE3" t="inlineStr">
+      <c r="BI3" t="inlineStr">
         <is>
           <t>20756844.0</t>
         </is>
       </c>
-      <c r="BF3" t="n">
+      <c r="BJ3" t="n">
         <v>35969648.4</v>
       </c>
-      <c r="BG3" t="inlineStr">
+      <c r="BK3" t="inlineStr">
         <is>
           <t>85621796.0</t>
         </is>
       </c>
-      <c r="BH3" t="n">
+      <c r="BL3" t="n">
         <v>38506172.98</v>
       </c>
-      <c r="BI3" t="inlineStr">
+      <c r="BM3" t="inlineStr">
         <is>
           <t>-49652147</t>
         </is>
       </c>
-      <c r="BJ3" t="inlineStr">
+      <c r="BN3" t="inlineStr">
         <is>
           <t>5342576.042452438</t>
         </is>
       </c>
-      <c r="BK3" t="inlineStr">
+      <c r="BO3" t="inlineStr">
         <is>
           <t>-3500640.656066917</t>
         </is>
       </c>
-      <c r="BL3" t="inlineStr">
+      <c r="BP3" t="inlineStr">
         <is>
           <t>20756844.0</t>
         </is>
       </c>
-      <c r="BM3" t="inlineStr">
+      <c r="BQ3" t="inlineStr">
         <is>
           <t>2025-12-16</t>
         </is>
       </c>
-      <c r="BN3" t="inlineStr">
+      <c r="BR3" t="inlineStr">
         <is>
           <t>10.6</t>
         </is>
       </c>
-      <c r="BO3" t="inlineStr">
+      <c r="BS3" t="inlineStr">
         <is>
           <t>2025/12/10</t>
         </is>
       </c>
-      <c r="BP3" t="inlineStr">
+      <c r="BT3" t="inlineStr">
         <is>
           <t>0.47</t>
         </is>
       </c>
-      <c r="BQ3" t="inlineStr">
+      <c r="BU3" t="inlineStr">
         <is>
           <t>聯成</t>
         </is>
       </c>
-      <c r="BR3" t="inlineStr">
+      <c r="BV3" t="inlineStr">
         <is>
           <t>聯成</t>
         </is>
       </c>
-      <c r="BS3" t="inlineStr">
+      <c r="BW3" t="inlineStr">
         <is>
           <t>塑膠工業</t>
         </is>
       </c>
-      <c r="BT3" t="inlineStr">
+      <c r="BX3" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BU3" t="inlineStr">
+      <c r="BY3" t="inlineStr">
         <is>
           <t>0.76</t>
         </is>
       </c>
-      <c r="BV3" t="inlineStr">
+      <c r="BZ3" t="inlineStr">
         <is>
           <t>-11.96408371040724</t>
         </is>
       </c>
-      <c r="BW3" t="inlineStr">
+      <c r="CA3" t="inlineStr">
         <is>
           <t>-13.59414944504011</t>
         </is>
       </c>
-      <c r="BX3" t="inlineStr">
+      <c r="CB3" t="inlineStr">
         <is>
           <t>-19.633719693908</t>
         </is>
       </c>
-      <c r="BY3" t="inlineStr">
+      <c r="CC3" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ3" t="inlineStr">
+      <c r="CD3" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CA3" t="inlineStr">
+      <c r="CE3" t="inlineStr">
         <is>
           <t>0.48</t>
         </is>
       </c>
-      <c r="CB3" t="inlineStr">
+      <c r="CF3" t="inlineStr">
         <is>
           <t>1.41</t>
         </is>
       </c>
-      <c r="CC3" t="inlineStr">
+      <c r="CG3" t="inlineStr">
         <is>
           <t>10.97</t>
         </is>
       </c>
-      <c r="CD3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CE3" t="inlineStr">
+      <c r="CH3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CI3" t="inlineStr">
         <is>
           <t>0.96%</t>
         </is>
       </c>
-      <c r="CF3" t="inlineStr">
+      <c r="CJ3" t="inlineStr">
         <is>
           <t>-3.42%</t>
         </is>
       </c>
-      <c r="CG3" t="inlineStr">
+      <c r="CK3" t="inlineStr">
         <is>
           <t>63.44</t>
         </is>
       </c>
-      <c r="CH3" t="inlineStr">
+      <c r="CL3" t="inlineStr">
         <is>
           <t>14374</t>
         </is>
       </c>
-      <c r="CI3" t="inlineStr">
+      <c r="CM3" t="inlineStr">
         <is>
           <t>可塑劑(DOP)76.00%、聚氯乙烯13.00%、酸酐6.00%、其他5.00% (2024年)</t>
         </is>
       </c>
-      <c r="CJ3" t="inlineStr">
+      <c r="CN3" t="inlineStr">
         <is>
           <t>聯成-塑膠工業-上市</t>
         </is>
       </c>
-      <c r="CK3" t="inlineStr">
+      <c r="CO3" t="inlineStr">
         <is>
           <t>塑膠工業右下上市</t>
         </is>
       </c>
-      <c r="CL3" t="inlineStr">
+      <c r="CP3" t="inlineStr">
         <is>
           <t>10.95</t>
         </is>
       </c>
-      <c r="CM3" t="inlineStr">
+      <c r="CQ3" t="inlineStr">
         <is>
           <t>11.2</t>
         </is>
       </c>
-      <c r="CN3" t="inlineStr">
+      <c r="CR3" t="inlineStr">
         <is>
           <t>10.65</t>
         </is>
       </c>
-      <c r="CO3" t="inlineStr">
+      <c r="CS3" t="inlineStr">
         <is>
           <t>10.65</t>
         </is>
       </c>
-      <c r="CP3" t="inlineStr">
+      <c r="CT3" t="inlineStr">
         <is>
           <t>22.32</t>
         </is>
       </c>
-      <c r="CQ3" t="inlineStr">
+      <c r="CU3" t="inlineStr">
         <is>
           <t>** 石化及塑橡膠 - 塑化劑(可塑劑)</t>
         </is>
       </c>
-      <c r="CR3" t="inlineStr">
+      <c r="CV3" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -1972,325 +2032,345 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
+          <t>-0.03</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
           <t>2025/11/21</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>9.53</t>
         </is>
       </c>
-      <c r="AD4" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>2025/09/22</t>
         </is>
       </c>
-      <c r="AE4" t="inlineStr">
+      <c r="AF4" t="inlineStr">
         <is>
           <t>10.15</t>
         </is>
       </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>-0.03</t>
-        </is>
-      </c>
       <c r="AG4" t="inlineStr">
         <is>
+          <t>2025/11/17</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>10.1</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>2025/10/28</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>10.3</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AH4" t="inlineStr">
+      <c r="AL4" t="inlineStr">
         <is>
           <t>5.69</t>
         </is>
       </c>
-      <c r="AI4" t="inlineStr">
+      <c r="AM4" t="inlineStr">
         <is>
           <t>1.44</t>
         </is>
       </c>
-      <c r="AJ4" t="inlineStr">
+      <c r="AN4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK4" t="inlineStr"/>
-      <c r="AL4" t="inlineStr">
+      <c r="AO4" t="inlineStr"/>
+      <c r="AP4" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
+      <c r="AQ4" t="inlineStr">
         <is>
           <t>1703</t>
         </is>
       </c>
-      <c r="AN4" t="inlineStr">
+      <c r="AR4" t="inlineStr">
         <is>
           <t>29.41</t>
         </is>
       </c>
-      <c r="AO4" t="inlineStr">
+      <c r="AS4" t="inlineStr">
         <is>
           <t>45.47</t>
         </is>
       </c>
-      <c r="AP4" t="n">
+      <c r="AT4" t="n">
         <v>-1</v>
       </c>
-      <c r="AQ4" t="n">
+      <c r="AU4" t="n">
         <v>5.51</v>
       </c>
-      <c r="AR4" t="inlineStr">
+      <c r="AV4" t="inlineStr">
         <is>
           <t>0.23</t>
         </is>
       </c>
-      <c r="AS4" t="inlineStr">
+      <c r="AW4" t="inlineStr">
         <is>
           <t>0.53</t>
         </is>
       </c>
-      <c r="AT4" t="inlineStr">
+      <c r="AX4" t="inlineStr">
         <is>
           <t>10.96</t>
         </is>
       </c>
-      <c r="AU4" t="n">
+      <c r="AY4" t="n">
         <v>10.39</v>
       </c>
-      <c r="AV4" t="n">
+      <c r="AZ4" t="n">
         <v>10.36</v>
       </c>
-      <c r="AW4" t="inlineStr">
+      <c r="BA4" t="inlineStr">
         <is>
           <t>10.31</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
+      <c r="BB4" t="inlineStr">
         <is>
           <t>35.30</t>
         </is>
       </c>
-      <c r="AY4" t="n">
+      <c r="BC4" t="n">
         <v>0.23</v>
       </c>
-      <c r="AZ4" t="n">
+      <c r="BD4" t="n">
         <v>0.17</v>
       </c>
-      <c r="BA4" t="inlineStr">
+      <c r="BE4" t="inlineStr">
         <is>
           <t>0.54</t>
         </is>
       </c>
-      <c r="BB4" t="inlineStr">
+      <c r="BF4" t="inlineStr">
         <is>
           <t>-67.80</t>
         </is>
       </c>
-      <c r="BC4" t="inlineStr">
+      <c r="BG4" t="inlineStr">
         <is>
           <t>2025/11/28</t>
         </is>
       </c>
-      <c r="BD4" t="inlineStr">
+      <c r="BH4" t="inlineStr">
         <is>
           <t>39643582.14396068</t>
         </is>
       </c>
-      <c r="BE4" t="inlineStr">
+      <c r="BI4" t="inlineStr">
         <is>
           <t>21031488.0</t>
         </is>
       </c>
-      <c r="BF4" t="n">
+      <c r="BJ4" t="n">
         <v>41281758.4</v>
       </c>
-      <c r="BG4" t="inlineStr">
+      <c r="BK4" t="inlineStr">
         <is>
           <t>87966629.1</t>
         </is>
       </c>
-      <c r="BH4" t="n">
+      <c r="BL4" t="n">
         <v>38425696.6</v>
       </c>
-      <c r="BI4" t="inlineStr">
+      <c r="BM4" t="inlineStr">
         <is>
           <t>-46684870</t>
         </is>
       </c>
-      <c r="BJ4" t="inlineStr">
+      <c r="BN4" t="inlineStr">
         <is>
           <t>6950433.624001412</t>
         </is>
       </c>
-      <c r="BK4" t="inlineStr">
+      <c r="BO4" t="inlineStr">
         <is>
           <t>-814632.4345590472</t>
         </is>
       </c>
-      <c r="BL4" t="inlineStr">
+      <c r="BP4" t="inlineStr">
         <is>
           <t>21031488.0</t>
         </is>
       </c>
-      <c r="BM4" t="inlineStr">
+      <c r="BQ4" t="inlineStr">
         <is>
           <t>2025-12-16</t>
         </is>
       </c>
-      <c r="BN4" t="inlineStr">
+      <c r="BR4" t="inlineStr">
         <is>
           <t>10.6</t>
         </is>
       </c>
-      <c r="BO4" t="inlineStr">
+      <c r="BS4" t="inlineStr">
         <is>
           <t>2025/12/10</t>
         </is>
       </c>
-      <c r="BP4" t="inlineStr">
+      <c r="BT4" t="inlineStr">
         <is>
           <t>2.36</t>
         </is>
       </c>
-      <c r="BQ4" t="inlineStr">
+      <c r="BU4" t="inlineStr">
         <is>
           <t>聯成</t>
         </is>
       </c>
-      <c r="BR4" t="inlineStr">
+      <c r="BV4" t="inlineStr">
         <is>
           <t>聯成</t>
         </is>
       </c>
-      <c r="BS4" t="inlineStr">
+      <c r="BW4" t="inlineStr">
         <is>
           <t>塑膠工業</t>
         </is>
       </c>
-      <c r="BT4" t="inlineStr">
+      <c r="BX4" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BU4" t="inlineStr">
+      <c r="BY4" t="inlineStr">
         <is>
           <t>0.76</t>
         </is>
       </c>
-      <c r="BV4" t="inlineStr">
+      <c r="BZ4" t="inlineStr">
         <is>
           <t>-11.96408371040724</t>
         </is>
       </c>
-      <c r="BW4" t="inlineStr">
+      <c r="CA4" t="inlineStr">
         <is>
           <t>-13.59414944504011</t>
         </is>
       </c>
-      <c r="BX4" t="inlineStr">
+      <c r="CB4" t="inlineStr">
         <is>
           <t>-19.633719693908</t>
         </is>
       </c>
-      <c r="BY4" t="inlineStr">
+      <c r="CC4" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ4" t="inlineStr">
+      <c r="CD4" t="inlineStr">
         <is>
           <t>價漲量-</t>
         </is>
       </c>
-      <c r="CA4" t="inlineStr">
+      <c r="CE4" t="inlineStr">
         <is>
           <t>0.49</t>
         </is>
       </c>
-      <c r="CB4" t="inlineStr">
+      <c r="CF4" t="inlineStr">
         <is>
           <t>1.41</t>
         </is>
       </c>
-      <c r="CC4" t="inlineStr">
+      <c r="CG4" t="inlineStr">
         <is>
           <t>10.97</t>
         </is>
       </c>
-      <c r="CD4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CE4" t="inlineStr">
+      <c r="CH4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CI4" t="inlineStr">
         <is>
           <t>0.96%</t>
         </is>
       </c>
-      <c r="CF4" t="inlineStr">
+      <c r="CJ4" t="inlineStr">
         <is>
           <t>-3.42%</t>
         </is>
       </c>
-      <c r="CG4" t="inlineStr">
+      <c r="CK4" t="inlineStr">
         <is>
           <t>63.44</t>
         </is>
       </c>
-      <c r="CH4" t="inlineStr">
+      <c r="CL4" t="inlineStr">
         <is>
           <t>14374</t>
         </is>
       </c>
-      <c r="CI4" t="inlineStr">
+      <c r="CM4" t="inlineStr">
         <is>
           <t>可塑劑(DOP)76.00%、聚氯乙烯13.00%、酸酐6.00%、其他5.00% (2024年)</t>
         </is>
       </c>
-      <c r="CJ4" t="inlineStr">
+      <c r="CN4" t="inlineStr">
         <is>
           <t>聯成-塑膠工業-上市</t>
         </is>
       </c>
-      <c r="CK4" t="inlineStr">
+      <c r="CO4" t="inlineStr">
         <is>
           <t>塑膠工業右下上市</t>
         </is>
       </c>
-      <c r="CL4" t="inlineStr">
+      <c r="CP4" t="inlineStr">
         <is>
           <t>10.6</t>
         </is>
       </c>
-      <c r="CM4" t="inlineStr">
+      <c r="CQ4" t="inlineStr">
         <is>
           <t>10.95</t>
         </is>
       </c>
-      <c r="CN4" t="inlineStr">
+      <c r="CR4" t="inlineStr">
         <is>
           <t>10.6</t>
         </is>
       </c>
-      <c r="CO4" t="inlineStr">
+      <c r="CS4" t="inlineStr">
         <is>
           <t>10.85</t>
         </is>
       </c>
-      <c r="CP4" t="inlineStr">
+      <c r="CT4" t="inlineStr">
         <is>
           <t>22.32</t>
         </is>
       </c>
-      <c r="CQ4" t="inlineStr">
+      <c r="CU4" t="inlineStr">
         <is>
           <t>** 石化及塑橡膠 - 塑化劑(可塑劑)</t>
         </is>
       </c>
-      <c r="CR4" t="inlineStr">
+      <c r="CV4" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -2434,325 +2514,345 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
+          <t>-0.06</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
           <t>2025/11/21</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>9.53</t>
         </is>
       </c>
-      <c r="AD5" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>2025/09/22</t>
         </is>
       </c>
-      <c r="AE5" t="inlineStr">
+      <c r="AF5" t="inlineStr">
         <is>
           <t>10.15</t>
         </is>
       </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>-0.06</t>
-        </is>
-      </c>
       <c r="AG5" t="inlineStr">
         <is>
+          <t>2025/11/17</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>10.1</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>2025/10/28</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>10.3</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
           <t>2025-12-10</t>
         </is>
       </c>
-      <c r="AH5" t="inlineStr">
+      <c r="AL5" t="inlineStr">
         <is>
           <t>13.85</t>
         </is>
       </c>
-      <c r="AI5" t="inlineStr">
+      <c r="AM5" t="inlineStr">
         <is>
           <t>-5.19</t>
         </is>
       </c>
-      <c r="AJ5" t="inlineStr">
+      <c r="AN5" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK5" t="inlineStr"/>
-      <c r="AL5" t="inlineStr">
+      <c r="AO5" t="inlineStr"/>
+      <c r="AP5" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
+      <c r="AQ5" t="inlineStr">
         <is>
           <t>1703</t>
         </is>
       </c>
-      <c r="AN5" t="inlineStr">
+      <c r="AR5" t="inlineStr">
         <is>
           <t>22.73</t>
         </is>
       </c>
-      <c r="AO5" t="inlineStr">
+      <c r="AS5" t="inlineStr">
         <is>
           <t>61.38</t>
         </is>
       </c>
-      <c r="AP5" t="n">
+      <c r="AT5" t="n">
         <v>-4.33</v>
       </c>
-      <c r="AQ5" t="n">
+      <c r="AU5" t="n">
         <v>6.85</v>
       </c>
-      <c r="AR5" t="inlineStr">
+      <c r="AV5" t="inlineStr">
         <is>
           <t>0.11</t>
         </is>
       </c>
-      <c r="AS5" t="inlineStr">
+      <c r="AW5" t="inlineStr">
         <is>
           <t>0.57</t>
         </is>
       </c>
-      <c r="AT5" t="inlineStr">
+      <c r="AX5" t="inlineStr">
         <is>
           <t>11.08</t>
         </is>
       </c>
-      <c r="AU5" t="n">
+      <c r="AY5" t="n">
         <v>10.37</v>
       </c>
-      <c r="AV5" t="n">
+      <c r="AZ5" t="n">
         <v>10.36</v>
       </c>
-      <c r="AW5" t="inlineStr">
+      <c r="BA5" t="inlineStr">
         <is>
           <t>10.3</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
+      <c r="BB5" t="inlineStr">
         <is>
           <t>54.76</t>
         </is>
       </c>
-      <c r="AY5" t="n">
+      <c r="BC5" t="n">
         <v>0.24</v>
       </c>
-      <c r="AZ5" t="n">
+      <c r="BD5" t="n">
         <v>0.16</v>
       </c>
-      <c r="BA5" t="inlineStr">
+      <c r="BE5" t="inlineStr">
         <is>
           <t>0.54</t>
         </is>
       </c>
-      <c r="BB5" t="inlineStr">
+      <c r="BF5" t="inlineStr">
         <is>
           <t>-70.64</t>
         </is>
       </c>
-      <c r="BC5" t="inlineStr">
+      <c r="BG5" t="inlineStr">
         <is>
           <t>2025/11/28</t>
         </is>
       </c>
-      <c r="BD5" t="inlineStr">
+      <c r="BH5" t="inlineStr">
         <is>
           <t>39643582.14396068</t>
         </is>
       </c>
-      <c r="BE5" t="inlineStr">
+      <c r="BI5" t="inlineStr">
         <is>
           <t>51040578.0</t>
         </is>
       </c>
-      <c r="BF5" t="n">
+      <c r="BJ5" t="n">
         <v>47317430</v>
       </c>
-      <c r="BG5" t="inlineStr">
+      <c r="BK5" t="inlineStr">
         <is>
           <t>87113843.5</t>
         </is>
       </c>
-      <c r="BH5" t="n">
+      <c r="BL5" t="n">
         <v>38674174.84</v>
       </c>
-      <c r="BI5" t="inlineStr">
+      <c r="BM5" t="inlineStr">
         <is>
           <t>-39796413</t>
         </is>
       </c>
-      <c r="BJ5" t="inlineStr">
+      <c r="BN5" t="inlineStr">
         <is>
           <t>8362263.81646695</t>
         </is>
       </c>
-      <c r="BK5" t="inlineStr">
+      <c r="BO5" t="inlineStr">
         <is>
           <t>3022190.040257879</t>
         </is>
       </c>
-      <c r="BL5" t="inlineStr">
+      <c r="BP5" t="inlineStr">
         <is>
           <t>51040578.0</t>
         </is>
       </c>
-      <c r="BM5" t="inlineStr">
+      <c r="BQ5" t="inlineStr">
         <is>
           <t>2025-12-16</t>
         </is>
       </c>
-      <c r="BN5" t="inlineStr">
+      <c r="BR5" t="inlineStr">
         <is>
           <t>10.6</t>
         </is>
       </c>
-      <c r="BO5" t="inlineStr">
+      <c r="BS5" t="inlineStr">
         <is>
           <t>2025/12/10</t>
         </is>
       </c>
-      <c r="BP5" t="inlineStr">
+      <c r="BT5" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="BQ5" t="inlineStr">
+      <c r="BU5" t="inlineStr">
         <is>
           <t>聯成</t>
         </is>
       </c>
-      <c r="BR5" t="inlineStr">
+      <c r="BV5" t="inlineStr">
         <is>
           <t>聯成</t>
         </is>
       </c>
-      <c r="BS5" t="inlineStr">
+      <c r="BW5" t="inlineStr">
         <is>
           <t>塑膠工業</t>
         </is>
       </c>
-      <c r="BT5" t="inlineStr">
+      <c r="BX5" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BU5" t="inlineStr">
+      <c r="BY5" t="inlineStr">
         <is>
           <t>0.76</t>
         </is>
       </c>
-      <c r="BV5" t="inlineStr">
+      <c r="BZ5" t="inlineStr">
         <is>
           <t>-11.96408371040724</t>
         </is>
       </c>
-      <c r="BW5" t="inlineStr">
+      <c r="CA5" t="inlineStr">
         <is>
           <t>-13.59414944504011</t>
         </is>
       </c>
-      <c r="BX5" t="inlineStr">
+      <c r="CB5" t="inlineStr">
         <is>
           <t>-19.633719693908</t>
         </is>
       </c>
-      <c r="BY5" t="inlineStr">
+      <c r="CC5" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ5" t="inlineStr">
+      <c r="CD5" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CA5" t="inlineStr">
+      <c r="CE5" t="inlineStr">
         <is>
           <t>0.47</t>
         </is>
       </c>
-      <c r="CB5" t="inlineStr">
+      <c r="CF5" t="inlineStr">
         <is>
           <t>1.41</t>
         </is>
       </c>
-      <c r="CC5" t="inlineStr">
+      <c r="CG5" t="inlineStr">
         <is>
           <t>10.97</t>
         </is>
       </c>
-      <c r="CD5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CE5" t="inlineStr">
+      <c r="CH5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CI5" t="inlineStr">
         <is>
           <t>0.96%</t>
         </is>
       </c>
-      <c r="CF5" t="inlineStr">
+      <c r="CJ5" t="inlineStr">
         <is>
           <t>-3.42%</t>
         </is>
       </c>
-      <c r="CG5" t="inlineStr">
+      <c r="CK5" t="inlineStr">
         <is>
           <t>63.44</t>
         </is>
       </c>
-      <c r="CH5" t="inlineStr">
+      <c r="CL5" t="inlineStr">
         <is>
           <t>14374</t>
         </is>
       </c>
-      <c r="CI5" t="inlineStr">
+      <c r="CM5" t="inlineStr">
         <is>
           <t>可塑劑(DOP)76.00%、聚氯乙烯13.00%、酸酐6.00%、其他5.00% (2024年)</t>
         </is>
       </c>
-      <c r="CJ5" t="inlineStr">
+      <c r="CN5" t="inlineStr">
         <is>
           <t>聯成-塑膠工業-上市</t>
         </is>
       </c>
-      <c r="CK5" t="inlineStr">
+      <c r="CO5" t="inlineStr">
         <is>
           <t>塑膠工業右下上市</t>
         </is>
       </c>
-      <c r="CL5" t="inlineStr">
+      <c r="CP5" t="inlineStr">
         <is>
           <t>11.2</t>
         </is>
       </c>
-      <c r="CM5" t="inlineStr">
+      <c r="CQ5" t="inlineStr">
         <is>
           <t>11.2</t>
         </is>
       </c>
-      <c r="CN5" t="inlineStr">
+      <c r="CR5" t="inlineStr">
         <is>
           <t>10.55</t>
         </is>
       </c>
-      <c r="CO5" t="inlineStr">
+      <c r="CS5" t="inlineStr">
         <is>
           <t>10.6</t>
         </is>
       </c>
-      <c r="CP5" t="inlineStr">
+      <c r="CT5" t="inlineStr">
         <is>
           <t>22.32</t>
         </is>
       </c>
-      <c r="CQ5" t="inlineStr">
+      <c r="CU5" t="inlineStr">
         <is>
           <t>** 石化及塑橡膠 - 塑化劑(可塑劑)</t>
         </is>
       </c>
-      <c r="CR5" t="inlineStr">
+      <c r="CV5" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -2896,325 +2996,345 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
+          <t>-0.01</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
           <t>2025/11/21</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>9.53</t>
         </is>
       </c>
-      <c r="AD6" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>2025/09/22</t>
         </is>
       </c>
-      <c r="AE6" t="inlineStr">
+      <c r="AF6" t="inlineStr">
         <is>
           <t>10.15</t>
         </is>
       </c>
-      <c r="AF6" t="inlineStr">
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>2025/11/17</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>10.1</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>2025/10/28</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>10.3</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>13.39</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>5.71</t>
+        </is>
+      </c>
+      <c r="AN6" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr"/>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>1703</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>84.28</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>81.16</t>
+        </is>
+      </c>
+      <c r="AT6" t="n">
+        <v>-0.18</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>8.33</v>
+      </c>
+      <c r="AV6" t="inlineStr">
         <is>
           <t>-0.01</t>
         </is>
       </c>
-      <c r="AG6" t="inlineStr">
-        <is>
-          <t>2025-12-09</t>
-        </is>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>13.39</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>5.71</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr"/>
-      <c r="AL6" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>1703</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>84.28</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>81.16</t>
-        </is>
-      </c>
-      <c r="AP6" t="n">
-        <v>-0.18</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>8.33</v>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>-0.01</t>
-        </is>
-      </c>
-      <c r="AS6" t="inlineStr">
+      <c r="AW6" t="inlineStr">
         <is>
           <t>0.62</t>
         </is>
       </c>
-      <c r="AT6" t="inlineStr">
+      <c r="AX6" t="inlineStr">
         <is>
           <t>11.22</t>
         </is>
       </c>
-      <c r="AU6" t="n">
+      <c r="AY6" t="n">
         <v>10.36</v>
       </c>
-      <c r="AV6" t="n">
+      <c r="AZ6" t="n">
         <v>10.36</v>
       </c>
-      <c r="AW6" t="inlineStr">
+      <c r="BA6" t="inlineStr">
         <is>
           <t>10.29</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
+      <c r="BB6" t="inlineStr">
         <is>
           <t>104.81</t>
         </is>
       </c>
-      <c r="AY6" t="n">
+      <c r="BC6" t="n">
         <v>0.28</v>
       </c>
-      <c r="AZ6" t="n">
+      <c r="BD6" t="n">
         <v>0.14</v>
       </c>
-      <c r="BA6" t="inlineStr">
+      <c r="BE6" t="inlineStr">
         <is>
           <t>0.54</t>
         </is>
       </c>
-      <c r="BB6" t="inlineStr">
+      <c r="BF6" t="inlineStr">
         <is>
           <t>-74.66</t>
         </is>
       </c>
-      <c r="BC6" t="inlineStr">
+      <c r="BG6" t="inlineStr">
         <is>
           <t>2025/11/28</t>
         </is>
       </c>
-      <c r="BD6" t="inlineStr">
+      <c r="BH6" t="inlineStr">
         <is>
           <t>39643582.14396068</t>
         </is>
       </c>
-      <c r="BE6" t="inlineStr">
+      <c r="BI6" t="inlineStr">
         <is>
           <t>50183303.0</t>
         </is>
       </c>
-      <c r="BF6" t="n">
+      <c r="BJ6" t="n">
         <v>61147746.2</v>
       </c>
-      <c r="BG6" t="inlineStr">
+      <c r="BK6" t="inlineStr">
         <is>
           <t>83319151.2</t>
         </is>
       </c>
-      <c r="BH6" t="n">
+      <c r="BL6" t="n">
         <v>38351204.62</v>
       </c>
-      <c r="BI6" t="inlineStr">
+      <c r="BM6" t="inlineStr">
         <is>
           <t>-22171405</t>
         </is>
       </c>
-      <c r="BJ6" t="inlineStr">
+      <c r="BN6" t="inlineStr">
         <is>
           <t>9333186.321232235</t>
         </is>
       </c>
-      <c r="BK6" t="inlineStr">
+      <c r="BO6" t="inlineStr">
         <is>
           <t>5180170.002844289</t>
         </is>
       </c>
-      <c r="BL6" t="inlineStr">
+      <c r="BP6" t="inlineStr">
         <is>
           <t>50183303.0</t>
         </is>
       </c>
-      <c r="BM6" t="inlineStr">
+      <c r="BQ6" t="inlineStr">
         <is>
           <t>2025-12-16</t>
         </is>
       </c>
-      <c r="BN6" t="inlineStr">
+      <c r="BR6" t="inlineStr">
         <is>
           <t>10.6</t>
         </is>
       </c>
-      <c r="BO6" t="inlineStr">
+      <c r="BS6" t="inlineStr">
         <is>
           <t>2025/12/10</t>
         </is>
       </c>
-      <c r="BP6" t="inlineStr">
+      <c r="BT6" t="inlineStr">
         <is>
           <t>5.66</t>
         </is>
       </c>
-      <c r="BQ6" t="inlineStr">
+      <c r="BU6" t="inlineStr">
         <is>
           <t>聯成</t>
         </is>
       </c>
-      <c r="BR6" t="inlineStr">
+      <c r="BV6" t="inlineStr">
         <is>
           <t>聯成</t>
         </is>
       </c>
-      <c r="BS6" t="inlineStr">
+      <c r="BW6" t="inlineStr">
         <is>
           <t>塑膠工業</t>
         </is>
       </c>
-      <c r="BT6" t="inlineStr">
+      <c r="BX6" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BU6" t="inlineStr">
+      <c r="BY6" t="inlineStr">
         <is>
           <t>0.76</t>
         </is>
       </c>
-      <c r="BV6" t="inlineStr">
+      <c r="BZ6" t="inlineStr">
         <is>
           <t>-11.96408371040724</t>
         </is>
       </c>
-      <c r="BW6" t="inlineStr">
+      <c r="CA6" t="inlineStr">
         <is>
           <t>-13.59414944504011</t>
         </is>
       </c>
-      <c r="BX6" t="inlineStr">
+      <c r="CB6" t="inlineStr">
         <is>
           <t>-19.633719693908</t>
         </is>
       </c>
-      <c r="BY6" t="inlineStr">
+      <c r="CC6" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ6" t="inlineStr">
+      <c r="CD6" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CA6" t="inlineStr">
+      <c r="CE6" t="inlineStr">
         <is>
           <t>0.50</t>
         </is>
       </c>
-      <c r="CB6" t="inlineStr">
+      <c r="CF6" t="inlineStr">
         <is>
           <t>1.41</t>
         </is>
       </c>
-      <c r="CC6" t="inlineStr">
+      <c r="CG6" t="inlineStr">
         <is>
           <t>10.97</t>
         </is>
       </c>
-      <c r="CD6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CE6" t="inlineStr">
+      <c r="CH6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CI6" t="inlineStr">
         <is>
           <t>0.96%</t>
         </is>
       </c>
-      <c r="CF6" t="inlineStr">
+      <c r="CJ6" t="inlineStr">
         <is>
           <t>-3.42%</t>
         </is>
       </c>
-      <c r="CG6" t="inlineStr">
+      <c r="CK6" t="inlineStr">
         <is>
           <t>63.44</t>
         </is>
       </c>
-      <c r="CH6" t="inlineStr">
+      <c r="CL6" t="inlineStr">
         <is>
           <t>14374</t>
         </is>
       </c>
-      <c r="CI6" t="inlineStr">
+      <c r="CM6" t="inlineStr">
         <is>
           <t>可塑劑(DOP)76.00%、聚氯乙烯13.00%、酸酐6.00%、其他5.00% (2024年)</t>
         </is>
       </c>
-      <c r="CJ6" t="inlineStr">
+      <c r="CN6" t="inlineStr">
         <is>
           <t>聯成-塑膠工業-上市</t>
         </is>
       </c>
-      <c r="CK6" t="inlineStr">
+      <c r="CO6" t="inlineStr">
         <is>
           <t>塑膠工業右下上市</t>
         </is>
       </c>
-      <c r="CL6" t="inlineStr">
+      <c r="CP6" t="inlineStr">
         <is>
           <t>11.0</t>
         </is>
       </c>
-      <c r="CM6" t="inlineStr">
+      <c r="CQ6" t="inlineStr">
         <is>
           <t>11.25</t>
         </is>
       </c>
-      <c r="CN6" t="inlineStr">
+      <c r="CR6" t="inlineStr">
         <is>
           <t>10.55</t>
         </is>
       </c>
-      <c r="CO6" t="inlineStr">
+      <c r="CS6" t="inlineStr">
         <is>
           <t>11.2</t>
         </is>
       </c>
-      <c r="CP6" t="inlineStr">
+      <c r="CT6" t="inlineStr">
         <is>
           <t>22.32</t>
         </is>
       </c>
-      <c r="CQ6" t="inlineStr">
+      <c r="CU6" t="inlineStr">
         <is>
           <t>** 石化及塑橡膠 - 塑化劑(可塑劑)</t>
         </is>
       </c>
-      <c r="CR6" t="inlineStr">
+      <c r="CV6" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -3358,325 +3478,345 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
+          <t>-0.02</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
           <t>2025/11/21</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>9.53</t>
         </is>
       </c>
-      <c r="AD7" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>2025/09/22</t>
         </is>
       </c>
-      <c r="AE7" t="inlineStr">
+      <c r="AF7" t="inlineStr">
         <is>
           <t>10.15</t>
         </is>
       </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>-0.02</t>
-        </is>
-      </c>
       <c r="AG7" t="inlineStr">
         <is>
+          <t>2025/11/17</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>10.1</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>2025/10/28</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>10.3</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
           <t>2025-12-08</t>
         </is>
       </c>
-      <c r="AH7" t="inlineStr">
+      <c r="AL7" t="inlineStr">
         <is>
           <t>9.87</t>
         </is>
       </c>
-      <c r="AI7" t="inlineStr">
+      <c r="AM7" t="inlineStr">
         <is>
           <t>2.82</t>
         </is>
       </c>
-      <c r="AJ7" t="inlineStr">
+      <c r="AN7" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK7" t="inlineStr"/>
-      <c r="AL7" t="inlineStr">
+      <c r="AO7" t="inlineStr"/>
+      <c r="AP7" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
+      <c r="AQ7" t="inlineStr">
         <is>
           <t>1703</t>
         </is>
       </c>
-      <c r="AN7" t="inlineStr">
+      <c r="AR7" t="inlineStr">
         <is>
           <t>77.14</t>
         </is>
       </c>
-      <c r="AO7" t="inlineStr">
+      <c r="AS7" t="inlineStr">
         <is>
           <t>86.4</t>
         </is>
       </c>
-      <c r="AP7" t="n">
+      <c r="AT7" t="n">
         <v>-1.69</v>
       </c>
-      <c r="AQ7" t="n">
+      <c r="AU7" t="n">
         <v>9.07</v>
       </c>
-      <c r="AR7" t="inlineStr">
+      <c r="AV7" t="inlineStr">
         <is>
           <t>-0.31</t>
         </is>
       </c>
-      <c r="AS7" t="inlineStr">
+      <c r="AW7" t="inlineStr">
         <is>
           <t>0.54</t>
         </is>
       </c>
-      <c r="AT7" t="inlineStr">
+      <c r="AX7" t="inlineStr">
         <is>
           <t>11.24</t>
         </is>
       </c>
-      <c r="AU7" t="n">
+      <c r="AY7" t="n">
         <v>10.3</v>
       </c>
-      <c r="AV7" t="n">
+      <c r="AZ7" t="n">
         <v>10.34</v>
       </c>
-      <c r="AW7" t="inlineStr">
+      <c r="BA7" t="inlineStr">
         <is>
           <t>10.28</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
+      <c r="BB7" t="inlineStr">
         <is>
           <t>156.80</t>
         </is>
       </c>
-      <c r="AY7" t="n">
+      <c r="BC7" t="n">
         <v>0.26</v>
       </c>
-      <c r="AZ7" t="n">
+      <c r="BD7" t="n">
         <v>0.1</v>
       </c>
-      <c r="BA7" t="inlineStr">
+      <c r="BE7" t="inlineStr">
         <is>
           <t>0.54</t>
         </is>
       </c>
-      <c r="BB7" t="inlineStr">
+      <c r="BF7" t="inlineStr">
         <is>
           <t>-81.30</t>
         </is>
       </c>
-      <c r="BC7" t="inlineStr">
+      <c r="BG7" t="inlineStr">
         <is>
           <t>2025/11/28</t>
         </is>
       </c>
-      <c r="BD7" t="inlineStr">
+      <c r="BH7" t="inlineStr">
         <is>
           <t>39643582.14396068</t>
         </is>
       </c>
-      <c r="BE7" t="inlineStr">
+      <c r="BI7" t="inlineStr">
         <is>
           <t>36836029.0</t>
         </is>
       </c>
-      <c r="BF7" t="n">
+      <c r="BJ7" t="n">
         <v>129269925</v>
       </c>
-      <c r="BG7" t="inlineStr">
+      <c r="BK7" t="inlineStr">
         <is>
           <t>79767305.4</t>
         </is>
       </c>
-      <c r="BH7" t="n">
+      <c r="BL7" t="n">
         <v>38038480.18</v>
       </c>
-      <c r="BI7" t="inlineStr">
+      <c r="BM7" t="inlineStr">
         <is>
           <t>49502619</t>
         </is>
       </c>
-      <c r="BJ7" t="inlineStr">
+      <c r="BN7" t="inlineStr">
         <is>
           <t>10088280.19730277</t>
         </is>
       </c>
-      <c r="BK7" t="inlineStr">
+      <c r="BO7" t="inlineStr">
         <is>
           <t>8169843.34215185</t>
         </is>
       </c>
-      <c r="BL7" t="inlineStr">
+      <c r="BP7" t="inlineStr">
         <is>
           <t>36836029.0</t>
         </is>
       </c>
-      <c r="BM7" t="inlineStr">
+      <c r="BQ7" t="inlineStr">
         <is>
           <t>2025-12-16</t>
         </is>
       </c>
-      <c r="BN7" t="inlineStr">
+      <c r="BR7" t="inlineStr">
         <is>
           <t>10.6</t>
         </is>
       </c>
-      <c r="BO7" t="inlineStr">
+      <c r="BS7" t="inlineStr">
         <is>
           <t>2025/12/10</t>
         </is>
       </c>
-      <c r="BP7" t="inlineStr">
+      <c r="BT7" t="inlineStr">
         <is>
           <t>4.25</t>
         </is>
       </c>
-      <c r="BQ7" t="inlineStr">
+      <c r="BU7" t="inlineStr">
         <is>
           <t>聯成</t>
         </is>
       </c>
-      <c r="BR7" t="inlineStr">
+      <c r="BV7" t="inlineStr">
         <is>
           <t>聯成</t>
         </is>
       </c>
-      <c r="BS7" t="inlineStr">
+      <c r="BW7" t="inlineStr">
         <is>
           <t>塑膠工業</t>
         </is>
       </c>
-      <c r="BT7" t="inlineStr">
+      <c r="BX7" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BU7" t="inlineStr">
+      <c r="BY7" t="inlineStr">
         <is>
           <t>0.76</t>
         </is>
       </c>
-      <c r="BV7" t="inlineStr">
+      <c r="BZ7" t="inlineStr">
         <is>
           <t>-11.96408371040724</t>
         </is>
       </c>
-      <c r="BW7" t="inlineStr">
+      <c r="CA7" t="inlineStr">
         <is>
           <t>-13.59414944504011</t>
         </is>
       </c>
-      <c r="BX7" t="inlineStr">
+      <c r="CB7" t="inlineStr">
         <is>
           <t>-19.633719693908</t>
         </is>
       </c>
-      <c r="BY7" t="inlineStr">
+      <c r="CC7" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ7" t="inlineStr">
+      <c r="CD7" t="inlineStr">
         <is>
           <t>價-量縮</t>
         </is>
       </c>
-      <c r="CA7" t="inlineStr">
+      <c r="CE7" t="inlineStr">
         <is>
           <t>0.50</t>
         </is>
       </c>
-      <c r="CB7" t="inlineStr">
+      <c r="CF7" t="inlineStr">
         <is>
           <t>1.41</t>
         </is>
       </c>
-      <c r="CC7" t="inlineStr">
+      <c r="CG7" t="inlineStr">
         <is>
           <t>10.97</t>
         </is>
       </c>
-      <c r="CD7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CE7" t="inlineStr">
+      <c r="CH7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CI7" t="inlineStr">
         <is>
           <t>0.96%</t>
         </is>
       </c>
-      <c r="CF7" t="inlineStr">
+      <c r="CJ7" t="inlineStr">
         <is>
           <t>-3.42%</t>
         </is>
       </c>
-      <c r="CG7" t="inlineStr">
+      <c r="CK7" t="inlineStr">
         <is>
           <t>63.44</t>
         </is>
       </c>
-      <c r="CH7" t="inlineStr">
+      <c r="CL7" t="inlineStr">
         <is>
           <t>14374</t>
         </is>
       </c>
-      <c r="CI7" t="inlineStr">
+      <c r="CM7" t="inlineStr">
         <is>
           <t>可塑劑(DOP)76.00%、聚氯乙烯13.00%、酸酐6.00%、其他5.00% (2024年)</t>
         </is>
       </c>
-      <c r="CJ7" t="inlineStr">
+      <c r="CN7" t="inlineStr">
         <is>
           <t>聯成-塑膠工業-上市</t>
         </is>
       </c>
-      <c r="CK7" t="inlineStr">
+      <c r="CO7" t="inlineStr">
         <is>
           <t>塑膠工業右下上市</t>
         </is>
       </c>
-      <c r="CL7" t="inlineStr">
+      <c r="CP7" t="inlineStr">
         <is>
           <t>11.0</t>
         </is>
       </c>
-      <c r="CM7" t="inlineStr">
+      <c r="CQ7" t="inlineStr">
         <is>
           <t>11.1</t>
         </is>
       </c>
-      <c r="CN7" t="inlineStr">
+      <c r="CR7" t="inlineStr">
         <is>
           <t>10.7</t>
         </is>
       </c>
-      <c r="CO7" t="inlineStr">
+      <c r="CS7" t="inlineStr">
         <is>
           <t>11.05</t>
         </is>
       </c>
-      <c r="CP7" t="inlineStr">
+      <c r="CT7" t="inlineStr">
         <is>
           <t>22.32</t>
         </is>
       </c>
-      <c r="CQ7" t="inlineStr">
+      <c r="CU7" t="inlineStr">
         <is>
           <t>** 石化及塑橡膠 - 塑化劑(可塑劑)</t>
         </is>
       </c>
-      <c r="CR7" t="inlineStr">
+      <c r="CV7" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -3820,325 +3960,345 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
+          <t>-0.02</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
           <t>2025/11/21</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>9.53</t>
         </is>
       </c>
-      <c r="AD8" t="inlineStr">
+      <c r="AE8" t="inlineStr">
         <is>
           <t>2025/09/22</t>
         </is>
       </c>
-      <c r="AE8" t="inlineStr">
+      <c r="AF8" t="inlineStr">
         <is>
           <t>10.15</t>
         </is>
       </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>-0.02</t>
-        </is>
-      </c>
       <c r="AG8" t="inlineStr">
         <is>
+          <t>2025/11/17</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>10.1</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>2025/10/28</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>10.3</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="AH8" t="inlineStr">
+      <c r="AL8" t="inlineStr">
         <is>
           <t>12.40</t>
         </is>
       </c>
-      <c r="AI8" t="inlineStr">
+      <c r="AM8" t="inlineStr">
         <is>
           <t>-1.34</t>
         </is>
       </c>
-      <c r="AJ8" t="inlineStr">
+      <c r="AN8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK8" t="inlineStr"/>
-      <c r="AL8" t="inlineStr">
+      <c r="AO8" t="inlineStr"/>
+      <c r="AP8" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
+      <c r="AQ8" t="inlineStr">
         <is>
           <t>1703</t>
         </is>
       </c>
-      <c r="AN8" t="inlineStr">
+      <c r="AR8" t="inlineStr">
         <is>
           <t>82.05</t>
         </is>
       </c>
-      <c r="AO8" t="inlineStr">
+      <c r="AS8" t="inlineStr">
         <is>
           <t>94.02</t>
         </is>
       </c>
-      <c r="AP8" t="n">
+      <c r="AT8" t="n">
         <v>-0.63</v>
       </c>
-      <c r="AQ8" t="n">
+      <c r="AU8" t="n">
         <v>8.99</v>
       </c>
-      <c r="AR8" t="inlineStr">
+      <c r="AV8" t="inlineStr">
         <is>
           <t>-0.75</t>
         </is>
       </c>
-      <c r="AS8" t="inlineStr">
+      <c r="AW8" t="inlineStr">
         <is>
           <t>0.56</t>
         </is>
       </c>
-      <c r="AT8" t="inlineStr">
+      <c r="AX8" t="inlineStr">
         <is>
           <t>11.17</t>
         </is>
       </c>
-      <c r="AU8" t="n">
+      <c r="AY8" t="n">
         <v>10.25</v>
       </c>
-      <c r="AV8" t="n">
+      <c r="AZ8" t="n">
         <v>10.33</v>
       </c>
-      <c r="AW8" t="inlineStr">
+      <c r="BA8" t="inlineStr">
         <is>
           <t>10.27</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
+      <c r="BB8" t="inlineStr">
         <is>
           <t>297.70</t>
         </is>
       </c>
-      <c r="AY8" t="n">
+      <c r="BC8" t="n">
         <v>0.24</v>
       </c>
-      <c r="AZ8" t="n">
+      <c r="BD8" t="n">
         <v>0.06</v>
       </c>
-      <c r="BA8" t="inlineStr">
+      <c r="BE8" t="inlineStr">
         <is>
           <t>0.54</t>
         </is>
       </c>
-      <c r="BB8" t="inlineStr">
+      <c r="BF8" t="inlineStr">
         <is>
           <t>-88.63</t>
         </is>
       </c>
-      <c r="BC8" t="inlineStr">
+      <c r="BG8" t="inlineStr">
         <is>
           <t>2025/11/28</t>
         </is>
       </c>
-      <c r="BD8" t="inlineStr">
+      <c r="BH8" t="inlineStr">
         <is>
           <t>39643582.14396068</t>
         </is>
       </c>
-      <c r="BE8" t="inlineStr">
+      <c r="BI8" t="inlineStr">
         <is>
           <t>47317394.0</t>
         </is>
       </c>
-      <c r="BF8" t="n">
+      <c r="BJ8" t="n">
         <v>135273943.6</v>
       </c>
-      <c r="BG8" t="inlineStr">
+      <c r="BK8" t="inlineStr">
         <is>
           <t>77843851.4</t>
         </is>
       </c>
-      <c r="BH8" t="n">
+      <c r="BL8" t="n">
         <v>38862439.4</v>
       </c>
-      <c r="BI8" t="inlineStr">
+      <c r="BM8" t="inlineStr">
         <is>
           <t>57430092</t>
         </is>
       </c>
-      <c r="BJ8" t="inlineStr">
+      <c r="BN8" t="inlineStr">
         <is>
           <t>10437086.8982393</t>
         </is>
       </c>
-      <c r="BK8" t="inlineStr">
+      <c r="BO8" t="inlineStr">
         <is>
           <t>13579090.20751438</t>
         </is>
       </c>
-      <c r="BL8" t="inlineStr">
+      <c r="BP8" t="inlineStr">
         <is>
           <t>47317394.0</t>
         </is>
       </c>
-      <c r="BM8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN8" t="inlineStr">
+      <c r="BQ8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR8" t="inlineStr">
         <is>
           <t>10.6</t>
         </is>
       </c>
-      <c r="BO8" t="inlineStr">
+      <c r="BS8" t="inlineStr">
         <is>
           <t>2025/12/10</t>
         </is>
       </c>
-      <c r="BP8" t="inlineStr">
+      <c r="BT8" t="inlineStr">
         <is>
           <t>4.72</t>
         </is>
       </c>
-      <c r="BQ8" t="inlineStr">
+      <c r="BU8" t="inlineStr">
         <is>
           <t>聯成</t>
         </is>
       </c>
-      <c r="BR8" t="inlineStr">
+      <c r="BV8" t="inlineStr">
         <is>
           <t>聯成</t>
         </is>
       </c>
-      <c r="BS8" t="inlineStr">
+      <c r="BW8" t="inlineStr">
         <is>
           <t>塑膠工業</t>
         </is>
       </c>
-      <c r="BT8" t="inlineStr">
+      <c r="BX8" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BU8" t="inlineStr">
+      <c r="BY8" t="inlineStr">
         <is>
           <t>0.76</t>
         </is>
       </c>
-      <c r="BV8" t="inlineStr">
+      <c r="BZ8" t="inlineStr">
         <is>
           <t>-11.96408371040724</t>
         </is>
       </c>
-      <c r="BW8" t="inlineStr">
+      <c r="CA8" t="inlineStr">
         <is>
           <t>-13.59414944504011</t>
         </is>
       </c>
-      <c r="BX8" t="inlineStr">
+      <c r="CB8" t="inlineStr">
         <is>
           <t>-19.633719693908</t>
         </is>
       </c>
-      <c r="BY8" t="inlineStr">
+      <c r="CC8" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ8" t="inlineStr">
+      <c r="CD8" t="inlineStr">
         <is>
           <t>價跌量縮</t>
         </is>
       </c>
-      <c r="CA8" t="inlineStr">
+      <c r="CE8" t="inlineStr">
         <is>
           <t>0.50</t>
         </is>
       </c>
-      <c r="CB8" t="inlineStr">
+      <c r="CF8" t="inlineStr">
         <is>
           <t>1.41</t>
         </is>
       </c>
-      <c r="CC8" t="inlineStr">
+      <c r="CG8" t="inlineStr">
         <is>
           <t>10.97</t>
         </is>
       </c>
-      <c r="CD8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CE8" t="inlineStr">
+      <c r="CH8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CI8" t="inlineStr">
         <is>
           <t>0.96%</t>
         </is>
       </c>
-      <c r="CF8" t="inlineStr">
+      <c r="CJ8" t="inlineStr">
         <is>
           <t>-3.42%</t>
         </is>
       </c>
-      <c r="CG8" t="inlineStr">
+      <c r="CK8" t="inlineStr">
         <is>
           <t>63.44</t>
         </is>
       </c>
-      <c r="CH8" t="inlineStr">
+      <c r="CL8" t="inlineStr">
         <is>
           <t>14374</t>
         </is>
       </c>
-      <c r="CI8" t="inlineStr">
+      <c r="CM8" t="inlineStr">
         <is>
           <t>可塑劑(DOP)76.00%、聚氯乙烯13.00%、酸酐6.00%、其他5.00% (2024年)</t>
         </is>
       </c>
-      <c r="CJ8" t="inlineStr">
+      <c r="CN8" t="inlineStr">
         <is>
           <t>聯成-塑膠工業-上市</t>
         </is>
       </c>
-      <c r="CK8" t="inlineStr">
+      <c r="CO8" t="inlineStr">
         <is>
           <t>塑膠工業右下上市</t>
         </is>
       </c>
-      <c r="CL8" t="inlineStr">
+      <c r="CP8" t="inlineStr">
         <is>
           <t>11.35</t>
         </is>
       </c>
-      <c r="CM8" t="inlineStr">
+      <c r="CQ8" t="inlineStr">
         <is>
           <t>11.35</t>
         </is>
       </c>
-      <c r="CN8" t="inlineStr">
+      <c r="CR8" t="inlineStr">
         <is>
           <t>11.0</t>
         </is>
       </c>
-      <c r="CO8" t="inlineStr">
+      <c r="CS8" t="inlineStr">
         <is>
           <t>11.1</t>
         </is>
       </c>
-      <c r="CP8" t="inlineStr">
+      <c r="CT8" t="inlineStr">
         <is>
           <t>22.32</t>
         </is>
       </c>
-      <c r="CQ8" t="inlineStr">
+      <c r="CU8" t="inlineStr">
         <is>
           <t>** 石化及塑橡膠 - 塑化劑(可塑劑)</t>
         </is>
       </c>
-      <c r="CR8" t="inlineStr">
+      <c r="CV8" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -4282,325 +4442,345 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
           <t>2025/11/21</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
+      <c r="AD9" t="inlineStr">
         <is>
           <t>9.53</t>
         </is>
       </c>
-      <c r="AD9" t="inlineStr">
+      <c r="AE9" t="inlineStr">
         <is>
           <t>2025/09/22</t>
         </is>
       </c>
-      <c r="AE9" t="inlineStr">
+      <c r="AF9" t="inlineStr">
         <is>
           <t>10.15</t>
         </is>
       </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>0.02</t>
-        </is>
-      </c>
       <c r="AG9" t="inlineStr">
         <is>
+          <t>2025/11/17</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>10.1</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>2025/10/28</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>10.3</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
           <t>2025-12-04</t>
         </is>
       </c>
-      <c r="AH9" t="inlineStr">
+      <c r="AL9" t="inlineStr">
         <is>
           <t>13.10</t>
         </is>
       </c>
-      <c r="AI9" t="inlineStr">
+      <c r="AM9" t="inlineStr">
         <is>
           <t>1.38</t>
         </is>
       </c>
-      <c r="AJ9" t="inlineStr">
+      <c r="AN9" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK9" t="inlineStr"/>
-      <c r="AL9" t="inlineStr">
+      <c r="AO9" t="inlineStr"/>
+      <c r="AP9" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
+      <c r="AQ9" t="inlineStr">
         <is>
           <t>1703</t>
         </is>
       </c>
-      <c r="AN9" t="inlineStr">
+      <c r="AR9" t="inlineStr">
         <is>
           <t>100.0</t>
         </is>
       </c>
-      <c r="AO9" t="inlineStr">
+      <c r="AS9" t="inlineStr">
         <is>
           <t>100.0</t>
         </is>
       </c>
-      <c r="AP9" t="n">
+      <c r="AT9" t="n">
         <v>3.9</v>
       </c>
-      <c r="AQ9" t="n">
+      <c r="AU9" t="n">
         <v>7.97</v>
       </c>
-      <c r="AR9" t="inlineStr">
+      <c r="AV9" t="inlineStr">
         <is>
           <t>-0.98</t>
         </is>
       </c>
-      <c r="AS9" t="inlineStr">
+      <c r="AW9" t="inlineStr">
         <is>
           <t>0.54</t>
         </is>
       </c>
-      <c r="AT9" t="inlineStr">
+      <c r="AX9" t="inlineStr">
         <is>
           <t>11.02</t>
         </is>
       </c>
-      <c r="AU9" t="n">
+      <c r="AY9" t="n">
         <v>10.21</v>
       </c>
-      <c r="AV9" t="n">
+      <c r="AZ9" t="n">
         <v>10.31</v>
       </c>
-      <c r="AW9" t="inlineStr">
+      <c r="BA9" t="inlineStr">
         <is>
           <t>10.25</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
+      <c r="BB9" t="inlineStr">
         <is>
           <t>1276.76</t>
         </is>
       </c>
-      <c r="AY9" t="n">
+      <c r="BC9" t="n">
         <v>0.22</v>
       </c>
-      <c r="AZ9" t="n">
+      <c r="BD9" t="n">
         <v>0.02</v>
       </c>
-      <c r="BA9" t="inlineStr">
+      <c r="BE9" t="inlineStr">
         <is>
           <t>0.54</t>
         </is>
       </c>
-      <c r="BB9" t="inlineStr">
+      <c r="BF9" t="inlineStr">
         <is>
           <t>-97.09</t>
         </is>
       </c>
-      <c r="BC9" t="inlineStr">
+      <c r="BG9" t="inlineStr">
         <is>
           <t>2025/11/28</t>
         </is>
       </c>
-      <c r="BD9" t="inlineStr">
+      <c r="BH9" t="inlineStr">
         <is>
           <t>39643582.14396068</t>
         </is>
       </c>
-      <c r="BE9" t="inlineStr">
+      <c r="BI9" t="inlineStr">
         <is>
           <t>51209846.0</t>
         </is>
       </c>
-      <c r="BF9" t="n">
+      <c r="BJ9" t="n">
         <v>134651499.8</v>
       </c>
-      <c r="BG9" t="inlineStr">
+      <c r="BK9" t="inlineStr">
         <is>
           <t>75791338.0</t>
         </is>
       </c>
-      <c r="BH9" t="n">
+      <c r="BL9" t="n">
         <v>38375557.84</v>
       </c>
-      <c r="BI9" t="inlineStr">
+      <c r="BM9" t="inlineStr">
         <is>
           <t>58860161</t>
         </is>
       </c>
-      <c r="BJ9" t="inlineStr">
+      <c r="BN9" t="inlineStr">
         <is>
           <t>9865813.569280198</t>
         </is>
       </c>
-      <c r="BK9" t="inlineStr">
+      <c r="BO9" t="inlineStr">
         <is>
           <t>19698614.82919247</t>
         </is>
       </c>
-      <c r="BL9" t="inlineStr">
+      <c r="BP9" t="inlineStr">
         <is>
           <t>51209846.0</t>
         </is>
       </c>
-      <c r="BM9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN9" t="inlineStr">
+      <c r="BQ9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR9" t="inlineStr">
         <is>
           <t>10.6</t>
         </is>
       </c>
-      <c r="BO9" t="inlineStr">
+      <c r="BS9" t="inlineStr">
         <is>
           <t>2025/12/10</t>
         </is>
       </c>
-      <c r="BP9" t="inlineStr">
+      <c r="BT9" t="inlineStr">
         <is>
           <t>8.02</t>
         </is>
       </c>
-      <c r="BQ9" t="inlineStr">
+      <c r="BU9" t="inlineStr">
         <is>
           <t>聯成</t>
         </is>
       </c>
-      <c r="BR9" t="inlineStr">
+      <c r="BV9" t="inlineStr">
         <is>
           <t>聯成</t>
         </is>
       </c>
-      <c r="BS9" t="inlineStr">
+      <c r="BW9" t="inlineStr">
         <is>
           <t>塑膠工業</t>
         </is>
       </c>
-      <c r="BT9" t="inlineStr">
+      <c r="BX9" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BU9" t="inlineStr">
+      <c r="BY9" t="inlineStr">
         <is>
           <t>0.76</t>
         </is>
       </c>
-      <c r="BV9" t="inlineStr">
+      <c r="BZ9" t="inlineStr">
         <is>
           <t>-11.96408371040724</t>
         </is>
       </c>
-      <c r="BW9" t="inlineStr">
+      <c r="CA9" t="inlineStr">
         <is>
           <t>-13.59414944504011</t>
         </is>
       </c>
-      <c r="BX9" t="inlineStr">
+      <c r="CB9" t="inlineStr">
         <is>
           <t>-19.633719693908</t>
         </is>
       </c>
-      <c r="BY9" t="inlineStr">
+      <c r="CC9" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ9" t="inlineStr">
+      <c r="CD9" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CA9" t="inlineStr">
+      <c r="CE9" t="inlineStr">
         <is>
           <t>0.51</t>
         </is>
       </c>
-      <c r="CB9" t="inlineStr">
+      <c r="CF9" t="inlineStr">
         <is>
           <t>1.41</t>
         </is>
       </c>
-      <c r="CC9" t="inlineStr">
+      <c r="CG9" t="inlineStr">
         <is>
           <t>10.97</t>
         </is>
       </c>
-      <c r="CD9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CE9" t="inlineStr">
+      <c r="CH9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CI9" t="inlineStr">
         <is>
           <t>0.96%</t>
         </is>
       </c>
-      <c r="CF9" t="inlineStr">
+      <c r="CJ9" t="inlineStr">
         <is>
           <t>-3.42%</t>
         </is>
       </c>
-      <c r="CG9" t="inlineStr">
+      <c r="CK9" t="inlineStr">
         <is>
           <t>63.44</t>
         </is>
       </c>
-      <c r="CH9" t="inlineStr">
+      <c r="CL9" t="inlineStr">
         <is>
           <t>14374</t>
         </is>
       </c>
-      <c r="CI9" t="inlineStr">
+      <c r="CM9" t="inlineStr">
         <is>
           <t>可塑劑(DOP)76.00%、聚氯乙烯13.00%、酸酐6.00%、其他5.00% (2024年)</t>
         </is>
       </c>
-      <c r="CJ9" t="inlineStr">
+      <c r="CN9" t="inlineStr">
         <is>
           <t>聯成-塑膠工業-上市</t>
         </is>
       </c>
-      <c r="CK9" t="inlineStr">
+      <c r="CO9" t="inlineStr">
         <is>
           <t>塑膠工業右下上市</t>
         </is>
       </c>
-      <c r="CL9" t="inlineStr">
+      <c r="CP9" t="inlineStr">
         <is>
           <t>11.4</t>
         </is>
       </c>
-      <c r="CM9" t="inlineStr">
+      <c r="CQ9" t="inlineStr">
         <is>
           <t>11.6</t>
         </is>
       </c>
-      <c r="CN9" t="inlineStr">
+      <c r="CR9" t="inlineStr">
         <is>
           <t>11.15</t>
         </is>
       </c>
-      <c r="CO9" t="inlineStr">
+      <c r="CS9" t="inlineStr">
         <is>
           <t>11.45</t>
         </is>
       </c>
-      <c r="CP9" t="inlineStr">
+      <c r="CT9" t="inlineStr">
         <is>
           <t>22.32</t>
         </is>
       </c>
-      <c r="CQ9" t="inlineStr">
+      <c r="CU9" t="inlineStr">
         <is>
           <t>** 石化及塑橡膠 - 塑化劑(可塑劑)</t>
         </is>
       </c>
-      <c r="CR9" t="inlineStr">
+      <c r="CV9" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -4744,325 +4924,345 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
           <t>2025/11/21</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
+      <c r="AD10" t="inlineStr">
         <is>
           <t>9.53</t>
         </is>
       </c>
-      <c r="AD10" t="inlineStr">
+      <c r="AE10" t="inlineStr">
         <is>
           <t>2025/09/22</t>
         </is>
       </c>
-      <c r="AE10" t="inlineStr">
+      <c r="AF10" t="inlineStr">
         <is>
           <t>10.15</t>
         </is>
       </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>0.04</t>
-        </is>
-      </c>
       <c r="AG10" t="inlineStr">
         <is>
+          <t>2025/11/17</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>10.1</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>2025/10/28</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>10.3</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
           <t>2025-12-03</t>
         </is>
       </c>
-      <c r="AH10" t="inlineStr">
+      <c r="AL10" t="inlineStr">
         <is>
           <t>30.68</t>
         </is>
       </c>
-      <c r="AI10" t="inlineStr">
+      <c r="AM10" t="inlineStr">
         <is>
           <t>-2.16</t>
         </is>
       </c>
-      <c r="AJ10" t="inlineStr">
+      <c r="AN10" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK10" t="inlineStr"/>
-      <c r="AL10" t="inlineStr">
+      <c r="AO10" t="inlineStr"/>
+      <c r="AP10" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
+      <c r="AQ10" t="inlineStr">
         <is>
           <t>1703</t>
         </is>
       </c>
-      <c r="AN10" t="inlineStr">
+      <c r="AR10" t="inlineStr">
         <is>
           <t>100.0</t>
         </is>
       </c>
-      <c r="AO10" t="inlineStr">
+      <c r="AS10" t="inlineStr">
         <is>
           <t>100.0</t>
         </is>
       </c>
-      <c r="AP10" t="n">
+      <c r="AT10" t="n">
         <v>5.59</v>
       </c>
-      <c r="AQ10" t="n">
+      <c r="AU10" t="n">
         <v>5.32</v>
       </c>
-      <c r="AR10" t="inlineStr">
+      <c r="AV10" t="inlineStr">
         <is>
           <t>-1.12</t>
         </is>
       </c>
-      <c r="AS10" t="inlineStr">
+      <c r="AW10" t="inlineStr">
         <is>
           <t>0.47</t>
         </is>
       </c>
-      <c r="AT10" t="inlineStr">
+      <c r="AX10" t="inlineStr">
         <is>
           <t>10.702</t>
         </is>
       </c>
-      <c r="AU10" t="n">
+      <c r="AY10" t="n">
         <v>10.16</v>
       </c>
-      <c r="AV10" t="n">
+      <c r="AZ10" t="n">
         <v>10.28</v>
       </c>
-      <c r="AW10" t="inlineStr">
+      <c r="BA10" t="inlineStr">
         <is>
           <t>10.23</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
+      <c r="BB10" t="inlineStr">
         <is>
           <t>511.12</t>
         </is>
       </c>
-      <c r="AY10" t="n">
+      <c r="BC10" t="n">
         <v>0.14</v>
       </c>
-      <c r="AZ10" t="n">
+      <c r="BD10" t="n">
         <v>-0.03</v>
       </c>
-      <c r="BA10" t="inlineStr">
+      <c r="BE10" t="inlineStr">
         <is>
           <t>0.54</t>
         </is>
       </c>
-      <c r="BB10" t="inlineStr">
+      <c r="BF10" t="inlineStr">
         <is>
           <t>-106.37</t>
         </is>
       </c>
-      <c r="BC10" t="inlineStr">
+      <c r="BG10" t="inlineStr">
         <is>
           <t>2025/11/28</t>
         </is>
       </c>
-      <c r="BD10" t="inlineStr">
+      <c r="BH10" t="inlineStr">
         <is>
           <t>39643582.14396068</t>
         </is>
       </c>
-      <c r="BE10" t="inlineStr">
+      <c r="BI10" t="inlineStr">
         <is>
           <t>120192159.0</t>
         </is>
       </c>
-      <c r="BF10" t="n">
+      <c r="BJ10" t="n">
         <v>126910257</v>
       </c>
-      <c r="BG10" t="inlineStr">
+      <c r="BK10" t="inlineStr">
         <is>
           <t>72495141.9</t>
         </is>
       </c>
-      <c r="BH10" t="n">
+      <c r="BL10" t="n">
         <v>37850914.22</v>
       </c>
-      <c r="BI10" t="inlineStr">
+      <c r="BM10" t="inlineStr">
         <is>
           <t>54415115</t>
         </is>
       </c>
-      <c r="BJ10" t="inlineStr">
+      <c r="BN10" t="inlineStr">
         <is>
           <t>8078031.522023421</t>
         </is>
       </c>
-      <c r="BK10" t="inlineStr">
+      <c r="BO10" t="inlineStr">
         <is>
           <t>27320222.47340429</t>
         </is>
       </c>
-      <c r="BL10" t="inlineStr">
+      <c r="BP10" t="inlineStr">
         <is>
           <t>120192159.0</t>
         </is>
       </c>
-      <c r="BM10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN10" t="inlineStr">
+      <c r="BQ10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR10" t="inlineStr">
         <is>
           <t>10.6</t>
         </is>
       </c>
-      <c r="BO10" t="inlineStr">
+      <c r="BS10" t="inlineStr">
         <is>
           <t>2025/12/10</t>
         </is>
       </c>
-      <c r="BP10" t="inlineStr">
+      <c r="BT10" t="inlineStr">
         <is>
           <t>6.60</t>
         </is>
       </c>
-      <c r="BQ10" t="inlineStr">
+      <c r="BU10" t="inlineStr">
         <is>
           <t>聯成</t>
         </is>
       </c>
-      <c r="BR10" t="inlineStr">
+      <c r="BV10" t="inlineStr">
         <is>
           <t>聯成</t>
         </is>
       </c>
-      <c r="BS10" t="inlineStr">
+      <c r="BW10" t="inlineStr">
         <is>
           <t>塑膠工業</t>
         </is>
       </c>
-      <c r="BT10" t="inlineStr">
+      <c r="BX10" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BU10" t="inlineStr">
+      <c r="BY10" t="inlineStr">
         <is>
           <t>0.76</t>
         </is>
       </c>
-      <c r="BV10" t="inlineStr">
+      <c r="BZ10" t="inlineStr">
         <is>
           <t>-11.96408371040724</t>
         </is>
       </c>
-      <c r="BW10" t="inlineStr">
+      <c r="CA10" t="inlineStr">
         <is>
           <t>-13.59414944504011</t>
         </is>
       </c>
-      <c r="BX10" t="inlineStr">
+      <c r="CB10" t="inlineStr">
         <is>
           <t>-19.633719693908</t>
         </is>
       </c>
-      <c r="BY10" t="inlineStr">
+      <c r="CC10" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ10" t="inlineStr">
+      <c r="CD10" t="inlineStr">
         <is>
           <t>價漲量增</t>
         </is>
       </c>
-      <c r="CA10" t="inlineStr">
+      <c r="CE10" t="inlineStr">
         <is>
           <t>0.51</t>
         </is>
       </c>
-      <c r="CB10" t="inlineStr">
+      <c r="CF10" t="inlineStr">
         <is>
           <t>1.41</t>
         </is>
       </c>
-      <c r="CC10" t="inlineStr">
+      <c r="CG10" t="inlineStr">
         <is>
           <t>10.97</t>
         </is>
       </c>
-      <c r="CD10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CE10" t="inlineStr">
+      <c r="CH10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CI10" t="inlineStr">
         <is>
           <t>0.96%</t>
         </is>
       </c>
-      <c r="CF10" t="inlineStr">
+      <c r="CJ10" t="inlineStr">
         <is>
           <t>-3.42%</t>
         </is>
       </c>
-      <c r="CG10" t="inlineStr">
+      <c r="CK10" t="inlineStr">
         <is>
           <t>63.44</t>
         </is>
       </c>
-      <c r="CH10" t="inlineStr">
+      <c r="CL10" t="inlineStr">
         <is>
           <t>14374</t>
         </is>
       </c>
-      <c r="CI10" t="inlineStr">
+      <c r="CM10" t="inlineStr">
         <is>
           <t>可塑劑(DOP)76.00%、聚氯乙烯13.00%、酸酐6.00%、其他5.00% (2024年)</t>
         </is>
       </c>
-      <c r="CJ10" t="inlineStr">
+      <c r="CN10" t="inlineStr">
         <is>
           <t>聯成-塑膠工業-上市</t>
         </is>
       </c>
-      <c r="CK10" t="inlineStr">
+      <c r="CO10" t="inlineStr">
         <is>
           <t>塑膠工業右下上市</t>
         </is>
       </c>
-      <c r="CL10" t="inlineStr">
+      <c r="CP10" t="inlineStr">
         <is>
           <t>11.15</t>
         </is>
       </c>
-      <c r="CM10" t="inlineStr">
+      <c r="CQ10" t="inlineStr">
         <is>
           <t>11.8</t>
         </is>
       </c>
-      <c r="CN10" t="inlineStr">
+      <c r="CR10" t="inlineStr">
         <is>
           <t>11.05</t>
         </is>
       </c>
-      <c r="CO10" t="inlineStr">
+      <c r="CS10" t="inlineStr">
         <is>
           <t>11.3</t>
         </is>
       </c>
-      <c r="CP10" t="inlineStr">
+      <c r="CT10" t="inlineStr">
         <is>
           <t>22.32</t>
         </is>
       </c>
-      <c r="CQ10" t="inlineStr">
+      <c r="CU10" t="inlineStr">
         <is>
           <t>** 石化及塑橡膠 - 塑化劑(可塑劑)</t>
         </is>
       </c>
-      <c r="CR10" t="inlineStr">
+      <c r="CV10" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -5206,325 +5406,345 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
+          <t>0.07</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
           <t>2025/11/21</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
+      <c r="AD11" t="inlineStr">
         <is>
           <t>9.53</t>
         </is>
       </c>
-      <c r="AD11" t="inlineStr">
+      <c r="AE11" t="inlineStr">
         <is>
           <t>2025/09/22</t>
         </is>
       </c>
-      <c r="AE11" t="inlineStr">
+      <c r="AF11" t="inlineStr">
         <is>
           <t>10.15</t>
         </is>
       </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>0.07</t>
-        </is>
-      </c>
       <c r="AG11" t="inlineStr">
         <is>
+          <t>2025/11/17</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>10.1</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>2025/10/28</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>10.3</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
           <t>2025-12-02</t>
         </is>
       </c>
-      <c r="AH11" t="inlineStr">
+      <c r="AL11" t="inlineStr">
         <is>
           <t>100.00</t>
         </is>
       </c>
-      <c r="AI11" t="inlineStr">
+      <c r="AM11" t="inlineStr">
         <is>
           <t>1.63</t>
         </is>
       </c>
-      <c r="AJ11" t="inlineStr">
+      <c r="AN11" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK11" t="inlineStr"/>
-      <c r="AL11" t="inlineStr">
+      <c r="AO11" t="inlineStr"/>
+      <c r="AP11" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
+      <c r="AQ11" t="inlineStr">
         <is>
           <t>1703</t>
         </is>
       </c>
-      <c r="AN11" t="inlineStr">
+      <c r="AR11" t="inlineStr">
         <is>
           <t>100.0</t>
         </is>
       </c>
-      <c r="AO11" t="inlineStr">
+      <c r="AS11" t="inlineStr">
         <is>
           <t>100.0</t>
         </is>
       </c>
-      <c r="AP11" t="n">
+      <c r="AT11" t="n">
         <v>8.84</v>
       </c>
-      <c r="AQ11" t="n">
+      <c r="AU11" t="n">
         <v>2.78</v>
       </c>
-      <c r="AR11" t="inlineStr">
+      <c r="AV11" t="inlineStr">
         <is>
           <t>-1.45</t>
         </is>
       </c>
-      <c r="AS11" t="inlineStr">
+      <c r="AW11" t="inlineStr">
         <is>
           <t>0.40</t>
         </is>
       </c>
-      <c r="AT11" t="inlineStr">
+      <c r="AX11" t="inlineStr">
         <is>
           <t>10.382</t>
         </is>
       </c>
-      <c r="AU11" t="n">
+      <c r="AY11" t="n">
         <v>10.1</v>
       </c>
-      <c r="AV11" t="n">
+      <c r="AZ11" t="n">
         <v>10.25</v>
       </c>
-      <c r="AW11" t="inlineStr">
+      <c r="BA11" t="inlineStr">
         <is>
           <t>10.21</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
+      <c r="BB11" t="inlineStr">
         <is>
           <t>175.85</t>
         </is>
       </c>
-      <c r="AY11" t="n">
+      <c r="BC11" t="n">
         <v>0.06</v>
       </c>
-      <c r="AZ11" t="n">
+      <c r="BD11" t="n">
         <v>-0.08</v>
       </c>
-      <c r="BA11" t="inlineStr">
+      <c r="BE11" t="inlineStr">
         <is>
           <t>0.54</t>
         </is>
       </c>
-      <c r="BB11" t="inlineStr">
+      <c r="BF11" t="inlineStr">
         <is>
           <t>-114.52</t>
         </is>
       </c>
-      <c r="BC11" t="inlineStr">
+      <c r="BG11" t="inlineStr">
         <is>
           <t>2025/11/28</t>
         </is>
       </c>
-      <c r="BD11" t="inlineStr">
+      <c r="BH11" t="inlineStr">
         <is>
           <t>39643582.14396068</t>
         </is>
       </c>
-      <c r="BE11" t="inlineStr">
+      <c r="BI11" t="inlineStr">
         <is>
           <t>390794197.0</t>
         </is>
       </c>
-      <c r="BF11" t="n">
+      <c r="BJ11" t="n">
         <v>105490556.2</v>
       </c>
-      <c r="BG11" t="inlineStr">
+      <c r="BK11" t="inlineStr">
         <is>
           <t>64310538.4</t>
         </is>
       </c>
-      <c r="BH11" t="n">
+      <c r="BL11" t="n">
         <v>35931629.66</v>
       </c>
-      <c r="BI11" t="inlineStr">
+      <c r="BM11" t="inlineStr">
         <is>
           <t>41180017</t>
         </is>
       </c>
-      <c r="BJ11" t="inlineStr">
+      <c r="BN11" t="inlineStr">
         <is>
           <t>4579451.34904508</t>
         </is>
       </c>
-      <c r="BK11" t="inlineStr">
+      <c r="BO11" t="inlineStr">
         <is>
           <t>29841549.05537103</t>
         </is>
       </c>
-      <c r="BL11" t="inlineStr">
+      <c r="BP11" t="inlineStr">
         <is>
           <t>390794197.0</t>
         </is>
       </c>
-      <c r="BM11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN11" t="inlineStr">
+      <c r="BQ11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR11" t="inlineStr">
         <is>
           <t>10.6</t>
         </is>
       </c>
-      <c r="BO11" t="inlineStr">
+      <c r="BS11" t="inlineStr">
         <is>
           <t>2025/12/10</t>
         </is>
       </c>
-      <c r="BP11" t="inlineStr">
+      <c r="BT11" t="inlineStr">
         <is>
           <t>6.60</t>
         </is>
       </c>
-      <c r="BQ11" t="inlineStr">
+      <c r="BU11" t="inlineStr">
         <is>
           <t>聯成</t>
         </is>
       </c>
-      <c r="BR11" t="inlineStr">
+      <c r="BV11" t="inlineStr">
         <is>
           <t>聯成</t>
         </is>
       </c>
-      <c r="BS11" t="inlineStr">
+      <c r="BW11" t="inlineStr">
         <is>
           <t>塑膠工業</t>
         </is>
       </c>
-      <c r="BT11" t="inlineStr">
+      <c r="BX11" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BU11" t="inlineStr">
+      <c r="BY11" t="inlineStr">
         <is>
           <t>0.76</t>
         </is>
       </c>
-      <c r="BV11" t="inlineStr">
+      <c r="BZ11" t="inlineStr">
         <is>
           <t>-11.96408371040724</t>
         </is>
       </c>
-      <c r="BW11" t="inlineStr">
+      <c r="CA11" t="inlineStr">
         <is>
           <t>-13.59414944504011</t>
         </is>
       </c>
-      <c r="BX11" t="inlineStr">
+      <c r="CB11" t="inlineStr">
         <is>
           <t>-19.633719693908</t>
         </is>
       </c>
-      <c r="BY11" t="inlineStr">
+      <c r="CC11" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
-      <c r="BZ11" t="inlineStr">
+      <c r="CD11" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CA11" t="inlineStr">
+      <c r="CE11" t="inlineStr">
         <is>
           <t>0.51</t>
         </is>
       </c>
-      <c r="CB11" t="inlineStr">
+      <c r="CF11" t="inlineStr">
         <is>
           <t>1.41</t>
         </is>
       </c>
-      <c r="CC11" t="inlineStr">
+      <c r="CG11" t="inlineStr">
         <is>
           <t>10.97</t>
         </is>
       </c>
-      <c r="CD11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CE11" t="inlineStr">
+      <c r="CH11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CI11" t="inlineStr">
         <is>
           <t>0.96%</t>
         </is>
       </c>
-      <c r="CF11" t="inlineStr">
+      <c r="CJ11" t="inlineStr">
         <is>
           <t>-3.42%</t>
         </is>
       </c>
-      <c r="CG11" t="inlineStr">
+      <c r="CK11" t="inlineStr">
         <is>
           <t>63.44</t>
         </is>
       </c>
-      <c r="CH11" t="inlineStr">
+      <c r="CL11" t="inlineStr">
         <is>
           <t>14374</t>
         </is>
       </c>
-      <c r="CI11" t="inlineStr">
+      <c r="CM11" t="inlineStr">
         <is>
           <t>可塑劑(DOP)76.00%、聚氯乙烯13.00%、酸酐6.00%、其他5.00% (2024年)</t>
         </is>
       </c>
-      <c r="CJ11" t="inlineStr">
+      <c r="CN11" t="inlineStr">
         <is>
           <t>聯成-塑膠工業-上市</t>
         </is>
       </c>
-      <c r="CK11" t="inlineStr">
+      <c r="CO11" t="inlineStr">
         <is>
           <t>塑膠工業右下上市</t>
         </is>
       </c>
-      <c r="CL11" t="inlineStr">
+      <c r="CP11" t="inlineStr">
         <is>
           <t>10.7</t>
         </is>
       </c>
-      <c r="CM11" t="inlineStr">
+      <c r="CQ11" t="inlineStr">
         <is>
           <t>11.75</t>
         </is>
       </c>
-      <c r="CN11" t="inlineStr">
+      <c r="CR11" t="inlineStr">
         <is>
           <t>10.7</t>
         </is>
       </c>
-      <c r="CO11" t="inlineStr">
+      <c r="CS11" t="inlineStr">
         <is>
           <t>11.3</t>
         </is>
       </c>
-      <c r="CP11" t="inlineStr">
+      <c r="CT11" t="inlineStr">
         <is>
           <t>22.32</t>
         </is>
       </c>
-      <c r="CQ11" t="inlineStr">
+      <c r="CU11" t="inlineStr">
         <is>
           <t>** 石化及塑橡膠 - 塑化劑(可塑劑)</t>
         </is>
       </c>
-      <c r="CR11" t="inlineStr">
+      <c r="CV11" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -5668,325 +5888,345 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
+          <t>0.06</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
           <t>2025/11/21</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
+      <c r="AD12" t="inlineStr">
         <is>
           <t>9.53</t>
         </is>
       </c>
-      <c r="AD12" t="inlineStr">
+      <c r="AE12" t="inlineStr">
         <is>
           <t>2025/09/22</t>
         </is>
       </c>
-      <c r="AE12" t="inlineStr">
+      <c r="AF12" t="inlineStr">
         <is>
           <t>10.15</t>
         </is>
       </c>
-      <c r="AF12" t="inlineStr">
-        <is>
-          <t>0.06</t>
-        </is>
-      </c>
       <c r="AG12" t="inlineStr">
         <is>
+          <t>2025/11/17</t>
+        </is>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>10.1</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>2025/10/28</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>10.3</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
           <t>2025-12-01</t>
         </is>
       </c>
-      <c r="AH12" t="inlineStr">
+      <c r="AL12" t="inlineStr">
         <is>
           <t>18.31</t>
         </is>
       </c>
-      <c r="AI12" t="inlineStr">
+      <c r="AM12" t="inlineStr">
         <is>
           <t>2.95</t>
         </is>
       </c>
-      <c r="AJ12" t="inlineStr">
+      <c r="AN12" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK12" t="inlineStr"/>
-      <c r="AL12" t="inlineStr">
+      <c r="AO12" t="inlineStr"/>
+      <c r="AP12" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
+      <c r="AQ12" t="inlineStr">
         <is>
           <t>1703</t>
         </is>
       </c>
-      <c r="AN12" t="inlineStr">
+      <c r="AR12" t="inlineStr">
         <is>
           <t>100.0</t>
         </is>
       </c>
-      <c r="AO12" t="inlineStr">
+      <c r="AS12" t="inlineStr">
         <is>
           <t>88.73</t>
         </is>
       </c>
-      <c r="AP12" t="n">
+      <c r="AT12" t="n">
         <v>6.77</v>
       </c>
-      <c r="AQ12" t="n">
+      <c r="AU12" t="n">
         <v>-0.22</v>
       </c>
-      <c r="AR12" t="inlineStr">
+      <c r="AV12" t="inlineStr">
         <is>
           <t>-1.69</t>
         </is>
       </c>
-      <c r="AS12" t="inlineStr">
+      <c r="AW12" t="inlineStr">
         <is>
           <t>0.26</t>
         </is>
       </c>
-      <c r="AT12" t="inlineStr">
+      <c r="AX12" t="inlineStr">
         <is>
           <t>10.022</t>
         </is>
       </c>
-      <c r="AU12" t="n">
+      <c r="AY12" t="n">
         <v>10.04</v>
       </c>
-      <c r="AV12" t="n">
+      <c r="AZ12" t="n">
         <v>10.22</v>
       </c>
-      <c r="AW12" t="inlineStr">
+      <c r="BA12" t="inlineStr">
         <is>
           <t>10.19</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
+      <c r="BB12" t="inlineStr">
         <is>
           <t>59.14</t>
         </is>
       </c>
-      <c r="AY12" t="n">
+      <c r="BC12" t="n">
         <v>-0.05</v>
       </c>
-      <c r="AZ12" t="n">
+      <c r="BD12" t="n">
         <v>-0.11</v>
       </c>
-      <c r="BA12" t="inlineStr">
+      <c r="BE12" t="inlineStr">
         <is>
           <t>0.54</t>
         </is>
       </c>
-      <c r="BB12" t="inlineStr">
+      <c r="BF12" t="inlineStr">
         <is>
           <t>-120.90</t>
         </is>
       </c>
-      <c r="BC12" t="inlineStr">
+      <c r="BG12" t="inlineStr">
         <is>
           <t>2025/11/28</t>
         </is>
       </c>
-      <c r="BD12" t="inlineStr">
+      <c r="BH12" t="inlineStr">
         <is>
           <t>39643582.14396068</t>
         </is>
       </c>
-      <c r="BE12" t="inlineStr">
+      <c r="BI12" t="inlineStr">
         <is>
           <t>66856122.0</t>
         </is>
       </c>
-      <c r="BF12" t="n">
+      <c r="BJ12" t="n">
         <v>30264685.8</v>
       </c>
-      <c r="BG12" t="inlineStr">
+      <c r="BK12" t="inlineStr">
         <is>
           <t>27741544.4</t>
         </is>
       </c>
-      <c r="BH12" t="n">
+      <c r="BL12" t="n">
         <v>28239844.66</v>
       </c>
-      <c r="BI12" t="inlineStr">
+      <c r="BM12" t="inlineStr">
         <is>
           <t>2523141</t>
         </is>
       </c>
-      <c r="BJ12" t="inlineStr">
+      <c r="BN12" t="inlineStr">
         <is>
           <t>-13657.32483236655</t>
         </is>
       </c>
-      <c r="BK12" t="inlineStr">
+      <c r="BO12" t="inlineStr">
         <is>
           <t>3384599.063345991</t>
         </is>
       </c>
-      <c r="BL12" t="inlineStr">
+      <c r="BP12" t="inlineStr">
         <is>
           <t>66856122.0</t>
         </is>
       </c>
-      <c r="BM12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN12" t="inlineStr">
+      <c r="BQ12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR12" t="inlineStr">
         <is>
           <t>10.6</t>
         </is>
       </c>
-      <c r="BO12" t="inlineStr">
+      <c r="BS12" t="inlineStr">
         <is>
           <t>2025/12/10</t>
         </is>
       </c>
-      <c r="BP12" t="inlineStr">
+      <c r="BT12" t="inlineStr">
         <is>
           <t>0.94</t>
         </is>
       </c>
-      <c r="BQ12" t="inlineStr">
+      <c r="BU12" t="inlineStr">
         <is>
           <t>聯成</t>
         </is>
       </c>
-      <c r="BR12" t="inlineStr">
+      <c r="BV12" t="inlineStr">
         <is>
           <t>聯成</t>
         </is>
       </c>
-      <c r="BS12" t="inlineStr">
+      <c r="BW12" t="inlineStr">
         <is>
           <t>塑膠工業</t>
         </is>
       </c>
-      <c r="BT12" t="inlineStr">
+      <c r="BX12" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BU12" t="inlineStr">
+      <c r="BY12" t="inlineStr">
         <is>
           <t>0.76</t>
         </is>
       </c>
-      <c r="BV12" t="inlineStr">
+      <c r="BZ12" t="inlineStr">
         <is>
           <t>-11.96408371040724</t>
         </is>
       </c>
-      <c r="BW12" t="inlineStr">
+      <c r="CA12" t="inlineStr">
         <is>
           <t>-13.59414944504011</t>
         </is>
       </c>
-      <c r="BX12" t="inlineStr">
+      <c r="CB12" t="inlineStr">
         <is>
           <t>-19.633719693908</t>
         </is>
       </c>
-      <c r="BY12" t="inlineStr">
+      <c r="CC12" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
-      <c r="BZ12" t="inlineStr">
+      <c r="CD12" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CA12" t="inlineStr">
+      <c r="CE12" t="inlineStr">
         <is>
           <t>0.48</t>
         </is>
       </c>
-      <c r="CB12" t="inlineStr">
+      <c r="CF12" t="inlineStr">
         <is>
           <t>1.41</t>
         </is>
       </c>
-      <c r="CC12" t="inlineStr">
+      <c r="CG12" t="inlineStr">
         <is>
           <t>10.97</t>
         </is>
       </c>
-      <c r="CD12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CE12" t="inlineStr">
+      <c r="CH12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CI12" t="inlineStr">
         <is>
           <t>0.96%</t>
         </is>
       </c>
-      <c r="CF12" t="inlineStr">
+      <c r="CJ12" t="inlineStr">
         <is>
           <t>-3.42%</t>
         </is>
       </c>
-      <c r="CG12" t="inlineStr">
+      <c r="CK12" t="inlineStr">
         <is>
           <t>63.44</t>
         </is>
       </c>
-      <c r="CH12" t="inlineStr">
+      <c r="CL12" t="inlineStr">
         <is>
           <t>14374</t>
         </is>
       </c>
-      <c r="CI12" t="inlineStr">
+      <c r="CM12" t="inlineStr">
         <is>
           <t>可塑劑(DOP)76.00%、聚氯乙烯13.00%、酸酐6.00%、其他5.00% (2024年)</t>
         </is>
       </c>
-      <c r="CJ12" t="inlineStr">
+      <c r="CN12" t="inlineStr">
         <is>
           <t>聯成-塑膠工業-上市</t>
         </is>
       </c>
-      <c r="CK12" t="inlineStr">
+      <c r="CO12" t="inlineStr">
         <is>
           <t>塑膠工業右下上市</t>
         </is>
       </c>
-      <c r="CL12" t="inlineStr">
+      <c r="CP12" t="inlineStr">
         <is>
           <t>10.3</t>
         </is>
       </c>
-      <c r="CM12" t="inlineStr">
+      <c r="CQ12" t="inlineStr">
         <is>
           <t>10.8</t>
         </is>
       </c>
-      <c r="CN12" t="inlineStr">
+      <c r="CR12" t="inlineStr">
         <is>
           <t>10.3</t>
         </is>
       </c>
-      <c r="CO12" t="inlineStr">
+      <c r="CS12" t="inlineStr">
         <is>
           <t>10.7</t>
         </is>
       </c>
-      <c r="CP12" t="inlineStr">
+      <c r="CT12" t="inlineStr">
         <is>
           <t>22.32</t>
         </is>
       </c>
-      <c r="CQ12" t="inlineStr">
+      <c r="CU12" t="inlineStr">
         <is>
           <t>** 石化及塑橡膠 - 塑化劑(可塑劑)</t>
         </is>
       </c>
-      <c r="CR12" t="inlineStr">
+      <c r="CV12" t="inlineStr">
         <is>
           <t>True</t>
         </is>

--- a/Result/checksun_type/塑化劑(可塑劑).xlsx
+++ b/Result/checksun_type/塑化劑(可塑劑).xlsx
@@ -933,7 +933,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>【b1】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -943,94 +943,94 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>-2.34</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2761.366</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>10.4</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>1703.083</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>-1.06</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>-37.21</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>-65.0</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>2025-12-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>2025-12-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>2025-10-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>2025-10-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>11.05</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>10.4</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>11.05</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
         <is>
           <t>10.65</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>0.18</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>-60.06</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>2025-12-08</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>-50.0</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>2025-12-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>2025-12-16 00:00:00</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>2025-10-27 00:00:00</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>2025-10-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>11.05</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>11.05</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>10.65</t>
-        </is>
-      </c>
       <c r="U2" t="inlineStr">
         <is>
           <t>10.3</t>
@@ -1038,12 +1038,12 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>-3.62</t>
+          <t>-5.88</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -1093,37 +1093,37 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
+          <t>2025/12/16</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>10.4</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
           <t>2025/11/17</t>
         </is>
       </c>
-      <c r="AH2" t="inlineStr">
+      <c r="AJ2" t="inlineStr">
         <is>
           <t>10.1</t>
         </is>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>2025/10/28</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>10.3</t>
-        </is>
-      </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>4.97</t>
+          <t>8.06</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>-1.40</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
@@ -1134,50 +1134,50 @@
       <c r="AO2" t="inlineStr"/>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>1703</t>
+          <t>2761</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>5.88</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>13.73</t>
+          <t>3.92</t>
         </is>
       </c>
       <c r="AT2" t="n">
-        <v>-1.3</v>
+        <v>-2.16</v>
       </c>
       <c r="AU2" t="n">
-        <v>3.5</v>
+        <v>1.77</v>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>10.79</t>
+          <t>10.63</t>
         </is>
       </c>
       <c r="AY2" t="n">
-        <v>10.42</v>
+        <v>10.44</v>
       </c>
       <c r="AZ2" t="n">
-        <v>10.37</v>
+        <v>10.38</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1186,14 +1186,14 @@
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>-16.83</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>0.18</v>
+        <v>0.14</v>
       </c>
       <c r="BD2" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>-66.34</t>
+          <t>-67.70</t>
         </is>
       </c>
       <c r="BG2" t="inlineStr">
@@ -1212,43 +1212,43 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>39643582.14396068</t>
+          <t>39648620.88008415</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>18268876.0</t>
+          <t>28824134.0</t>
         </is>
       </c>
       <c r="BJ2" t="n">
-        <v>32256217.8</v>
+        <v>27984384</v>
       </c>
       <c r="BK2" t="inlineStr">
         <is>
-          <t>80763071.4</t>
+          <t>44566065.1</t>
         </is>
       </c>
       <c r="BL2" t="n">
-        <v>38610965.58</v>
+        <v>38475388.26</v>
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>-48506853</t>
+          <t>-16581681</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>3677575.421348871</t>
+          <t>2198442.805462827</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>-5479927.99472075</t>
+          <t>-5936786.581910416</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>18268876.0</t>
+          <t>28824134.0</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
@@ -1268,67 +1268,67 @@
       </c>
       <c r="BT2" t="inlineStr">
         <is>
+          <t>-1.89</t>
+        </is>
+      </c>
+      <c r="BU2" t="inlineStr">
+        <is>
+          <t>聯成</t>
+        </is>
+      </c>
+      <c r="BV2" t="inlineStr">
+        <is>
+          <t>聯成</t>
+        </is>
+      </c>
+      <c r="BW2" t="inlineStr">
+        <is>
+          <t>塑膠工業</t>
+        </is>
+      </c>
+      <c r="BX2" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BY2" t="inlineStr">
+        <is>
+          <t>0.77</t>
+        </is>
+      </c>
+      <c r="BZ2" t="inlineStr">
+        <is>
+          <t>-11.96408371040724</t>
+        </is>
+      </c>
+      <c r="CA2" t="inlineStr">
+        <is>
+          <t>-13.59414944504011</t>
+        </is>
+      </c>
+      <c r="CB2" t="inlineStr">
+        <is>
+          <t>-19.633719693908</t>
+        </is>
+      </c>
+      <c r="CC2" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="CD2" t="inlineStr">
+        <is>
+          <t>價跌量-</t>
+        </is>
+      </c>
+      <c r="CE2" t="inlineStr">
+        <is>
           <t>0.47</t>
         </is>
       </c>
-      <c r="BU2" t="inlineStr">
-        <is>
-          <t>聯成</t>
-        </is>
-      </c>
-      <c r="BV2" t="inlineStr">
-        <is>
-          <t>聯成</t>
-        </is>
-      </c>
-      <c r="BW2" t="inlineStr">
-        <is>
-          <t>塑膠工業</t>
-        </is>
-      </c>
-      <c r="BX2" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BY2" t="inlineStr">
-        <is>
-          <t>0.76</t>
-        </is>
-      </c>
-      <c r="BZ2" t="inlineStr">
-        <is>
-          <t>-11.96408371040724</t>
-        </is>
-      </c>
-      <c r="CA2" t="inlineStr">
-        <is>
-          <t>-13.59414944504011</t>
-        </is>
-      </c>
-      <c r="CB2" t="inlineStr">
-        <is>
-          <t>-19.633719693908</t>
-        </is>
-      </c>
-      <c r="CC2" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="CD2" t="inlineStr">
-        <is>
-          <t>價漲量-</t>
-        </is>
-      </c>
-      <c r="CE2" t="inlineStr">
-        <is>
-          <t>0.48</t>
-        </is>
-      </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1353,12 +1353,12 @@
       </c>
       <c r="CK2" t="inlineStr">
         <is>
-          <t>63.44</t>
+          <t>63.18</t>
         </is>
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>14374</t>
+          <t>14037</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
@@ -1378,22 +1378,22 @@
       </c>
       <c r="CP2" t="inlineStr">
         <is>
-          <t>10.6</t>
+          <t>10.7</t>
         </is>
       </c>
       <c r="CQ2" t="inlineStr">
         <is>
-          <t>10.9</t>
+          <t>10.7</t>
         </is>
       </c>
       <c r="CR2" t="inlineStr">
         <is>
-          <t>10.55</t>
+          <t>10.3</t>
         </is>
       </c>
       <c r="CS2" t="inlineStr">
         <is>
-          <t>10.65</t>
+          <t>10.4</t>
         </is>
       </c>
       <c r="CT2" t="inlineStr">
@@ -1408,7 +1408,7 @@
       </c>
       <c r="CV2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1425,12 +1425,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1904.815</t>
+          <t>1703.083</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1450,17 +1450,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-2.4</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-57.99</t>
+          <t>-60.06</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1500,7 +1500,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10.4</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -1525,7 +1525,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1550,7 +1550,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1575,37 +1575,37 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
+          <t>2025/12/16</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>10.4</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
           <t>2025/11/17</t>
         </is>
       </c>
-      <c r="AH3" t="inlineStr">
+      <c r="AJ3" t="inlineStr">
         <is>
           <t>10.1</t>
         </is>
       </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>2025/10/28</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>10.3</t>
-        </is>
-      </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>5.56</t>
+          <t>4.97</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>-5.16</t>
+          <t>-1.40</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
@@ -1616,12 +1616,12 @@
       <c r="AO3" t="inlineStr"/>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>1703</t>
+          <t>2761</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
@@ -1631,32 +1631,32 @@
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>19.34</t>
+          <t>13.73</t>
         </is>
       </c>
       <c r="AT3" t="n">
-        <v>-2.02</v>
+        <v>-1.3</v>
       </c>
       <c r="AU3" t="n">
-        <v>4.54</v>
+        <v>3.5</v>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>10.87</t>
+          <t>10.79</t>
         </is>
       </c>
       <c r="AY3" t="n">
-        <v>10.4</v>
+        <v>10.42</v>
       </c>
       <c r="AZ3" t="n">
         <v>10.37</v>
@@ -1668,11 +1668,11 @@
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>15.38</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>0.21</v>
+        <v>0.18</v>
       </c>
       <c r="BD3" t="n">
         <v>0.18</v>
@@ -1684,7 +1684,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>-66.51</t>
+          <t>-66.34</t>
         </is>
       </c>
       <c r="BG3" t="inlineStr">
@@ -1694,43 +1694,43 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>39643582.14396068</t>
+          <t>39648620.88008415</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>20756844.0</t>
+          <t>18268876.0</t>
         </is>
       </c>
       <c r="BJ3" t="n">
-        <v>35969648.4</v>
+        <v>32256217.8</v>
       </c>
       <c r="BK3" t="inlineStr">
         <is>
-          <t>85621796.0</t>
+          <t>80763071.4</t>
         </is>
       </c>
       <c r="BL3" t="n">
-        <v>38506172.98</v>
+        <v>38610965.58</v>
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>-49652147</t>
+          <t>-48506853</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>5342576.042452438</t>
+          <t>3677575.421348871</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>-3500640.656066917</t>
+          <t>-5479927.99472075</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>20756844.0</t>
+          <t>18268876.0</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1835,12 +1835,12 @@
       </c>
       <c r="CK3" t="inlineStr">
         <is>
-          <t>63.44</t>
+          <t>63.18</t>
         </is>
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>14374</t>
+          <t>14037</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
@@ -1860,24 +1860,24 @@
       </c>
       <c r="CP3" t="inlineStr">
         <is>
-          <t>10.95</t>
+          <t>10.6</t>
         </is>
       </c>
       <c r="CQ3" t="inlineStr">
         <is>
-          <t>11.2</t>
+          <t>10.9</t>
         </is>
       </c>
       <c r="CR3" t="inlineStr">
         <is>
+          <t>10.55</t>
+        </is>
+      </c>
+      <c r="CS3" t="inlineStr">
+        <is>
           <t>10.65</t>
         </is>
       </c>
-      <c r="CS3" t="inlineStr">
-        <is>
-          <t>10.65</t>
-        </is>
-      </c>
       <c r="CT3" t="inlineStr">
         <is>
           <t>22.32</t>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="CV3" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1907,12 +1907,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1950.665</t>
+          <t>1904.815</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>10.85</t>
+          <t>10.65</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1932,17 +1932,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>-2.4</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-53.07</t>
+          <t>-57.99</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1982,7 +1982,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10.4</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -2002,12 +2002,12 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>-3.62</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -2057,37 +2057,37 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
+          <t>2025/12/16</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>10.4</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
           <t>2025/11/17</t>
         </is>
       </c>
-      <c r="AH4" t="inlineStr">
+      <c r="AJ4" t="inlineStr">
         <is>
           <t>10.1</t>
         </is>
       </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>2025/10/28</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>10.3</t>
-        </is>
-      </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>5.69</t>
+          <t>5.56</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>-5.16</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
@@ -2098,66 +2098,66 @@
       <c r="AO4" t="inlineStr"/>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>1703</t>
+          <t>2761</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>29.41</t>
+          <t>5.88</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>45.47</t>
+          <t>19.34</t>
         </is>
       </c>
       <c r="AT4" t="n">
-        <v>-1</v>
+        <v>-2.02</v>
       </c>
       <c r="AU4" t="n">
-        <v>5.51</v>
+        <v>4.54</v>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>10.96</t>
+          <t>10.87</t>
         </is>
       </c>
       <c r="AY4" t="n">
-        <v>10.39</v>
+        <v>10.4</v>
       </c>
       <c r="AZ4" t="n">
-        <v>10.36</v>
+        <v>10.37</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>10.31</t>
+          <t>10.3</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>35.30</t>
+          <t>15.38</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2166,7 +2166,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>-67.80</t>
+          <t>-66.51</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
@@ -2176,43 +2176,43 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>39643582.14396068</t>
+          <t>39648620.88008415</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>21031488.0</t>
+          <t>20756844.0</t>
         </is>
       </c>
       <c r="BJ4" t="n">
-        <v>41281758.4</v>
+        <v>35969648.4</v>
       </c>
       <c r="BK4" t="inlineStr">
         <is>
-          <t>87966629.1</t>
+          <t>85621796.0</t>
         </is>
       </c>
       <c r="BL4" t="n">
-        <v>38425696.6</v>
+        <v>38506172.98</v>
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>-46684870</t>
+          <t>-49652147</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>6950433.624001412</t>
+          <t>5342576.042452438</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>-814632.4345590472</t>
+          <t>-3500640.656066917</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>21031488.0</t>
+          <t>20756844.0</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2277,22 +2277,22 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2317,12 +2317,12 @@
       </c>
       <c r="CK4" t="inlineStr">
         <is>
-          <t>63.44</t>
+          <t>63.18</t>
         </is>
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>14374</t>
+          <t>14037</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
@@ -2342,22 +2342,22 @@
       </c>
       <c r="CP4" t="inlineStr">
         <is>
-          <t>10.6</t>
+          <t>10.95</t>
         </is>
       </c>
       <c r="CQ4" t="inlineStr">
         <is>
-          <t>10.95</t>
+          <t>11.2</t>
         </is>
       </c>
       <c r="CR4" t="inlineStr">
         <is>
-          <t>10.6</t>
+          <t>10.65</t>
         </is>
       </c>
       <c r="CS4" t="inlineStr">
         <is>
-          <t>10.85</t>
+          <t>10.65</t>
         </is>
       </c>
       <c r="CT4" t="inlineStr">
@@ -2372,7 +2372,7 @@
       </c>
       <c r="CV4" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -2389,12 +2389,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-5.36</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>4746.574</t>
+          <t>1950.665</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>10.6</t>
+          <t>10.85</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2414,17 +2414,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>-4.33</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-45.68</t>
+          <t>-53.07</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2434,7 +2434,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10.4</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>-4.07</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4.33</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2514,7 +2514,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -2539,37 +2539,37 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
+          <t>2025/12/16</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>10.4</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
           <t>2025/11/17</t>
         </is>
       </c>
-      <c r="AH5" t="inlineStr">
+      <c r="AJ5" t="inlineStr">
         <is>
           <t>10.1</t>
         </is>
       </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>2025/10/28</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>10.3</t>
-        </is>
-      </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>13.85</t>
+          <t>5.69</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>-5.19</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
@@ -2580,66 +2580,66 @@
       <c r="AO5" t="inlineStr"/>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>1703</t>
+          <t>2761</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>22.73</t>
+          <t>29.41</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>61.38</t>
+          <t>45.47</t>
         </is>
       </c>
       <c r="AT5" t="n">
-        <v>-4.33</v>
+        <v>-1</v>
       </c>
       <c r="AU5" t="n">
-        <v>6.85</v>
+        <v>5.51</v>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>11.08</t>
+          <t>10.96</t>
         </is>
       </c>
       <c r="AY5" t="n">
-        <v>10.37</v>
+        <v>10.39</v>
       </c>
       <c r="AZ5" t="n">
         <v>10.36</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>10.3</t>
+          <t>10.31</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>54.76</t>
+          <t>35.30</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>-70.64</t>
+          <t>-67.80</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
@@ -2658,43 +2658,43 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>39643582.14396068</t>
+          <t>39648620.88008415</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>51040578.0</t>
+          <t>21031488.0</t>
         </is>
       </c>
       <c r="BJ5" t="n">
-        <v>47317430</v>
+        <v>41281758.4</v>
       </c>
       <c r="BK5" t="inlineStr">
         <is>
-          <t>87113843.5</t>
+          <t>87966629.1</t>
         </is>
       </c>
       <c r="BL5" t="n">
-        <v>38674174.84</v>
+        <v>38425696.6</v>
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>-39796413</t>
+          <t>-46684870</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>8362263.81646695</t>
+          <t>6950433.624001412</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>3022190.040257879</t>
+          <t>-814632.4345590472</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>51040578.0</t>
+          <t>21031488.0</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
@@ -2714,7 +2714,7 @@
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2739,7 +2739,7 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2759,22 +2759,22 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2799,12 +2799,12 @@
       </c>
       <c r="CK5" t="inlineStr">
         <is>
-          <t>63.44</t>
+          <t>63.18</t>
         </is>
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>14374</t>
+          <t>14037</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
@@ -2824,22 +2824,22 @@
       </c>
       <c r="CP5" t="inlineStr">
         <is>
-          <t>11.2</t>
+          <t>10.6</t>
         </is>
       </c>
       <c r="CQ5" t="inlineStr">
         <is>
-          <t>11.2</t>
+          <t>10.95</t>
         </is>
       </c>
       <c r="CR5" t="inlineStr">
         <is>
-          <t>10.55</t>
+          <t>10.6</t>
         </is>
       </c>
       <c r="CS5" t="inlineStr">
         <is>
-          <t>10.6</t>
+          <t>10.85</t>
         </is>
       </c>
       <c r="CT5" t="inlineStr">
@@ -2854,14 +2854,14 @@
       </c>
       <c r="CV5" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>【d1】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2871,12 +2871,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>-5.36</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>4587.903</t>
+          <t>4746.574</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2886,7 +2886,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>11.2</t>
+          <t>10.6</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2896,17 +2896,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-5.16</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-26.61</t>
+          <t>-45.68</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2916,7 +2916,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10.4</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -2966,12 +2966,12 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>-4.07</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -3021,37 +3021,37 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
+          <t>2025/12/16</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>10.4</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
           <t>2025/11/17</t>
         </is>
       </c>
-      <c r="AH6" t="inlineStr">
+      <c r="AJ6" t="inlineStr">
         <is>
           <t>10.1</t>
         </is>
       </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>2025/10/28</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>10.3</t>
-        </is>
-      </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>13.39</t>
+          <t>13.85</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>5.71</t>
+          <t>-5.19</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
@@ -3062,66 +3062,66 @@
       <c r="AO6" t="inlineStr"/>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>1703</t>
+          <t>2761</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>84.28</t>
+          <t>22.73</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>81.16</t>
+          <t>61.38</t>
         </is>
       </c>
       <c r="AT6" t="n">
-        <v>-0.18</v>
+        <v>-4.33</v>
       </c>
       <c r="AU6" t="n">
-        <v>8.33</v>
+        <v>6.85</v>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>11.22</t>
+          <t>11.08</t>
         </is>
       </c>
       <c r="AY6" t="n">
-        <v>10.36</v>
+        <v>10.37</v>
       </c>
       <c r="AZ6" t="n">
         <v>10.36</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>10.29</t>
+          <t>10.3</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>104.81</t>
+          <t>54.76</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>0.28</v>
+        <v>0.24</v>
       </c>
       <c r="BD6" t="n">
-        <v>0.14</v>
+        <v>0.16</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3130,7 +3130,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>-74.66</t>
+          <t>-70.64</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr">
@@ -3140,43 +3140,43 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>39643582.14396068</t>
+          <t>39648620.88008415</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>50183303.0</t>
+          <t>51040578.0</t>
         </is>
       </c>
       <c r="BJ6" t="n">
-        <v>61147746.2</v>
+        <v>47317430</v>
       </c>
       <c r="BK6" t="inlineStr">
         <is>
-          <t>83319151.2</t>
+          <t>87113843.5</t>
         </is>
       </c>
       <c r="BL6" t="n">
-        <v>38351204.62</v>
+        <v>38674174.84</v>
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>-22171405</t>
+          <t>-39796413</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>9333186.321232235</t>
+          <t>8362263.81646695</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>5180170.002844289</t>
+          <t>3022190.040257879</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>50183303.0</t>
+          <t>51040578.0</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
@@ -3196,7 +3196,7 @@
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>5.66</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -3221,7 +3221,7 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="CK6" t="inlineStr">
         <is>
-          <t>63.44</t>
+          <t>63.18</t>
         </is>
       </c>
       <c r="CL6" t="inlineStr">
         <is>
-          <t>14374</t>
+          <t>14037</t>
         </is>
       </c>
       <c r="CM6" t="inlineStr">
@@ -3306,12 +3306,12 @@
       </c>
       <c r="CP6" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>11.2</t>
         </is>
       </c>
       <c r="CQ6" t="inlineStr">
         <is>
-          <t>11.25</t>
+          <t>11.2</t>
         </is>
       </c>
       <c r="CR6" t="inlineStr">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="CS6" t="inlineStr">
         <is>
-          <t>11.2</t>
+          <t>10.6</t>
         </is>
       </c>
       <c r="CT6" t="inlineStr">
@@ -3336,7 +3336,7 @@
       </c>
       <c r="CV6" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -3353,12 +3353,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>3380.77</t>
+          <t>4587.903</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3368,74 +3368,74 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
+          <t>11.2</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-7.69</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>-1.06</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>-26.61</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>-65.0</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>2025-12-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2025-12-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>2025-10-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>2025-10-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
           <t>11.05</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>-3.76</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>0.18</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>62.06</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>2025-12-08</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>-50.0</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>2025-12-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>2025-12-16 00:00:00</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>2025-10-27 00:00:00</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>2025-10-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>10.4</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
         <is>
           <t>11.05</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>11.05</t>
-        </is>
-      </c>
       <c r="T7" t="inlineStr">
         <is>
           <t>10.65</t>
@@ -3448,12 +3448,12 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7.69</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -3503,37 +3503,37 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
+          <t>2025/12/16</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>10.4</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
           <t>2025/11/17</t>
         </is>
       </c>
-      <c r="AH7" t="inlineStr">
+      <c r="AJ7" t="inlineStr">
         <is>
           <t>10.1</t>
         </is>
       </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>2025/10/28</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>10.3</t>
-        </is>
-      </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>9.87</t>
+          <t>13.39</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>2.82</t>
+          <t>5.71</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
@@ -3544,75 +3544,75 @@
       <c r="AO7" t="inlineStr"/>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>1703</t>
+          <t>2761</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>77.14</t>
+          <t>84.28</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>86.4</t>
+          <t>81.16</t>
         </is>
       </c>
       <c r="AT7" t="n">
-        <v>-1.69</v>
+        <v>-0.18</v>
       </c>
       <c r="AU7" t="n">
-        <v>9.07</v>
+        <v>8.33</v>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
+          <t>0.62</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>11.22</t>
+        </is>
+      </c>
+      <c r="AY7" t="n">
+        <v>10.36</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>10.36</v>
+      </c>
+      <c r="BA7" t="inlineStr">
+        <is>
+          <t>10.29</t>
+        </is>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>104.81</t>
+        </is>
+      </c>
+      <c r="BC7" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="BE7" t="inlineStr">
+        <is>
           <t>0.54</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>11.24</t>
-        </is>
-      </c>
-      <c r="AY7" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>10.34</v>
-      </c>
-      <c r="BA7" t="inlineStr">
-        <is>
-          <t>10.28</t>
-        </is>
-      </c>
-      <c r="BB7" t="inlineStr">
-        <is>
-          <t>156.80</t>
-        </is>
-      </c>
-      <c r="BC7" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="BE7" t="inlineStr">
-        <is>
-          <t>0.54</t>
-        </is>
-      </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>-81.30</t>
+          <t>-74.66</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr">
@@ -3622,43 +3622,43 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>39643582.14396068</t>
+          <t>39648620.88008415</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>36836029.0</t>
+          <t>50183303.0</t>
         </is>
       </c>
       <c r="BJ7" t="n">
-        <v>129269925</v>
+        <v>61147746.2</v>
       </c>
       <c r="BK7" t="inlineStr">
         <is>
-          <t>79767305.4</t>
+          <t>83319151.2</t>
         </is>
       </c>
       <c r="BL7" t="n">
-        <v>38038480.18</v>
+        <v>38351204.62</v>
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>49502619</t>
+          <t>-22171405</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>10088280.19730277</t>
+          <t>9333186.321232235</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>8169843.34215185</t>
+          <t>5180170.002844289</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>36836029.0</t>
+          <t>50183303.0</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
@@ -3678,7 +3678,7 @@
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>4.25</t>
+          <t>5.66</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3703,7 +3703,7 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
@@ -3738,7 +3738,7 @@
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3763,12 +3763,12 @@
       </c>
       <c r="CK7" t="inlineStr">
         <is>
-          <t>63.44</t>
+          <t>63.18</t>
         </is>
       </c>
       <c r="CL7" t="inlineStr">
         <is>
-          <t>14374</t>
+          <t>14037</t>
         </is>
       </c>
       <c r="CM7" t="inlineStr">
@@ -3793,17 +3793,17 @@
       </c>
       <c r="CQ7" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>11.25</t>
         </is>
       </c>
       <c r="CR7" t="inlineStr">
         <is>
-          <t>10.7</t>
+          <t>10.55</t>
         </is>
       </c>
       <c r="CS7" t="inlineStr">
         <is>
-          <t>11.05</t>
+          <t>11.2</t>
         </is>
       </c>
       <c r="CT7" t="inlineStr">
@@ -3818,7 +3818,7 @@
       </c>
       <c r="CV7" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -3835,12 +3835,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-3.08</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>4250.244</t>
+          <t>3380.77</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3850,7 +3850,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>11.05</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3860,27 +3860,27 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-4.23</t>
+          <t>-6.25</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>73.78</t>
+          <t>62.06</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10.4</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>11.05</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
@@ -3930,12 +3930,12 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6.25</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3985,37 +3985,37 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
+          <t>2025/12/16</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>10.4</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
           <t>2025/11/17</t>
         </is>
       </c>
-      <c r="AH8" t="inlineStr">
+      <c r="AJ8" t="inlineStr">
         <is>
           <t>10.1</t>
         </is>
       </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>2025/10/28</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>10.3</t>
-        </is>
-      </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>12.40</t>
+          <t>9.87</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>2.82</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
@@ -4026,66 +4026,66 @@
       <c r="AO8" t="inlineStr"/>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>1703</t>
+          <t>2761</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>82.05</t>
+          <t>77.14</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>94.02</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="AT8" t="n">
-        <v>-0.63</v>
+        <v>-1.69</v>
       </c>
       <c r="AU8" t="n">
-        <v>8.99</v>
+        <v>9.07</v>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>11.17</t>
+          <t>11.24</t>
         </is>
       </c>
       <c r="AY8" t="n">
-        <v>10.25</v>
+        <v>10.3</v>
       </c>
       <c r="AZ8" t="n">
-        <v>10.33</v>
+        <v>10.34</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>10.27</t>
+          <t>10.28</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>297.70</t>
+          <t>156.80</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>0.24</v>
+        <v>0.26</v>
       </c>
       <c r="BD8" t="n">
-        <v>0.06</v>
+        <v>0.1</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>-88.63</t>
+          <t>-81.30</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr">
@@ -4104,135 +4104,135 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>39643582.14396068</t>
+          <t>39648620.88008415</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>47317394.0</t>
+          <t>36836029.0</t>
         </is>
       </c>
       <c r="BJ8" t="n">
-        <v>135273943.6</v>
+        <v>129269925</v>
       </c>
       <c r="BK8" t="inlineStr">
         <is>
-          <t>77843851.4</t>
+          <t>79767305.4</t>
         </is>
       </c>
       <c r="BL8" t="n">
-        <v>38862439.4</v>
+        <v>38038480.18</v>
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>57430092</t>
+          <t>49502619</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>10437086.8982393</t>
+          <t>10088280.19730277</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>13579090.20751438</t>
+          <t>8169843.34215185</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>47317394.0</t>
+          <t>36836029.0</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
+          <t>2025-12-16</t>
+        </is>
+      </c>
+      <c r="BR8" t="inlineStr">
+        <is>
+          <t>10.6</t>
+        </is>
+      </c>
+      <c r="BS8" t="inlineStr">
+        <is>
+          <t>2025/12/10</t>
+        </is>
+      </c>
+      <c r="BT8" t="inlineStr">
+        <is>
+          <t>4.25</t>
+        </is>
+      </c>
+      <c r="BU8" t="inlineStr">
+        <is>
+          <t>聯成</t>
+        </is>
+      </c>
+      <c r="BV8" t="inlineStr">
+        <is>
+          <t>聯成</t>
+        </is>
+      </c>
+      <c r="BW8" t="inlineStr">
+        <is>
+          <t>塑膠工業</t>
+        </is>
+      </c>
+      <c r="BX8" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BY8" t="inlineStr">
+        <is>
+          <t>0.77</t>
+        </is>
+      </c>
+      <c r="BZ8" t="inlineStr">
+        <is>
+          <t>-11.96408371040724</t>
+        </is>
+      </c>
+      <c r="CA8" t="inlineStr">
+        <is>
+          <t>-13.59414944504011</t>
+        </is>
+      </c>
+      <c r="CB8" t="inlineStr">
+        <is>
+          <t>-19.633719693908</t>
+        </is>
+      </c>
+      <c r="CC8" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="CD8" t="inlineStr">
+        <is>
+          <t>價-量縮</t>
+        </is>
+      </c>
+      <c r="CE8" t="inlineStr">
+        <is>
+          <t>0.50</t>
+        </is>
+      </c>
+      <c r="CF8" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="CG8" t="inlineStr">
+        <is>
+          <t>10.97</t>
+        </is>
+      </c>
+      <c r="CH8" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="BR8" t="inlineStr">
-        <is>
-          <t>10.6</t>
-        </is>
-      </c>
-      <c r="BS8" t="inlineStr">
-        <is>
-          <t>2025/12/10</t>
-        </is>
-      </c>
-      <c r="BT8" t="inlineStr">
-        <is>
-          <t>4.72</t>
-        </is>
-      </c>
-      <c r="BU8" t="inlineStr">
-        <is>
-          <t>聯成</t>
-        </is>
-      </c>
-      <c r="BV8" t="inlineStr">
-        <is>
-          <t>聯成</t>
-        </is>
-      </c>
-      <c r="BW8" t="inlineStr">
-        <is>
-          <t>塑膠工業</t>
-        </is>
-      </c>
-      <c r="BX8" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BY8" t="inlineStr">
-        <is>
-          <t>0.76</t>
-        </is>
-      </c>
-      <c r="BZ8" t="inlineStr">
-        <is>
-          <t>-11.96408371040724</t>
-        </is>
-      </c>
-      <c r="CA8" t="inlineStr">
-        <is>
-          <t>-13.59414944504011</t>
-        </is>
-      </c>
-      <c r="CB8" t="inlineStr">
-        <is>
-          <t>-19.633719693908</t>
-        </is>
-      </c>
-      <c r="CC8" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="CD8" t="inlineStr">
-        <is>
-          <t>價跌量縮</t>
-        </is>
-      </c>
-      <c r="CE8" t="inlineStr">
-        <is>
-          <t>0.50</t>
-        </is>
-      </c>
-      <c r="CF8" t="inlineStr">
-        <is>
-          <t>1.41</t>
-        </is>
-      </c>
-      <c r="CG8" t="inlineStr">
-        <is>
-          <t>10.97</t>
-        </is>
-      </c>
-      <c r="CH8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="CI8" t="inlineStr">
         <is>
           <t>0.96%</t>
@@ -4245,12 +4245,12 @@
       </c>
       <c r="CK8" t="inlineStr">
         <is>
-          <t>63.44</t>
+          <t>63.18</t>
         </is>
       </c>
       <c r="CL8" t="inlineStr">
         <is>
-          <t>14374</t>
+          <t>14037</t>
         </is>
       </c>
       <c r="CM8" t="inlineStr">
@@ -4270,22 +4270,22 @@
       </c>
       <c r="CP8" t="inlineStr">
         <is>
-          <t>11.35</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="CQ8" t="inlineStr">
         <is>
-          <t>11.35</t>
+          <t>11.1</t>
         </is>
       </c>
       <c r="CR8" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>10.7</t>
         </is>
       </c>
       <c r="CS8" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>11.05</t>
         </is>
       </c>
       <c r="CT8" t="inlineStr">
@@ -4300,7 +4300,7 @@
       </c>
       <c r="CV8" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -4317,12 +4317,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>-3.08</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>4488.958</t>
+          <t>4250.244</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4332,7 +4332,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>11.45</t>
+          <t>11.1</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -4342,17 +4342,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-7.51</t>
+          <t>-6.73</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>77.66</t>
+          <t>73.78</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4362,7 +4362,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -4392,32 +4392,32 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
+          <t>10.4</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>10.65</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>10.3</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>10.65</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>10.3</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6.73</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4442,7 +4442,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -4467,37 +4467,37 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
+          <t>2025/12/16</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>10.4</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
           <t>2025/11/17</t>
         </is>
       </c>
-      <c r="AH9" t="inlineStr">
+      <c r="AJ9" t="inlineStr">
         <is>
           <t>10.1</t>
         </is>
       </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>2025/10/28</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>10.3</t>
-        </is>
-      </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>13.10</t>
+          <t>12.40</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
@@ -4508,75 +4508,75 @@
       <c r="AO9" t="inlineStr"/>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>1703</t>
+          <t>2761</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>82.05</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>94.02</t>
         </is>
       </c>
       <c r="AT9" t="n">
-        <v>3.9</v>
+        <v>-0.63</v>
       </c>
       <c r="AU9" t="n">
-        <v>7.97</v>
+        <v>8.99</v>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
+          <t>0.56</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>11.17</t>
+        </is>
+      </c>
+      <c r="AY9" t="n">
+        <v>10.25</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>10.33</v>
+      </c>
+      <c r="BA9" t="inlineStr">
+        <is>
+          <t>10.27</t>
+        </is>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>297.70</t>
+        </is>
+      </c>
+      <c r="BC9" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="BE9" t="inlineStr">
+        <is>
           <t>0.54</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>11.02</t>
-        </is>
-      </c>
-      <c r="AY9" t="n">
-        <v>10.21</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>10.31</v>
-      </c>
-      <c r="BA9" t="inlineStr">
-        <is>
-          <t>10.25</t>
-        </is>
-      </c>
-      <c r="BB9" t="inlineStr">
-        <is>
-          <t>1276.76</t>
-        </is>
-      </c>
-      <c r="BC9" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="BE9" t="inlineStr">
-        <is>
-          <t>0.54</t>
-        </is>
-      </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>-97.09</t>
+          <t>-88.63</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
@@ -4586,43 +4586,43 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>39643582.14396068</t>
+          <t>39648620.88008415</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>51209846.0</t>
+          <t>47317394.0</t>
         </is>
       </c>
       <c r="BJ9" t="n">
-        <v>134651499.8</v>
+        <v>135273943.6</v>
       </c>
       <c r="BK9" t="inlineStr">
         <is>
-          <t>75791338.0</t>
+          <t>77843851.4</t>
         </is>
       </c>
       <c r="BL9" t="n">
-        <v>38375557.84</v>
+        <v>38862439.4</v>
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>58860161</t>
+          <t>57430092</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>9865813.569280198</t>
+          <t>10437086.8982393</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>19698614.82919247</t>
+          <t>13579090.20751438</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>51209846.0</t>
+          <t>47317394.0</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
@@ -4642,7 +4642,7 @@
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>8.02</t>
+          <t>4.72</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4667,7 +4667,7 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4687,22 +4687,22 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4727,12 +4727,12 @@
       </c>
       <c r="CK9" t="inlineStr">
         <is>
-          <t>63.44</t>
+          <t>63.18</t>
         </is>
       </c>
       <c r="CL9" t="inlineStr">
         <is>
-          <t>14374</t>
+          <t>14037</t>
         </is>
       </c>
       <c r="CM9" t="inlineStr">
@@ -4752,22 +4752,22 @@
       </c>
       <c r="CP9" t="inlineStr">
         <is>
-          <t>11.4</t>
+          <t>11.35</t>
         </is>
       </c>
       <c r="CQ9" t="inlineStr">
         <is>
-          <t>11.6</t>
+          <t>11.35</t>
         </is>
       </c>
       <c r="CR9" t="inlineStr">
         <is>
-          <t>11.15</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="CS9" t="inlineStr">
         <is>
-          <t>11.45</t>
+          <t>11.1</t>
         </is>
       </c>
       <c r="CT9" t="inlineStr">
@@ -4782,7 +4782,7 @@
       </c>
       <c r="CV9" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -4799,12 +4799,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>10514.261</t>
+          <t>4488.958</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>11.3</t>
+          <t>11.45</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4824,17 +4824,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-6.1</t>
+          <t>-10.1</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>75.06</t>
+          <t>77.66</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4844,7 +4844,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4874,32 +4874,32 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
+          <t>10.4</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>10.65</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>10.3</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>10.65</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>10.3</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10.10</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4924,7 +4924,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -4949,37 +4949,37 @@
       </c>
       <c r="AG10" t="inlineStr">
         <is>
+          <t>2025/12/16</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>10.4</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
           <t>2025/11/17</t>
         </is>
       </c>
-      <c r="AH10" t="inlineStr">
+      <c r="AJ10" t="inlineStr">
         <is>
           <t>10.1</t>
         </is>
       </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>2025/10/28</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>10.3</t>
-        </is>
-      </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>30.68</t>
+          <t>13.10</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>-2.16</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
@@ -4990,12 +4990,12 @@
       <c r="AO10" t="inlineStr"/>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>1703</t>
+          <t>2761</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
@@ -5009,47 +5009,47 @@
         </is>
       </c>
       <c r="AT10" t="n">
-        <v>5.59</v>
+        <v>3.9</v>
       </c>
       <c r="AU10" t="n">
-        <v>5.32</v>
+        <v>7.97</v>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>10.702</t>
+          <t>11.02</t>
         </is>
       </c>
       <c r="AY10" t="n">
-        <v>10.16</v>
+        <v>10.21</v>
       </c>
       <c r="AZ10" t="n">
-        <v>10.28</v>
+        <v>10.31</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>10.23</t>
+          <t>10.25</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>511.12</t>
+          <t>1276.76</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>0.14</v>
+        <v>0.22</v>
       </c>
       <c r="BD10" t="n">
-        <v>-0.03</v>
+        <v>0.02</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -5058,7 +5058,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>-106.37</t>
+          <t>-97.09</t>
         </is>
       </c>
       <c r="BG10" t="inlineStr">
@@ -5068,43 +5068,43 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>39643582.14396068</t>
+          <t>39648620.88008415</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>120192159.0</t>
+          <t>51209846.0</t>
         </is>
       </c>
       <c r="BJ10" t="n">
-        <v>126910257</v>
+        <v>134651499.8</v>
       </c>
       <c r="BK10" t="inlineStr">
         <is>
-          <t>72495141.9</t>
+          <t>75791338.0</t>
         </is>
       </c>
       <c r="BL10" t="n">
-        <v>37850914.22</v>
+        <v>38375557.84</v>
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>54415115</t>
+          <t>58860161</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>8078031.522023421</t>
+          <t>9865813.569280198</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>27320222.47340429</t>
+          <t>19698614.82919247</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>120192159.0</t>
+          <t>51209846.0</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>6.60</t>
+          <t>8.02</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -5149,7 +5149,7 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -5169,7 +5169,7 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
@@ -5184,7 +5184,7 @@
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -5209,12 +5209,12 @@
       </c>
       <c r="CK10" t="inlineStr">
         <is>
-          <t>63.44</t>
+          <t>63.18</t>
         </is>
       </c>
       <c r="CL10" t="inlineStr">
         <is>
-          <t>14374</t>
+          <t>14037</t>
         </is>
       </c>
       <c r="CM10" t="inlineStr">
@@ -5234,22 +5234,22 @@
       </c>
       <c r="CP10" t="inlineStr">
         <is>
+          <t>11.4</t>
+        </is>
+      </c>
+      <c r="CQ10" t="inlineStr">
+        <is>
+          <t>11.6</t>
+        </is>
+      </c>
+      <c r="CR10" t="inlineStr">
+        <is>
           <t>11.15</t>
         </is>
       </c>
-      <c r="CQ10" t="inlineStr">
-        <is>
-          <t>11.8</t>
-        </is>
-      </c>
-      <c r="CR10" t="inlineStr">
-        <is>
-          <t>11.05</t>
-        </is>
-      </c>
       <c r="CS10" t="inlineStr">
         <is>
-          <t>11.3</t>
+          <t>11.45</t>
         </is>
       </c>
       <c r="CT10" t="inlineStr">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="CV10" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -5281,12 +5281,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>5.61</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>34269.781</t>
+          <t>10514.261</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -5306,17 +5306,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-6.1</t>
+          <t>-8.65</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>64.03</t>
+          <t>75.06</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -5326,7 +5326,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -5356,32 +5356,32 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
+          <t>10.4</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>10.65</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>10.3</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>10.65</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>10.3</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8.65</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -5406,7 +5406,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -5431,37 +5431,37 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
+          <t>2025/12/16</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>10.4</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
           <t>2025/11/17</t>
         </is>
       </c>
-      <c r="AH11" t="inlineStr">
+      <c r="AJ11" t="inlineStr">
         <is>
           <t>10.1</t>
         </is>
       </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>2025/10/28</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>10.3</t>
-        </is>
-      </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>100.00</t>
+          <t>30.68</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>-2.16</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
@@ -5472,12 +5472,12 @@
       <c r="AO11" t="inlineStr"/>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>1703</t>
+          <t>2761</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
@@ -5491,47 +5491,47 @@
         </is>
       </c>
       <c r="AT11" t="n">
-        <v>8.84</v>
+        <v>5.59</v>
       </c>
       <c r="AU11" t="n">
-        <v>2.78</v>
+        <v>5.32</v>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>-1.45</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>10.382</t>
+          <t>10.702</t>
         </is>
       </c>
       <c r="AY11" t="n">
-        <v>10.1</v>
+        <v>10.16</v>
       </c>
       <c r="AZ11" t="n">
-        <v>10.25</v>
+        <v>10.28</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>10.21</t>
+          <t>10.23</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>175.85</t>
+          <t>511.12</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>0.06</v>
+        <v>0.14</v>
       </c>
       <c r="BD11" t="n">
-        <v>-0.08</v>
+        <v>-0.03</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5540,7 +5540,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>-114.52</t>
+          <t>-106.37</t>
         </is>
       </c>
       <c r="BG11" t="inlineStr">
@@ -5550,43 +5550,43 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>39643582.14396068</t>
+          <t>39648620.88008415</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>390794197.0</t>
+          <t>120192159.0</t>
         </is>
       </c>
       <c r="BJ11" t="n">
-        <v>105490556.2</v>
+        <v>126910257</v>
       </c>
       <c r="BK11" t="inlineStr">
         <is>
-          <t>64310538.4</t>
+          <t>72495141.9</t>
         </is>
       </c>
       <c r="BL11" t="n">
-        <v>35931629.66</v>
+        <v>37850914.22</v>
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>41180017</t>
+          <t>54415115</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>4579451.34904508</t>
+          <t>8078031.522023421</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>29841549.05537103</t>
+          <t>27320222.47340429</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>390794197.0</t>
+          <t>120192159.0</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5631,7 +5631,7 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5651,7 +5651,7 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
@@ -5666,7 +5666,7 @@
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="CK11" t="inlineStr">
         <is>
-          <t>63.44</t>
+          <t>63.18</t>
         </is>
       </c>
       <c r="CL11" t="inlineStr">
         <is>
-          <t>14374</t>
+          <t>14037</t>
         </is>
       </c>
       <c r="CM11" t="inlineStr">
@@ -5716,17 +5716,17 @@
       </c>
       <c r="CP11" t="inlineStr">
         <is>
-          <t>10.7</t>
+          <t>11.15</t>
         </is>
       </c>
       <c r="CQ11" t="inlineStr">
         <is>
-          <t>11.75</t>
+          <t>11.8</t>
         </is>
       </c>
       <c r="CR11" t="inlineStr">
         <is>
-          <t>10.7</t>
+          <t>11.05</t>
         </is>
       </c>
       <c r="CS11" t="inlineStr">
@@ -5746,14 +5746,14 @@
       </c>
       <c r="CV11" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5763,12 +5763,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>5.61</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>6273.16</t>
+          <t>34269.781</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5778,7 +5778,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>10.7</t>
+          <t>11.3</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5788,17 +5788,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>-8.65</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>9.10</t>
+          <t>64.03</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5808,7 +5808,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5838,32 +5838,32 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
+          <t>10.4</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>10.65</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>10.3</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>10.65</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>10.3</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8.65</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5888,7 +5888,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -5913,37 +5913,37 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
+          <t>2025/12/16</t>
+        </is>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>10.4</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
           <t>2025/11/17</t>
         </is>
       </c>
-      <c r="AH12" t="inlineStr">
+      <c r="AJ12" t="inlineStr">
         <is>
           <t>10.1</t>
         </is>
       </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>2025/10/28</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>10.3</t>
-        </is>
-      </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>18.31</t>
+          <t>100.00</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>2.95</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
@@ -5954,12 +5954,12 @@
       <c r="AO12" t="inlineStr"/>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>1703</t>
+          <t>2761</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
@@ -5969,51 +5969,51 @@
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>88.73</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AT12" t="n">
-        <v>6.77</v>
+        <v>8.84</v>
       </c>
       <c r="AU12" t="n">
-        <v>-0.22</v>
+        <v>2.78</v>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>-1.69</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>10.022</t>
+          <t>10.382</t>
         </is>
       </c>
       <c r="AY12" t="n">
-        <v>10.04</v>
+        <v>10.1</v>
       </c>
       <c r="AZ12" t="n">
-        <v>10.22</v>
+        <v>10.25</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>10.19</t>
+          <t>10.21</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>59.14</t>
+          <t>175.85</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>-0.05</v>
+        <v>0.06</v>
       </c>
       <c r="BD12" t="n">
-        <v>-0.11</v>
+        <v>-0.08</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -6022,7 +6022,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>-120.90</t>
+          <t>-114.52</t>
         </is>
       </c>
       <c r="BG12" t="inlineStr">
@@ -6032,43 +6032,43 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>39643582.14396068</t>
+          <t>39648620.88008415</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>66856122.0</t>
+          <t>390794197.0</t>
         </is>
       </c>
       <c r="BJ12" t="n">
-        <v>30264685.8</v>
+        <v>105490556.2</v>
       </c>
       <c r="BK12" t="inlineStr">
         <is>
-          <t>27741544.4</t>
+          <t>64310538.4</t>
         </is>
       </c>
       <c r="BL12" t="n">
-        <v>28239844.66</v>
+        <v>35931629.66</v>
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>2523141</t>
+          <t>41180017</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>-13657.32483236655</t>
+          <t>4579451.34904508</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>3384599.063345991</t>
+          <t>29841549.05537103</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>66856122.0</t>
+          <t>390794197.0</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -6088,7 +6088,7 @@
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>6.60</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -6113,7 +6113,7 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -6133,7 +6133,7 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
@@ -6143,12 +6143,12 @@
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
@@ -6173,12 +6173,12 @@
       </c>
       <c r="CK12" t="inlineStr">
         <is>
-          <t>63.44</t>
+          <t>63.18</t>
         </is>
       </c>
       <c r="CL12" t="inlineStr">
         <is>
-          <t>14374</t>
+          <t>14037</t>
         </is>
       </c>
       <c r="CM12" t="inlineStr">
@@ -6198,22 +6198,22 @@
       </c>
       <c r="CP12" t="inlineStr">
         <is>
-          <t>10.3</t>
+          <t>10.7</t>
         </is>
       </c>
       <c r="CQ12" t="inlineStr">
         <is>
-          <t>10.8</t>
+          <t>11.75</t>
         </is>
       </c>
       <c r="CR12" t="inlineStr">
         <is>
-          <t>10.3</t>
+          <t>10.7</t>
         </is>
       </c>
       <c r="CS12" t="inlineStr">
         <is>
-          <t>10.7</t>
+          <t>11.3</t>
         </is>
       </c>
       <c r="CT12" t="inlineStr">
@@ -6228,7 +6228,7 @@
       </c>
       <c r="CV12" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>

--- a/Result/checksun_type/塑化劑(可塑劑).xlsx
+++ b/Result/checksun_type/塑化劑(可塑劑).xlsx
@@ -943,12 +943,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2761.366</t>
+          <t>4478.968</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -973,17 +973,17 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-2.64</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-37.21</t>
+          <t>-27.47</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>11.05</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -1038,7 +1038,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>-5.88</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -1113,17 +1113,17 @@
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>8.06</t>
+          <t>13.07</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
@@ -1139,7 +1139,7 @@
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>2761</t>
+          <t>4479</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
@@ -1149,51 +1149,51 @@
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>3.92</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="AT2" t="n">
-        <v>-2.16</v>
+        <v>-1.79</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.77</v>
+        <v>1</v>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>10.63</t>
+          <t>10.59</t>
         </is>
       </c>
       <c r="AY2" t="n">
-        <v>10.44</v>
+        <v>10.49</v>
       </c>
       <c r="AZ2" t="n">
         <v>10.38</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>10.3</t>
+          <t>10.29</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-16.83</t>
+          <t>-30.95</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>0.14</v>
+        <v>0.11</v>
       </c>
       <c r="BD2" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>-67.70</t>
+          <t>-70.02</t>
         </is>
       </c>
       <c r="BG2" t="inlineStr">
@@ -1212,48 +1212,48 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>39648620.88008415</t>
+          <t>39689204.57773109</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>28824134.0</t>
+          <t>45750254.0</t>
         </is>
       </c>
       <c r="BJ2" t="n">
-        <v>27984384</v>
+        <v>26926319.2</v>
       </c>
       <c r="BK2" t="inlineStr">
         <is>
-          <t>44566065.1</t>
+          <t>37121874.6</t>
         </is>
       </c>
       <c r="BL2" t="n">
-        <v>38475388.26</v>
+        <v>38227445.28</v>
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>-16581681</t>
+          <t>-10195555</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>2198442.805462827</t>
+          <t>1115804.077176941</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>-5936786.581910416</t>
+          <t>-4838708.928395428</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>28824134.0</t>
+          <t>45750254.0</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
@@ -1353,7 +1353,7 @@
       </c>
       <c r="CK2" t="inlineStr">
         <is>
-          <t>63.18</t>
+          <t>63.3</t>
         </is>
       </c>
       <c r="CL2" t="inlineStr">
@@ -1378,17 +1378,17 @@
       </c>
       <c r="CP2" t="inlineStr">
         <is>
-          <t>10.7</t>
+          <t>10.4</t>
         </is>
       </c>
       <c r="CQ2" t="inlineStr">
         <is>
-          <t>10.7</t>
+          <t>10.5</t>
         </is>
       </c>
       <c r="CR2" t="inlineStr">
         <is>
-          <t>10.3</t>
+          <t>10.05</t>
         </is>
       </c>
       <c r="CS2" t="inlineStr">
@@ -1415,7 +1415,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>【b1】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1425,164 +1425,164 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>-2.34</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2761.366</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>10.4</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>1703.083</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>-2.64</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>-37.21</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>-65.0</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2025-12-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2025-12-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>2025-10-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2025-10-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>11.05</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>10.4</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>11.05</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
         <is>
           <t>10.65</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>-2.4</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>-1.06</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>-60.06</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>2025-12-08</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>-65.0</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>2025-12-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>2025-12-16 00:00:00</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>2025-10-27 00:00:00</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>2025-10-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>11.05</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>10.3</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>-5.88</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>7.28</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025/10/14</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>10.5</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>-0.03</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>2025/11/21</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>9.53</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>2025/09/22</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>10.15</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>2025/12/16</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
         <is>
           <t>10.4</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>11.05</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>10.65</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>10.3</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>-3.62</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>2.40</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>7.28</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>2025/10/14</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>10.5</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>-0.02</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>2025/11/21</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>9.53</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>2025/09/22</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>10.15</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>2025/12/16</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>10.4</t>
-        </is>
-      </c>
       <c r="AI3" t="inlineStr">
         <is>
           <t>2025/11/17</t>
@@ -1595,17 +1595,17 @@
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>4.97</t>
+          <t>8.06</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>-1.40</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
@@ -1621,45 +1621,45 @@
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>2761</t>
+          <t>4479</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>5.88</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>13.73</t>
+          <t>3.92</t>
         </is>
       </c>
       <c r="AT3" t="n">
-        <v>-1.3</v>
+        <v>-2.16</v>
       </c>
       <c r="AU3" t="n">
-        <v>3.5</v>
+        <v>1.77</v>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>10.79</t>
+          <t>10.63</t>
         </is>
       </c>
       <c r="AY3" t="n">
-        <v>10.42</v>
+        <v>10.44</v>
       </c>
       <c r="AZ3" t="n">
-        <v>10.37</v>
+        <v>10.38</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1668,14 +1668,14 @@
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>-16.83</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>0.18</v>
+        <v>0.14</v>
       </c>
       <c r="BD3" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>-66.34</t>
+          <t>-67.70</t>
         </is>
       </c>
       <c r="BG3" t="inlineStr">
@@ -1694,43 +1694,43 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>39648620.88008415</t>
+          <t>39689204.57773109</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>18268876.0</t>
+          <t>28824134.0</t>
         </is>
       </c>
       <c r="BJ3" t="n">
-        <v>32256217.8</v>
+        <v>27984384</v>
       </c>
       <c r="BK3" t="inlineStr">
         <is>
-          <t>80763071.4</t>
+          <t>44566065.1</t>
         </is>
       </c>
       <c r="BL3" t="n">
-        <v>38610965.58</v>
+        <v>38475388.26</v>
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>-48506853</t>
+          <t>-16581681</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>3677575.421348871</t>
+          <t>2198442.805462827</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>-5479927.99472075</t>
+          <t>-5936786.581910416</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>18268876.0</t>
+          <t>28824134.0</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
@@ -1750,64 +1750,64 @@
       </c>
       <c r="BT3" t="inlineStr">
         <is>
+          <t>-1.89</t>
+        </is>
+      </c>
+      <c r="BU3" t="inlineStr">
+        <is>
+          <t>聯成</t>
+        </is>
+      </c>
+      <c r="BV3" t="inlineStr">
+        <is>
+          <t>聯成</t>
+        </is>
+      </c>
+      <c r="BW3" t="inlineStr">
+        <is>
+          <t>塑膠工業</t>
+        </is>
+      </c>
+      <c r="BX3" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BY3" t="inlineStr">
+        <is>
+          <t>0.77</t>
+        </is>
+      </c>
+      <c r="BZ3" t="inlineStr">
+        <is>
+          <t>-11.96408371040724</t>
+        </is>
+      </c>
+      <c r="CA3" t="inlineStr">
+        <is>
+          <t>-13.59414944504011</t>
+        </is>
+      </c>
+      <c r="CB3" t="inlineStr">
+        <is>
+          <t>-19.633719693908</t>
+        </is>
+      </c>
+      <c r="CC3" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="CD3" t="inlineStr">
+        <is>
+          <t>價跌量-</t>
+        </is>
+      </c>
+      <c r="CE3" t="inlineStr">
+        <is>
           <t>0.47</t>
         </is>
       </c>
-      <c r="BU3" t="inlineStr">
-        <is>
-          <t>聯成</t>
-        </is>
-      </c>
-      <c r="BV3" t="inlineStr">
-        <is>
-          <t>聯成</t>
-        </is>
-      </c>
-      <c r="BW3" t="inlineStr">
-        <is>
-          <t>塑膠工業</t>
-        </is>
-      </c>
-      <c r="BX3" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BY3" t="inlineStr">
-        <is>
-          <t>0.77</t>
-        </is>
-      </c>
-      <c r="BZ3" t="inlineStr">
-        <is>
-          <t>-11.96408371040724</t>
-        </is>
-      </c>
-      <c r="CA3" t="inlineStr">
-        <is>
-          <t>-13.59414944504011</t>
-        </is>
-      </c>
-      <c r="CB3" t="inlineStr">
-        <is>
-          <t>-19.633719693908</t>
-        </is>
-      </c>
-      <c r="CC3" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="CD3" t="inlineStr">
-        <is>
-          <t>價漲量-</t>
-        </is>
-      </c>
-      <c r="CE3" t="inlineStr">
-        <is>
-          <t>0.48</t>
-        </is>
-      </c>
       <c r="CF3" t="inlineStr">
         <is>
           <t>1.44</t>
@@ -1835,7 +1835,7 @@
       </c>
       <c r="CK3" t="inlineStr">
         <is>
-          <t>63.18</t>
+          <t>63.3</t>
         </is>
       </c>
       <c r="CL3" t="inlineStr">
@@ -1860,22 +1860,22 @@
       </c>
       <c r="CP3" t="inlineStr">
         <is>
-          <t>10.6</t>
+          <t>10.7</t>
         </is>
       </c>
       <c r="CQ3" t="inlineStr">
         <is>
-          <t>10.9</t>
+          <t>10.7</t>
         </is>
       </c>
       <c r="CR3" t="inlineStr">
         <is>
-          <t>10.55</t>
+          <t>10.3</t>
         </is>
       </c>
       <c r="CS3" t="inlineStr">
         <is>
-          <t>10.65</t>
+          <t>10.4</t>
         </is>
       </c>
       <c r="CT3" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1904.815</t>
+          <t>1703.083</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-2.64</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-57.99</t>
+          <t>-60.06</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -2077,17 +2077,17 @@
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>5.56</t>
+          <t>4.97</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>-5.16</t>
+          <t>-1.40</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
@@ -2103,7 +2103,7 @@
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>2761</t>
+          <t>4479</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
@@ -2113,32 +2113,32 @@
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>19.34</t>
+          <t>13.73</t>
         </is>
       </c>
       <c r="AT4" t="n">
-        <v>-2.02</v>
+        <v>-1.3</v>
       </c>
       <c r="AU4" t="n">
-        <v>4.54</v>
+        <v>3.5</v>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>10.87</t>
+          <t>10.79</t>
         </is>
       </c>
       <c r="AY4" t="n">
-        <v>10.4</v>
+        <v>10.42</v>
       </c>
       <c r="AZ4" t="n">
         <v>10.37</v>
@@ -2150,11 +2150,11 @@
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>15.38</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>0.21</v>
+        <v>0.18</v>
       </c>
       <c r="BD4" t="n">
         <v>0.18</v>
@@ -2166,7 +2166,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>-66.51</t>
+          <t>-66.34</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
@@ -2176,43 +2176,43 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>39648620.88008415</t>
+          <t>39689204.57773109</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>20756844.0</t>
+          <t>18268876.0</t>
         </is>
       </c>
       <c r="BJ4" t="n">
-        <v>35969648.4</v>
+        <v>32256217.8</v>
       </c>
       <c r="BK4" t="inlineStr">
         <is>
-          <t>85621796.0</t>
+          <t>80763071.4</t>
         </is>
       </c>
       <c r="BL4" t="n">
-        <v>38506172.98</v>
+        <v>38610965.58</v>
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>-49652147</t>
+          <t>-48506853</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>5342576.042452438</t>
+          <t>3677575.421348871</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>-3500640.656066917</t>
+          <t>-5479927.99472075</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>20756844.0</t>
+          <t>18268876.0</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
@@ -2317,7 +2317,7 @@
       </c>
       <c r="CK4" t="inlineStr">
         <is>
-          <t>63.18</t>
+          <t>63.3</t>
         </is>
       </c>
       <c r="CL4" t="inlineStr">
@@ -2342,17 +2342,17 @@
       </c>
       <c r="CP4" t="inlineStr">
         <is>
-          <t>10.95</t>
+          <t>10.6</t>
         </is>
       </c>
       <c r="CQ4" t="inlineStr">
         <is>
-          <t>11.2</t>
+          <t>10.9</t>
         </is>
       </c>
       <c r="CR4" t="inlineStr">
         <is>
-          <t>10.65</t>
+          <t>10.55</t>
         </is>
       </c>
       <c r="CS4" t="inlineStr">
@@ -2389,12 +2389,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1950.665</t>
+          <t>1904.815</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>10.85</t>
+          <t>10.65</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2414,17 +2414,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-4.33</t>
+          <t>-2.4</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-2.64</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-53.07</t>
+          <t>-57.99</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>-3.62</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2559,17 +2559,17 @@
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>5.69</t>
+          <t>5.56</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>-5.16</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
@@ -2585,61 +2585,61 @@
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>2761</t>
+          <t>4479</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>29.41</t>
+          <t>5.88</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>45.47</t>
+          <t>19.34</t>
         </is>
       </c>
       <c r="AT5" t="n">
-        <v>-1</v>
+        <v>-2.02</v>
       </c>
       <c r="AU5" t="n">
-        <v>5.51</v>
+        <v>4.54</v>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>10.96</t>
+          <t>10.87</t>
         </is>
       </c>
       <c r="AY5" t="n">
-        <v>10.39</v>
+        <v>10.4</v>
       </c>
       <c r="AZ5" t="n">
-        <v>10.36</v>
+        <v>10.37</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>10.31</t>
+          <t>10.3</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>35.30</t>
+          <t>15.38</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>-67.80</t>
+          <t>-66.51</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
@@ -2658,43 +2658,43 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>39648620.88008415</t>
+          <t>39689204.57773109</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>21031488.0</t>
+          <t>20756844.0</t>
         </is>
       </c>
       <c r="BJ5" t="n">
-        <v>41281758.4</v>
+        <v>35969648.4</v>
       </c>
       <c r="BK5" t="inlineStr">
         <is>
-          <t>87966629.1</t>
+          <t>85621796.0</t>
         </is>
       </c>
       <c r="BL5" t="n">
-        <v>38425696.6</v>
+        <v>38506172.98</v>
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>-46684870</t>
+          <t>-49652147</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>6950433.624001412</t>
+          <t>5342576.042452438</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>-814632.4345590472</t>
+          <t>-3500640.656066917</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>21031488.0</t>
+          <t>20756844.0</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
@@ -2714,7 +2714,7 @@
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2759,17 +2759,17 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
@@ -2799,7 +2799,7 @@
       </c>
       <c r="CK5" t="inlineStr">
         <is>
-          <t>63.18</t>
+          <t>63.3</t>
         </is>
       </c>
       <c r="CL5" t="inlineStr">
@@ -2824,22 +2824,22 @@
       </c>
       <c r="CP5" t="inlineStr">
         <is>
-          <t>10.6</t>
+          <t>10.95</t>
         </is>
       </c>
       <c r="CQ5" t="inlineStr">
         <is>
-          <t>10.95</t>
+          <t>11.2</t>
         </is>
       </c>
       <c r="CR5" t="inlineStr">
         <is>
-          <t>10.6</t>
+          <t>10.65</t>
         </is>
       </c>
       <c r="CS5" t="inlineStr">
         <is>
-          <t>10.85</t>
+          <t>10.65</t>
         </is>
       </c>
       <c r="CT5" t="inlineStr">
@@ -2871,12 +2871,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-5.36</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>4746.574</t>
+          <t>1950.665</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2886,7 +2886,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>10.6</t>
+          <t>10.85</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2896,17 +2896,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>-4.33</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-2.64</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-45.68</t>
+          <t>-53.07</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2966,12 +2966,12 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>-4.07</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>4.33</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -3041,17 +3041,17 @@
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>13.85</t>
+          <t>5.69</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>-5.19</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
@@ -3067,61 +3067,61 @@
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>2761</t>
+          <t>4479</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>22.73</t>
+          <t>29.41</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>61.38</t>
+          <t>45.47</t>
         </is>
       </c>
       <c r="AT6" t="n">
-        <v>-4.33</v>
+        <v>-1</v>
       </c>
       <c r="AU6" t="n">
-        <v>6.85</v>
+        <v>5.51</v>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>11.08</t>
+          <t>10.96</t>
         </is>
       </c>
       <c r="AY6" t="n">
-        <v>10.37</v>
+        <v>10.39</v>
       </c>
       <c r="AZ6" t="n">
         <v>10.36</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>10.3</t>
+          <t>10.31</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>54.76</t>
+          <t>35.30</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="BD6" t="n">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3130,7 +3130,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>-70.64</t>
+          <t>-67.80</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr">
@@ -3140,43 +3140,43 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>39648620.88008415</t>
+          <t>39689204.57773109</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>51040578.0</t>
+          <t>21031488.0</t>
         </is>
       </c>
       <c r="BJ6" t="n">
-        <v>47317430</v>
+        <v>41281758.4</v>
       </c>
       <c r="BK6" t="inlineStr">
         <is>
-          <t>87113843.5</t>
+          <t>87966629.1</t>
         </is>
       </c>
       <c r="BL6" t="n">
-        <v>38674174.84</v>
+        <v>38425696.6</v>
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>-39796413</t>
+          <t>-46684870</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>8362263.81646695</t>
+          <t>6950433.624001412</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>3022190.040257879</t>
+          <t>-814632.4345590472</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>51040578.0</t>
+          <t>21031488.0</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
@@ -3196,7 +3196,7 @@
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -3241,17 +3241,17 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
@@ -3281,7 +3281,7 @@
       </c>
       <c r="CK6" t="inlineStr">
         <is>
-          <t>63.18</t>
+          <t>63.3</t>
         </is>
       </c>
       <c r="CL6" t="inlineStr">
@@ -3306,22 +3306,22 @@
       </c>
       <c r="CP6" t="inlineStr">
         <is>
-          <t>11.2</t>
+          <t>10.6</t>
         </is>
       </c>
       <c r="CQ6" t="inlineStr">
         <is>
-          <t>11.2</t>
+          <t>10.95</t>
         </is>
       </c>
       <c r="CR6" t="inlineStr">
         <is>
-          <t>10.55</t>
+          <t>10.6</t>
         </is>
       </c>
       <c r="CS6" t="inlineStr">
         <is>
-          <t>10.6</t>
+          <t>10.85</t>
         </is>
       </c>
       <c r="CT6" t="inlineStr">
@@ -3343,7 +3343,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>【d1】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3353,12 +3353,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>-5.36</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>4587.903</t>
+          <t>4746.574</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3368,7 +3368,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>11.2</t>
+          <t>10.6</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3378,17 +3378,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-7.69</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-2.64</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-26.61</t>
+          <t>-45.68</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3448,12 +3448,12 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>-4.07</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>7.69</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>13.39</t>
+          <t>13.85</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>5.71</t>
+          <t>-5.19</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
@@ -3549,61 +3549,61 @@
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>2761</t>
+          <t>4479</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>84.28</t>
+          <t>22.73</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>81.16</t>
+          <t>61.38</t>
         </is>
       </c>
       <c r="AT7" t="n">
-        <v>-0.18</v>
+        <v>-4.33</v>
       </c>
       <c r="AU7" t="n">
-        <v>8.33</v>
+        <v>6.85</v>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>11.22</t>
+          <t>11.08</t>
         </is>
       </c>
       <c r="AY7" t="n">
-        <v>10.36</v>
+        <v>10.37</v>
       </c>
       <c r="AZ7" t="n">
         <v>10.36</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>10.29</t>
+          <t>10.3</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>104.81</t>
+          <t>54.76</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>0.28</v>
+        <v>0.24</v>
       </c>
       <c r="BD7" t="n">
-        <v>0.14</v>
+        <v>0.16</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>-74.66</t>
+          <t>-70.64</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr">
@@ -3622,43 +3622,43 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>39648620.88008415</t>
+          <t>39689204.57773109</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>50183303.0</t>
+          <t>51040578.0</t>
         </is>
       </c>
       <c r="BJ7" t="n">
-        <v>61147746.2</v>
+        <v>47317430</v>
       </c>
       <c r="BK7" t="inlineStr">
         <is>
-          <t>83319151.2</t>
+          <t>87113843.5</t>
         </is>
       </c>
       <c r="BL7" t="n">
-        <v>38351204.62</v>
+        <v>38674174.84</v>
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>-22171405</t>
+          <t>-39796413</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>9333186.321232235</t>
+          <t>8362263.81646695</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>5180170.002844289</t>
+          <t>3022190.040257879</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>50183303.0</t>
+          <t>51040578.0</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
@@ -3678,7 +3678,7 @@
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>5.66</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3723,7 +3723,7 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
@@ -3733,7 +3733,7 @@
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
@@ -3763,7 +3763,7 @@
       </c>
       <c r="CK7" t="inlineStr">
         <is>
-          <t>63.18</t>
+          <t>63.3</t>
         </is>
       </c>
       <c r="CL7" t="inlineStr">
@@ -3788,12 +3788,12 @@
       </c>
       <c r="CP7" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>11.2</t>
         </is>
       </c>
       <c r="CQ7" t="inlineStr">
         <is>
-          <t>11.25</t>
+          <t>11.2</t>
         </is>
       </c>
       <c r="CR7" t="inlineStr">
@@ -3803,7 +3803,7 @@
       </c>
       <c r="CS7" t="inlineStr">
         <is>
-          <t>11.2</t>
+          <t>10.6</t>
         </is>
       </c>
       <c r="CT7" t="inlineStr">
@@ -3835,12 +3835,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>3380.77</t>
+          <t>4587.903</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3850,149 +3850,149 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
+          <t>11.2</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-7.69</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>-2.64</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>-26.61</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>-65.0</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>2025-12-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>2025-12-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>2025-10-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>2025-10-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
           <t>11.05</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>-6.25</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>-1.06</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>62.06</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>2025-12-08</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>-65.0</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>2025-12-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>2025-12-16 00:00:00</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>2025-10-27 00:00:00</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>2025-10-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>10.4</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
         <is>
           <t>11.05</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>10.65</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>10.3</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>7.69</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>7.28</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025/10/14</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>10.5</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>-0.01</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>2025/11/21</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>9.53</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>2025/09/22</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>10.15</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>2025/12/16</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
         <is>
           <t>10.4</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>11.05</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>10.65</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>10.3</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>6.25</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>7.28</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>2025/10/14</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>10.5</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>-0.02</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>2025/11/21</t>
-        </is>
-      </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>9.53</t>
-        </is>
-      </c>
-      <c r="AE8" t="inlineStr">
-        <is>
-          <t>2025/09/22</t>
-        </is>
-      </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>10.15</t>
-        </is>
-      </c>
-      <c r="AG8" t="inlineStr">
-        <is>
-          <t>2025/12/16</t>
-        </is>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>10.4</t>
-        </is>
-      </c>
       <c r="AI8" t="inlineStr">
         <is>
           <t>2025/11/17</t>
@@ -4005,17 +4005,17 @@
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>9.87</t>
+          <t>13.39</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>2.82</t>
+          <t>5.71</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
@@ -4031,70 +4031,70 @@
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>2761</t>
+          <t>4479</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>77.14</t>
+          <t>84.28</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>86.4</t>
+          <t>81.16</t>
         </is>
       </c>
       <c r="AT8" t="n">
-        <v>-1.69</v>
+        <v>-0.18</v>
       </c>
       <c r="AU8" t="n">
-        <v>9.07</v>
+        <v>8.33</v>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
+          <t>0.62</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>11.22</t>
+        </is>
+      </c>
+      <c r="AY8" t="n">
+        <v>10.36</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>10.36</v>
+      </c>
+      <c r="BA8" t="inlineStr">
+        <is>
+          <t>10.29</t>
+        </is>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>104.81</t>
+        </is>
+      </c>
+      <c r="BC8" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="BE8" t="inlineStr">
+        <is>
           <t>0.54</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>11.24</t>
-        </is>
-      </c>
-      <c r="AY8" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>10.34</v>
-      </c>
-      <c r="BA8" t="inlineStr">
-        <is>
-          <t>10.28</t>
-        </is>
-      </c>
-      <c r="BB8" t="inlineStr">
-        <is>
-          <t>156.80</t>
-        </is>
-      </c>
-      <c r="BC8" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="BE8" t="inlineStr">
-        <is>
-          <t>0.54</t>
-        </is>
-      </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>-81.30</t>
+          <t>-74.66</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr">
@@ -4104,43 +4104,43 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>39648620.88008415</t>
+          <t>39689204.57773109</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>36836029.0</t>
+          <t>50183303.0</t>
         </is>
       </c>
       <c r="BJ8" t="n">
-        <v>129269925</v>
+        <v>61147746.2</v>
       </c>
       <c r="BK8" t="inlineStr">
         <is>
-          <t>79767305.4</t>
+          <t>83319151.2</t>
         </is>
       </c>
       <c r="BL8" t="n">
-        <v>38038480.18</v>
+        <v>38351204.62</v>
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>49502619</t>
+          <t>-22171405</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>10088280.19730277</t>
+          <t>9333186.321232235</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>8169843.34215185</t>
+          <t>5180170.002844289</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>36836029.0</t>
+          <t>50183303.0</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
@@ -4160,7 +4160,7 @@
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>4.25</t>
+          <t>5.66</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -4205,12 +4205,12 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
@@ -4245,7 +4245,7 @@
       </c>
       <c r="CK8" t="inlineStr">
         <is>
-          <t>63.18</t>
+          <t>63.3</t>
         </is>
       </c>
       <c r="CL8" t="inlineStr">
@@ -4275,17 +4275,17 @@
       </c>
       <c r="CQ8" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>11.25</t>
         </is>
       </c>
       <c r="CR8" t="inlineStr">
         <is>
-          <t>10.7</t>
+          <t>10.55</t>
         </is>
       </c>
       <c r="CS8" t="inlineStr">
         <is>
-          <t>11.05</t>
+          <t>11.2</t>
         </is>
       </c>
       <c r="CT8" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-3.08</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>4250.244</t>
+          <t>3380.77</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4332,7 +4332,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>11.05</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -4342,22 +4342,22 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-6.73</t>
+          <t>-6.25</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-2.64</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>73.78</t>
+          <t>62.06</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -4397,7 +4397,7 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>11.05</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>6.73</t>
+          <t>6.25</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4487,17 +4487,17 @@
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>12.40</t>
+          <t>9.87</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>2.82</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
@@ -4513,61 +4513,61 @@
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>2761</t>
+          <t>4479</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>82.05</t>
+          <t>77.14</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>94.02</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="AT9" t="n">
-        <v>-0.63</v>
+        <v>-1.69</v>
       </c>
       <c r="AU9" t="n">
-        <v>8.99</v>
+        <v>9.07</v>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>11.17</t>
+          <t>11.24</t>
         </is>
       </c>
       <c r="AY9" t="n">
-        <v>10.25</v>
+        <v>10.3</v>
       </c>
       <c r="AZ9" t="n">
-        <v>10.33</v>
+        <v>10.34</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>10.27</t>
+          <t>10.28</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>297.70</t>
+          <t>156.80</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>0.24</v>
+        <v>0.26</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.06</v>
+        <v>0.1</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4576,7 +4576,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>-88.63</t>
+          <t>-81.30</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
@@ -4586,135 +4586,135 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>39648620.88008415</t>
+          <t>39689204.57773109</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>47317394.0</t>
+          <t>36836029.0</t>
         </is>
       </c>
       <c r="BJ9" t="n">
-        <v>135273943.6</v>
+        <v>129269925</v>
       </c>
       <c r="BK9" t="inlineStr">
         <is>
-          <t>77843851.4</t>
+          <t>79767305.4</t>
         </is>
       </c>
       <c r="BL9" t="n">
-        <v>38862439.4</v>
+        <v>38038480.18</v>
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>57430092</t>
+          <t>49502619</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>10437086.8982393</t>
+          <t>10088280.19730277</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>13579090.20751438</t>
+          <t>8169843.34215185</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>47317394.0</t>
+          <t>36836029.0</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
+          <t>2025-12-16</t>
+        </is>
+      </c>
+      <c r="BR9" t="inlineStr">
+        <is>
+          <t>10.6</t>
+        </is>
+      </c>
+      <c r="BS9" t="inlineStr">
+        <is>
+          <t>2025/12/10</t>
+        </is>
+      </c>
+      <c r="BT9" t="inlineStr">
+        <is>
+          <t>4.25</t>
+        </is>
+      </c>
+      <c r="BU9" t="inlineStr">
+        <is>
+          <t>聯成</t>
+        </is>
+      </c>
+      <c r="BV9" t="inlineStr">
+        <is>
+          <t>聯成</t>
+        </is>
+      </c>
+      <c r="BW9" t="inlineStr">
+        <is>
+          <t>塑膠工業</t>
+        </is>
+      </c>
+      <c r="BX9" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BY9" t="inlineStr">
+        <is>
+          <t>0.77</t>
+        </is>
+      </c>
+      <c r="BZ9" t="inlineStr">
+        <is>
+          <t>-11.96408371040724</t>
+        </is>
+      </c>
+      <c r="CA9" t="inlineStr">
+        <is>
+          <t>-13.59414944504011</t>
+        </is>
+      </c>
+      <c r="CB9" t="inlineStr">
+        <is>
+          <t>-19.633719693908</t>
+        </is>
+      </c>
+      <c r="CC9" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="CD9" t="inlineStr">
+        <is>
+          <t>價-量縮</t>
+        </is>
+      </c>
+      <c r="CE9" t="inlineStr">
+        <is>
+          <t>0.50</t>
+        </is>
+      </c>
+      <c r="CF9" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="CG9" t="inlineStr">
+        <is>
+          <t>10.97</t>
+        </is>
+      </c>
+      <c r="CH9" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="BR9" t="inlineStr">
-        <is>
-          <t>10.6</t>
-        </is>
-      </c>
-      <c r="BS9" t="inlineStr">
-        <is>
-          <t>2025/12/10</t>
-        </is>
-      </c>
-      <c r="BT9" t="inlineStr">
-        <is>
-          <t>4.72</t>
-        </is>
-      </c>
-      <c r="BU9" t="inlineStr">
-        <is>
-          <t>聯成</t>
-        </is>
-      </c>
-      <c r="BV9" t="inlineStr">
-        <is>
-          <t>聯成</t>
-        </is>
-      </c>
-      <c r="BW9" t="inlineStr">
-        <is>
-          <t>塑膠工業</t>
-        </is>
-      </c>
-      <c r="BX9" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BY9" t="inlineStr">
-        <is>
-          <t>0.77</t>
-        </is>
-      </c>
-      <c r="BZ9" t="inlineStr">
-        <is>
-          <t>-11.96408371040724</t>
-        </is>
-      </c>
-      <c r="CA9" t="inlineStr">
-        <is>
-          <t>-13.59414944504011</t>
-        </is>
-      </c>
-      <c r="CB9" t="inlineStr">
-        <is>
-          <t>-19.633719693908</t>
-        </is>
-      </c>
-      <c r="CC9" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="CD9" t="inlineStr">
-        <is>
-          <t>價跌量縮</t>
-        </is>
-      </c>
-      <c r="CE9" t="inlineStr">
-        <is>
-          <t>0.50</t>
-        </is>
-      </c>
-      <c r="CF9" t="inlineStr">
-        <is>
-          <t>1.44</t>
-        </is>
-      </c>
-      <c r="CG9" t="inlineStr">
-        <is>
-          <t>10.97</t>
-        </is>
-      </c>
-      <c r="CH9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="CI9" t="inlineStr">
         <is>
           <t>0.96%</t>
@@ -4727,7 +4727,7 @@
       </c>
       <c r="CK9" t="inlineStr">
         <is>
-          <t>63.18</t>
+          <t>63.3</t>
         </is>
       </c>
       <c r="CL9" t="inlineStr">
@@ -4752,22 +4752,22 @@
       </c>
       <c r="CP9" t="inlineStr">
         <is>
-          <t>11.35</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="CQ9" t="inlineStr">
         <is>
-          <t>11.35</t>
+          <t>11.1</t>
         </is>
       </c>
       <c r="CR9" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>10.7</t>
         </is>
       </c>
       <c r="CS9" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>11.05</t>
         </is>
       </c>
       <c r="CT9" t="inlineStr">
@@ -4799,12 +4799,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>-3.08</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>4488.958</t>
+          <t>4250.244</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>11.45</t>
+          <t>11.1</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4824,17 +4824,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-10.1</t>
+          <t>-6.73</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-2.64</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>77.66</t>
+          <t>73.78</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4899,7 +4899,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>10.10</t>
+          <t>6.73</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4924,7 +4924,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -4969,17 +4969,17 @@
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>13.10</t>
+          <t>12.40</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
@@ -4995,70 +4995,70 @@
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>2761</t>
+          <t>4479</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>82.05</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>94.02</t>
         </is>
       </c>
       <c r="AT10" t="n">
-        <v>3.9</v>
+        <v>-0.63</v>
       </c>
       <c r="AU10" t="n">
-        <v>7.97</v>
+        <v>8.99</v>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
+          <t>0.56</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>11.17</t>
+        </is>
+      </c>
+      <c r="AY10" t="n">
+        <v>10.25</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>10.33</v>
+      </c>
+      <c r="BA10" t="inlineStr">
+        <is>
+          <t>10.27</t>
+        </is>
+      </c>
+      <c r="BB10" t="inlineStr">
+        <is>
+          <t>297.70</t>
+        </is>
+      </c>
+      <c r="BC10" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="BE10" t="inlineStr">
+        <is>
           <t>0.54</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>11.02</t>
-        </is>
-      </c>
-      <c r="AY10" t="n">
-        <v>10.21</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>10.31</v>
-      </c>
-      <c r="BA10" t="inlineStr">
-        <is>
-          <t>10.25</t>
-        </is>
-      </c>
-      <c r="BB10" t="inlineStr">
-        <is>
-          <t>1276.76</t>
-        </is>
-      </c>
-      <c r="BC10" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="BE10" t="inlineStr">
-        <is>
-          <t>0.54</t>
-        </is>
-      </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>-97.09</t>
+          <t>-88.63</t>
         </is>
       </c>
       <c r="BG10" t="inlineStr">
@@ -5068,43 +5068,43 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>39648620.88008415</t>
+          <t>39689204.57773109</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>51209846.0</t>
+          <t>47317394.0</t>
         </is>
       </c>
       <c r="BJ10" t="n">
-        <v>134651499.8</v>
+        <v>135273943.6</v>
       </c>
       <c r="BK10" t="inlineStr">
         <is>
-          <t>75791338.0</t>
+          <t>77843851.4</t>
         </is>
       </c>
       <c r="BL10" t="n">
-        <v>38375557.84</v>
+        <v>38862439.4</v>
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>58860161</t>
+          <t>57430092</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>9865813.569280198</t>
+          <t>10437086.8982393</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>19698614.82919247</t>
+          <t>13579090.20751438</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>51209846.0</t>
+          <t>47317394.0</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>8.02</t>
+          <t>4.72</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -5169,17 +5169,17 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
@@ -5209,7 +5209,7 @@
       </c>
       <c r="CK10" t="inlineStr">
         <is>
-          <t>63.18</t>
+          <t>63.3</t>
         </is>
       </c>
       <c r="CL10" t="inlineStr">
@@ -5234,22 +5234,22 @@
       </c>
       <c r="CP10" t="inlineStr">
         <is>
-          <t>11.4</t>
+          <t>11.35</t>
         </is>
       </c>
       <c r="CQ10" t="inlineStr">
         <is>
-          <t>11.6</t>
+          <t>11.35</t>
         </is>
       </c>
       <c r="CR10" t="inlineStr">
         <is>
-          <t>11.15</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="CS10" t="inlineStr">
         <is>
-          <t>11.45</t>
+          <t>11.1</t>
         </is>
       </c>
       <c r="CT10" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>10514.261</t>
+          <t>4488.958</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -5296,7 +5296,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>11.3</t>
+          <t>11.45</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -5306,17 +5306,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-8.65</t>
+          <t>-10.1</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-2.64</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>75.06</t>
+          <t>77.66</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -5381,7 +5381,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>8.65</t>
+          <t>10.10</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -5406,7 +5406,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -5451,17 +5451,17 @@
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>30.68</t>
+          <t>13.10</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>-2.16</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
@@ -5477,7 +5477,7 @@
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>2761</t>
+          <t>4479</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
@@ -5491,47 +5491,47 @@
         </is>
       </c>
       <c r="AT11" t="n">
-        <v>5.59</v>
+        <v>3.9</v>
       </c>
       <c r="AU11" t="n">
-        <v>5.32</v>
+        <v>7.97</v>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>10.702</t>
+          <t>11.02</t>
         </is>
       </c>
       <c r="AY11" t="n">
-        <v>10.16</v>
+        <v>10.21</v>
       </c>
       <c r="AZ11" t="n">
-        <v>10.28</v>
+        <v>10.31</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>10.23</t>
+          <t>10.25</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>511.12</t>
+          <t>1276.76</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>0.14</v>
+        <v>0.22</v>
       </c>
       <c r="BD11" t="n">
-        <v>-0.03</v>
+        <v>0.02</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5540,7 +5540,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>-106.37</t>
+          <t>-97.09</t>
         </is>
       </c>
       <c r="BG11" t="inlineStr">
@@ -5550,43 +5550,43 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>39648620.88008415</t>
+          <t>39689204.57773109</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>120192159.0</t>
+          <t>51209846.0</t>
         </is>
       </c>
       <c r="BJ11" t="n">
-        <v>126910257</v>
+        <v>134651499.8</v>
       </c>
       <c r="BK11" t="inlineStr">
         <is>
-          <t>72495141.9</t>
+          <t>75791338.0</t>
         </is>
       </c>
       <c r="BL11" t="n">
-        <v>37850914.22</v>
+        <v>38375557.84</v>
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>54415115</t>
+          <t>58860161</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>8078031.522023421</t>
+          <t>9865813.569280198</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>27320222.47340429</t>
+          <t>19698614.82919247</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>120192159.0</t>
+          <t>51209846.0</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>6.60</t>
+          <t>8.02</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5651,7 +5651,7 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
@@ -5691,7 +5691,7 @@
       </c>
       <c r="CK11" t="inlineStr">
         <is>
-          <t>63.18</t>
+          <t>63.3</t>
         </is>
       </c>
       <c r="CL11" t="inlineStr">
@@ -5716,22 +5716,22 @@
       </c>
       <c r="CP11" t="inlineStr">
         <is>
+          <t>11.4</t>
+        </is>
+      </c>
+      <c r="CQ11" t="inlineStr">
+        <is>
+          <t>11.6</t>
+        </is>
+      </c>
+      <c r="CR11" t="inlineStr">
+        <is>
           <t>11.15</t>
         </is>
       </c>
-      <c r="CQ11" t="inlineStr">
-        <is>
-          <t>11.8</t>
-        </is>
-      </c>
-      <c r="CR11" t="inlineStr">
-        <is>
-          <t>11.05</t>
-        </is>
-      </c>
       <c r="CS11" t="inlineStr">
         <is>
-          <t>11.3</t>
+          <t>11.45</t>
         </is>
       </c>
       <c r="CT11" t="inlineStr">
@@ -5763,12 +5763,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>5.61</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>34269.781</t>
+          <t>10514.261</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5793,12 +5793,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-2.64</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>64.03</t>
+          <t>75.06</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5888,7 +5888,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -5933,17 +5933,17 @@
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>100.00</t>
+          <t>30.68</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>-2.16</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
@@ -5959,7 +5959,7 @@
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>2761</t>
+          <t>4479</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
@@ -5973,47 +5973,47 @@
         </is>
       </c>
       <c r="AT12" t="n">
-        <v>8.84</v>
+        <v>5.59</v>
       </c>
       <c r="AU12" t="n">
-        <v>2.78</v>
+        <v>5.32</v>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>-1.45</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>10.382</t>
+          <t>10.702</t>
         </is>
       </c>
       <c r="AY12" t="n">
-        <v>10.1</v>
+        <v>10.16</v>
       </c>
       <c r="AZ12" t="n">
-        <v>10.25</v>
+        <v>10.28</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>10.21</t>
+          <t>10.23</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>175.85</t>
+          <t>511.12</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>0.06</v>
+        <v>0.14</v>
       </c>
       <c r="BD12" t="n">
-        <v>-0.08</v>
+        <v>-0.03</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -6022,7 +6022,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>-114.52</t>
+          <t>-106.37</t>
         </is>
       </c>
       <c r="BG12" t="inlineStr">
@@ -6032,43 +6032,43 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>39648620.88008415</t>
+          <t>39689204.57773109</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>390794197.0</t>
+          <t>120192159.0</t>
         </is>
       </c>
       <c r="BJ12" t="n">
-        <v>105490556.2</v>
+        <v>126910257</v>
       </c>
       <c r="BK12" t="inlineStr">
         <is>
-          <t>64310538.4</t>
+          <t>72495141.9</t>
         </is>
       </c>
       <c r="BL12" t="n">
-        <v>35931629.66</v>
+        <v>37850914.22</v>
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>41180017</t>
+          <t>54415115</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>4579451.34904508</t>
+          <t>8078031.522023421</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>29841549.05537103</t>
+          <t>27320222.47340429</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>390794197.0</t>
+          <t>120192159.0</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -6133,7 +6133,7 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
@@ -6173,7 +6173,7 @@
       </c>
       <c r="CK12" t="inlineStr">
         <is>
-          <t>63.18</t>
+          <t>63.3</t>
         </is>
       </c>
       <c r="CL12" t="inlineStr">
@@ -6198,17 +6198,17 @@
       </c>
       <c r="CP12" t="inlineStr">
         <is>
-          <t>10.7</t>
+          <t>11.15</t>
         </is>
       </c>
       <c r="CQ12" t="inlineStr">
         <is>
-          <t>11.75</t>
+          <t>11.8</t>
         </is>
       </c>
       <c r="CR12" t="inlineStr">
         <is>
-          <t>10.7</t>
+          <t>11.05</t>
         </is>
       </c>
       <c r="CS12" t="inlineStr">

--- a/Result/checksun_type/塑化劑(可塑劑).xlsx
+++ b/Result/checksun_type/塑化劑(可塑劑).xlsx
@@ -943,164 +943,164 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>-0.48</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>1699.955</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>10.35</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>4478.968</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>-3.0</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>-22.33</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>-65.0</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>2025-12-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>2025-12-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>2025-10-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>2025-10-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>11.05</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
         <is>
           <t>10.4</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>-2.64</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>-27.47</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>10.65</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>10.3</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>-65.0</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>2025-12-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>2025-12-16 00:00:00</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>2025-10-27 00:00:00</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>2025-10-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>11.05</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>-0.48</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>7.28</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>2025/10/14</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>10.5</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>-0.01</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>2025/11/21</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>9.53</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>2025/09/22</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>10.15</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>2025/12/16</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
         <is>
           <t>10.4</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>10.65</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>10.3</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>7.28</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>2025/10/14</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>10.5</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>-0.02</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>2025/11/21</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>9.53</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>2025/09/22</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>10.15</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>2025/12/16</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>10.4</t>
-        </is>
-      </c>
       <c r="AI2" t="inlineStr">
         <is>
           <t>2025/11/17</t>
@@ -1113,17 +1113,17 @@
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>13.07</t>
+          <t>4.96</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
@@ -1134,12 +1134,12 @@
       <c r="AO2" t="inlineStr"/>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>4479</t>
+          <t>1700</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
@@ -1149,51 +1149,51 @@
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT2" t="n">
-        <v>-1.79</v>
+        <v>-1.33</v>
       </c>
       <c r="AU2" t="n">
-        <v>1</v>
+        <v>-0.25</v>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>10.59</t>
+          <t>10.49</t>
         </is>
       </c>
       <c r="AY2" t="n">
-        <v>10.49</v>
+        <v>10.52</v>
       </c>
       <c r="AZ2" t="n">
         <v>10.38</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>10.29</t>
+          <t>10.28</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-30.95</t>
+          <t>-44.76</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>0.11</v>
+        <v>0.08</v>
       </c>
       <c r="BD2" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>-70.02</t>
+          <t>-73.04</t>
         </is>
       </c>
       <c r="BG2" t="inlineStr">
@@ -1212,43 +1212,43 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>39689204.57773109</t>
+          <t>39670313.17132867</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>45750254.0</t>
+          <t>17454566.0</t>
         </is>
       </c>
       <c r="BJ2" t="n">
-        <v>26926319.2</v>
+        <v>26210934.8</v>
       </c>
       <c r="BK2" t="inlineStr">
         <is>
-          <t>37121874.6</t>
+          <t>33746346.6</t>
         </is>
       </c>
       <c r="BL2" t="n">
-        <v>38227445.28</v>
+        <v>38098690.76</v>
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>-10195555</t>
+          <t>-7535411</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>1115804.077176941</t>
+          <t>10101.38103817427</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>-4838708.928395428</t>
+          <t>-6071263.447725043</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>45750254.0</t>
+          <t>17454566.0</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1313,22 +1313,22 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1353,12 +1353,12 @@
       </c>
       <c r="CK2" t="inlineStr">
         <is>
-          <t>63.3</t>
+          <t>63.46</t>
         </is>
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>14037</t>
+          <t>13969</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
@@ -1383,17 +1383,17 @@
       </c>
       <c r="CQ2" t="inlineStr">
         <is>
-          <t>10.5</t>
+          <t>10.4</t>
         </is>
       </c>
       <c r="CR2" t="inlineStr">
         <is>
-          <t>10.05</t>
+          <t>10.15</t>
         </is>
       </c>
       <c r="CS2" t="inlineStr">
         <is>
-          <t>10.4</t>
+          <t>10.35</t>
         </is>
       </c>
       <c r="CT2" t="inlineStr">
@@ -1425,12 +1425,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2761.366</t>
+          <t>4478.968</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1450,22 +1450,22 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-2.64</t>
+          <t>-3.0</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-37.21</t>
+          <t>-27.47</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>11.05</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>-5.88</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -1550,7 +1550,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1595,17 +1595,17 @@
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>8.06</t>
+          <t>13.07</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
@@ -1616,12 +1616,12 @@
       <c r="AO3" t="inlineStr"/>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>4479</t>
+          <t>1700</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
@@ -1631,51 +1631,51 @@
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>3.92</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="AT3" t="n">
-        <v>-2.16</v>
+        <v>-1.79</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.77</v>
+        <v>1</v>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>10.63</t>
+          <t>10.59</t>
         </is>
       </c>
       <c r="AY3" t="n">
-        <v>10.44</v>
+        <v>10.49</v>
       </c>
       <c r="AZ3" t="n">
         <v>10.38</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>10.3</t>
+          <t>10.29</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-16.83</t>
+          <t>-30.95</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>0.14</v>
+        <v>0.11</v>
       </c>
       <c r="BD3" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>-67.70</t>
+          <t>-70.02</t>
         </is>
       </c>
       <c r="BG3" t="inlineStr">
@@ -1694,48 +1694,48 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>39689204.57773109</t>
+          <t>39670313.17132867</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>28824134.0</t>
+          <t>45750254.0</t>
         </is>
       </c>
       <c r="BJ3" t="n">
-        <v>27984384</v>
+        <v>26926319.2</v>
       </c>
       <c r="BK3" t="inlineStr">
         <is>
-          <t>44566065.1</t>
+          <t>37121874.6</t>
         </is>
       </c>
       <c r="BL3" t="n">
-        <v>38475388.26</v>
+        <v>38227445.28</v>
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>-16581681</t>
+          <t>-10195555</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>2198442.805462827</t>
+          <t>1115804.077176941</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>-5936786.581910416</t>
+          <t>-4838708.928395428</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>28824134.0</t>
+          <t>45750254.0</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1835,12 +1835,12 @@
       </c>
       <c r="CK3" t="inlineStr">
         <is>
-          <t>63.3</t>
+          <t>63.46</t>
         </is>
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>14037</t>
+          <t>13969</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
@@ -1860,17 +1860,17 @@
       </c>
       <c r="CP3" t="inlineStr">
         <is>
-          <t>10.7</t>
+          <t>10.4</t>
         </is>
       </c>
       <c r="CQ3" t="inlineStr">
         <is>
-          <t>10.7</t>
+          <t>10.5</t>
         </is>
       </c>
       <c r="CR3" t="inlineStr">
         <is>
-          <t>10.3</t>
+          <t>10.05</t>
         </is>
       </c>
       <c r="CS3" t="inlineStr">
@@ -1897,7 +1897,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>【b1】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1703.083</t>
+          <t>2761.366</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1922,149 +1922,149 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>10.4</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-0.48</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>-3.0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>-37.21</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>-65.0</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2025-12-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2025-12-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>2025-10-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>2025-10-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>11.05</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>10.4</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>11.05</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
           <t>10.65</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>-2.4</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>-2.64</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>-60.06</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>2025-12-08</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>-65.0</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>2025-12-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>2025-12-16 00:00:00</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>2025-10-27 00:00:00</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>2025-10-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>11.05</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>10.3</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>-5.88</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>7.28</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025/10/14</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>10.5</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>-0.03</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>2025/11/21</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>9.53</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>2025/09/22</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>10.15</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>2025/12/16</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
         <is>
           <t>10.4</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>11.05</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>10.65</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>10.3</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>-3.62</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>2.40</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>7.28</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>2025/10/14</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>10.5</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>-0.02</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>2025/11/21</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>9.53</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>2025/09/22</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>10.15</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>2025/12/16</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>10.4</t>
-        </is>
-      </c>
       <c r="AI4" t="inlineStr">
         <is>
           <t>2025/11/17</t>
@@ -2077,17 +2077,17 @@
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>4.97</t>
+          <t>8.06</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>-1.40</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
@@ -2098,50 +2098,50 @@
       <c r="AO4" t="inlineStr"/>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>4479</t>
+          <t>1700</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>5.88</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>13.73</t>
+          <t>3.92</t>
         </is>
       </c>
       <c r="AT4" t="n">
-        <v>-1.3</v>
+        <v>-2.16</v>
       </c>
       <c r="AU4" t="n">
-        <v>3.5</v>
+        <v>1.77</v>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>10.79</t>
+          <t>10.63</t>
         </is>
       </c>
       <c r="AY4" t="n">
-        <v>10.42</v>
+        <v>10.44</v>
       </c>
       <c r="AZ4" t="n">
-        <v>10.37</v>
+        <v>10.38</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2150,14 +2150,14 @@
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>-16.83</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>0.18</v>
+        <v>0.14</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2166,7 +2166,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>-66.34</t>
+          <t>-67.70</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
@@ -2176,43 +2176,43 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>39689204.57773109</t>
+          <t>39670313.17132867</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>18268876.0</t>
+          <t>28824134.0</t>
         </is>
       </c>
       <c r="BJ4" t="n">
-        <v>32256217.8</v>
+        <v>27984384</v>
       </c>
       <c r="BK4" t="inlineStr">
         <is>
-          <t>80763071.4</t>
+          <t>44566065.1</t>
         </is>
       </c>
       <c r="BL4" t="n">
-        <v>38610965.58</v>
+        <v>38475388.26</v>
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>-48506853</t>
+          <t>-16581681</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>3677575.421348871</t>
+          <t>2198442.805462827</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>-5479927.99472075</t>
+          <t>-5936786.581910416</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>18268876.0</t>
+          <t>28824134.0</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
@@ -2232,67 +2232,67 @@
       </c>
       <c r="BT4" t="inlineStr">
         <is>
+          <t>-1.89</t>
+        </is>
+      </c>
+      <c r="BU4" t="inlineStr">
+        <is>
+          <t>聯成</t>
+        </is>
+      </c>
+      <c r="BV4" t="inlineStr">
+        <is>
+          <t>聯成</t>
+        </is>
+      </c>
+      <c r="BW4" t="inlineStr">
+        <is>
+          <t>塑膠工業</t>
+        </is>
+      </c>
+      <c r="BX4" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BY4" t="inlineStr">
+        <is>
+          <t>0.77</t>
+        </is>
+      </c>
+      <c r="BZ4" t="inlineStr">
+        <is>
+          <t>-11.96408371040724</t>
+        </is>
+      </c>
+      <c r="CA4" t="inlineStr">
+        <is>
+          <t>-13.59414944504011</t>
+        </is>
+      </c>
+      <c r="CB4" t="inlineStr">
+        <is>
+          <t>-19.633719693908</t>
+        </is>
+      </c>
+      <c r="CC4" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="CD4" t="inlineStr">
+        <is>
+          <t>價跌量-</t>
+        </is>
+      </c>
+      <c r="CE4" t="inlineStr">
+        <is>
           <t>0.47</t>
         </is>
       </c>
-      <c r="BU4" t="inlineStr">
-        <is>
-          <t>聯成</t>
-        </is>
-      </c>
-      <c r="BV4" t="inlineStr">
-        <is>
-          <t>聯成</t>
-        </is>
-      </c>
-      <c r="BW4" t="inlineStr">
-        <is>
-          <t>塑膠工業</t>
-        </is>
-      </c>
-      <c r="BX4" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BY4" t="inlineStr">
-        <is>
-          <t>0.77</t>
-        </is>
-      </c>
-      <c r="BZ4" t="inlineStr">
-        <is>
-          <t>-11.96408371040724</t>
-        </is>
-      </c>
-      <c r="CA4" t="inlineStr">
-        <is>
-          <t>-13.59414944504011</t>
-        </is>
-      </c>
-      <c r="CB4" t="inlineStr">
-        <is>
-          <t>-19.633719693908</t>
-        </is>
-      </c>
-      <c r="CC4" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="CD4" t="inlineStr">
-        <is>
-          <t>價漲量-</t>
-        </is>
-      </c>
-      <c r="CE4" t="inlineStr">
-        <is>
-          <t>0.48</t>
-        </is>
-      </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2317,12 +2317,12 @@
       </c>
       <c r="CK4" t="inlineStr">
         <is>
-          <t>63.3</t>
+          <t>63.46</t>
         </is>
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>14037</t>
+          <t>13969</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
@@ -2342,22 +2342,22 @@
       </c>
       <c r="CP4" t="inlineStr">
         <is>
-          <t>10.6</t>
+          <t>10.7</t>
         </is>
       </c>
       <c r="CQ4" t="inlineStr">
         <is>
-          <t>10.9</t>
+          <t>10.7</t>
         </is>
       </c>
       <c r="CR4" t="inlineStr">
         <is>
-          <t>10.55</t>
+          <t>10.3</t>
         </is>
       </c>
       <c r="CS4" t="inlineStr">
         <is>
-          <t>10.65</t>
+          <t>10.4</t>
         </is>
       </c>
       <c r="CT4" t="inlineStr">
@@ -2389,12 +2389,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1904.815</t>
+          <t>1703.083</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2414,17 +2414,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-2.4</t>
+          <t>-2.9</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-2.64</t>
+          <t>-3.0</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-57.99</t>
+          <t>-60.06</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2514,7 +2514,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -2559,17 +2559,17 @@
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>5.56</t>
+          <t>4.97</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>-5.16</t>
+          <t>-1.40</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
@@ -2580,12 +2580,12 @@
       <c r="AO5" t="inlineStr"/>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>4479</t>
+          <t>1700</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
@@ -2595,32 +2595,32 @@
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>19.34</t>
+          <t>13.73</t>
         </is>
       </c>
       <c r="AT5" t="n">
-        <v>-2.02</v>
+        <v>-1.3</v>
       </c>
       <c r="AU5" t="n">
-        <v>4.54</v>
+        <v>3.5</v>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>10.87</t>
+          <t>10.79</t>
         </is>
       </c>
       <c r="AY5" t="n">
-        <v>10.4</v>
+        <v>10.42</v>
       </c>
       <c r="AZ5" t="n">
         <v>10.37</v>
@@ -2632,11 +2632,11 @@
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>15.38</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>0.21</v>
+        <v>0.18</v>
       </c>
       <c r="BD5" t="n">
         <v>0.18</v>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>-66.51</t>
+          <t>-66.34</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
@@ -2658,43 +2658,43 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>39689204.57773109</t>
+          <t>39670313.17132867</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>20756844.0</t>
+          <t>18268876.0</t>
         </is>
       </c>
       <c r="BJ5" t="n">
-        <v>35969648.4</v>
+        <v>32256217.8</v>
       </c>
       <c r="BK5" t="inlineStr">
         <is>
-          <t>85621796.0</t>
+          <t>80763071.4</t>
         </is>
       </c>
       <c r="BL5" t="n">
-        <v>38506172.98</v>
+        <v>38610965.58</v>
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>-49652147</t>
+          <t>-48506853</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>5342576.042452438</t>
+          <t>3677575.421348871</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>-3500640.656066917</t>
+          <t>-5479927.99472075</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>20756844.0</t>
+          <t>18268876.0</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
@@ -2759,12 +2759,12 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="CG5" 